--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C0C01C-0779-485E-AB5D-90AE395506B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C69DE9-CA20-4A7F-A6C9-2EF6FDD8B2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -350,6 +350,39 @@
   <si>
     <t xml:space="preserve">Prime Mart </t>
   </si>
+  <si>
+    <t>LGS</t>
+  </si>
+  <si>
+    <t>E2 Johar Town</t>
+  </si>
+  <si>
+    <t>Shahzad (asif Bro)</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wapda Town </t>
+  </si>
+  <si>
+    <t>Defence Road</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behria Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sohail Traders </t>
+  </si>
+  <si>
+    <t>Kasoor</t>
+  </si>
 </sst>
 </file>
 
@@ -1244,7 +1277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1616,6 +1649,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2250,18 +2291,18 @@
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="156">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46270</v>
-      </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
+        <v>46273</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2283,10 +2324,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2316,13 +2357,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="145"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="148" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="149"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2341,8 +2382,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="153"/>
-      <c r="B3" s="158"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2370,29 +2411,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="150" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="151"/>
-      <c r="N3" s="152"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="160" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="161"/>
-      <c r="S3" s="161"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="163" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="164"/>
-      <c r="W3" s="164"/>
-      <c r="X3" s="165"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="153"/>
-      <c r="B4" s="159"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -2732,7 +2773,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="33">
-        <f t="shared" ref="M7:M38" si="15">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M8:M38" si="15">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N8" s="43"/>
@@ -3163,26 +3204,37 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="72"/>
+      <c r="A14" s="72">
+        <v>46270</v>
+      </c>
       <c r="B14" s="41">
         <v>10</v>
       </c>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
+      <c r="C14" s="140" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="140" t="s">
+        <v>110</v>
+      </c>
       <c r="E14" s="44"/>
       <c r="F14" s="44"/>
       <c r="G14" s="69"/>
       <c r="H14" s="43"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="70"/>
+      <c r="I14" s="44">
+        <v>40</v>
+      </c>
+      <c r="J14" s="69">
+        <v>40</v>
+      </c>
+      <c r="K14" s="70">
+        <v>40</v>
+      </c>
       <c r="L14" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N14" s="43"/>
       <c r="O14" s="67">
@@ -3191,7 +3243,7 @@
       </c>
       <c r="P14" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3227,22 +3279,28 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="72"/>
-      <c r="B15" s="41">
+      <c r="A15" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B15" s="144">
         <v>11</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="70"/>
+      <c r="C15" s="145" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="145"/>
+      <c r="E15" s="146">
+        <v>385</v>
+      </c>
+      <c r="F15" s="146"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="148"/>
       <c r="L15" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="M15" s="33">
         <f t="shared" si="15"/>
@@ -3291,22 +3349,36 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="72"/>
-      <c r="B16" s="41">
+      <c r="A16" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B16" s="144">
         <v>12</v>
       </c>
-      <c r="C16" s="140"/>
-      <c r="D16" s="140"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="70"/>
+      <c r="C16" s="145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="145" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146">
+        <v>40</v>
+      </c>
+      <c r="G16" s="147"/>
+      <c r="H16" s="50">
+        <v>40</v>
+      </c>
+      <c r="I16" s="146"/>
+      <c r="J16" s="147">
+        <v>40</v>
+      </c>
+      <c r="K16" s="148">
+        <v>40</v>
+      </c>
       <c r="L16" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="15"/>
@@ -3315,11 +3387,11 @@
       <c r="N16" s="43"/>
       <c r="O16" s="67">
         <f t="shared" ref="O16:O17" si="18">SUM(F16:H16)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" s="34">
         <f t="shared" ref="P16:P17" si="19">SUM(I16:K16)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3355,22 +3427,40 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A17" s="72"/>
-      <c r="B17" s="41">
+      <c r="A17" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B17" s="144">
         <v>13</v>
       </c>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="70"/>
+      <c r="C17" s="145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="145" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="146"/>
+      <c r="F17" s="146">
+        <v>40</v>
+      </c>
+      <c r="G17" s="147">
+        <v>120</v>
+      </c>
+      <c r="H17" s="50">
+        <v>200</v>
+      </c>
+      <c r="I17" s="146">
+        <v>80</v>
+      </c>
+      <c r="J17" s="147">
+        <v>40</v>
+      </c>
+      <c r="K17" s="148">
+        <v>240</v>
+      </c>
       <c r="L17" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="15"/>
@@ -3379,11 +3469,11 @@
       <c r="N17" s="43"/>
       <c r="O17" s="67">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P17" s="34">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q17" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3419,22 +3509,38 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A18" s="72"/>
-      <c r="B18" s="41">
+      <c r="A18" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="144">
         <v>14</v>
       </c>
-      <c r="C18" s="140"/>
-      <c r="D18" s="140"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="70"/>
+      <c r="C18" s="145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="145" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146">
+        <v>80</v>
+      </c>
+      <c r="G18" s="147"/>
+      <c r="H18" s="50">
+        <v>40</v>
+      </c>
+      <c r="I18" s="146">
+        <v>200</v>
+      </c>
+      <c r="J18" s="147">
+        <v>160</v>
+      </c>
+      <c r="K18" s="148">
+        <v>280</v>
+      </c>
       <c r="L18" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="15"/>
@@ -3443,11 +3549,11 @@
       <c r="N18" s="43"/>
       <c r="O18" s="67">
         <f t="shared" ref="O18:O20" si="24">SUM(F18:H18)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P18" s="34">
         <f t="shared" ref="P18:P20" si="25">SUM(I18:K18)/20</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3483,22 +3589,34 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A19" s="72"/>
-      <c r="B19" s="41">
+      <c r="A19" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B19" s="144">
         <v>15</v>
       </c>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="70"/>
+      <c r="C19" s="145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="145" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="146"/>
+      <c r="F19" s="146">
+        <v>40</v>
+      </c>
+      <c r="G19" s="147">
+        <v>80</v>
+      </c>
+      <c r="H19" s="50"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="148">
+        <v>200</v>
+      </c>
       <c r="L19" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="15"/>
@@ -3507,11 +3625,11 @@
       <c r="N19" s="43"/>
       <c r="O19" s="67">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P19" s="34">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q19" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3547,22 +3665,38 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A20" s="72"/>
-      <c r="B20" s="41">
+      <c r="A20" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B20" s="144">
         <v>16</v>
       </c>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="70"/>
+      <c r="C20" s="145" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="145" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="146"/>
+      <c r="F20" s="146">
+        <v>200</v>
+      </c>
+      <c r="G20" s="147">
+        <v>120</v>
+      </c>
+      <c r="H20" s="50"/>
+      <c r="I20" s="146">
+        <v>40</v>
+      </c>
+      <c r="J20" s="147">
+        <v>80</v>
+      </c>
+      <c r="K20" s="148">
+        <v>440</v>
+      </c>
       <c r="L20" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="15"/>
@@ -3571,11 +3705,11 @@
       <c r="N20" s="43"/>
       <c r="O20" s="67">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P20" s="34">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q20" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3611,22 +3745,36 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A21" s="72"/>
-      <c r="B21" s="41">
+      <c r="A21" s="143">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="144">
         <v>17</v>
       </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="70"/>
+      <c r="C21" s="145" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="145" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="146">
+        <v>1600</v>
+      </c>
+      <c r="F21" s="146"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="146">
+        <v>600</v>
+      </c>
+      <c r="J21" s="147">
+        <v>1000</v>
+      </c>
+      <c r="K21" s="148">
+        <v>800</v>
+      </c>
       <c r="L21" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="15"/>
@@ -3639,7 +3787,7 @@
       </c>
       <c r="P21" s="34">
         <f t="shared" ref="P21:P23" si="31">SUM(I21:K21)/20</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" s="45" t="e">
         <f t="shared" si="1"/>
@@ -10809,42 +10957,42 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="166" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="167"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
-        <v>280</v>
+        <v>2265</v>
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>520</v>
+        <v>920</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>520</v>
+        <v>840</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>760</v>
+        <v>1720</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>600</v>
+        <v>1960</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>85</v>
+        <v>268.625</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -10856,11 +11004,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>68</v>
+        <v>286</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11066,10 +11214,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="154" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="155"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11153,46 +11301,46 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="143" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="144"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
-        <v>280</v>
+        <v>2265</v>
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>520</v>
+        <v>920</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>520</v>
+        <v>840</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>760</v>
+        <v>1720</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>600</v>
+        <v>1960</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>85</v>
+        <v>268.625</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11200,11 +11348,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>296</v>
+        <v>396</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>256</v>
+        <v>692</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11287,25 +11435,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="174" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="K3" s="176" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
-      <c r="O3" s="176"/>
-      <c r="P3" s="176"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11350,19 +11498,25 @@
       <c r="C5" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
+      <c r="D5" s="82">
+        <v>228</v>
+      </c>
+      <c r="E5" s="73">
+        <v>288</v>
+      </c>
+      <c r="F5" s="73">
+        <v>100</v>
+      </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-10000</v>
+        <v>-9384</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11386,19 +11540,19 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>0</v>
+        <v>11520</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>0</v>
+        <v>24640</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11406,7 +11560,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-400000</v>
+        <v>-375360</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11534,11 +11688,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>0</v>
+        <v>-228</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>0</v>
+        <v>-288</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11622,14 +11776,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="173" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="F11" s="173" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="173"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -11681,7 +11835,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>4200</v>
+        <v>4816</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -11733,12 +11887,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>168000</v>
-      </c>
-      <c r="S13" s="168" t="s">
+        <v>192640</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="168"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -11827,13 +11981,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="169" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="169"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
-      <c r="H20" s="169"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C69DE9-CA20-4A7F-A6C9-2EF6FDD8B2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001412D-21D4-4480-80E7-1FAC0ABE7BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="126">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t>Kasoor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shekhpura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gujranwala </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISB Pindi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen </t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1650,13 +1668,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2296,13 +2307,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="157">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+        <v>46274</v>
+      </c>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2324,10 +2335,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="158" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2357,13 +2368,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="146"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="148"/>
+      <c r="O2" s="149" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="150"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2382,8 +2393,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="154"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2411,29 +2422,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="153"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="164" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="165"/>
+      <c r="W3" s="165"/>
+      <c r="X3" s="166"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="154"/>
+      <c r="B4" s="160"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -3279,25 +3290,25 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="143">
+      <c r="A15" s="72">
         <v>46272</v>
       </c>
-      <c r="B15" s="144">
+      <c r="B15" s="41">
         <v>11</v>
       </c>
-      <c r="C15" s="145" t="s">
+      <c r="C15" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="145"/>
-      <c r="E15" s="146">
+      <c r="D15" s="140"/>
+      <c r="E15" s="44">
         <v>385</v>
       </c>
-      <c r="F15" s="146"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="148"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70"/>
       <c r="L15" s="42">
         <f t="shared" si="0"/>
         <v>9.625</v>
@@ -3349,31 +3360,31 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="143">
+      <c r="A16" s="72">
         <v>46272</v>
       </c>
-      <c r="B16" s="144">
+      <c r="B16" s="41">
         <v>12</v>
       </c>
-      <c r="C16" s="145" t="s">
+      <c r="C16" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="145" t="s">
+      <c r="D16" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="146"/>
-      <c r="F16" s="146">
+      <c r="E16" s="44"/>
+      <c r="F16" s="44">
         <v>40</v>
       </c>
-      <c r="G16" s="147"/>
-      <c r="H16" s="50">
+      <c r="G16" s="69"/>
+      <c r="H16" s="43">
         <v>40</v>
       </c>
-      <c r="I16" s="146"/>
-      <c r="J16" s="147">
+      <c r="I16" s="44"/>
+      <c r="J16" s="69">
         <v>40</v>
       </c>
-      <c r="K16" s="148">
+      <c r="K16" s="70">
         <v>40</v>
       </c>
       <c r="L16" s="42">
@@ -3427,35 +3438,35 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A17" s="143">
+      <c r="A17" s="72">
         <v>46272</v>
       </c>
-      <c r="B17" s="144">
+      <c r="B17" s="41">
         <v>13</v>
       </c>
-      <c r="C17" s="145" t="s">
+      <c r="C17" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="145" t="s">
+      <c r="D17" s="140" t="s">
         <v>114</v>
       </c>
-      <c r="E17" s="146"/>
-      <c r="F17" s="146">
+      <c r="E17" s="44"/>
+      <c r="F17" s="44">
         <v>40</v>
       </c>
-      <c r="G17" s="147">
+      <c r="G17" s="69">
         <v>120</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="43">
         <v>200</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="44">
         <v>80</v>
       </c>
-      <c r="J17" s="147">
+      <c r="J17" s="69">
         <v>40</v>
       </c>
-      <c r="K17" s="148">
+      <c r="K17" s="70">
         <v>240</v>
       </c>
       <c r="L17" s="42">
@@ -3509,33 +3520,33 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A18" s="143">
+      <c r="A18" s="72">
         <v>46272</v>
       </c>
-      <c r="B18" s="144">
+      <c r="B18" s="41">
         <v>14</v>
       </c>
-      <c r="C18" s="145" t="s">
+      <c r="C18" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="145" t="s">
+      <c r="D18" s="140" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="146"/>
-      <c r="F18" s="146">
+      <c r="E18" s="44"/>
+      <c r="F18" s="44">
         <v>80</v>
       </c>
-      <c r="G18" s="147"/>
-      <c r="H18" s="50">
+      <c r="G18" s="69"/>
+      <c r="H18" s="43">
         <v>40</v>
       </c>
-      <c r="I18" s="146">
+      <c r="I18" s="44">
         <v>200</v>
       </c>
-      <c r="J18" s="147">
+      <c r="J18" s="69">
         <v>160</v>
       </c>
-      <c r="K18" s="148">
+      <c r="K18" s="70">
         <v>280</v>
       </c>
       <c r="L18" s="42">
@@ -3589,29 +3600,29 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A19" s="143">
+      <c r="A19" s="72">
         <v>46272</v>
       </c>
-      <c r="B19" s="144">
+      <c r="B19" s="41">
         <v>15</v>
       </c>
-      <c r="C19" s="145" t="s">
+      <c r="C19" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="145" t="s">
+      <c r="D19" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="146"/>
-      <c r="F19" s="146">
+      <c r="E19" s="44"/>
+      <c r="F19" s="44">
         <v>40</v>
       </c>
-      <c r="G19" s="147">
+      <c r="G19" s="69">
         <v>80</v>
       </c>
-      <c r="H19" s="50"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="147"/>
-      <c r="K19" s="148">
+      <c r="H19" s="43"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="70">
         <v>200</v>
       </c>
       <c r="L19" s="42">
@@ -3665,33 +3676,33 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A20" s="143">
+      <c r="A20" s="72">
         <v>46272</v>
       </c>
-      <c r="B20" s="144">
+      <c r="B20" s="41">
         <v>16</v>
       </c>
-      <c r="C20" s="145" t="s">
+      <c r="C20" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="145" t="s">
+      <c r="D20" s="140" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="146"/>
-      <c r="F20" s="146">
+      <c r="E20" s="44"/>
+      <c r="F20" s="44">
         <v>200</v>
       </c>
-      <c r="G20" s="147">
+      <c r="G20" s="69">
         <v>120</v>
       </c>
-      <c r="H20" s="50"/>
-      <c r="I20" s="146">
+      <c r="H20" s="43"/>
+      <c r="I20" s="44">
         <v>40</v>
       </c>
-      <c r="J20" s="147">
+      <c r="J20" s="69">
         <v>80</v>
       </c>
-      <c r="K20" s="148">
+      <c r="K20" s="70">
         <v>440</v>
       </c>
       <c r="L20" s="42">
@@ -3745,31 +3756,31 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A21" s="143">
+      <c r="A21" s="72">
         <v>46272</v>
       </c>
-      <c r="B21" s="144">
+      <c r="B21" s="41">
         <v>17</v>
       </c>
-      <c r="C21" s="145" t="s">
+      <c r="C21" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="145" t="s">
+      <c r="D21" s="140" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="146">
+      <c r="E21" s="44">
         <v>1600</v>
       </c>
-      <c r="F21" s="146"/>
-      <c r="G21" s="147"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="146">
+      <c r="F21" s="44"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44">
         <v>600</v>
       </c>
-      <c r="J21" s="147">
+      <c r="J21" s="69">
         <v>1000</v>
       </c>
-      <c r="K21" s="148">
+      <c r="K21" s="70">
         <v>800</v>
       </c>
       <c r="L21" s="42">
@@ -3823,22 +3834,38 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A22" s="72"/>
+      <c r="A22" s="143">
+        <v>46273</v>
+      </c>
       <c r="B22" s="41">
         <v>18</v>
       </c>
-      <c r="C22" s="140"/>
-      <c r="D22" s="140"/>
+      <c r="C22" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="140" t="s">
+        <v>121</v>
+      </c>
       <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="43"/>
+      <c r="F22" s="44">
+        <v>40</v>
+      </c>
+      <c r="G22" s="69">
+        <v>40</v>
+      </c>
+      <c r="H22" s="43">
+        <v>80</v>
+      </c>
       <c r="I22" s="44"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="70"/>
+      <c r="J22" s="69">
+        <v>80</v>
+      </c>
+      <c r="K22" s="70">
+        <v>80</v>
+      </c>
       <c r="L22" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="15"/>
@@ -3847,11 +3874,11 @@
       <c r="N22" s="43"/>
       <c r="O22" s="67">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P22" s="34">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q22" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3887,22 +3914,36 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A23" s="72"/>
+      <c r="A23" s="143">
+        <v>46273</v>
+      </c>
       <c r="B23" s="41">
         <v>19</v>
       </c>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
+      <c r="C23" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="140" t="s">
+        <v>122</v>
+      </c>
       <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="69"/>
+      <c r="F23" s="44">
+        <v>40</v>
+      </c>
+      <c r="G23" s="69">
+        <v>40</v>
+      </c>
       <c r="H23" s="43"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="69"/>
+      <c r="I23" s="44">
+        <v>240</v>
+      </c>
+      <c r="J23" s="69">
+        <v>80</v>
+      </c>
       <c r="K23" s="70"/>
       <c r="L23" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M23" s="33">
         <f t="shared" si="15"/>
@@ -3911,11 +3952,11 @@
       <c r="N23" s="43"/>
       <c r="O23" s="67">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P23" s="34">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3951,22 +3992,38 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A24" s="72"/>
+      <c r="A24" s="143">
+        <v>46273</v>
+      </c>
       <c r="B24" s="41">
         <v>20</v>
       </c>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
+      <c r="C24" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="140" t="s">
+        <v>123</v>
+      </c>
       <c r="E24" s="44"/>
       <c r="F24" s="44"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="70"/>
+      <c r="G24" s="69">
+        <v>40</v>
+      </c>
+      <c r="H24" s="43">
+        <v>40</v>
+      </c>
+      <c r="I24" s="44">
+        <v>40</v>
+      </c>
+      <c r="J24" s="69">
+        <v>40</v>
+      </c>
+      <c r="K24" s="70">
+        <v>200</v>
+      </c>
       <c r="L24" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M24" s="33">
         <f t="shared" si="15"/>
@@ -3975,11 +4032,11 @@
       <c r="N24" s="43"/>
       <c r="O24" s="67">
         <f t="shared" ref="O24:O27" si="37">SUM(F24:H24)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24" s="34">
         <f t="shared" ref="P24:P27" si="38">SUM(I24:K24)/20</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4015,22 +4072,40 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A25" s="72"/>
+      <c r="A25" s="143">
+        <v>46273</v>
+      </c>
       <c r="B25" s="41">
         <v>21</v>
       </c>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
+      <c r="C25" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="140" t="s">
+        <v>124</v>
+      </c>
       <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="70"/>
+      <c r="F25" s="44">
+        <v>40</v>
+      </c>
+      <c r="G25" s="69">
+        <v>40</v>
+      </c>
+      <c r="H25" s="43">
+        <v>0</v>
+      </c>
+      <c r="I25" s="44">
+        <v>38</v>
+      </c>
+      <c r="J25" s="69">
+        <v>0</v>
+      </c>
+      <c r="K25" s="70">
+        <v>200</v>
+      </c>
       <c r="L25" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="M25" s="33">
         <f t="shared" si="15"/>
@@ -4039,11 +4114,11 @@
       <c r="N25" s="43"/>
       <c r="O25" s="67">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P25" s="34">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="Q25" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4079,22 +4154,38 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A26" s="72"/>
+      <c r="A26" s="143">
+        <v>46273</v>
+      </c>
       <c r="B26" s="41">
         <v>22</v>
       </c>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
+      <c r="C26" s="140" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="140" t="s">
+        <v>99</v>
+      </c>
       <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
+      <c r="F26" s="44">
+        <v>80</v>
+      </c>
       <c r="G26" s="69"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="70"/>
+      <c r="H26" s="43">
+        <v>80</v>
+      </c>
+      <c r="I26" s="44">
+        <v>80</v>
+      </c>
+      <c r="J26" s="69">
+        <v>80</v>
+      </c>
+      <c r="K26" s="70">
+        <v>80</v>
+      </c>
       <c r="L26" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M26" s="33">
         <f t="shared" si="15"/>
@@ -4103,11 +4194,11 @@
       <c r="N26" s="43"/>
       <c r="O26" s="67">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P26" s="34">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4143,7 +4234,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="72"/>
+      <c r="A27" s="143"/>
       <c r="B27" s="41">
         <v>23</v>
       </c>
@@ -10957,10 +11048,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="168"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -10968,31 +11059,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>920</v>
+        <v>1120</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>840</v>
+        <v>1000</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>1720</v>
+        <v>2118</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>1960</v>
+        <v>2240</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>2040</v>
+        <v>2600</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>268.625</v>
+        <v>313.57499999999999</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11004,11 +11095,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>286</v>
+        <v>347.9</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11214,10 +11305,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="155" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="156"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11301,10 +11392,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="145"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11312,31 +11403,31 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>920</v>
+        <v>1120</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>840</v>
+        <v>1000</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>1720</v>
+        <v>2118</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>1960</v>
+        <v>2240</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>2040</v>
+        <v>2600</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>268.625</v>
+        <v>313.57499999999999</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
@@ -11348,11 +11439,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>692</v>
+        <v>815.8</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11435,25 +11526,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="176"/>
+      <c r="K3" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11499,24 +11590,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E5" s="73">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>616</v>
+        <v>701</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-9384</v>
+        <v>-9299</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11525,11 +11616,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>5914</v>
+        <v>5972</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>147.85</v>
+        <v>149.30000000000001</v>
       </c>
       <c r="O5" s="75"/>
       <c r="P5" s="142"/>
@@ -11540,11 +11631,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>9120</v>
+        <v>10720</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>11520</v>
+        <v>13320</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11552,7 +11643,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>24640</v>
+        <v>28040</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11560,7 +11651,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-375360</v>
+        <v>-371960</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11569,11 +11660,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>3824</v>
+        <v>7579</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>95.6</v>
+        <v>189.47499999999999</v>
       </c>
       <c r="O6" s="75"/>
       <c r="P6" s="142"/>
@@ -11604,11 +11695,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>1272</v>
+        <v>4029</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>31.8</v>
+        <v>100.72499999999999</v>
       </c>
       <c r="O7" s="75"/>
       <c r="P7" s="142"/>
@@ -11648,11 +11739,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>6217</v>
+        <v>5849</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>155.42500000000001</v>
+        <v>146.22499999999999</v>
       </c>
       <c r="O8" s="75">
         <v>50</v>
@@ -11688,11 +11779,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-228</v>
+        <v>-268</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-288</v>
+        <v>-333</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11701,11 +11792,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>7343</v>
+        <v>6849</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>183.57499999999999</v>
+        <v>171.22499999999999</v>
       </c>
       <c r="O9" s="75">
         <v>23</v>
@@ -11745,11 +11836,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>727</v>
+        <v>4278</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>18.175000000000001</v>
+        <v>106.95</v>
       </c>
       <c r="O10" s="75"/>
       <c r="P10" s="142"/>
@@ -11776,14 +11867,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="174"/>
+      <c r="F11" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="174"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -11791,11 +11882,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>8761</v>
+        <v>3243</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>219.02500000000001</v>
+        <v>81.075000000000003</v>
       </c>
       <c r="O11" s="75">
         <v>125</v>
@@ -11835,7 +11926,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>4816</v>
+        <v>4901</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -11843,11 +11934,11 @@
       <c r="L12" s="75"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>34058</v>
+        <v>37799</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>851.44999999999993</v>
+        <v>944.97500000000014</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -11887,12 +11978,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>192640</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>196040</v>
+      </c>
+      <c r="S13" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="169"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -11946,7 +12037,7 @@
       <c r="N17" s="115"/>
       <c r="O17" s="116">
         <f>N17-M5</f>
-        <v>-5914</v>
+        <v>-5972</v>
       </c>
     </row>
     <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11960,7 +12051,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="116">
         <f>N18-M6</f>
-        <v>-3824</v>
+        <v>-7579</v>
       </c>
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11977,17 +12068,17 @@
       <c r="N19" s="5"/>
       <c r="O19" s="116">
         <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>-1272</v>
+        <v>-4029</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -11998,7 +12089,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="116">
         <f t="shared" si="4"/>
-        <v>-6217</v>
+        <v>-5849</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12027,7 +12118,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="116">
         <f t="shared" si="4"/>
-        <v>-7343</v>
+        <v>-6849</v>
       </c>
     </row>
     <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12053,7 +12144,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="116">
         <f t="shared" si="4"/>
-        <v>-727</v>
+        <v>-4278</v>
       </c>
     </row>
     <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12079,7 +12170,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="116">
         <f t="shared" si="4"/>
-        <v>-8761</v>
+        <v>-3243</v>
       </c>
     </row>
     <row r="24" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12109,7 +12200,7 @@
       </c>
       <c r="O24" s="111">
         <f>SUM(O17:O23)</f>
-        <v>-34058</v>
+        <v>-37799</v>
       </c>
     </row>
     <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12139,7 +12230,7 @@
       </c>
       <c r="O25" s="111">
         <f>O24/40</f>
-        <v>-851.45</v>
+        <v>-944.97500000000002</v>
       </c>
     </row>
     <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001412D-21D4-4480-80E7-1FAC0ABE7BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10AE29-754D-4A8A-9391-2B2DDC5724A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -400,6 +400,18 @@
   </si>
   <si>
     <t xml:space="preserve">Risen </t>
+  </si>
+  <si>
+    <t>Main Market</t>
+  </si>
+  <si>
+    <t>Kashif BDM</t>
+  </si>
+  <si>
+    <t>Zubaida Associate</t>
+  </si>
+  <si>
+    <t>Attari Darbar</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1668,6 +1680,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2307,13 +2326,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="157">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46274</v>
-      </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
+        <v>46275</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2335,10 +2354,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2368,13 +2387,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="146"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="149" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="150"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2393,8 +2412,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="154"/>
-      <c r="B3" s="159"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2422,29 +2441,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="151" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="152"/>
-      <c r="N3" s="153"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="161" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="164" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="165"/>
-      <c r="W3" s="165"/>
-      <c r="X3" s="166"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="154"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -3392,8 +3411,7 @@
         <v>4</v>
       </c>
       <c r="M16" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N16" s="43"/>
       <c r="O16" s="67">
@@ -3474,8 +3492,7 @@
         <v>18</v>
       </c>
       <c r="M17" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N17" s="43"/>
       <c r="O17" s="67">
@@ -3554,8 +3571,7 @@
         <v>19</v>
       </c>
       <c r="M18" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N18" s="43"/>
       <c r="O18" s="67">
@@ -3630,8 +3646,7 @@
         <v>8</v>
       </c>
       <c r="M19" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N19" s="43"/>
       <c r="O19" s="67">
@@ -3710,8 +3725,7 @@
         <v>22</v>
       </c>
       <c r="M20" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N20" s="43"/>
       <c r="O20" s="67">
@@ -3788,8 +3802,7 @@
         <v>100</v>
       </c>
       <c r="M21" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N21" s="43"/>
       <c r="O21" s="67">
@@ -3834,7 +3847,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A22" s="143">
+      <c r="A22" s="72">
         <v>46273</v>
       </c>
       <c r="B22" s="41">
@@ -3868,8 +3881,7 @@
         <v>8</v>
       </c>
       <c r="M22" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N22" s="43"/>
       <c r="O22" s="67">
@@ -3914,7 +3926,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A23" s="143">
+      <c r="A23" s="72">
         <v>46273</v>
       </c>
       <c r="B23" s="41">
@@ -3946,8 +3958,7 @@
         <v>10</v>
       </c>
       <c r="M23" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N23" s="43"/>
       <c r="O23" s="67">
@@ -3992,7 +4003,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A24" s="143">
+      <c r="A24" s="72">
         <v>46273</v>
       </c>
       <c r="B24" s="41">
@@ -4026,8 +4037,7 @@
         <v>9</v>
       </c>
       <c r="M24" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N24" s="43"/>
       <c r="O24" s="67">
@@ -4072,7 +4082,7 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A25" s="143">
+      <c r="A25" s="72">
         <v>46273</v>
       </c>
       <c r="B25" s="41">
@@ -4108,8 +4118,7 @@
         <v>7.95</v>
       </c>
       <c r="M25" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N25" s="43"/>
       <c r="O25" s="67">
@@ -4154,7 +4163,7 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A26" s="143">
+      <c r="A26" s="72">
         <v>46273</v>
       </c>
       <c r="B26" s="41">
@@ -4188,8 +4197,7 @@
         <v>10</v>
       </c>
       <c r="M26" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N26" s="43"/>
       <c r="O26" s="67">
@@ -4234,35 +4242,52 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="143"/>
-      <c r="B27" s="41">
+      <c r="A27" s="143">
+        <v>46274</v>
+      </c>
+      <c r="B27" s="144">
         <v>23</v>
       </c>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="70"/>
+      <c r="C27" s="145" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="145" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="146"/>
+      <c r="F27" s="146">
+        <v>80</v>
+      </c>
+      <c r="G27" s="147">
+        <v>80</v>
+      </c>
+      <c r="H27" s="50">
+        <v>120</v>
+      </c>
+      <c r="I27" s="146">
+        <v>120</v>
+      </c>
+      <c r="J27" s="147">
+        <v>120</v>
+      </c>
+      <c r="K27" s="148">
+        <v>120</v>
+      </c>
       <c r="L27" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M27" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N27" s="43"/>
       <c r="O27" s="67">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P27" s="34">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4298,31 +4323,40 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A28" s="72"/>
-      <c r="B28" s="41">
+      <c r="A28" s="143">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="144">
         <v>24</v>
       </c>
-      <c r="C28" s="140"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="70"/>
+      <c r="C28" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="146">
+        <v>60</v>
+      </c>
+      <c r="G28" s="147">
+        <v>50</v>
+      </c>
+      <c r="H28" s="50">
+        <v>50</v>
+      </c>
+      <c r="I28" s="146"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="148"/>
       <c r="L28" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N28" s="43"/>
       <c r="O28" s="67">
         <f t="shared" ref="O28:O61" si="41">SUM(F28:H28)/20</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P28" s="34">
         <f t="shared" ref="P28:P61" si="42">SUM(I28:K28)/20</f>
@@ -4362,35 +4396,52 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A29" s="72"/>
-      <c r="B29" s="41">
+      <c r="A29" s="143">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="144">
         <v>25</v>
       </c>
-      <c r="C29" s="140"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="70"/>
+      <c r="C29" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="145" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="146"/>
+      <c r="F29" s="146">
+        <v>400</v>
+      </c>
+      <c r="G29" s="147">
+        <v>600</v>
+      </c>
+      <c r="H29" s="50">
+        <v>1200</v>
+      </c>
+      <c r="I29" s="146">
+        <v>600</v>
+      </c>
+      <c r="J29" s="147">
+        <v>1200</v>
+      </c>
+      <c r="K29" s="148">
+        <v>2000</v>
+      </c>
       <c r="L29" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M29" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N29" s="43"/>
       <c r="O29" s="67">
         <f t="shared" ref="O29" si="47">SUM(F29:H29)/20</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="P29" s="34">
         <f t="shared" ref="P29" si="48">SUM(I29:K29)/20</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="Q29" s="45" t="e">
         <f t="shared" si="1"/>
@@ -11048,10 +11099,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="167" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="168"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11059,31 +11110,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>1120</v>
+        <v>1660</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>1000</v>
+        <v>1730</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>1200</v>
+        <v>2570</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>2118</v>
+        <v>2838</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>2240</v>
+        <v>3560</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>2600</v>
+        <v>4720</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>313.57499999999999</v>
+        <v>483.57499999999999</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11095,11 +11146,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>166</v>
+        <v>298</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>347.9</v>
+        <v>555.9</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11305,10 +11356,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="155" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="156"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11392,10 +11443,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="144" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="145"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11403,35 +11454,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>1120</v>
+        <v>1660</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>1000</v>
+        <v>1730</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>1200</v>
+        <v>2570</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>2118</v>
+        <v>2838</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>2240</v>
+        <v>3560</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>2600</v>
+        <v>4720</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>313.57499999999999</v>
+        <v>483.57499999999999</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>108</v>
+        <v>305</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11439,11 +11490,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>452</v>
+        <v>716</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>815.8</v>
+        <v>1231.8</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11526,25 +11577,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="175" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="176"/>
-      <c r="K3" s="177" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="177"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="177"/>
-      <c r="O3" s="177"/>
-      <c r="P3" s="177"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11590,24 +11641,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>268</v>
+        <v>360</v>
       </c>
       <c r="E5" s="73">
-        <v>333</v>
+        <v>504</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>701</v>
+        <v>964</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-9299</v>
+        <v>-9036</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11631,11 +11682,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>10720</v>
+        <v>14400</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>13320</v>
+        <v>20160</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11643,7 +11694,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>28040</v>
+        <v>38560</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11651,7 +11702,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-371960</v>
+        <v>-361440</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11779,11 +11830,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-268</v>
+        <v>-360</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-333</v>
+        <v>-504</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11867,14 +11918,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="174"/>
-      <c r="F11" s="174" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="174"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -11926,7 +11977,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>4901</v>
+        <v>5164</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -11978,12 +12029,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>196040</v>
-      </c>
-      <c r="S13" s="169" t="s">
+        <v>206560</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="169"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12072,13 +12123,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="170" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10AE29-754D-4A8A-9391-2B2DDC5724A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92485F03-FD78-46D1-A0DC-4E75B010EB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -412,6 +412,21 @@
   </si>
   <si>
     <t>Attari Darbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valencia Town </t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Behria Orchard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake city </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raja Sahb </t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1687,6 +1702,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1726,42 +1777,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1789,6 +1804,17 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2319,20 +2345,20 @@
   <dimension ref="A1:X138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
-      </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+        <v>46276</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2354,10 +2380,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2387,13 +2413,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="167"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2412,8 +2438,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2441,29 +2467,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="170"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -4242,35 +4268,35 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="143">
+      <c r="A27" s="183">
         <v>46274</v>
       </c>
-      <c r="B27" s="144">
+      <c r="B27" s="184">
         <v>23</v>
       </c>
-      <c r="C27" s="145" t="s">
+      <c r="C27" s="185" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="145" t="s">
+      <c r="D27" s="185" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="146"/>
-      <c r="F27" s="146">
+      <c r="E27" s="186"/>
+      <c r="F27" s="186">
         <v>80</v>
       </c>
-      <c r="G27" s="147">
+      <c r="G27" s="187">
         <v>80</v>
       </c>
-      <c r="H27" s="50">
+      <c r="H27" s="188">
         <v>120</v>
       </c>
-      <c r="I27" s="146">
+      <c r="I27" s="186">
         <v>120</v>
       </c>
-      <c r="J27" s="147">
+      <c r="J27" s="187">
         <v>120</v>
       </c>
-      <c r="K27" s="148">
+      <c r="K27" s="189">
         <v>120</v>
       </c>
       <c r="L27" s="42">
@@ -4323,29 +4349,29 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A28" s="143">
+      <c r="A28" s="183">
         <v>46274</v>
       </c>
-      <c r="B28" s="144">
+      <c r="B28" s="184">
         <v>24</v>
       </c>
-      <c r="C28" s="145" t="s">
+      <c r="C28" s="185" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="145"/>
-      <c r="E28" s="146"/>
-      <c r="F28" s="146">
+      <c r="D28" s="185"/>
+      <c r="E28" s="186"/>
+      <c r="F28" s="186">
         <v>60</v>
       </c>
-      <c r="G28" s="147">
+      <c r="G28" s="187">
         <v>50</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="188">
         <v>50</v>
       </c>
-      <c r="I28" s="146"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="148"/>
+      <c r="I28" s="186"/>
+      <c r="J28" s="187"/>
+      <c r="K28" s="189"/>
       <c r="L28" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4396,35 +4422,35 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A29" s="143">
+      <c r="A29" s="183">
         <v>46274</v>
       </c>
-      <c r="B29" s="144">
+      <c r="B29" s="184">
         <v>25</v>
       </c>
-      <c r="C29" s="145" t="s">
+      <c r="C29" s="185" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="145" t="s">
+      <c r="D29" s="185" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="146"/>
-      <c r="F29" s="146">
+      <c r="E29" s="186"/>
+      <c r="F29" s="186">
         <v>400</v>
       </c>
-      <c r="G29" s="147">
+      <c r="G29" s="187">
         <v>600</v>
       </c>
-      <c r="H29" s="50">
+      <c r="H29" s="188">
         <v>1200</v>
       </c>
-      <c r="I29" s="146">
+      <c r="I29" s="186">
         <v>600</v>
       </c>
-      <c r="J29" s="147">
+      <c r="J29" s="187">
         <v>1200</v>
       </c>
-      <c r="K29" s="148">
+      <c r="K29" s="189">
         <v>2000</v>
       </c>
       <c r="L29" s="42">
@@ -4477,35 +4503,52 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30" s="72"/>
-      <c r="B30" s="41">
+      <c r="A30" s="143">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="144">
         <v>26</v>
       </c>
-      <c r="C30" s="140"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="70"/>
+      <c r="C30" s="145" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="145" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="146"/>
+      <c r="F30" s="146">
+        <v>20</v>
+      </c>
+      <c r="G30" s="147">
+        <v>40</v>
+      </c>
+      <c r="H30" s="50">
+        <v>40</v>
+      </c>
+      <c r="I30" s="146">
+        <v>20</v>
+      </c>
+      <c r="J30" s="147">
+        <v>40</v>
+      </c>
+      <c r="K30" s="148">
+        <v>40</v>
+      </c>
       <c r="L30" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M30" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N30" s="43"/>
       <c r="O30" s="67">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" s="34">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4541,26 +4584,37 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A31" s="72"/>
-      <c r="B31" s="41">
+      <c r="A31" s="143">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="144">
         <v>27</v>
       </c>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="70"/>
+      <c r="C31" s="145" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" s="145" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="146"/>
+      <c r="F31" s="146"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="146">
+        <v>80</v>
+      </c>
+      <c r="J31" s="147">
+        <v>40</v>
+      </c>
+      <c r="K31" s="148">
+        <v>80</v>
+      </c>
       <c r="L31" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M31" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N31" s="43"/>
       <c r="O31" s="67">
@@ -4569,7 +4623,7 @@
       </c>
       <c r="P31" s="34">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q31" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4605,35 +4659,52 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A32" s="72"/>
-      <c r="B32" s="41">
+      <c r="A32" s="143">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="144">
         <v>28</v>
       </c>
-      <c r="C32" s="140"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="70"/>
+      <c r="C32" s="145" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="145" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="146"/>
+      <c r="F32" s="146">
+        <v>80</v>
+      </c>
+      <c r="G32" s="147">
+        <v>40</v>
+      </c>
+      <c r="H32" s="50">
+        <v>80</v>
+      </c>
+      <c r="I32" s="146">
+        <v>40</v>
+      </c>
+      <c r="J32" s="147">
+        <v>40</v>
+      </c>
+      <c r="K32" s="148">
+        <v>40</v>
+      </c>
       <c r="L32" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M32" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N32" s="43"/>
       <c r="O32" s="67">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P32" s="34">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4669,35 +4740,44 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A33" s="72"/>
-      <c r="B33" s="41">
+      <c r="A33" s="143">
+        <v>46275</v>
+      </c>
+      <c r="B33" s="144">
         <v>29</v>
       </c>
-      <c r="C33" s="140"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="70"/>
+      <c r="C33" s="145" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="145" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="146"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="147"/>
+      <c r="H33" s="50">
+        <v>80</v>
+      </c>
+      <c r="I33" s="146"/>
+      <c r="J33" s="147"/>
+      <c r="K33" s="148">
+        <v>200</v>
+      </c>
       <c r="L33" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M33" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N33" s="43"/>
       <c r="O33" s="67">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" s="34">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q33" s="45" t="e">
         <f t="shared" si="1"/>
@@ -11099,10 +11179,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="160"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11110,31 +11190,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>1660</v>
+        <v>1760</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>1730</v>
+        <v>1810</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>2570</v>
+        <v>2770</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>2838</v>
+        <v>2978</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>3560</v>
+        <v>3680</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>4720</v>
+        <v>5080</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>483.57499999999999</v>
+        <v>508.57499999999999</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11146,11 +11226,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>555.9</v>
+        <v>586.9</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11356,10 +11436,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="173"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11443,10 +11523,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="162"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11454,35 +11534,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>1660</v>
+        <v>1760</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>1730</v>
+        <v>1810</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>2570</v>
+        <v>2770</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>2838</v>
+        <v>2978</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>3560</v>
+        <v>3680</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>4720</v>
+        <v>5080</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>483.57499999999999</v>
+        <v>508.57499999999999</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11490,11 +11570,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>716</v>
+        <v>754</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1231.8</v>
+        <v>1293.8</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11531,17 +11611,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11641,24 +11721,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="E5" s="73">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>964</v>
+        <v>1039</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-9036</v>
+        <v>-8961</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11682,11 +11762,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>14400</v>
+        <v>16400</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>20160</v>
+        <v>21160</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11694,7 +11774,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>38560</v>
+        <v>41560</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11702,7 +11782,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-361440</v>
+        <v>-358440</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11830,11 +11910,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-360</v>
+        <v>-410</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-504</v>
+        <v>-529</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11977,7 +12057,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>5164</v>
+        <v>5239</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12029,7 +12109,7 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>206560</v>
+        <v>209560</v>
       </c>
       <c r="S13" s="174" t="s">
         <v>83</v>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92485F03-FD78-46D1-A0DC-4E75B010EB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE7165-40CD-46F3-8E5A-F748F26A2252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="140">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -427,6 +427,21 @@
   </si>
   <si>
     <t xml:space="preserve">Raja Sahb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pak Madina </t>
+  </si>
+  <si>
+    <t>Raheem Store</t>
+  </si>
+  <si>
+    <t>Al Rehman Garden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iqbal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheikhupura </t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1695,13 +1710,49 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1736,45 +1787,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2347,18 +2359,18 @@
   <cols>
     <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="161">
         <f ca="1">TODAY()</f>
-        <v>46276</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46277</v>
+      </c>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2380,10 +2392,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="162" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2413,13 +2425,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166" t="s">
+      <c r="L2" s="150"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="153" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="167"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2438,8 +2450,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="163"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2467,29 +2479,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="170"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="157"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="167"/>
+      <c r="U3" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="169"/>
+      <c r="W3" s="169"/>
+      <c r="X3" s="170"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="164"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -4268,35 +4280,35 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="183">
+      <c r="A27" s="72">
         <v>46274</v>
       </c>
-      <c r="B27" s="184">
+      <c r="B27" s="41">
         <v>23</v>
       </c>
-      <c r="C27" s="185" t="s">
+      <c r="C27" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="185" t="s">
+      <c r="D27" s="140" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="186"/>
-      <c r="F27" s="186">
+      <c r="E27" s="44"/>
+      <c r="F27" s="44">
         <v>80</v>
       </c>
-      <c r="G27" s="187">
+      <c r="G27" s="69">
         <v>80</v>
       </c>
-      <c r="H27" s="188">
+      <c r="H27" s="43">
         <v>120</v>
       </c>
-      <c r="I27" s="186">
+      <c r="I27" s="44">
         <v>120</v>
       </c>
-      <c r="J27" s="187">
+      <c r="J27" s="69">
         <v>120</v>
       </c>
-      <c r="K27" s="189">
+      <c r="K27" s="70">
         <v>120</v>
       </c>
       <c r="L27" s="42">
@@ -4349,29 +4361,29 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A28" s="183">
+      <c r="A28" s="72">
         <v>46274</v>
       </c>
-      <c r="B28" s="184">
+      <c r="B28" s="41">
         <v>24</v>
       </c>
-      <c r="C28" s="185" t="s">
+      <c r="C28" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="185"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186">
+      <c r="D28" s="140"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44">
         <v>60</v>
       </c>
-      <c r="G28" s="187">
+      <c r="G28" s="69">
         <v>50</v>
       </c>
-      <c r="H28" s="188">
+      <c r="H28" s="43">
         <v>50</v>
       </c>
-      <c r="I28" s="186"/>
-      <c r="J28" s="187"/>
-      <c r="K28" s="189"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="70"/>
       <c r="L28" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4422,35 +4434,35 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A29" s="183">
+      <c r="A29" s="72">
         <v>46274</v>
       </c>
-      <c r="B29" s="184">
+      <c r="B29" s="41">
         <v>25</v>
       </c>
-      <c r="C29" s="185" t="s">
+      <c r="C29" s="140" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="185" t="s">
+      <c r="D29" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="186"/>
-      <c r="F29" s="186">
+      <c r="E29" s="44"/>
+      <c r="F29" s="44">
         <v>400</v>
       </c>
-      <c r="G29" s="187">
+      <c r="G29" s="69">
         <v>600</v>
       </c>
-      <c r="H29" s="188">
+      <c r="H29" s="43">
         <v>1200</v>
       </c>
-      <c r="I29" s="186">
+      <c r="I29" s="44">
         <v>600</v>
       </c>
-      <c r="J29" s="187">
+      <c r="J29" s="69">
         <v>1200</v>
       </c>
-      <c r="K29" s="189">
+      <c r="K29" s="70">
         <v>2000</v>
       </c>
       <c r="L29" s="42">
@@ -4503,35 +4515,35 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30" s="143">
+      <c r="A30" s="182">
         <v>46275</v>
       </c>
-      <c r="B30" s="144">
+      <c r="B30" s="183">
         <v>26</v>
       </c>
-      <c r="C30" s="145" t="s">
+      <c r="C30" s="184" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="145" t="s">
+      <c r="D30" s="184" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="146"/>
-      <c r="F30" s="146">
+      <c r="E30" s="185"/>
+      <c r="F30" s="185">
         <v>20</v>
       </c>
-      <c r="G30" s="147">
+      <c r="G30" s="186">
         <v>40</v>
       </c>
-      <c r="H30" s="50">
+      <c r="H30" s="187">
         <v>40</v>
       </c>
-      <c r="I30" s="146">
+      <c r="I30" s="185">
         <v>20</v>
       </c>
-      <c r="J30" s="147">
+      <c r="J30" s="186">
         <v>40</v>
       </c>
-      <c r="K30" s="148">
+      <c r="K30" s="188">
         <v>40</v>
       </c>
       <c r="L30" s="42">
@@ -4584,29 +4596,29 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A31" s="143">
+      <c r="A31" s="182">
         <v>46275</v>
       </c>
-      <c r="B31" s="144">
+      <c r="B31" s="183">
         <v>27</v>
       </c>
-      <c r="C31" s="145" t="s">
+      <c r="C31" s="184" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="145" t="s">
+      <c r="D31" s="184" t="s">
         <v>132</v>
       </c>
-      <c r="E31" s="146"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="146">
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="185">
         <v>80</v>
       </c>
-      <c r="J31" s="147">
+      <c r="J31" s="186">
         <v>40</v>
       </c>
-      <c r="K31" s="148">
+      <c r="K31" s="188">
         <v>80</v>
       </c>
       <c r="L31" s="42">
@@ -4659,35 +4671,35 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A32" s="143">
+      <c r="A32" s="182">
         <v>46275</v>
       </c>
-      <c r="B32" s="144">
+      <c r="B32" s="183">
         <v>28</v>
       </c>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="184" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="145" t="s">
+      <c r="D32" s="184" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="146"/>
-      <c r="F32" s="146">
+      <c r="E32" s="185"/>
+      <c r="F32" s="185">
         <v>80</v>
       </c>
-      <c r="G32" s="147">
+      <c r="G32" s="186">
         <v>40</v>
       </c>
-      <c r="H32" s="50">
+      <c r="H32" s="187">
         <v>80</v>
       </c>
-      <c r="I32" s="146">
+      <c r="I32" s="185">
         <v>40</v>
       </c>
-      <c r="J32" s="147">
+      <c r="J32" s="186">
         <v>40</v>
       </c>
-      <c r="K32" s="148">
+      <c r="K32" s="188">
         <v>40</v>
       </c>
       <c r="L32" s="42">
@@ -4740,27 +4752,27 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A33" s="143">
+      <c r="A33" s="182">
         <v>46275</v>
       </c>
-      <c r="B33" s="144">
+      <c r="B33" s="183">
         <v>29</v>
       </c>
-      <c r="C33" s="145" t="s">
+      <c r="C33" s="184" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="145" t="s">
+      <c r="D33" s="184" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="146"/>
-      <c r="F33" s="146"/>
-      <c r="G33" s="147"/>
-      <c r="H33" s="50">
+      <c r="E33" s="185"/>
+      <c r="F33" s="185"/>
+      <c r="G33" s="186"/>
+      <c r="H33" s="187">
         <v>80</v>
       </c>
-      <c r="I33" s="146"/>
-      <c r="J33" s="147"/>
-      <c r="K33" s="148">
+      <c r="I33" s="185"/>
+      <c r="J33" s="186"/>
+      <c r="K33" s="188">
         <v>200</v>
       </c>
       <c r="L33" s="42">
@@ -4813,26 +4825,43 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A34" s="72"/>
+      <c r="A34" s="143">
+        <v>46276</v>
+      </c>
       <c r="B34" s="41">
         <v>30</v>
       </c>
-      <c r="C34" s="140"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="70"/>
+      <c r="C34" s="144" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="144" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145">
+        <v>80</v>
+      </c>
+      <c r="G34" s="146">
+        <v>80</v>
+      </c>
+      <c r="H34" s="50">
+        <v>160</v>
+      </c>
+      <c r="I34" s="145">
+        <v>160</v>
+      </c>
+      <c r="J34" s="146">
+        <v>120</v>
+      </c>
+      <c r="K34" s="147">
+        <v>520</v>
+      </c>
       <c r="L34" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M34" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N34" s="43">
         <f t="shared" ref="N34:N65" si="53">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
@@ -4840,11 +4869,11 @@
       </c>
       <c r="O34" s="67">
         <f t="shared" ref="O34:O47" si="54">SUM(F34:H34)/20</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P34" s="34">
         <f t="shared" ref="P34:P47" si="55">SUM(I34:K34)/20</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q34" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4880,26 +4909,39 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A35" s="72"/>
+      <c r="A35" s="143">
+        <v>46276</v>
+      </c>
       <c r="B35" s="41">
         <v>31</v>
       </c>
-      <c r="C35" s="140"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="70"/>
+      <c r="C35" s="144" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" s="144" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="145"/>
+      <c r="F35" s="145">
+        <v>40</v>
+      </c>
+      <c r="G35" s="146"/>
+      <c r="H35" s="50">
+        <v>160</v>
+      </c>
+      <c r="I35" s="145"/>
+      <c r="J35" s="146">
+        <v>160</v>
+      </c>
+      <c r="K35" s="147">
+        <v>80</v>
+      </c>
       <c r="L35" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M35" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N35" s="43">
         <f t="shared" si="53"/>
@@ -4907,11 +4949,11 @@
       </c>
       <c r="O35" s="67">
         <f t="shared" ref="O35" si="60">SUM(F35:H35)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P35" s="34">
         <f t="shared" ref="P35" si="61">SUM(I35:K35)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q35" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4947,26 +4989,41 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A36" s="72"/>
+      <c r="A36" s="143">
+        <v>46276</v>
+      </c>
       <c r="B36" s="41">
         <v>32</v>
       </c>
-      <c r="C36" s="140"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="70"/>
+      <c r="C36" s="144" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="145"/>
+      <c r="F36" s="145"/>
+      <c r="G36" s="146">
+        <v>160</v>
+      </c>
+      <c r="H36" s="50">
+        <v>200</v>
+      </c>
+      <c r="I36" s="145">
+        <v>200</v>
+      </c>
+      <c r="J36" s="146">
+        <v>200</v>
+      </c>
+      <c r="K36" s="147">
+        <v>400</v>
+      </c>
       <c r="L36" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M36" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N36" s="43">
         <f t="shared" si="53"/>
@@ -4974,11 +5031,11 @@
       </c>
       <c r="O36" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P36" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q36" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5014,26 +5071,43 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A37" s="72"/>
+      <c r="A37" s="143">
+        <v>46276</v>
+      </c>
       <c r="B37" s="41">
         <v>33</v>
       </c>
-      <c r="C37" s="140"/>
-      <c r="D37" s="140"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="70"/>
+      <c r="C37" s="144" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="144" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="145"/>
+      <c r="F37" s="145">
+        <v>120</v>
+      </c>
+      <c r="G37" s="146">
+        <v>120</v>
+      </c>
+      <c r="H37" s="50">
+        <v>200</v>
+      </c>
+      <c r="I37" s="145">
+        <v>120</v>
+      </c>
+      <c r="J37" s="146">
+        <v>80</v>
+      </c>
+      <c r="K37" s="147">
+        <v>200</v>
+      </c>
       <c r="L37" s="42">
         <f t="shared" ref="L37:L68" si="66">SUM(E37:K37)/40</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M37" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N37" s="43">
         <f t="shared" si="53"/>
@@ -5041,11 +5115,11 @@
       </c>
       <c r="O37" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P37" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q37" s="45" t="e">
         <f t="shared" si="1"/>
@@ -11179,10 +11253,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="159" t="s">
+      <c r="B133" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="160"/>
+      <c r="C133" s="172"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11190,31 +11264,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>1760</v>
+        <v>2000</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>1810</v>
+        <v>2170</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>2770</v>
+        <v>3490</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>2978</v>
+        <v>3458</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>3680</v>
+        <v>4240</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>5080</v>
+        <v>6280</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>508.57499999999999</v>
+        <v>597.57500000000005</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11226,11 +11300,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>586.9</v>
+        <v>698.9</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11436,10 +11510,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="172" t="s">
+      <c r="B137" s="159" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="173"/>
+      <c r="C137" s="160"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11523,10 +11597,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="161" t="s">
+      <c r="B138" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="162"/>
+      <c r="C138" s="149"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11534,35 +11608,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>1760</v>
+        <v>2000</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>1810</v>
+        <v>2170</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>2770</v>
+        <v>3490</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>2978</v>
+        <v>3458</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>3680</v>
+        <v>4240</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>5080</v>
+        <v>6280</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>508.57499999999999</v>
+        <v>597.57500000000005</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11570,11 +11644,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>754</v>
+        <v>886</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1293.8</v>
+        <v>1517.8</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11611,17 +11685,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11657,25 +11731,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="179" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="180"/>
+      <c r="K3" s="181" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="181"/>
+      <c r="M3" s="181"/>
+      <c r="N3" s="181"/>
+      <c r="O3" s="181"/>
+      <c r="P3" s="181"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11721,24 +11795,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="E5" s="73">
-        <v>529</v>
+        <v>618</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1039</v>
+        <v>1156</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8961</v>
+        <v>-8844</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11762,11 +11836,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>16400</v>
+        <v>17520</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>21160</v>
+        <v>24720</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11774,7 +11848,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>41560</v>
+        <v>46240</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11782,7 +11856,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-358440</v>
+        <v>-353760</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11910,11 +11984,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-410</v>
+        <v>-438</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-529</v>
+        <v>-618</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11998,14 +12072,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="178" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="178"/>
+      <c r="F11" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="178"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12057,7 +12131,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>5239</v>
+        <v>5356</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12109,12 +12183,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>209560</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>214240</v>
+      </c>
+      <c r="S13" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="173"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12203,13 +12277,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="174"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE7165-40CD-46F3-8E5A-F748F26A2252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06D90D0-4663-4AE9-9B9F-57321C6E5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="145">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -442,6 +442,21 @@
   </si>
   <si>
     <t xml:space="preserve">Sheikhupura </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fateh Gher </t>
+  </si>
+  <si>
+    <t>Barki Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Mega Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gari Shahu </t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1714,6 +1729,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1816,17 +1834,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2364,13 +2371,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="161">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46277</v>
-      </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
+        <v>46280</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2392,10 +2399,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2425,13 +2432,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="153" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="154"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2450,8 +2457,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="158"/>
-      <c r="B3" s="163"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2479,29 +2486,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="155" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="156"/>
-      <c r="N3" s="157"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="165" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="166"/>
-      <c r="S3" s="166"/>
-      <c r="T3" s="167"/>
-      <c r="U3" s="168" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="169"/>
-      <c r="W3" s="169"/>
-      <c r="X3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="158"/>
-      <c r="B4" s="164"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -2841,7 +2848,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="33">
-        <f t="shared" ref="M8:M38" si="15">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M8:M15" si="15">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N8" s="43"/>
@@ -4515,35 +4522,35 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30" s="182">
+      <c r="A30" s="72">
         <v>46275</v>
       </c>
-      <c r="B30" s="183">
+      <c r="B30" s="41">
         <v>26</v>
       </c>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="140" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="184" t="s">
+      <c r="D30" s="140" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185">
+      <c r="E30" s="44"/>
+      <c r="F30" s="44">
         <v>20</v>
       </c>
-      <c r="G30" s="186">
+      <c r="G30" s="69">
         <v>40</v>
       </c>
-      <c r="H30" s="187">
+      <c r="H30" s="43">
         <v>40</v>
       </c>
-      <c r="I30" s="185">
+      <c r="I30" s="44">
         <v>20</v>
       </c>
-      <c r="J30" s="186">
+      <c r="J30" s="69">
         <v>40</v>
       </c>
-      <c r="K30" s="188">
+      <c r="K30" s="70">
         <v>40</v>
       </c>
       <c r="L30" s="42">
@@ -4596,29 +4603,29 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A31" s="182">
+      <c r="A31" s="72">
         <v>46275</v>
       </c>
-      <c r="B31" s="183">
+      <c r="B31" s="41">
         <v>27</v>
       </c>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="D31" s="140" t="s">
         <v>132</v>
       </c>
-      <c r="E31" s="185"/>
-      <c r="F31" s="185"/>
-      <c r="G31" s="186"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="185">
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="44">
         <v>80</v>
       </c>
-      <c r="J31" s="186">
+      <c r="J31" s="69">
         <v>40</v>
       </c>
-      <c r="K31" s="188">
+      <c r="K31" s="70">
         <v>80</v>
       </c>
       <c r="L31" s="42">
@@ -4671,35 +4678,35 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A32" s="182">
+      <c r="A32" s="72">
         <v>46275</v>
       </c>
-      <c r="B32" s="183">
+      <c r="B32" s="41">
         <v>28</v>
       </c>
-      <c r="C32" s="184" t="s">
+      <c r="C32" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="184" t="s">
+      <c r="D32" s="140" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185">
+      <c r="E32" s="44"/>
+      <c r="F32" s="44">
         <v>80</v>
       </c>
-      <c r="G32" s="186">
+      <c r="G32" s="69">
         <v>40</v>
       </c>
-      <c r="H32" s="187">
+      <c r="H32" s="43">
         <v>80</v>
       </c>
-      <c r="I32" s="185">
+      <c r="I32" s="44">
         <v>40</v>
       </c>
-      <c r="J32" s="186">
+      <c r="J32" s="69">
         <v>40</v>
       </c>
-      <c r="K32" s="188">
+      <c r="K32" s="70">
         <v>40</v>
       </c>
       <c r="L32" s="42">
@@ -4752,27 +4759,27 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A33" s="182">
+      <c r="A33" s="72">
         <v>46275</v>
       </c>
-      <c r="B33" s="183">
+      <c r="B33" s="41">
         <v>29</v>
       </c>
-      <c r="C33" s="184" t="s">
+      <c r="C33" s="140" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="184" t="s">
+      <c r="D33" s="140" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="185"/>
-      <c r="F33" s="185"/>
-      <c r="G33" s="186"/>
-      <c r="H33" s="187">
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="43">
         <v>80</v>
       </c>
-      <c r="I33" s="185"/>
-      <c r="J33" s="186"/>
-      <c r="K33" s="188">
+      <c r="I33" s="44"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="70">
         <v>200</v>
       </c>
       <c r="L33" s="42">
@@ -4825,35 +4832,35 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A34" s="143">
+      <c r="A34" s="72">
         <v>46276</v>
       </c>
       <c r="B34" s="41">
         <v>30</v>
       </c>
-      <c r="C34" s="144" t="s">
+      <c r="C34" s="140" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="144" t="s">
+      <c r="D34" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="E34" s="145"/>
-      <c r="F34" s="145">
+      <c r="E34" s="44"/>
+      <c r="F34" s="44">
         <v>80</v>
       </c>
-      <c r="G34" s="146">
+      <c r="G34" s="69">
         <v>80</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="43">
         <v>160</v>
       </c>
-      <c r="I34" s="145">
+      <c r="I34" s="44">
         <v>160</v>
       </c>
-      <c r="J34" s="146">
+      <c r="J34" s="69">
         <v>120</v>
       </c>
-      <c r="K34" s="147">
+      <c r="K34" s="70">
         <v>520</v>
       </c>
       <c r="L34" s="42">
@@ -4909,31 +4916,31 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A35" s="143">
+      <c r="A35" s="72">
         <v>46276</v>
       </c>
       <c r="B35" s="41">
         <v>31</v>
       </c>
-      <c r="C35" s="144" t="s">
+      <c r="C35" s="140" t="s">
         <v>135</v>
       </c>
-      <c r="D35" s="144" t="s">
+      <c r="D35" s="140" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="145"/>
-      <c r="F35" s="145">
+      <c r="E35" s="44"/>
+      <c r="F35" s="44">
         <v>40</v>
       </c>
-      <c r="G35" s="146"/>
-      <c r="H35" s="50">
+      <c r="G35" s="69"/>
+      <c r="H35" s="43">
         <v>160</v>
       </c>
-      <c r="I35" s="145"/>
-      <c r="J35" s="146">
+      <c r="I35" s="44"/>
+      <c r="J35" s="69">
         <v>160</v>
       </c>
-      <c r="K35" s="147">
+      <c r="K35" s="70">
         <v>80</v>
       </c>
       <c r="L35" s="42">
@@ -4989,33 +4996,33 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A36" s="143">
+      <c r="A36" s="72">
         <v>46276</v>
       </c>
       <c r="B36" s="41">
         <v>32</v>
       </c>
-      <c r="C36" s="144" t="s">
+      <c r="C36" s="140" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="144" t="s">
+      <c r="D36" s="140" t="s">
         <v>138</v>
       </c>
-      <c r="E36" s="145"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="146">
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="69">
         <v>160</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="43">
         <v>200</v>
       </c>
-      <c r="I36" s="145">
+      <c r="I36" s="44">
         <v>200</v>
       </c>
-      <c r="J36" s="146">
+      <c r="J36" s="69">
         <v>200</v>
       </c>
-      <c r="K36" s="147">
+      <c r="K36" s="70">
         <v>400</v>
       </c>
       <c r="L36" s="42">
@@ -5071,35 +5078,35 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A37" s="143">
+      <c r="A37" s="72">
         <v>46276</v>
       </c>
       <c r="B37" s="41">
         <v>33</v>
       </c>
-      <c r="C37" s="144" t="s">
+      <c r="C37" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="D37" s="144" t="s">
+      <c r="D37" s="140" t="s">
         <v>137</v>
       </c>
-      <c r="E37" s="145"/>
-      <c r="F37" s="145">
+      <c r="E37" s="44"/>
+      <c r="F37" s="44">
         <v>120</v>
       </c>
-      <c r="G37" s="146">
+      <c r="G37" s="69">
         <v>120</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="43">
         <v>200</v>
       </c>
-      <c r="I37" s="145">
+      <c r="I37" s="44">
         <v>120</v>
       </c>
-      <c r="J37" s="146">
+      <c r="J37" s="69">
         <v>80</v>
       </c>
-      <c r="K37" s="147">
+      <c r="K37" s="70">
         <v>200</v>
       </c>
       <c r="L37" s="42">
@@ -5155,26 +5162,35 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="72"/>
-      <c r="B38" s="41">
+      <c r="A38" s="143">
+        <v>46277</v>
+      </c>
+      <c r="B38" s="148">
         <v>34</v>
       </c>
-      <c r="C38" s="140"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="70"/>
+      <c r="C38" s="144" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="144" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="146"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="145">
+        <v>400</v>
+      </c>
+      <c r="J38" s="146">
+        <v>200</v>
+      </c>
+      <c r="K38" s="147"/>
       <c r="L38" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M38" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N38" s="43">
         <f t="shared" si="53"/>
@@ -5186,7 +5202,7 @@
       </c>
       <c r="P38" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q38" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5222,26 +5238,39 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="72"/>
-      <c r="B39" s="41">
+      <c r="A39" s="143">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="148">
         <v>35</v>
       </c>
-      <c r="C39" s="140"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="70"/>
+      <c r="C39" s="144" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="144" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="145"/>
+      <c r="F39" s="145">
+        <v>40</v>
+      </c>
+      <c r="G39" s="146"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="145">
+        <v>120</v>
+      </c>
+      <c r="J39" s="146">
+        <v>80</v>
+      </c>
+      <c r="K39" s="147">
+        <v>280</v>
+      </c>
       <c r="L39" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M39" s="33">
-        <f t="shared" ref="M39:M70" si="67">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N39" s="43">
         <f t="shared" si="53"/>
@@ -5249,11 +5278,11 @@
       </c>
       <c r="O39" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5289,26 +5318,43 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="72"/>
-      <c r="B40" s="41">
+      <c r="A40" s="143">
+        <v>46277</v>
+      </c>
+      <c r="B40" s="148">
         <v>36</v>
       </c>
-      <c r="C40" s="140"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="70"/>
+      <c r="C40" s="144" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="144" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="145"/>
+      <c r="F40" s="145">
+        <v>80</v>
+      </c>
+      <c r="G40" s="146">
+        <v>80</v>
+      </c>
+      <c r="H40" s="50">
+        <v>120</v>
+      </c>
+      <c r="I40" s="145">
+        <v>120</v>
+      </c>
+      <c r="J40" s="146">
+        <v>80</v>
+      </c>
+      <c r="K40" s="147">
+        <v>120</v>
+      </c>
       <c r="L40" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M40" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N40" s="43">
         <f t="shared" si="53"/>
@@ -5316,11 +5362,11 @@
       </c>
       <c r="O40" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P40" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q40" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5356,26 +5402,43 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="72"/>
-      <c r="B41" s="41">
+      <c r="A41" s="143">
+        <v>46277</v>
+      </c>
+      <c r="B41" s="148">
         <v>37</v>
       </c>
-      <c r="C41" s="140"/>
-      <c r="D41" s="140"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="70"/>
+      <c r="C41" s="144" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="144" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145">
+        <v>120</v>
+      </c>
+      <c r="G41" s="146">
+        <v>80</v>
+      </c>
+      <c r="H41" s="50">
+        <v>80</v>
+      </c>
+      <c r="I41" s="145">
+        <v>120</v>
+      </c>
+      <c r="J41" s="146">
+        <v>80</v>
+      </c>
+      <c r="K41" s="147">
+        <v>120</v>
+      </c>
       <c r="L41" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M41" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N41" s="43">
         <f t="shared" si="53"/>
@@ -5383,11 +5446,11 @@
       </c>
       <c r="O41" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P41" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q41" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5441,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" ref="M42:M70" si="67">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N42" s="43">
@@ -11253,10 +11316,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="171" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="172"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11264,31 +11327,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>2000</v>
+        <v>2240</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>2170</v>
+        <v>2330</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>3490</v>
+        <v>3690</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>3458</v>
+        <v>4218</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>4240</v>
+        <v>4680</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>6280</v>
+        <v>6800</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>597.57500000000005</v>
+        <v>655.57500000000005</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11300,11 +11363,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>698.9</v>
+        <v>784.9</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11510,10 +11573,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="159" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="160"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11597,10 +11660,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="148" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="149"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11608,35 +11671,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>2000</v>
+        <v>2240</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>2170</v>
+        <v>2330</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>3490</v>
+        <v>3690</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>3458</v>
+        <v>4218</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>4240</v>
+        <v>4680</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>6280</v>
+        <v>6800</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>597.57500000000005</v>
+        <v>655.57500000000005</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11644,11 +11707,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>886</v>
+        <v>946</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1517.8</v>
+        <v>1689.8</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11731,25 +11794,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="175" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="179" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="180"/>
-      <c r="K3" s="181" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="181"/>
-      <c r="M3" s="181"/>
-      <c r="N3" s="181"/>
-      <c r="O3" s="181"/>
-      <c r="P3" s="181"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11795,24 +11858,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>438</v>
+        <v>489</v>
       </c>
       <c r="E5" s="73">
-        <v>618</v>
+        <v>676</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1156</v>
+        <v>1265</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8844</v>
+        <v>-8735</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11821,11 +11884,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>5972</v>
+        <v>14570</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>149.30000000000001</v>
+        <v>364.25</v>
       </c>
       <c r="O5" s="75"/>
       <c r="P5" s="142"/>
@@ -11836,11 +11899,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>17520</v>
+        <v>19560</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>24720</v>
+        <v>27040</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11848,7 +11911,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>46240</v>
+        <v>50600</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11856,7 +11919,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-353760</v>
+        <v>-349400</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -11865,11 +11928,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>7579</v>
+        <v>10551</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>189.47499999999999</v>
+        <v>263.77499999999998</v>
       </c>
       <c r="O6" s="75"/>
       <c r="P6" s="142"/>
@@ -11900,11 +11963,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>4029</v>
+        <v>8643</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>100.72499999999999</v>
+        <v>216.07499999999999</v>
       </c>
       <c r="O7" s="75"/>
       <c r="P7" s="142"/>
@@ -11944,11 +12007,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>5849</v>
+        <v>10038</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>146.22499999999999</v>
+        <v>250.95</v>
       </c>
       <c r="O8" s="75">
         <v>50</v>
@@ -11984,11 +12047,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-438</v>
+        <v>-489</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-618</v>
+        <v>-676</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -11997,11 +12060,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>6849</v>
+        <v>9254</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>171.22499999999999</v>
+        <v>231.35</v>
       </c>
       <c r="O9" s="75">
         <v>23</v>
@@ -12041,11 +12104,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>4278</v>
+        <v>15938</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>106.95</v>
+        <v>398.45</v>
       </c>
       <c r="O10" s="75"/>
       <c r="P10" s="142"/>
@@ -12072,14 +12135,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="178"/>
-      <c r="F11" s="178" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="178"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12087,11 +12150,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>3243</v>
+        <v>1839</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>81.075000000000003</v>
+        <v>45.975000000000001</v>
       </c>
       <c r="O11" s="75">
         <v>125</v>
@@ -12131,7 +12194,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>5356</v>
+        <v>5465</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12139,11 +12202,11 @@
       <c r="L12" s="75"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>37799</v>
+        <v>70833</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>944.97500000000014</v>
+        <v>1770.8249999999998</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -12183,12 +12246,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>214240</v>
-      </c>
-      <c r="S13" s="173" t="s">
+        <v>218600</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="173"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12242,7 +12305,7 @@
       <c r="N17" s="115"/>
       <c r="O17" s="116">
         <f>N17-M5</f>
-        <v>-5972</v>
+        <v>-14570</v>
       </c>
     </row>
     <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12256,7 +12319,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="116">
         <f>N18-M6</f>
-        <v>-7579</v>
+        <v>-10551</v>
       </c>
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12273,17 +12336,17 @@
       <c r="N19" s="5"/>
       <c r="O19" s="116">
         <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>-4029</v>
+        <v>-8643</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="174" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="174"/>
-      <c r="F20" s="174"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="174"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -12294,7 +12357,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="116">
         <f t="shared" si="4"/>
-        <v>-5849</v>
+        <v>-10038</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12323,7 +12386,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="116">
         <f t="shared" si="4"/>
-        <v>-6849</v>
+        <v>-9254</v>
       </c>
     </row>
     <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12349,7 +12412,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="116">
         <f t="shared" si="4"/>
-        <v>-4278</v>
+        <v>-15938</v>
       </c>
     </row>
     <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12375,7 +12438,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="116">
         <f t="shared" si="4"/>
-        <v>-3243</v>
+        <v>-1839</v>
       </c>
     </row>
     <row r="24" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12405,7 +12468,7 @@
       </c>
       <c r="O24" s="111">
         <f>SUM(O17:O23)</f>
-        <v>-37799</v>
+        <v>-70833</v>
       </c>
     </row>
     <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12435,7 +12498,7 @@
       </c>
       <c r="O25" s="111">
         <f>O24/40</f>
-        <v>-944.97500000000002</v>
+        <v>-1770.825</v>
       </c>
     </row>
     <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06D90D0-4663-4AE9-9B9F-57321C6E5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA64E776-6BDA-463C-A2E4-A382B8EDCB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="153">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -457,6 +457,30 @@
   </si>
   <si>
     <t xml:space="preserve">Gari Shahu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manavan </t>
+  </si>
+  <si>
+    <t>Jala Sons</t>
+  </si>
+  <si>
+    <t>Phase 5</t>
+  </si>
+  <si>
+    <t>Shadipura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kot Khwaja </t>
+  </si>
+  <si>
+    <t>Baghbanpura</t>
+  </si>
+  <si>
+    <t>Zaraar Shaheed Road</t>
+  </si>
+  <si>
+    <t>Gourmet Food</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1729,9 +1753,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2365,19 +2386,19 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="161">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
-      </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+        <v>46281</v>
+      </c>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2399,10 +2420,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="162" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2432,13 +2453,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="150"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="153" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2457,8 +2478,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="163"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2486,29 +2507,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="157"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="167"/>
+      <c r="U3" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="169"/>
+      <c r="W3" s="169"/>
+      <c r="X3" s="170"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="164"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -5162,29 +5183,29 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="143">
+      <c r="A38" s="72">
         <v>46277</v>
       </c>
-      <c r="B38" s="148">
+      <c r="B38" s="41">
         <v>34</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="140" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="144" t="s">
+      <c r="D38" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="E38" s="145"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="145">
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="44">
         <v>400</v>
       </c>
-      <c r="J38" s="146">
+      <c r="J38" s="69">
         <v>200</v>
       </c>
-      <c r="K38" s="147"/>
+      <c r="K38" s="70"/>
       <c r="L38" s="42">
         <f t="shared" si="66"/>
         <v>15</v>
@@ -5238,31 +5259,31 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="143">
+      <c r="A39" s="72">
         <v>46277</v>
       </c>
-      <c r="B39" s="148">
+      <c r="B39" s="41">
         <v>35</v>
       </c>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="140" t="s">
         <v>120</v>
       </c>
-      <c r="D39" s="144" t="s">
+      <c r="D39" s="140" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="145"/>
-      <c r="F39" s="145">
+      <c r="E39" s="44"/>
+      <c r="F39" s="44">
         <v>40</v>
       </c>
-      <c r="G39" s="146"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="145">
+      <c r="G39" s="69"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="44">
         <v>120</v>
       </c>
-      <c r="J39" s="146">
+      <c r="J39" s="69">
         <v>80</v>
       </c>
-      <c r="K39" s="147">
+      <c r="K39" s="70">
         <v>280</v>
       </c>
       <c r="L39" s="42">
@@ -5318,35 +5339,35 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="143">
+      <c r="A40" s="72">
         <v>46277</v>
       </c>
-      <c r="B40" s="148">
+      <c r="B40" s="41">
         <v>36</v>
       </c>
-      <c r="C40" s="144" t="s">
+      <c r="C40" s="140" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="144" t="s">
+      <c r="D40" s="140" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="145"/>
-      <c r="F40" s="145">
+      <c r="E40" s="44"/>
+      <c r="F40" s="44">
         <v>80</v>
       </c>
-      <c r="G40" s="146">
+      <c r="G40" s="69">
         <v>80</v>
       </c>
-      <c r="H40" s="50">
+      <c r="H40" s="43">
         <v>120</v>
       </c>
-      <c r="I40" s="145">
+      <c r="I40" s="44">
         <v>120</v>
       </c>
-      <c r="J40" s="146">
+      <c r="J40" s="69">
         <v>80</v>
       </c>
-      <c r="K40" s="147">
+      <c r="K40" s="70">
         <v>120</v>
       </c>
       <c r="L40" s="42">
@@ -5402,35 +5423,35 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="143">
+      <c r="A41" s="72">
         <v>46277</v>
       </c>
-      <c r="B41" s="148">
+      <c r="B41" s="41">
         <v>37</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="140" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="144" t="s">
+      <c r="D41" s="140" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="145"/>
-      <c r="F41" s="145">
+      <c r="E41" s="44"/>
+      <c r="F41" s="44">
         <v>120</v>
       </c>
-      <c r="G41" s="146">
+      <c r="G41" s="69">
         <v>80</v>
       </c>
-      <c r="H41" s="50">
+      <c r="H41" s="43">
         <v>80</v>
       </c>
-      <c r="I41" s="145">
+      <c r="I41" s="44">
         <v>120</v>
       </c>
-      <c r="J41" s="146">
+      <c r="J41" s="69">
         <v>80</v>
       </c>
-      <c r="K41" s="147">
+      <c r="K41" s="70">
         <v>120</v>
       </c>
       <c r="L41" s="42">
@@ -5486,26 +5507,41 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="72"/>
+      <c r="A42" s="143">
+        <v>46280</v>
+      </c>
       <c r="B42" s="41">
         <v>38</v>
       </c>
-      <c r="C42" s="140"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="70"/>
+      <c r="C42" s="144" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="144" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="145"/>
+      <c r="F42" s="145">
+        <v>120</v>
+      </c>
+      <c r="G42" s="146">
+        <v>40</v>
+      </c>
+      <c r="H42" s="50">
+        <v>80</v>
+      </c>
+      <c r="I42" s="145">
+        <v>120</v>
+      </c>
+      <c r="J42" s="146">
+        <v>120</v>
+      </c>
+      <c r="K42" s="147"/>
       <c r="L42" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M42" s="33">
-        <f t="shared" ref="M42:M70" si="67">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N42" s="43">
         <f t="shared" si="53"/>
@@ -5513,11 +5549,11 @@
       </c>
       <c r="O42" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P42" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q42" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5553,26 +5589,43 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A43" s="72"/>
+      <c r="A43" s="143">
+        <v>46280</v>
+      </c>
       <c r="B43" s="41">
         <v>39</v>
       </c>
-      <c r="C43" s="140"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="69"/>
-      <c r="K43" s="70"/>
+      <c r="C43" s="144" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="144" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="145"/>
+      <c r="F43" s="145">
+        <v>40</v>
+      </c>
+      <c r="G43" s="146">
+        <v>40</v>
+      </c>
+      <c r="H43" s="50">
+        <v>40</v>
+      </c>
+      <c r="I43" s="145">
+        <v>40</v>
+      </c>
+      <c r="J43" s="146">
+        <v>40</v>
+      </c>
+      <c r="K43" s="147">
+        <v>40</v>
+      </c>
       <c r="L43" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M43" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N43" s="43">
         <f t="shared" si="53"/>
@@ -5580,11 +5633,11 @@
       </c>
       <c r="O43" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P43" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q43" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5620,26 +5673,41 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="72"/>
+      <c r="A44" s="143">
+        <v>46280</v>
+      </c>
       <c r="B44" s="41">
         <v>40</v>
       </c>
-      <c r="C44" s="140"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="69"/>
-      <c r="K44" s="70"/>
+      <c r="C44" s="144" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="144" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145">
+        <v>118</v>
+      </c>
+      <c r="G44" s="146">
+        <v>40</v>
+      </c>
+      <c r="H44" s="50">
+        <v>80</v>
+      </c>
+      <c r="I44" s="145">
+        <v>117</v>
+      </c>
+      <c r="J44" s="146">
+        <v>117</v>
+      </c>
+      <c r="K44" s="147"/>
       <c r="L44" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="M44" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N44" s="43">
         <f t="shared" si="53"/>
@@ -5647,11 +5715,11 @@
       </c>
       <c r="O44" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="P44" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="Q44" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5687,26 +5755,41 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="72"/>
+      <c r="A45" s="143">
+        <v>46280</v>
+      </c>
       <c r="B45" s="41">
         <v>41</v>
       </c>
-      <c r="C45" s="140"/>
-      <c r="D45" s="140"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="70"/>
+      <c r="C45" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="144" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="145"/>
+      <c r="F45" s="145">
+        <v>80</v>
+      </c>
+      <c r="G45" s="146">
+        <v>80</v>
+      </c>
+      <c r="H45" s="50">
+        <v>80</v>
+      </c>
+      <c r="I45" s="145"/>
+      <c r="J45" s="146">
+        <v>40</v>
+      </c>
+      <c r="K45" s="147">
+        <v>40</v>
+      </c>
       <c r="L45" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N45" s="43">
         <f t="shared" si="53"/>
@@ -5714,11 +5797,11 @@
       </c>
       <c r="O45" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P45" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q45" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5754,26 +5837,37 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="72"/>
+      <c r="A46" s="143">
+        <v>46280</v>
+      </c>
       <c r="B46" s="41">
         <v>42</v>
       </c>
-      <c r="C46" s="140"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="70"/>
+      <c r="C46" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="144" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="145"/>
+      <c r="F46" s="145"/>
+      <c r="G46" s="146"/>
+      <c r="H46" s="50">
+        <v>40</v>
+      </c>
+      <c r="I46" s="145"/>
+      <c r="J46" s="146">
+        <v>40</v>
+      </c>
+      <c r="K46" s="147">
+        <v>40</v>
+      </c>
       <c r="L46" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N46" s="43">
         <f t="shared" si="53"/>
@@ -5781,11 +5875,11 @@
       </c>
       <c r="O46" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P46" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q46" s="45" t="e">
         <f t="shared" si="1"/>
@@ -5821,26 +5915,41 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="72"/>
+      <c r="A47" s="143">
+        <v>46280</v>
+      </c>
       <c r="B47" s="41">
         <v>43</v>
       </c>
-      <c r="C47" s="140"/>
-      <c r="D47" s="140"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="70"/>
+      <c r="C47" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="144" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" s="145"/>
+      <c r="F47" s="145">
+        <v>40</v>
+      </c>
+      <c r="G47" s="146">
+        <v>40</v>
+      </c>
+      <c r="H47" s="50">
+        <v>40</v>
+      </c>
+      <c r="I47" s="145"/>
+      <c r="J47" s="146">
+        <v>40</v>
+      </c>
+      <c r="K47" s="147">
+        <v>40</v>
+      </c>
       <c r="L47" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M47" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N47" s="43">
         <f t="shared" si="53"/>
@@ -5848,11 +5957,11 @@
       </c>
       <c r="O47" s="67">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P47" s="34">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="45"/>
       <c r="R47" s="46"/>
@@ -5870,37 +5979,48 @@
       <c r="X47" s="50"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="72"/>
+      <c r="A48" s="143">
+        <v>46280</v>
+      </c>
       <c r="B48" s="41">
         <v>44</v>
       </c>
-      <c r="C48" s="140"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="70"/>
+      <c r="C48" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="144" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" s="145"/>
+      <c r="F48" s="145">
+        <v>40</v>
+      </c>
+      <c r="G48" s="146">
+        <v>40</v>
+      </c>
+      <c r="H48" s="50">
+        <v>40</v>
+      </c>
+      <c r="I48" s="145"/>
+      <c r="J48" s="146"/>
+      <c r="K48" s="147"/>
       <c r="L48" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N48" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O48" s="67">
-        <f t="shared" ref="O48:O60" si="68">SUM(F48:H48)/20</f>
-        <v>0</v>
+        <f t="shared" ref="O48:O60" si="67">SUM(F48:H48)/20</f>
+        <v>6</v>
       </c>
       <c r="P48" s="34">
-        <f t="shared" ref="P48:P60" si="69">SUM(I48:K48)/20</f>
+        <f t="shared" ref="P48:P60" si="68">SUM(I48:K48)/20</f>
         <v>0</v>
       </c>
       <c r="Q48" s="45"/>
@@ -5909,48 +6029,65 @@
       <c r="T48" s="47"/>
       <c r="U48" s="48"/>
       <c r="V48" s="49">
-        <f t="shared" ref="V48:V60" si="70">SUM(F48:H48)*$V$3</f>
+        <f t="shared" ref="V48:V60" si="69">SUM(F48:H48)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W48" s="49">
-        <f t="shared" ref="W48:W60" si="71">SUM(I48:K48)*$W$3</f>
+        <f t="shared" ref="W48:W60" si="70">SUM(I48:K48)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X48" s="50"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="72"/>
+      <c r="A49" s="143">
+        <v>46280</v>
+      </c>
       <c r="B49" s="41">
         <v>45</v>
       </c>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="70"/>
+      <c r="C49" s="144" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="144" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145">
+        <v>40</v>
+      </c>
+      <c r="G49" s="146">
+        <v>40</v>
+      </c>
+      <c r="H49" s="50">
+        <v>40</v>
+      </c>
+      <c r="I49" s="145">
+        <v>20</v>
+      </c>
+      <c r="J49" s="146">
+        <v>20</v>
+      </c>
+      <c r="K49" s="147">
+        <v>20</v>
+      </c>
       <c r="L49" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M49" s="33">
-        <f t="shared" si="67"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N49" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O49" s="67">
+        <f t="shared" si="67"/>
+        <v>6</v>
+      </c>
+      <c r="P49" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="34">
-        <f t="shared" si="69"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="45"/>
       <c r="R49" s="46"/>
@@ -5958,11 +6095,11 @@
       <c r="T49" s="47"/>
       <c r="U49" s="48"/>
       <c r="V49" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W49" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W49" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X49" s="50"/>
@@ -5986,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" ref="M50:M70" si="71">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N50" s="43">
@@ -5994,11 +6131,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O50" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q50" s="45"/>
@@ -6007,11 +6144,11 @@
       <c r="T50" s="47"/>
       <c r="U50" s="48"/>
       <c r="V50" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W50" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X50" s="50"/>
@@ -6035,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N51" s="43">
@@ -6043,11 +6180,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O51" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q51" s="45"/>
@@ -6056,11 +6193,11 @@
       <c r="T51" s="47"/>
       <c r="U51" s="48"/>
       <c r="V51" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X51" s="50"/>
@@ -6084,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N52" s="43">
@@ -6092,11 +6229,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O52" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P52" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q52" s="45"/>
@@ -6105,11 +6242,11 @@
       <c r="T52" s="47"/>
       <c r="U52" s="48"/>
       <c r="V52" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W52" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X52" s="50"/>
@@ -6133,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N53" s="43">
@@ -6141,11 +6278,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O53" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P53" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q53" s="45"/>
@@ -6154,11 +6291,11 @@
       <c r="T53" s="47"/>
       <c r="U53" s="48"/>
       <c r="V53" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W53" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W53" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X53" s="50"/>
@@ -6182,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N54" s="43">
@@ -6190,11 +6327,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O54" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P54" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q54" s="45"/>
@@ -6203,11 +6340,11 @@
       <c r="T54" s="47"/>
       <c r="U54" s="48"/>
       <c r="V54" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X54" s="50"/>
@@ -6231,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N55" s="43">
@@ -6239,11 +6376,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O55" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P55" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q55" s="45"/>
@@ -6252,11 +6389,11 @@
       <c r="T55" s="47"/>
       <c r="U55" s="48"/>
       <c r="V55" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W55" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X55" s="50"/>
@@ -6280,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N56" s="43">
@@ -6288,11 +6425,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O56" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q56" s="45"/>
@@ -6301,11 +6438,11 @@
       <c r="T56" s="47"/>
       <c r="U56" s="48"/>
       <c r="V56" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W56" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W56" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X56" s="50"/>
@@ -6329,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N57" s="43">
@@ -6337,11 +6474,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O57" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q57" s="45"/>
@@ -6350,11 +6487,11 @@
       <c r="T57" s="47"/>
       <c r="U57" s="48"/>
       <c r="V57" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W57" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W57" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X57" s="50"/>
@@ -6378,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N58" s="43">
@@ -6386,11 +6523,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O58" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q58" s="45"/>
@@ -6399,11 +6536,11 @@
       <c r="T58" s="47"/>
       <c r="U58" s="48"/>
       <c r="V58" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W58" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W58" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X58" s="50"/>
@@ -6427,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N59" s="43">
@@ -6435,11 +6572,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O59" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P59" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P59" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q59" s="45"/>
@@ -6448,11 +6585,11 @@
       <c r="T59" s="47"/>
       <c r="U59" s="48"/>
       <c r="V59" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W59" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W59" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X59" s="50"/>
@@ -6476,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N60" s="43">
@@ -6484,11 +6621,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O60" s="67">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P60" s="34">
-        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="Q60" s="45"/>
@@ -6497,11 +6634,11 @@
       <c r="T60" s="47"/>
       <c r="U60" s="48"/>
       <c r="V60" s="49">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="W60" s="49">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="W60" s="49">
-        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="X60" s="50"/>
@@ -6525,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N61" s="43">
@@ -6592,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N62" s="43">
@@ -6659,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N63" s="43">
@@ -6726,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N64" s="43">
@@ -6793,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N65" s="43">
@@ -6860,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N66" s="43">
@@ -6927,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N67" s="43">
@@ -6994,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N68" s="43">
@@ -7061,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N69" s="43">
@@ -7128,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="33">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="N70" s="43">
@@ -11316,10 +11453,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="172"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11327,31 +11464,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>2240</v>
+        <v>2718</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>2330</v>
+        <v>2650</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>3690</v>
+        <v>4130</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>4218</v>
+        <v>4515</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>4680</v>
+        <v>5097</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>6800</v>
+        <v>6980</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>655.57500000000005</v>
+        <v>708.875</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11363,11 +11500,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>413</v>
+        <v>474.9</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>784.9</v>
+        <v>829.6</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11573,10 +11710,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="159" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="160"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11660,10 +11797,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="149"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11671,35 +11808,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>2240</v>
+        <v>2718</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>2330</v>
+        <v>2650</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>3690</v>
+        <v>4130</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>4218</v>
+        <v>4515</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>4680</v>
+        <v>5097</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>6800</v>
+        <v>6980</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>655.57500000000005</v>
+        <v>708.875</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>455</v>
+        <v>588</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11707,11 +11844,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>946</v>
+        <v>1069.8</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1689.8</v>
+        <v>1779.2</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11794,25 +11931,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="177"/>
+      <c r="H3" s="179" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="180"/>
+      <c r="K3" s="181" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="181"/>
+      <c r="M3" s="181"/>
+      <c r="N3" s="181"/>
+      <c r="O3" s="181"/>
+      <c r="P3" s="181"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -11858,24 +11995,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>489</v>
+        <v>605</v>
       </c>
       <c r="E5" s="73">
-        <v>676</v>
+        <v>729</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1265</v>
+        <v>1434</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8735</v>
+        <v>-8566</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -11899,11 +12036,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>19560</v>
+        <v>24200</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>27040</v>
+        <v>29160</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -11911,7 +12048,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>50600</v>
+        <v>57360</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -11919,7 +12056,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-349400</v>
+        <v>-342640</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -12047,11 +12184,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-489</v>
+        <v>-605</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-676</v>
+        <v>-729</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -12135,14 +12272,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="178" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="178"/>
+      <c r="F11" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="178"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12194,7 +12331,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>5465</v>
+        <v>5634</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12246,12 +12383,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>218600</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>225360</v>
+      </c>
+      <c r="S13" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="173"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12340,13 +12477,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="174"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA64E776-6BDA-463C-A2E4-A382B8EDCB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8106A612-B1BA-4A3C-884C-9610506FB1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -481,6 +481,12 @@
   </si>
   <si>
     <t>Gourmet Food</t>
+  </si>
+  <si>
+    <t>Mart Zone</t>
+  </si>
+  <si>
+    <t>Opf Housing Society</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1749,10 +1755,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1792,42 +1830,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1855,6 +1857,17 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2387,18 +2400,18 @@
   <cols>
     <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="161">
+      <c r="B1" s="144">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
-      </c>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
+        <v>46282</v>
+      </c>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2420,10 +2433,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="145" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2453,13 +2466,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="153" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="154"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2478,8 +2491,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="158"/>
-      <c r="B3" s="163"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="146"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2507,29 +2520,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="155" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="156"/>
-      <c r="N3" s="157"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="165" t="s">
+      <c r="Q3" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="166"/>
-      <c r="S3" s="166"/>
-      <c r="T3" s="167"/>
-      <c r="U3" s="168" t="s">
+      <c r="R3" s="149"/>
+      <c r="S3" s="149"/>
+      <c r="T3" s="150"/>
+      <c r="U3" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="169"/>
-      <c r="W3" s="169"/>
-      <c r="X3" s="170"/>
+      <c r="V3" s="152"/>
+      <c r="W3" s="152"/>
+      <c r="X3" s="153"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="158"/>
-      <c r="B4" s="164"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="147"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -5507,35 +5520,35 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="143">
+      <c r="A42" s="178">
         <v>46280</v>
       </c>
-      <c r="B42" s="41">
+      <c r="B42" s="179">
         <v>38</v>
       </c>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="144" t="s">
+      <c r="D42" s="180" t="s">
         <v>145</v>
       </c>
-      <c r="E42" s="145"/>
-      <c r="F42" s="145">
+      <c r="E42" s="181"/>
+      <c r="F42" s="181">
         <v>120</v>
       </c>
-      <c r="G42" s="146">
+      <c r="G42" s="182">
         <v>40</v>
       </c>
-      <c r="H42" s="50">
+      <c r="H42" s="183">
         <v>80</v>
       </c>
-      <c r="I42" s="145">
+      <c r="I42" s="181">
         <v>120</v>
       </c>
-      <c r="J42" s="146">
+      <c r="J42" s="182">
         <v>120</v>
       </c>
-      <c r="K42" s="147"/>
+      <c r="K42" s="184"/>
       <c r="L42" s="42">
         <f t="shared" si="66"/>
         <v>12</v>
@@ -5589,35 +5602,35 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A43" s="143">
+      <c r="A43" s="178">
         <v>46280</v>
       </c>
-      <c r="B43" s="41">
+      <c r="B43" s="179">
         <v>39</v>
       </c>
-      <c r="C43" s="144" t="s">
+      <c r="C43" s="180" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="144" t="s">
+      <c r="D43" s="180" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="145"/>
-      <c r="F43" s="145">
+      <c r="E43" s="181"/>
+      <c r="F43" s="181">
         <v>40</v>
       </c>
-      <c r="G43" s="146">
+      <c r="G43" s="182">
         <v>40</v>
       </c>
-      <c r="H43" s="50">
+      <c r="H43" s="183">
         <v>40</v>
       </c>
-      <c r="I43" s="145">
+      <c r="I43" s="181">
         <v>40</v>
       </c>
-      <c r="J43" s="146">
+      <c r="J43" s="182">
         <v>40</v>
       </c>
-      <c r="K43" s="147">
+      <c r="K43" s="184">
         <v>40</v>
       </c>
       <c r="L43" s="42">
@@ -5673,35 +5686,35 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="143">
+      <c r="A44" s="178">
         <v>46280</v>
       </c>
-      <c r="B44" s="41">
+      <c r="B44" s="179">
         <v>40</v>
       </c>
-      <c r="C44" s="144" t="s">
+      <c r="C44" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="144" t="s">
+      <c r="D44" s="180" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="145"/>
-      <c r="F44" s="145">
+      <c r="E44" s="181"/>
+      <c r="F44" s="181">
         <v>118</v>
       </c>
-      <c r="G44" s="146">
+      <c r="G44" s="182">
         <v>40</v>
       </c>
-      <c r="H44" s="50">
+      <c r="H44" s="183">
         <v>80</v>
       </c>
-      <c r="I44" s="145">
+      <c r="I44" s="181">
         <v>117</v>
       </c>
-      <c r="J44" s="146">
+      <c r="J44" s="182">
         <v>117</v>
       </c>
-      <c r="K44" s="147"/>
+      <c r="K44" s="184"/>
       <c r="L44" s="42">
         <f t="shared" si="66"/>
         <v>11.8</v>
@@ -5755,33 +5768,33 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="143">
+      <c r="A45" s="178">
         <v>46280</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="179">
         <v>41</v>
       </c>
-      <c r="C45" s="144" t="s">
+      <c r="C45" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="144" t="s">
+      <c r="D45" s="180" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="145"/>
-      <c r="F45" s="145">
+      <c r="E45" s="181"/>
+      <c r="F45" s="181">
         <v>80</v>
       </c>
-      <c r="G45" s="146">
+      <c r="G45" s="182">
         <v>80</v>
       </c>
-      <c r="H45" s="50">
+      <c r="H45" s="183">
         <v>80</v>
       </c>
-      <c r="I45" s="145"/>
-      <c r="J45" s="146">
+      <c r="I45" s="181"/>
+      <c r="J45" s="182">
         <v>40</v>
       </c>
-      <c r="K45" s="147">
+      <c r="K45" s="184">
         <v>40</v>
       </c>
       <c r="L45" s="42">
@@ -5837,29 +5850,29 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="143">
+      <c r="A46" s="178">
         <v>46280</v>
       </c>
-      <c r="B46" s="41">
+      <c r="B46" s="179">
         <v>42</v>
       </c>
-      <c r="C46" s="144" t="s">
+      <c r="C46" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="144" t="s">
+      <c r="D46" s="180" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="145"/>
-      <c r="F46" s="145"/>
-      <c r="G46" s="146"/>
-      <c r="H46" s="50">
+      <c r="E46" s="181"/>
+      <c r="F46" s="181"/>
+      <c r="G46" s="182"/>
+      <c r="H46" s="183">
         <v>40</v>
       </c>
-      <c r="I46" s="145"/>
-      <c r="J46" s="146">
+      <c r="I46" s="181"/>
+      <c r="J46" s="182">
         <v>40</v>
       </c>
-      <c r="K46" s="147">
+      <c r="K46" s="184">
         <v>40</v>
       </c>
       <c r="L46" s="42">
@@ -5915,33 +5928,33 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="143">
+      <c r="A47" s="178">
         <v>46280</v>
       </c>
-      <c r="B47" s="41">
+      <c r="B47" s="179">
         <v>43</v>
       </c>
-      <c r="C47" s="144" t="s">
+      <c r="C47" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="144" t="s">
+      <c r="D47" s="180" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="145"/>
-      <c r="F47" s="145">
+      <c r="E47" s="181"/>
+      <c r="F47" s="181">
         <v>40</v>
       </c>
-      <c r="G47" s="146">
+      <c r="G47" s="182">
         <v>40</v>
       </c>
-      <c r="H47" s="50">
+      <c r="H47" s="183">
         <v>40</v>
       </c>
-      <c r="I47" s="145"/>
-      <c r="J47" s="146">
+      <c r="I47" s="181"/>
+      <c r="J47" s="182">
         <v>40</v>
       </c>
-      <c r="K47" s="147">
+      <c r="K47" s="184">
         <v>40</v>
       </c>
       <c r="L47" s="42">
@@ -5979,31 +5992,31 @@
       <c r="X47" s="50"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="143">
+      <c r="A48" s="178">
         <v>46280</v>
       </c>
-      <c r="B48" s="41">
+      <c r="B48" s="179">
         <v>44</v>
       </c>
-      <c r="C48" s="144" t="s">
+      <c r="C48" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="144" t="s">
+      <c r="D48" s="180" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="145"/>
-      <c r="F48" s="145">
+      <c r="E48" s="181"/>
+      <c r="F48" s="181">
         <v>40</v>
       </c>
-      <c r="G48" s="146">
+      <c r="G48" s="182">
         <v>40</v>
       </c>
-      <c r="H48" s="50">
+      <c r="H48" s="183">
         <v>40</v>
       </c>
-      <c r="I48" s="145"/>
-      <c r="J48" s="146"/>
-      <c r="K48" s="147"/>
+      <c r="I48" s="181"/>
+      <c r="J48" s="182"/>
+      <c r="K48" s="184"/>
       <c r="L48" s="42">
         <f t="shared" si="66"/>
         <v>3</v>
@@ -6039,35 +6052,35 @@
       <c r="X48" s="50"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="143">
+      <c r="A49" s="178">
         <v>46280</v>
       </c>
-      <c r="B49" s="41">
+      <c r="B49" s="179">
         <v>45</v>
       </c>
-      <c r="C49" s="144" t="s">
+      <c r="C49" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="144" t="s">
+      <c r="D49" s="180" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="145"/>
-      <c r="F49" s="145">
+      <c r="E49" s="181"/>
+      <c r="F49" s="181">
         <v>40</v>
       </c>
-      <c r="G49" s="146">
+      <c r="G49" s="182">
         <v>40</v>
       </c>
-      <c r="H49" s="50">
+      <c r="H49" s="183">
         <v>40</v>
       </c>
-      <c r="I49" s="145">
+      <c r="I49" s="181">
         <v>20</v>
       </c>
-      <c r="J49" s="146">
+      <c r="J49" s="182">
         <v>20</v>
       </c>
-      <c r="K49" s="147">
+      <c r="K49" s="184">
         <v>20</v>
       </c>
       <c r="L49" s="42">
@@ -6105,26 +6118,43 @@
       <c r="X49" s="50"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="72"/>
+      <c r="A50" s="143">
+        <v>46281</v>
+      </c>
       <c r="B50" s="41">
         <v>46</v>
       </c>
-      <c r="C50" s="140"/>
-      <c r="D50" s="140"/>
+      <c r="C50" s="140" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="140" t="s">
+        <v>154</v>
+      </c>
       <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="44"/>
-      <c r="J50" s="69"/>
-      <c r="K50" s="70"/>
+      <c r="F50" s="44">
+        <v>40</v>
+      </c>
+      <c r="G50" s="69">
+        <v>40</v>
+      </c>
+      <c r="H50" s="43">
+        <v>40</v>
+      </c>
+      <c r="I50" s="44">
+        <v>40</v>
+      </c>
+      <c r="J50" s="69">
+        <v>40</v>
+      </c>
+      <c r="K50" s="70">
+        <v>40</v>
+      </c>
       <c r="L50" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M50" s="33">
-        <f t="shared" ref="M50:M70" si="71">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N50" s="43">
         <f t="shared" si="53"/>
@@ -6132,11 +6162,11 @@
       </c>
       <c r="O50" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P50" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="45"/>
       <c r="R50" s="46"/>
@@ -6172,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="33">
-        <f t="shared" si="71"/>
+        <f t="shared" ref="M50:M70" si="71">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N51" s="43">
@@ -11453,10 +11483,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="171" t="s">
+      <c r="B133" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="172"/>
+      <c r="C133" s="155"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11464,31 +11494,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>2718</v>
+        <v>2758</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>4130</v>
+        <v>4170</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>4515</v>
+        <v>4555</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>5097</v>
+        <v>5137</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>6980</v>
+        <v>7020</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>708.875</v>
+        <v>714.875</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11500,11 +11530,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>474.9</v>
+        <v>480.9</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>829.6</v>
+        <v>835.6</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11710,10 +11740,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="159" t="s">
+      <c r="B137" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="160"/>
+      <c r="C137" s="168"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11797,10 +11827,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="148" t="s">
+      <c r="B138" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="149"/>
+      <c r="C138" s="157"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11808,35 +11838,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>2718</v>
+        <v>2758</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>4130</v>
+        <v>4170</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>4515</v>
+        <v>4555</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>5097</v>
+        <v>5137</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>6980</v>
+        <v>7020</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>708.875</v>
+        <v>714.875</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11844,11 +11874,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>1069.8</v>
+        <v>1081.8</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1779.2</v>
+        <v>1791.2</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11885,17 +11915,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11931,25 +11961,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="175" t="s">
+      <c r="C3" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="179" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="180"/>
-      <c r="K3" s="181" t="s">
+      <c r="I3" s="176"/>
+      <c r="K3" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="181"/>
-      <c r="M3" s="181"/>
-      <c r="N3" s="181"/>
-      <c r="O3" s="181"/>
-      <c r="P3" s="181"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -12272,14 +12302,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="178"/>
-      <c r="F11" s="178" t="s">
+      <c r="D11" s="174"/>
+      <c r="F11" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="178"/>
+      <c r="G11" s="174"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12385,10 +12415,10 @@
         <f>G12*40</f>
         <v>225360</v>
       </c>
-      <c r="S13" s="173" t="s">
+      <c r="S13" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="173"/>
+      <c r="T13" s="169"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12477,13 +12507,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="174" t="s">
+      <c r="D20" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="174"/>
-      <c r="F20" s="174"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="174"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8106A612-B1BA-4A3C-884C-9610506FB1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71356E1F-2D64-4402-B6B0-76EBB25522BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="183">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -487,6 +487,90 @@
   </si>
   <si>
     <t>Opf Housing Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decent Departmental </t>
+  </si>
+  <si>
+    <t>Wahdat Road</t>
+  </si>
+  <si>
+    <t>Gourmet Food Younaabad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Wahdat Road </t>
+  </si>
+  <si>
+    <t>Gourmet Food Riwind Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Muslim Town Ayoubia </t>
+  </si>
+  <si>
+    <t>Gourmet Food Barkat Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Kahna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Joahr Town B Block </t>
+  </si>
+  <si>
+    <t>Gourmet Food Faisal Town</t>
+  </si>
+  <si>
+    <t>Gourmet Food EME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food DHA Z Block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Central Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Bankers Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Air Line </t>
+  </si>
+  <si>
+    <t>Gourmet Food 12-G</t>
+  </si>
+  <si>
+    <t>younabad</t>
+  </si>
+  <si>
+    <t>kahnahna</t>
+  </si>
+  <si>
+    <t>Riwind Road</t>
+  </si>
+  <si>
+    <t>Barkat Market</t>
+  </si>
+  <si>
+    <t>Faisal Town</t>
+  </si>
+  <si>
+    <t>Central Park</t>
+  </si>
+  <si>
+    <t>Bankers Society</t>
+  </si>
+  <si>
+    <t>Air Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johar Town </t>
+  </si>
+  <si>
+    <t>Z Block</t>
+  </si>
+  <si>
+    <t>12-G</t>
+  </si>
+  <si>
+    <t>Imperia Departmental Store</t>
   </si>
 </sst>
 </file>
@@ -1755,6 +1839,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1857,17 +1954,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2399,19 +2485,19 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="3" max="3" width="30.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="144">
+      <c r="B1" s="151">
         <f ca="1">TODAY()</f>
-        <v>46282</v>
-      </c>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
+        <v>46283</v>
+      </c>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2433,10 +2519,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="173" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="152" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2466,13 +2552,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="165"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="169"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2491,8 +2577,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="146"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="153"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2520,29 +2606,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="171"/>
+      <c r="N3" s="172"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="148" t="s">
+      <c r="Q3" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="149"/>
-      <c r="S3" s="149"/>
-      <c r="T3" s="150"/>
-      <c r="U3" s="151" t="s">
+      <c r="R3" s="156"/>
+      <c r="S3" s="156"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="152"/>
-      <c r="W3" s="152"/>
-      <c r="X3" s="153"/>
+      <c r="V3" s="159"/>
+      <c r="W3" s="159"/>
+      <c r="X3" s="160"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="147"/>
+      <c r="A4" s="173"/>
+      <c r="B4" s="154"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -5520,35 +5606,35 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="178">
+      <c r="A42" s="72">
         <v>46280</v>
       </c>
-      <c r="B42" s="179">
+      <c r="B42" s="41">
         <v>38</v>
       </c>
-      <c r="C42" s="180" t="s">
+      <c r="C42" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="180" t="s">
+      <c r="D42" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="E42" s="181"/>
-      <c r="F42" s="181">
+      <c r="E42" s="44"/>
+      <c r="F42" s="44">
         <v>120</v>
       </c>
-      <c r="G42" s="182">
+      <c r="G42" s="69">
         <v>40</v>
       </c>
-      <c r="H42" s="183">
+      <c r="H42" s="43">
         <v>80</v>
       </c>
-      <c r="I42" s="181">
+      <c r="I42" s="44">
         <v>120</v>
       </c>
-      <c r="J42" s="182">
+      <c r="J42" s="69">
         <v>120</v>
       </c>
-      <c r="K42" s="184"/>
+      <c r="K42" s="70"/>
       <c r="L42" s="42">
         <f t="shared" si="66"/>
         <v>12</v>
@@ -5602,35 +5688,35 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A43" s="178">
+      <c r="A43" s="72">
         <v>46280</v>
       </c>
-      <c r="B43" s="179">
+      <c r="B43" s="41">
         <v>39</v>
       </c>
-      <c r="C43" s="180" t="s">
+      <c r="C43" s="140" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="180" t="s">
+      <c r="D43" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="181"/>
-      <c r="F43" s="181">
+      <c r="E43" s="44"/>
+      <c r="F43" s="44">
         <v>40</v>
       </c>
-      <c r="G43" s="182">
+      <c r="G43" s="69">
         <v>40</v>
       </c>
-      <c r="H43" s="183">
+      <c r="H43" s="43">
         <v>40</v>
       </c>
-      <c r="I43" s="181">
+      <c r="I43" s="44">
         <v>40</v>
       </c>
-      <c r="J43" s="182">
+      <c r="J43" s="69">
         <v>40</v>
       </c>
-      <c r="K43" s="184">
+      <c r="K43" s="70">
         <v>40</v>
       </c>
       <c r="L43" s="42">
@@ -5686,35 +5772,35 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="178">
+      <c r="A44" s="72">
         <v>46280</v>
       </c>
-      <c r="B44" s="179">
+      <c r="B44" s="41">
         <v>40</v>
       </c>
-      <c r="C44" s="180" t="s">
+      <c r="C44" s="140" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="180" t="s">
+      <c r="D44" s="140" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="181"/>
-      <c r="F44" s="181">
+      <c r="E44" s="44"/>
+      <c r="F44" s="44">
         <v>118</v>
       </c>
-      <c r="G44" s="182">
+      <c r="G44" s="69">
         <v>40</v>
       </c>
-      <c r="H44" s="183">
+      <c r="H44" s="43">
         <v>80</v>
       </c>
-      <c r="I44" s="181">
+      <c r="I44" s="44">
         <v>117</v>
       </c>
-      <c r="J44" s="182">
+      <c r="J44" s="69">
         <v>117</v>
       </c>
-      <c r="K44" s="184"/>
+      <c r="K44" s="70"/>
       <c r="L44" s="42">
         <f t="shared" si="66"/>
         <v>11.8</v>
@@ -5768,33 +5854,33 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="178">
+      <c r="A45" s="72">
         <v>46280</v>
       </c>
-      <c r="B45" s="179">
+      <c r="B45" s="41">
         <v>41</v>
       </c>
-      <c r="C45" s="180" t="s">
+      <c r="C45" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="180" t="s">
+      <c r="D45" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="181"/>
-      <c r="F45" s="181">
+      <c r="E45" s="44"/>
+      <c r="F45" s="44">
         <v>80</v>
       </c>
-      <c r="G45" s="182">
+      <c r="G45" s="69">
         <v>80</v>
       </c>
-      <c r="H45" s="183">
+      <c r="H45" s="43">
         <v>80</v>
       </c>
-      <c r="I45" s="181"/>
-      <c r="J45" s="182">
+      <c r="I45" s="44"/>
+      <c r="J45" s="69">
         <v>40</v>
       </c>
-      <c r="K45" s="184">
+      <c r="K45" s="70">
         <v>40</v>
       </c>
       <c r="L45" s="42">
@@ -5850,29 +5936,29 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="178">
+      <c r="A46" s="72">
         <v>46280</v>
       </c>
-      <c r="B46" s="179">
+      <c r="B46" s="41">
         <v>42</v>
       </c>
-      <c r="C46" s="180" t="s">
+      <c r="C46" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="180" t="s">
+      <c r="D46" s="140" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="181"/>
-      <c r="F46" s="181"/>
-      <c r="G46" s="182"/>
-      <c r="H46" s="183">
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="43">
         <v>40</v>
       </c>
-      <c r="I46" s="181"/>
-      <c r="J46" s="182">
+      <c r="I46" s="44"/>
+      <c r="J46" s="69">
         <v>40</v>
       </c>
-      <c r="K46" s="184">
+      <c r="K46" s="70">
         <v>40</v>
       </c>
       <c r="L46" s="42">
@@ -5928,33 +6014,33 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="178">
+      <c r="A47" s="72">
         <v>46280</v>
       </c>
-      <c r="B47" s="179">
+      <c r="B47" s="41">
         <v>43</v>
       </c>
-      <c r="C47" s="180" t="s">
+      <c r="C47" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="180" t="s">
+      <c r="D47" s="140" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="181"/>
-      <c r="F47" s="181">
+      <c r="E47" s="44"/>
+      <c r="F47" s="44">
         <v>40</v>
       </c>
-      <c r="G47" s="182">
+      <c r="G47" s="69">
         <v>40</v>
       </c>
-      <c r="H47" s="183">
+      <c r="H47" s="43">
         <v>40</v>
       </c>
-      <c r="I47" s="181"/>
-      <c r="J47" s="182">
+      <c r="I47" s="44"/>
+      <c r="J47" s="69">
         <v>40</v>
       </c>
-      <c r="K47" s="184">
+      <c r="K47" s="70">
         <v>40</v>
       </c>
       <c r="L47" s="42">
@@ -5992,31 +6078,31 @@
       <c r="X47" s="50"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="178">
+      <c r="A48" s="72">
         <v>46280</v>
       </c>
-      <c r="B48" s="179">
+      <c r="B48" s="41">
         <v>44</v>
       </c>
-      <c r="C48" s="180" t="s">
+      <c r="C48" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="180" t="s">
+      <c r="D48" s="140" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="181"/>
-      <c r="F48" s="181">
+      <c r="E48" s="44"/>
+      <c r="F48" s="44">
         <v>40</v>
       </c>
-      <c r="G48" s="182">
+      <c r="G48" s="69">
         <v>40</v>
       </c>
-      <c r="H48" s="183">
+      <c r="H48" s="43">
         <v>40</v>
       </c>
-      <c r="I48" s="181"/>
-      <c r="J48" s="182"/>
-      <c r="K48" s="184"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="70"/>
       <c r="L48" s="42">
         <f t="shared" si="66"/>
         <v>3</v>
@@ -6052,35 +6138,35 @@
       <c r="X48" s="50"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="178">
+      <c r="A49" s="72">
         <v>46280</v>
       </c>
-      <c r="B49" s="179">
+      <c r="B49" s="41">
         <v>45</v>
       </c>
-      <c r="C49" s="180" t="s">
+      <c r="C49" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="180" t="s">
+      <c r="D49" s="140" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="181"/>
-      <c r="F49" s="181">
+      <c r="E49" s="44"/>
+      <c r="F49" s="44">
         <v>40</v>
       </c>
-      <c r="G49" s="182">
+      <c r="G49" s="69">
         <v>40</v>
       </c>
-      <c r="H49" s="183">
+      <c r="H49" s="43">
         <v>40</v>
       </c>
-      <c r="I49" s="181">
+      <c r="I49" s="44">
         <v>20</v>
       </c>
-      <c r="J49" s="182">
+      <c r="J49" s="69">
         <v>20</v>
       </c>
-      <c r="K49" s="184">
+      <c r="K49" s="70">
         <v>20</v>
       </c>
       <c r="L49" s="42">
@@ -6118,7 +6204,7 @@
       <c r="X49" s="50"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="143">
+      <c r="A50" s="72">
         <v>46281</v>
       </c>
       <c r="B50" s="41">
@@ -6184,26 +6270,43 @@
       <c r="X50" s="50"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="72"/>
-      <c r="B51" s="41">
+      <c r="A51" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B51" s="144">
         <v>47</v>
       </c>
-      <c r="C51" s="140"/>
-      <c r="D51" s="140"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="44"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="44"/>
-      <c r="J51" s="69"/>
-      <c r="K51" s="70"/>
+      <c r="C51" s="145" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="145" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146">
+        <v>80</v>
+      </c>
+      <c r="G51" s="147">
+        <v>80</v>
+      </c>
+      <c r="H51" s="50">
+        <v>120</v>
+      </c>
+      <c r="I51" s="146">
+        <v>80</v>
+      </c>
+      <c r="J51" s="147">
+        <v>80</v>
+      </c>
+      <c r="K51" s="148">
+        <v>120</v>
+      </c>
       <c r="L51" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M51" s="33">
-        <f t="shared" ref="M50:M70" si="71">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N51" s="43">
         <f t="shared" si="53"/>
@@ -6211,11 +6314,11 @@
       </c>
       <c r="O51" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P51" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q51" s="45"/>
       <c r="R51" s="46"/>
@@ -6233,26 +6336,43 @@
       <c r="X51" s="50"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="72"/>
-      <c r="B52" s="41">
+      <c r="A52" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B52" s="144">
         <v>48</v>
       </c>
-      <c r="C52" s="140"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="69"/>
-      <c r="K52" s="70"/>
+      <c r="C52" s="145" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="145" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" s="146"/>
+      <c r="F52" s="146">
+        <v>80</v>
+      </c>
+      <c r="G52" s="147">
+        <v>80</v>
+      </c>
+      <c r="H52" s="50">
+        <v>80</v>
+      </c>
+      <c r="I52" s="146">
+        <v>40</v>
+      </c>
+      <c r="J52" s="147">
+        <v>40</v>
+      </c>
+      <c r="K52" s="148">
+        <v>40</v>
+      </c>
       <c r="L52" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M52" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N52" s="43">
         <f t="shared" si="53"/>
@@ -6260,11 +6380,11 @@
       </c>
       <c r="O52" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P52" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="45"/>
       <c r="R52" s="46"/>
@@ -6282,26 +6402,41 @@
       <c r="X52" s="50"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="72"/>
-      <c r="B53" s="41">
+      <c r="A53" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B53" s="144">
         <v>49</v>
       </c>
-      <c r="C53" s="132"/>
-      <c r="D53" s="132"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="69"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="44"/>
-      <c r="J53" s="69"/>
-      <c r="K53" s="70"/>
+      <c r="C53" s="149" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" s="149" t="s">
+        <v>156</v>
+      </c>
+      <c r="E53" s="146"/>
+      <c r="F53" s="146">
+        <v>40</v>
+      </c>
+      <c r="G53" s="147">
+        <v>40</v>
+      </c>
+      <c r="H53" s="50"/>
+      <c r="I53" s="146">
+        <v>40</v>
+      </c>
+      <c r="J53" s="147">
+        <v>40</v>
+      </c>
+      <c r="K53" s="148">
+        <v>40</v>
+      </c>
       <c r="L53" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M53" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N53" s="43">
         <f t="shared" si="53"/>
@@ -6309,11 +6444,11 @@
       </c>
       <c r="O53" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q53" s="45"/>
       <c r="R53" s="46"/>
@@ -6331,26 +6466,39 @@
       <c r="X53" s="50"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="72"/>
-      <c r="B54" s="41">
+      <c r="A54" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B54" s="144">
         <v>50</v>
       </c>
-      <c r="C54" s="132"/>
-      <c r="D54" s="132"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="69"/>
-      <c r="H54" s="43"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="69"/>
-      <c r="K54" s="70"/>
+      <c r="C54" s="149" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="149" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" s="146"/>
+      <c r="F54" s="146"/>
+      <c r="G54" s="147">
+        <v>40</v>
+      </c>
+      <c r="H54" s="50">
+        <v>40</v>
+      </c>
+      <c r="I54" s="146"/>
+      <c r="J54" s="147">
+        <v>40</v>
+      </c>
+      <c r="K54" s="148">
+        <v>40</v>
+      </c>
       <c r="L54" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M54" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N54" s="43">
         <f t="shared" si="53"/>
@@ -6358,11 +6506,11 @@
       </c>
       <c r="O54" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P54" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q54" s="45"/>
       <c r="R54" s="46"/>
@@ -6380,26 +6528,35 @@
       <c r="X54" s="50"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="72"/>
-      <c r="B55" s="41">
+      <c r="A55" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B55" s="144">
         <v>51</v>
       </c>
-      <c r="C55" s="132"/>
-      <c r="D55" s="132"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="43"/>
-      <c r="I55" s="44"/>
-      <c r="J55" s="69"/>
-      <c r="K55" s="70"/>
+      <c r="C55" s="149" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" s="149"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="146"/>
+      <c r="G55" s="147">
+        <v>40</v>
+      </c>
+      <c r="H55" s="50"/>
+      <c r="I55" s="146">
+        <v>40</v>
+      </c>
+      <c r="J55" s="147"/>
+      <c r="K55" s="148">
+        <v>40</v>
+      </c>
       <c r="L55" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M55" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N55" s="43">
         <f t="shared" si="53"/>
@@ -6407,11 +6564,11 @@
       </c>
       <c r="O55" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P55" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q55" s="45"/>
       <c r="R55" s="46"/>
@@ -6429,26 +6586,43 @@
       <c r="X55" s="50"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="72"/>
-      <c r="B56" s="41">
+      <c r="A56" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B56" s="144">
         <v>52</v>
       </c>
-      <c r="C56" s="132"/>
-      <c r="D56" s="132"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="43"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="70"/>
+      <c r="C56" s="149" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="149" t="s">
+        <v>174</v>
+      </c>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146">
+        <v>40</v>
+      </c>
+      <c r="G56" s="147">
+        <v>40</v>
+      </c>
+      <c r="H56" s="50">
+        <v>80</v>
+      </c>
+      <c r="I56" s="146">
+        <v>40</v>
+      </c>
+      <c r="J56" s="147">
+        <v>40</v>
+      </c>
+      <c r="K56" s="148">
+        <v>80</v>
+      </c>
       <c r="L56" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M56" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N56" s="43">
         <f t="shared" si="53"/>
@@ -6456,11 +6630,11 @@
       </c>
       <c r="O56" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P56" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q56" s="45"/>
       <c r="R56" s="46"/>
@@ -6478,26 +6652,43 @@
       <c r="X56" s="50"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="72"/>
-      <c r="B57" s="41">
+      <c r="A57" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B57" s="144">
         <v>53</v>
       </c>
-      <c r="C57" s="132"/>
-      <c r="D57" s="132"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="44"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="44"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="70"/>
+      <c r="C57" s="149" t="s">
+        <v>162</v>
+      </c>
+      <c r="D57" s="149" t="s">
+        <v>172</v>
+      </c>
+      <c r="E57" s="146"/>
+      <c r="F57" s="146">
+        <v>40</v>
+      </c>
+      <c r="G57" s="147">
+        <v>80</v>
+      </c>
+      <c r="H57" s="50">
+        <v>80</v>
+      </c>
+      <c r="I57" s="146">
+        <v>40</v>
+      </c>
+      <c r="J57" s="147">
+        <v>40</v>
+      </c>
+      <c r="K57" s="148">
+        <v>40</v>
+      </c>
       <c r="L57" s="42">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M57" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N57" s="43">
         <f t="shared" si="53"/>
@@ -6505,11 +6696,11 @@
       </c>
       <c r="O57" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P57" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="45"/>
       <c r="R57" s="46"/>
@@ -6527,26 +6718,43 @@
       <c r="X57" s="50"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="72"/>
-      <c r="B58" s="41">
+      <c r="A58" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B58" s="144">
         <v>54</v>
       </c>
-      <c r="C58" s="132"/>
-      <c r="D58" s="132"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="131"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
+      <c r="C58" s="149" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="149" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" s="146"/>
+      <c r="F58" s="147">
+        <v>40</v>
+      </c>
+      <c r="G58" s="147">
+        <v>40</v>
+      </c>
+      <c r="H58" s="150">
+        <v>80</v>
+      </c>
+      <c r="I58" s="147">
+        <v>40</v>
+      </c>
+      <c r="J58" s="147">
+        <v>40</v>
+      </c>
+      <c r="K58" s="147">
+        <v>40</v>
+      </c>
       <c r="L58" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M58" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N58" s="43">
         <f t="shared" si="53"/>
@@ -6554,11 +6762,11 @@
       </c>
       <c r="O58" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P58" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="45"/>
       <c r="R58" s="46"/>
@@ -6576,26 +6784,39 @@
       <c r="X58" s="50"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="72"/>
-      <c r="B59" s="41">
+      <c r="A59" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B59" s="144">
         <v>55</v>
       </c>
-      <c r="C59" s="132"/>
-      <c r="D59" s="132"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="131"/>
-      <c r="I59" s="69"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
+      <c r="C59" s="149" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="149" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="146"/>
+      <c r="F59" s="147"/>
+      <c r="G59" s="147">
+        <v>40</v>
+      </c>
+      <c r="H59" s="150">
+        <v>40</v>
+      </c>
+      <c r="I59" s="147">
+        <v>40</v>
+      </c>
+      <c r="J59" s="147"/>
+      <c r="K59" s="147">
+        <v>40</v>
+      </c>
       <c r="L59" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N59" s="43">
         <f t="shared" si="53"/>
@@ -6603,11 +6824,11 @@
       </c>
       <c r="O59" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P59" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q59" s="45"/>
       <c r="R59" s="46"/>
@@ -6625,26 +6846,41 @@
       <c r="X59" s="50"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="72"/>
-      <c r="B60" s="41">
+      <c r="A60" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B60" s="144">
         <v>56</v>
       </c>
-      <c r="C60" s="132"/>
-      <c r="D60" s="132"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="69"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="131"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="69"/>
-      <c r="K60" s="69"/>
+      <c r="C60" s="149" t="s">
+        <v>165</v>
+      </c>
+      <c r="D60" s="149" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" s="146"/>
+      <c r="F60" s="147">
+        <v>40</v>
+      </c>
+      <c r="G60" s="147">
+        <v>40</v>
+      </c>
+      <c r="H60" s="150">
+        <v>40</v>
+      </c>
+      <c r="I60" s="147">
+        <v>40</v>
+      </c>
+      <c r="J60" s="147">
+        <v>40</v>
+      </c>
+      <c r="K60" s="147"/>
       <c r="L60" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M60" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N60" s="43">
         <f t="shared" si="53"/>
@@ -6652,11 +6888,11 @@
       </c>
       <c r="O60" s="67">
         <f t="shared" si="67"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P60" s="34">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="45"/>
       <c r="R60" s="46"/>
@@ -6674,26 +6910,37 @@
       <c r="X60" s="50"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="72"/>
-      <c r="B61" s="41">
+      <c r="A61" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B61" s="144">
         <v>57</v>
       </c>
-      <c r="C61" s="132"/>
-      <c r="D61" s="132"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="131"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
+      <c r="C61" s="149" t="s">
+        <v>166</v>
+      </c>
+      <c r="D61" s="149" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="146"/>
+      <c r="F61" s="147"/>
+      <c r="G61" s="147">
+        <v>80</v>
+      </c>
+      <c r="H61" s="150"/>
+      <c r="I61" s="147"/>
+      <c r="J61" s="147">
+        <v>40</v>
+      </c>
+      <c r="K61" s="147">
+        <v>40</v>
+      </c>
       <c r="L61" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M61" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N61" s="43">
         <f t="shared" si="53"/>
@@ -6701,14 +6948,14 @@
       </c>
       <c r="O61" s="67">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P61" s="34">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q61" s="45" t="e">
-        <f t="shared" ref="Q61:Q92" si="72">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" ref="Q61:Q92" si="71">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R61" s="46">
@@ -6724,7 +6971,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U61" s="48" t="e">
-        <f t="shared" ref="U61:U92" si="73">SUM(E61:E61)*$U$3</f>
+        <f t="shared" ref="U61:U92" si="72">SUM(E61:E61)*$U$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="49">
@@ -6741,41 +6988,50 @@
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="72"/>
-      <c r="B62" s="41">
+      <c r="A62" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B62" s="144">
         <v>58</v>
       </c>
-      <c r="C62" s="132"/>
-      <c r="D62" s="132"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="69"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="131"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="69"/>
-      <c r="K62" s="69"/>
+      <c r="C62" s="149" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" s="149" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="146"/>
+      <c r="F62" s="147"/>
+      <c r="G62" s="147"/>
+      <c r="H62" s="150">
+        <v>80</v>
+      </c>
+      <c r="I62" s="147"/>
+      <c r="J62" s="147"/>
+      <c r="K62" s="147">
+        <v>20</v>
+      </c>
       <c r="L62" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M62" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N62" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O62" s="67">
-        <f t="shared" ref="O62:O79" si="74">SUM(F62:H62)/20</f>
-        <v>0</v>
+        <f t="shared" ref="O62:O79" si="73">SUM(F62:H62)/20</f>
+        <v>4</v>
       </c>
       <c r="P62" s="34">
-        <f t="shared" ref="P62:P79" si="75">SUM(I62:K62)/20</f>
-        <v>0</v>
+        <f t="shared" ref="P62:P79" si="74">SUM(I62:K62)/20</f>
+        <v>1</v>
       </c>
       <c r="Q62" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R62" s="46">
@@ -6787,62 +7043,77 @@
         <v>0</v>
       </c>
       <c r="T62" s="47" t="e">
-        <f t="shared" ref="T62:T79" si="76">SUM(Q62:S62)</f>
+        <f t="shared" ref="T62:T79" si="75">SUM(Q62:S62)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U62" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V62" s="49">
-        <f t="shared" ref="V62:V79" si="77">SUM(F62:H62)*$V$3</f>
+        <f t="shared" ref="V62:V79" si="76">SUM(F62:H62)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W62" s="49">
-        <f t="shared" ref="W62:W79" si="78">SUM(I62:K62)*$W$3</f>
+        <f t="shared" ref="W62:W79" si="77">SUM(I62:K62)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X62" s="50" t="e">
-        <f t="shared" ref="X62:X79" si="79">SUM(U62:W62)</f>
+        <f t="shared" ref="X62:X79" si="78">SUM(U62:W62)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="72"/>
-      <c r="B63" s="41">
+      <c r="A63" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B63" s="144">
         <v>59</v>
       </c>
-      <c r="C63" s="132"/>
-      <c r="D63" s="132"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="69"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="131"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="69"/>
-      <c r="K63" s="69"/>
+      <c r="C63" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" s="149" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="146"/>
+      <c r="F63" s="147">
+        <v>40</v>
+      </c>
+      <c r="G63" s="147"/>
+      <c r="H63" s="150">
+        <v>80</v>
+      </c>
+      <c r="I63" s="147">
+        <v>20</v>
+      </c>
+      <c r="J63" s="147">
+        <v>20</v>
+      </c>
+      <c r="K63" s="147">
+        <v>40</v>
+      </c>
       <c r="L63" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M63" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N63" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O63" s="67">
+        <f t="shared" si="73"/>
+        <v>6</v>
+      </c>
+      <c r="P63" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P63" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q63" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R63" s="46">
@@ -6854,62 +7125,79 @@
         <v>0</v>
       </c>
       <c r="T63" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U63" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V63" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U63" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V63" s="49">
+        <v>0</v>
+      </c>
+      <c r="W63" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W63" s="49">
+      <c r="X63" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X63" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="72"/>
-      <c r="B64" s="41">
+      <c r="A64" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B64" s="144">
         <v>60</v>
       </c>
-      <c r="C64" s="132"/>
-      <c r="D64" s="132"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="131"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
+      <c r="C64" s="149" t="s">
+        <v>169</v>
+      </c>
+      <c r="D64" s="149" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" s="146"/>
+      <c r="F64" s="147">
+        <v>40</v>
+      </c>
+      <c r="G64" s="147">
+        <v>40</v>
+      </c>
+      <c r="H64" s="150">
+        <v>40</v>
+      </c>
+      <c r="I64" s="147">
+        <v>20</v>
+      </c>
+      <c r="J64" s="147">
+        <v>20</v>
+      </c>
+      <c r="K64" s="147">
+        <v>20</v>
+      </c>
       <c r="L64" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M64" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N64" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O64" s="67">
+        <f t="shared" si="73"/>
+        <v>6</v>
+      </c>
+      <c r="P64" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R64" s="46">
@@ -6921,62 +7209,79 @@
         <v>0</v>
       </c>
       <c r="T64" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U64" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V64" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U64" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V64" s="49">
+        <v>0</v>
+      </c>
+      <c r="W64" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W64" s="49">
+      <c r="X64" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X64" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A65" s="72"/>
-      <c r="B65" s="41">
+      <c r="A65" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B65" s="144">
         <v>61</v>
       </c>
-      <c r="C65" s="132"/>
-      <c r="D65" s="132"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="131"/>
-      <c r="I65" s="69"/>
-      <c r="J65" s="69"/>
-      <c r="K65" s="69"/>
+      <c r="C65" s="149" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" s="149" t="s">
+        <v>181</v>
+      </c>
+      <c r="E65" s="146"/>
+      <c r="F65" s="147">
+        <v>80</v>
+      </c>
+      <c r="G65" s="147">
+        <v>80</v>
+      </c>
+      <c r="H65" s="150">
+        <v>80</v>
+      </c>
+      <c r="I65" s="147">
+        <v>40</v>
+      </c>
+      <c r="J65" s="147">
+        <v>40</v>
+      </c>
+      <c r="K65" s="147">
+        <v>20</v>
+      </c>
       <c r="L65" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M65" s="33">
-        <f t="shared" si="71"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N65" s="43">
         <f t="shared" si="53"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O65" s="67">
+        <f t="shared" si="73"/>
+        <v>12</v>
+      </c>
+      <c r="P65" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q65" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R65" s="46">
@@ -6988,62 +7293,79 @@
         <v>0</v>
       </c>
       <c r="T65" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U65" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V65" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U65" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V65" s="49">
+        <v>0</v>
+      </c>
+      <c r="W65" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W65" s="49">
+      <c r="X65" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A66" s="72"/>
-      <c r="B66" s="41">
+      <c r="A66" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B66" s="144">
         <v>62</v>
       </c>
-      <c r="C66" s="132"/>
-      <c r="D66" s="132"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
-      <c r="H66" s="131"/>
-      <c r="I66" s="69"/>
-      <c r="J66" s="69"/>
-      <c r="K66" s="69"/>
+      <c r="C66" s="149" t="s">
+        <v>182</v>
+      </c>
+      <c r="D66" s="149" t="s">
+        <v>156</v>
+      </c>
+      <c r="E66" s="146"/>
+      <c r="F66" s="147">
+        <v>40</v>
+      </c>
+      <c r="G66" s="147">
+        <v>40</v>
+      </c>
+      <c r="H66" s="150">
+        <v>80</v>
+      </c>
+      <c r="I66" s="147">
+        <v>40</v>
+      </c>
+      <c r="J66" s="147">
+        <v>40</v>
+      </c>
+      <c r="K66" s="147">
+        <v>80</v>
+      </c>
       <c r="L66" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M66" s="33">
+        <v>10</v>
+      </c>
+      <c r="N66" s="43">
+        <f t="shared" ref="N66:N97" si="79">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O66" s="67">
+        <f t="shared" si="73"/>
+        <v>8</v>
+      </c>
+      <c r="P66" s="34">
+        <f t="shared" si="74"/>
+        <v>8</v>
+      </c>
+      <c r="Q66" s="45" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="N66" s="43">
-        <f t="shared" ref="N66:N97" si="80">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O66" s="67">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="45" t="e">
-        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="R66" s="46">
@@ -7055,62 +7377,79 @@
         <v>0</v>
       </c>
       <c r="T66" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U66" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V66" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U66" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V66" s="49">
+        <v>0</v>
+      </c>
+      <c r="W66" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W66" s="49">
+      <c r="X66" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X66" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A67" s="72"/>
-      <c r="B67" s="41">
+      <c r="A67" s="143">
+        <v>46282</v>
+      </c>
+      <c r="B67" s="144">
         <v>63</v>
       </c>
-      <c r="C67" s="132"/>
-      <c r="D67" s="132"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="69"/>
-      <c r="G67" s="69"/>
-      <c r="H67" s="131"/>
-      <c r="I67" s="69"/>
-      <c r="J67" s="69"/>
-      <c r="K67" s="69"/>
+      <c r="C67" s="149" t="s">
+        <v>128</v>
+      </c>
+      <c r="D67" s="149" t="s">
+        <v>129</v>
+      </c>
+      <c r="E67" s="146"/>
+      <c r="F67" s="147">
+        <v>798</v>
+      </c>
+      <c r="G67" s="147">
+        <v>596</v>
+      </c>
+      <c r="H67" s="150">
+        <v>1600</v>
+      </c>
+      <c r="I67" s="147">
+        <v>1999</v>
+      </c>
+      <c r="J67" s="147">
+        <v>781</v>
+      </c>
+      <c r="K67" s="147">
+        <v>1998</v>
+      </c>
       <c r="L67" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>194.3</v>
       </c>
       <c r="M67" s="33">
+        <v>18</v>
+      </c>
+      <c r="N67" s="43">
+        <f t="shared" si="79"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O67" s="67">
+        <f t="shared" si="73"/>
+        <v>149.69999999999999</v>
+      </c>
+      <c r="P67" s="34">
+        <f t="shared" si="74"/>
+        <v>238.9</v>
+      </c>
+      <c r="Q67" s="45" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="N67" s="43">
-        <f t="shared" si="80"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O67" s="67">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P67" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="45" t="e">
-        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="R67" s="46">
@@ -7122,23 +7461,23 @@
         <v>0</v>
       </c>
       <c r="T67" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U67" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V67" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U67" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V67" s="49">
+        <v>0</v>
+      </c>
+      <c r="W67" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W67" s="49">
+      <c r="X67" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X67" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7161,23 +7500,23 @@
         <v>0</v>
       </c>
       <c r="M68" s="33">
+        <f t="shared" ref="M68:M70" si="80">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="43">
+        <f t="shared" si="79"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O68" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P68" s="34">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="45" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="N68" s="43">
-        <f t="shared" si="80"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O68" s="67">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="45" t="e">
-        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="R68" s="46">
@@ -7189,23 +7528,23 @@
         <v>0</v>
       </c>
       <c r="T68" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U68" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V68" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U68" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V68" s="49">
+        <v>0</v>
+      </c>
+      <c r="W68" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W68" s="49">
+      <c r="X68" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X68" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7228,23 +7567,23 @@
         <v>0</v>
       </c>
       <c r="M69" s="33">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="N69" s="43">
+        <f t="shared" si="79"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O69" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P69" s="34">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Q69" s="45" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="N69" s="43">
-        <f t="shared" si="80"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O69" s="67">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="45" t="e">
-        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="R69" s="46">
@@ -7256,23 +7595,23 @@
         <v>0</v>
       </c>
       <c r="T69" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U69" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V69" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U69" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V69" s="49">
+        <v>0</v>
+      </c>
+      <c r="W69" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W69" s="49">
+      <c r="X69" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X69" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7295,23 +7634,23 @@
         <v>0</v>
       </c>
       <c r="M70" s="33">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="43">
+        <f t="shared" si="79"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O70" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P70" s="34">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="45" t="e">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="N70" s="43">
-        <f t="shared" si="80"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O70" s="67">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="P70" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="45" t="e">
-        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="R70" s="46">
@@ -7323,23 +7662,23 @@
         <v>0</v>
       </c>
       <c r="T70" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U70" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V70" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U70" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V70" s="49">
+        <v>0</v>
+      </c>
+      <c r="W70" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W70" s="49">
+      <c r="X70" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X70" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7366,19 +7705,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O71" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P71" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P71" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q71" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R71" s="46">
@@ -7390,23 +7729,23 @@
         <v>0</v>
       </c>
       <c r="T71" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U71" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V71" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U71" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V71" s="49">
+        <v>0</v>
+      </c>
+      <c r="W71" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W71" s="49">
+      <c r="X71" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X71" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7433,19 +7772,19 @@
         <v>0</v>
       </c>
       <c r="N72" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O72" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P72" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P72" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q72" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R72" s="46">
@@ -7457,23 +7796,23 @@
         <v>0</v>
       </c>
       <c r="T72" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U72" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V72" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U72" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V72" s="49">
+        <v>0</v>
+      </c>
+      <c r="W72" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W72" s="49">
+      <c r="X72" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X72" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7500,19 +7839,19 @@
         <v>0</v>
       </c>
       <c r="N73" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O73" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P73" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P73" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q73" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R73" s="46">
@@ -7524,23 +7863,23 @@
         <v>0</v>
       </c>
       <c r="T73" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U73" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V73" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U73" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V73" s="49">
+        <v>0</v>
+      </c>
+      <c r="W73" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W73" s="49">
+      <c r="X73" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X73" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7567,19 +7906,19 @@
         <v>0</v>
       </c>
       <c r="N74" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O74" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P74" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P74" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q74" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R74" s="46">
@@ -7591,23 +7930,23 @@
         <v>0</v>
       </c>
       <c r="T74" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U74" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V74" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U74" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V74" s="49">
+        <v>0</v>
+      </c>
+      <c r="W74" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W74" s="49">
+      <c r="X74" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X74" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7634,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="N75" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O75" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P75" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P75" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q75" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R75" s="46">
@@ -7658,23 +7997,23 @@
         <v>0</v>
       </c>
       <c r="T75" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U75" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V75" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U75" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V75" s="49">
+        <v>0</v>
+      </c>
+      <c r="W75" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W75" s="49">
+      <c r="X75" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X75" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7701,19 +8040,19 @@
         <v>0</v>
       </c>
       <c r="N76" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O76" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P76" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P76" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q76" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R76" s="46">
@@ -7725,23 +8064,23 @@
         <v>0</v>
       </c>
       <c r="T76" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U76" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V76" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U76" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V76" s="49">
+        <v>0</v>
+      </c>
+      <c r="W76" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W76" s="49">
+      <c r="X76" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X76" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7768,19 +8107,19 @@
         <v>0</v>
       </c>
       <c r="N77" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O77" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P77" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P77" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q77" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R77" s="46">
@@ -7792,23 +8131,23 @@
         <v>0</v>
       </c>
       <c r="T77" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U77" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V77" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U77" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V77" s="49">
+        <v>0</v>
+      </c>
+      <c r="W77" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W77" s="49">
+      <c r="X77" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X77" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7835,19 +8174,19 @@
         <v>0</v>
       </c>
       <c r="N78" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O78" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P78" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P78" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q78" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R78" s="46">
@@ -7859,23 +8198,23 @@
         <v>0</v>
       </c>
       <c r="T78" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U78" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V78" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U78" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V78" s="49">
+        <v>0</v>
+      </c>
+      <c r="W78" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W78" s="49">
+      <c r="X78" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X78" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7902,19 +8241,19 @@
         <v>0</v>
       </c>
       <c r="N79" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O79" s="67">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="P79" s="34">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="P79" s="34">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
       <c r="Q79" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R79" s="46">
@@ -7926,23 +8265,23 @@
         <v>0</v>
       </c>
       <c r="T79" s="47" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U79" s="48" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V79" s="49">
         <f t="shared" si="76"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U79" s="48" t="e">
-        <f t="shared" si="73"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V79" s="49">
+        <v>0</v>
+      </c>
+      <c r="W79" s="49">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="W79" s="49">
+      <c r="X79" s="50" t="e">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="X79" s="50" t="e">
-        <f t="shared" si="79"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7969,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="N80" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O80" s="67">
@@ -7981,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R80" s="46">
@@ -7997,7 +8336,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U80" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="49">
@@ -8036,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O81" s="67">
@@ -8048,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R81" s="46">
@@ -8064,7 +8403,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U81" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V81" s="49">
@@ -8103,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O82" s="67">
@@ -8115,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R82" s="46">
@@ -8131,7 +8470,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U82" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V82" s="49">
@@ -8170,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O83" s="67">
@@ -8182,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R83" s="46">
@@ -8198,7 +8537,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U83" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="49">
@@ -8237,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O84" s="67">
@@ -8249,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R84" s="46">
@@ -8265,7 +8604,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U84" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="49">
@@ -8304,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O85" s="67">
@@ -8316,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R85" s="46">
@@ -8332,7 +8671,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U85" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V85" s="49">
@@ -8371,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O86" s="67">
@@ -8383,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R86" s="46">
@@ -8399,7 +8738,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U86" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V86" s="49">
@@ -8438,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O87" s="67">
@@ -8450,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R87" s="46">
@@ -8466,7 +8805,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U87" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V87" s="49">
@@ -8505,7 +8844,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O88" s="67">
@@ -8517,7 +8856,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R88" s="46">
@@ -8533,7 +8872,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U88" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V88" s="49">
@@ -8572,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O89" s="67">
@@ -8584,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R89" s="46">
@@ -8600,7 +8939,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U89" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V89" s="49">
@@ -8639,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O90" s="67">
@@ -8651,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R90" s="46">
@@ -8667,7 +9006,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U90" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V90" s="49">
@@ -8706,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O91" s="67">
@@ -8718,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R91" s="46">
@@ -8734,7 +9073,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U91" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V91" s="49">
@@ -8773,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O92" s="67">
@@ -8785,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="45" t="e">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
       <c r="R92" s="46">
@@ -8801,7 +9140,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U92" s="48" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>#VALUE!</v>
       </c>
       <c r="V92" s="49">
@@ -8840,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O93" s="67">
@@ -8907,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O94" s="67">
@@ -8974,7 +9313,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O95" s="67">
@@ -9041,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O96" s="67">
@@ -9108,7 +9447,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="43">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O97" s="67">
@@ -11483,10 +11822,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="154" t="s">
+      <c r="B133" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="155"/>
+      <c r="C133" s="162"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
@@ -11494,31 +11833,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="102"/>
-        <v>2758</v>
+        <v>3118</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="102"/>
-        <v>2690</v>
+        <v>3290</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="102"/>
-        <v>4170</v>
+        <v>4730</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="102"/>
-        <v>4555</v>
+        <v>4955</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="102"/>
-        <v>5137</v>
+        <v>5537</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="102"/>
-        <v>7020</v>
+        <v>7540</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
-        <v>714.875</v>
+        <v>785.875</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="99"/>
@@ -11530,11 +11869,11 @@
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>480.9</v>
+        <v>556.9</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>835.6</v>
+        <v>901.6</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="100"/>
@@ -11740,10 +12079,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="167" t="s">
+      <c r="B137" s="174" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="168"/>
+      <c r="C137" s="175"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -11827,10 +12166,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="156" t="s">
+      <c r="B138" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="157"/>
+      <c r="C138" s="164"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -11838,35 +12177,35 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
-        <v>2758</v>
+        <v>3118</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="109"/>
-        <v>2690</v>
+        <v>3290</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="109"/>
-        <v>4170</v>
+        <v>4730</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="109"/>
-        <v>4555</v>
+        <v>4955</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="109"/>
-        <v>5137</v>
+        <v>5537</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="109"/>
-        <v>7020</v>
+        <v>7540</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>714.875</v>
+        <v>785.875</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>598</v>
+        <v>890</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
@@ -11874,11 +12213,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="110"/>
-        <v>1081.8</v>
+        <v>1419.5</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="110"/>
-        <v>1791.2</v>
+        <v>2183.1</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="110"/>
@@ -11961,25 +12300,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="175" t="s">
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="180"/>
+      <c r="H3" s="182" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="176"/>
-      <c r="K3" s="177" t="s">
+      <c r="I3" s="183"/>
+      <c r="K3" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="177"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="177"/>
-      <c r="O3" s="177"/>
-      <c r="P3" s="177"/>
+      <c r="L3" s="184"/>
+      <c r="M3" s="184"/>
+      <c r="N3" s="184"/>
+      <c r="O3" s="184"/>
+      <c r="P3" s="184"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -12025,24 +12364,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>605</v>
+        <v>678</v>
       </c>
       <c r="E5" s="73">
-        <v>729</v>
+        <v>1030</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1434</v>
+        <v>1808</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8566</v>
+        <v>-8192</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -12066,11 +12405,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>24200</v>
+        <v>27120</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>29160</v>
+        <v>41200</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -12078,7 +12417,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>57360</v>
+        <v>72320</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -12086,7 +12425,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-342640</v>
+        <v>-327680</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -12214,11 +12553,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-605</v>
+        <v>-678</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-729</v>
+        <v>-1030</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -12302,14 +12641,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="181" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="174"/>
-      <c r="F11" s="174" t="s">
+      <c r="D11" s="181"/>
+      <c r="F11" s="181" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="174"/>
+      <c r="G11" s="181"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12361,7 +12700,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>5634</v>
+        <v>6008</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12413,12 +12752,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>225360</v>
-      </c>
-      <c r="S13" s="169" t="s">
+        <v>240320</v>
+      </c>
+      <c r="S13" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="169"/>
+      <c r="T13" s="176"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12507,13 +12846,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="170" t="s">
+      <c r="D20" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="177"/>
+      <c r="G20" s="177"/>
+      <c r="H20" s="177"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71356E1F-2D64-4402-B6B0-76EBB25522BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D2E77-2F78-422F-954C-A581D6B0C291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="186">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -571,6 +571,15 @@
   </si>
   <si>
     <t>Imperia Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>Shaikhpura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qamar Ijaz </t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1842,10 +1851,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2491,13 +2498,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="151">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
         <v>46283</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2519,10 +2526,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2552,13 +2559,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="165"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="169"/>
+      <c r="P2" s="167"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2577,8 +2584,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="173"/>
-      <c r="B3" s="153"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2606,29 +2613,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="170" t="s">
+      <c r="L3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="170"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="155" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="156"/>
-      <c r="S3" s="156"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="159"/>
-      <c r="W3" s="159"/>
-      <c r="X3" s="160"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="173"/>
-      <c r="B4" s="154"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -6270,35 +6277,35 @@
       <c r="X50" s="50"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="143">
+      <c r="A51" s="72">
         <v>46282</v>
       </c>
-      <c r="B51" s="144">
+      <c r="B51" s="41">
         <v>47</v>
       </c>
-      <c r="C51" s="145" t="s">
+      <c r="C51" s="140" t="s">
         <v>155</v>
       </c>
-      <c r="D51" s="145" t="s">
+      <c r="D51" s="140" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="146"/>
-      <c r="F51" s="146">
+      <c r="E51" s="44"/>
+      <c r="F51" s="44">
         <v>80</v>
       </c>
-      <c r="G51" s="147">
+      <c r="G51" s="69">
         <v>80</v>
       </c>
-      <c r="H51" s="50">
+      <c r="H51" s="43">
         <v>120</v>
       </c>
-      <c r="I51" s="146">
+      <c r="I51" s="44">
         <v>80</v>
       </c>
-      <c r="J51" s="147">
+      <c r="J51" s="69">
         <v>80</v>
       </c>
-      <c r="K51" s="148">
+      <c r="K51" s="70">
         <v>120</v>
       </c>
       <c r="L51" s="42">
@@ -6336,35 +6343,35 @@
       <c r="X51" s="50"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="143">
+      <c r="A52" s="72">
         <v>46282</v>
       </c>
-      <c r="B52" s="144">
+      <c r="B52" s="41">
         <v>48</v>
       </c>
-      <c r="C52" s="145" t="s">
+      <c r="C52" s="140" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="145" t="s">
+      <c r="D52" s="140" t="s">
         <v>171</v>
       </c>
-      <c r="E52" s="146"/>
-      <c r="F52" s="146">
+      <c r="E52" s="44"/>
+      <c r="F52" s="44">
         <v>80</v>
       </c>
-      <c r="G52" s="147">
+      <c r="G52" s="69">
         <v>80</v>
       </c>
-      <c r="H52" s="50">
+      <c r="H52" s="43">
         <v>80</v>
       </c>
-      <c r="I52" s="146">
-        <v>40</v>
-      </c>
-      <c r="J52" s="147">
-        <v>40</v>
-      </c>
-      <c r="K52" s="148">
+      <c r="I52" s="44">
+        <v>40</v>
+      </c>
+      <c r="J52" s="69">
+        <v>40</v>
+      </c>
+      <c r="K52" s="70">
         <v>40</v>
       </c>
       <c r="L52" s="42">
@@ -6402,33 +6409,33 @@
       <c r="X52" s="50"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="143">
+      <c r="A53" s="72">
         <v>46282</v>
       </c>
-      <c r="B53" s="144">
+      <c r="B53" s="41">
         <v>49</v>
       </c>
-      <c r="C53" s="149" t="s">
+      <c r="C53" s="132" t="s">
         <v>158</v>
       </c>
-      <c r="D53" s="149" t="s">
+      <c r="D53" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="E53" s="146"/>
-      <c r="F53" s="146">
-        <v>40</v>
-      </c>
-      <c r="G53" s="147">
-        <v>40</v>
-      </c>
-      <c r="H53" s="50"/>
-      <c r="I53" s="146">
-        <v>40</v>
-      </c>
-      <c r="J53" s="147">
-        <v>40</v>
-      </c>
-      <c r="K53" s="148">
+      <c r="E53" s="44"/>
+      <c r="F53" s="44">
+        <v>40</v>
+      </c>
+      <c r="G53" s="69">
+        <v>40</v>
+      </c>
+      <c r="H53" s="43"/>
+      <c r="I53" s="44">
+        <v>40</v>
+      </c>
+      <c r="J53" s="69">
+        <v>40</v>
+      </c>
+      <c r="K53" s="70">
         <v>40</v>
       </c>
       <c r="L53" s="42">
@@ -6466,31 +6473,31 @@
       <c r="X53" s="50"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="143">
+      <c r="A54" s="72">
         <v>46282</v>
       </c>
-      <c r="B54" s="144">
+      <c r="B54" s="41">
         <v>50</v>
       </c>
-      <c r="C54" s="149" t="s">
+      <c r="C54" s="132" t="s">
         <v>159</v>
       </c>
-      <c r="D54" s="149" t="s">
+      <c r="D54" s="132" t="s">
         <v>173</v>
       </c>
-      <c r="E54" s="146"/>
-      <c r="F54" s="146"/>
-      <c r="G54" s="147">
-        <v>40</v>
-      </c>
-      <c r="H54" s="50">
-        <v>40</v>
-      </c>
-      <c r="I54" s="146"/>
-      <c r="J54" s="147">
-        <v>40</v>
-      </c>
-      <c r="K54" s="148">
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="69">
+        <v>40</v>
+      </c>
+      <c r="H54" s="43">
+        <v>40</v>
+      </c>
+      <c r="I54" s="44"/>
+      <c r="J54" s="69">
+        <v>40</v>
+      </c>
+      <c r="K54" s="70">
         <v>40</v>
       </c>
       <c r="L54" s="42">
@@ -6528,27 +6535,27 @@
       <c r="X54" s="50"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="143">
+      <c r="A55" s="72">
         <v>46282</v>
       </c>
-      <c r="B55" s="144">
+      <c r="B55" s="41">
         <v>51</v>
       </c>
-      <c r="C55" s="149" t="s">
+      <c r="C55" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="D55" s="149"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="146"/>
-      <c r="G55" s="147">
-        <v>40</v>
-      </c>
-      <c r="H55" s="50"/>
-      <c r="I55" s="146">
-        <v>40</v>
-      </c>
-      <c r="J55" s="147"/>
-      <c r="K55" s="148">
+      <c r="D55" s="132"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="69">
+        <v>40</v>
+      </c>
+      <c r="H55" s="43"/>
+      <c r="I55" s="44">
+        <v>40</v>
+      </c>
+      <c r="J55" s="69"/>
+      <c r="K55" s="70">
         <v>40</v>
       </c>
       <c r="L55" s="42">
@@ -6586,35 +6593,35 @@
       <c r="X55" s="50"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="143">
+      <c r="A56" s="72">
         <v>46282</v>
       </c>
-      <c r="B56" s="144">
+      <c r="B56" s="41">
         <v>52</v>
       </c>
-      <c r="C56" s="149" t="s">
+      <c r="C56" s="132" t="s">
         <v>161</v>
       </c>
-      <c r="D56" s="149" t="s">
+      <c r="D56" s="132" t="s">
         <v>174</v>
       </c>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146">
-        <v>40</v>
-      </c>
-      <c r="G56" s="147">
-        <v>40</v>
-      </c>
-      <c r="H56" s="50">
+      <c r="E56" s="44"/>
+      <c r="F56" s="44">
+        <v>40</v>
+      </c>
+      <c r="G56" s="69">
+        <v>40</v>
+      </c>
+      <c r="H56" s="43">
         <v>80</v>
       </c>
-      <c r="I56" s="146">
-        <v>40</v>
-      </c>
-      <c r="J56" s="147">
-        <v>40</v>
-      </c>
-      <c r="K56" s="148">
+      <c r="I56" s="44">
+        <v>40</v>
+      </c>
+      <c r="J56" s="69">
+        <v>40</v>
+      </c>
+      <c r="K56" s="70">
         <v>80</v>
       </c>
       <c r="L56" s="42">
@@ -6652,35 +6659,35 @@
       <c r="X56" s="50"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="143">
+      <c r="A57" s="72">
         <v>46282</v>
       </c>
-      <c r="B57" s="144">
+      <c r="B57" s="41">
         <v>53</v>
       </c>
-      <c r="C57" s="149" t="s">
+      <c r="C57" s="132" t="s">
         <v>162</v>
       </c>
-      <c r="D57" s="149" t="s">
+      <c r="D57" s="132" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="146"/>
-      <c r="F57" s="146">
-        <v>40</v>
-      </c>
-      <c r="G57" s="147">
+      <c r="E57" s="44"/>
+      <c r="F57" s="44">
+        <v>40</v>
+      </c>
+      <c r="G57" s="69">
         <v>80</v>
       </c>
-      <c r="H57" s="50">
+      <c r="H57" s="43">
         <v>80</v>
       </c>
-      <c r="I57" s="146">
-        <v>40</v>
-      </c>
-      <c r="J57" s="147">
-        <v>40</v>
-      </c>
-      <c r="K57" s="148">
+      <c r="I57" s="44">
+        <v>40</v>
+      </c>
+      <c r="J57" s="69">
+        <v>40</v>
+      </c>
+      <c r="K57" s="70">
         <v>40</v>
       </c>
       <c r="L57" s="42">
@@ -6718,35 +6725,35 @@
       <c r="X57" s="50"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="143">
+      <c r="A58" s="72">
         <v>46282</v>
       </c>
-      <c r="B58" s="144">
+      <c r="B58" s="41">
         <v>54</v>
       </c>
-      <c r="C58" s="149" t="s">
+      <c r="C58" s="132" t="s">
         <v>163</v>
       </c>
-      <c r="D58" s="149" t="s">
+      <c r="D58" s="132" t="s">
         <v>179</v>
       </c>
-      <c r="E58" s="146"/>
-      <c r="F58" s="147">
-        <v>40</v>
-      </c>
-      <c r="G58" s="147">
-        <v>40</v>
-      </c>
-      <c r="H58" s="150">
+      <c r="E58" s="44"/>
+      <c r="F58" s="69">
+        <v>40</v>
+      </c>
+      <c r="G58" s="69">
+        <v>40</v>
+      </c>
+      <c r="H58" s="131">
         <v>80</v>
       </c>
-      <c r="I58" s="147">
-        <v>40</v>
-      </c>
-      <c r="J58" s="147">
-        <v>40</v>
-      </c>
-      <c r="K58" s="147">
+      <c r="I58" s="69">
+        <v>40</v>
+      </c>
+      <c r="J58" s="69">
+        <v>40</v>
+      </c>
+      <c r="K58" s="69">
         <v>40</v>
       </c>
       <c r="L58" s="122">
@@ -6784,31 +6791,31 @@
       <c r="X58" s="50"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="143">
+      <c r="A59" s="72">
         <v>46282</v>
       </c>
-      <c r="B59" s="144">
+      <c r="B59" s="41">
         <v>55</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="132" t="s">
         <v>164</v>
       </c>
-      <c r="D59" s="149" t="s">
+      <c r="D59" s="132" t="s">
         <v>175</v>
       </c>
-      <c r="E59" s="146"/>
-      <c r="F59" s="147"/>
-      <c r="G59" s="147">
-        <v>40</v>
-      </c>
-      <c r="H59" s="150">
-        <v>40</v>
-      </c>
-      <c r="I59" s="147">
-        <v>40</v>
-      </c>
-      <c r="J59" s="147"/>
-      <c r="K59" s="147">
+      <c r="E59" s="44"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69">
+        <v>40</v>
+      </c>
+      <c r="H59" s="131">
+        <v>40</v>
+      </c>
+      <c r="I59" s="69">
+        <v>40</v>
+      </c>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69">
         <v>40</v>
       </c>
       <c r="L59" s="122">
@@ -6846,35 +6853,35 @@
       <c r="X59" s="50"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="143">
+      <c r="A60" s="72">
         <v>46282</v>
       </c>
-      <c r="B60" s="144">
+      <c r="B60" s="41">
         <v>56</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="132" t="s">
         <v>165</v>
       </c>
-      <c r="D60" s="149" t="s">
+      <c r="D60" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="E60" s="146"/>
-      <c r="F60" s="147">
-        <v>40</v>
-      </c>
-      <c r="G60" s="147">
-        <v>40</v>
-      </c>
-      <c r="H60" s="150">
-        <v>40</v>
-      </c>
-      <c r="I60" s="147">
-        <v>40</v>
-      </c>
-      <c r="J60" s="147">
-        <v>40</v>
-      </c>
-      <c r="K60" s="147"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="69">
+        <v>40</v>
+      </c>
+      <c r="G60" s="69">
+        <v>40</v>
+      </c>
+      <c r="H60" s="131">
+        <v>40</v>
+      </c>
+      <c r="I60" s="69">
+        <v>40</v>
+      </c>
+      <c r="J60" s="69">
+        <v>40</v>
+      </c>
+      <c r="K60" s="69"/>
       <c r="L60" s="122">
         <f t="shared" si="66"/>
         <v>5</v>
@@ -6910,29 +6917,29 @@
       <c r="X60" s="50"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="143">
+      <c r="A61" s="72">
         <v>46282</v>
       </c>
-      <c r="B61" s="144">
+      <c r="B61" s="41">
         <v>57</v>
       </c>
-      <c r="C61" s="149" t="s">
+      <c r="C61" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="149" t="s">
+      <c r="D61" s="132" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="146"/>
-      <c r="F61" s="147"/>
-      <c r="G61" s="147">
+      <c r="E61" s="44"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69">
         <v>80</v>
       </c>
-      <c r="H61" s="150"/>
-      <c r="I61" s="147"/>
-      <c r="J61" s="147">
-        <v>40</v>
-      </c>
-      <c r="K61" s="147">
+      <c r="H61" s="131"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69">
+        <v>40</v>
+      </c>
+      <c r="K61" s="69">
         <v>40</v>
       </c>
       <c r="L61" s="122">
@@ -6988,27 +6995,27 @@
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="143">
+      <c r="A62" s="72">
         <v>46282</v>
       </c>
-      <c r="B62" s="144">
+      <c r="B62" s="41">
         <v>58</v>
       </c>
-      <c r="C62" s="149" t="s">
+      <c r="C62" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="D62" s="149" t="s">
+      <c r="D62" s="132" t="s">
         <v>176</v>
       </c>
-      <c r="E62" s="146"/>
-      <c r="F62" s="147"/>
-      <c r="G62" s="147"/>
-      <c r="H62" s="150">
+      <c r="E62" s="44"/>
+      <c r="F62" s="69"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="131">
         <v>80</v>
       </c>
-      <c r="I62" s="147"/>
-      <c r="J62" s="147"/>
-      <c r="K62" s="147">
+      <c r="I62" s="69"/>
+      <c r="J62" s="69"/>
+      <c r="K62" s="69">
         <v>20</v>
       </c>
       <c r="L62" s="122">
@@ -7064,33 +7071,33 @@
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="143">
+      <c r="A63" s="72">
         <v>46282</v>
       </c>
-      <c r="B63" s="144">
+      <c r="B63" s="41">
         <v>59</v>
       </c>
-      <c r="C63" s="149" t="s">
+      <c r="C63" s="132" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="149" t="s">
+      <c r="D63" s="132" t="s">
         <v>177</v>
       </c>
-      <c r="E63" s="146"/>
-      <c r="F63" s="147">
-        <v>40</v>
-      </c>
-      <c r="G63" s="147"/>
-      <c r="H63" s="150">
+      <c r="E63" s="44"/>
+      <c r="F63" s="69">
+        <v>40</v>
+      </c>
+      <c r="G63" s="69"/>
+      <c r="H63" s="131">
         <v>80</v>
       </c>
-      <c r="I63" s="147">
+      <c r="I63" s="69">
         <v>20</v>
       </c>
-      <c r="J63" s="147">
+      <c r="J63" s="69">
         <v>20</v>
       </c>
-      <c r="K63" s="147">
+      <c r="K63" s="69">
         <v>40</v>
       </c>
       <c r="L63" s="122">
@@ -7146,35 +7153,35 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="143">
+      <c r="A64" s="72">
         <v>46282</v>
       </c>
-      <c r="B64" s="144">
+      <c r="B64" s="41">
         <v>60</v>
       </c>
-      <c r="C64" s="149" t="s">
+      <c r="C64" s="132" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="149" t="s">
+      <c r="D64" s="132" t="s">
         <v>178</v>
       </c>
-      <c r="E64" s="146"/>
-      <c r="F64" s="147">
-        <v>40</v>
-      </c>
-      <c r="G64" s="147">
-        <v>40</v>
-      </c>
-      <c r="H64" s="150">
-        <v>40</v>
-      </c>
-      <c r="I64" s="147">
+      <c r="E64" s="44"/>
+      <c r="F64" s="69">
+        <v>40</v>
+      </c>
+      <c r="G64" s="69">
+        <v>40</v>
+      </c>
+      <c r="H64" s="131">
+        <v>40</v>
+      </c>
+      <c r="I64" s="69">
         <v>20</v>
       </c>
-      <c r="J64" s="147">
+      <c r="J64" s="69">
         <v>20</v>
       </c>
-      <c r="K64" s="147">
+      <c r="K64" s="69">
         <v>20</v>
       </c>
       <c r="L64" s="122">
@@ -7230,35 +7237,35 @@
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A65" s="143">
+      <c r="A65" s="72">
         <v>46282</v>
       </c>
-      <c r="B65" s="144">
+      <c r="B65" s="41">
         <v>61</v>
       </c>
-      <c r="C65" s="149" t="s">
+      <c r="C65" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="149" t="s">
+      <c r="D65" s="132" t="s">
         <v>181</v>
       </c>
-      <c r="E65" s="146"/>
-      <c r="F65" s="147">
+      <c r="E65" s="44"/>
+      <c r="F65" s="69">
         <v>80</v>
       </c>
-      <c r="G65" s="147">
+      <c r="G65" s="69">
         <v>80</v>
       </c>
-      <c r="H65" s="150">
+      <c r="H65" s="131">
         <v>80</v>
       </c>
-      <c r="I65" s="147">
-        <v>40</v>
-      </c>
-      <c r="J65" s="147">
-        <v>40</v>
-      </c>
-      <c r="K65" s="147">
+      <c r="I65" s="69">
+        <v>40</v>
+      </c>
+      <c r="J65" s="69">
+        <v>40</v>
+      </c>
+      <c r="K65" s="69">
         <v>20</v>
       </c>
       <c r="L65" s="122">
@@ -7314,35 +7321,35 @@
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A66" s="143">
+      <c r="A66" s="72">
         <v>46282</v>
       </c>
-      <c r="B66" s="144">
+      <c r="B66" s="41">
         <v>62</v>
       </c>
-      <c r="C66" s="149" t="s">
+      <c r="C66" s="132" t="s">
         <v>182</v>
       </c>
-      <c r="D66" s="149" t="s">
+      <c r="D66" s="132" t="s">
         <v>156</v>
       </c>
-      <c r="E66" s="146"/>
-      <c r="F66" s="147">
-        <v>40</v>
-      </c>
-      <c r="G66" s="147">
-        <v>40</v>
-      </c>
-      <c r="H66" s="150">
+      <c r="E66" s="44"/>
+      <c r="F66" s="69">
+        <v>40</v>
+      </c>
+      <c r="G66" s="69">
+        <v>40</v>
+      </c>
+      <c r="H66" s="131">
         <v>80</v>
       </c>
-      <c r="I66" s="147">
-        <v>40</v>
-      </c>
-      <c r="J66" s="147">
-        <v>40</v>
-      </c>
-      <c r="K66" s="147">
+      <c r="I66" s="69">
+        <v>40</v>
+      </c>
+      <c r="J66" s="69">
+        <v>40</v>
+      </c>
+      <c r="K66" s="69">
         <v>80</v>
       </c>
       <c r="L66" s="122">
@@ -7398,35 +7405,35 @@
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A67" s="143">
+      <c r="A67" s="72">
         <v>46282</v>
       </c>
-      <c r="B67" s="144">
+      <c r="B67" s="41">
         <v>63</v>
       </c>
-      <c r="C67" s="149" t="s">
+      <c r="C67" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="D67" s="149" t="s">
+      <c r="D67" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E67" s="146"/>
-      <c r="F67" s="147">
+      <c r="E67" s="44"/>
+      <c r="F67" s="69">
         <v>798</v>
       </c>
-      <c r="G67" s="147">
+      <c r="G67" s="69">
         <v>596</v>
       </c>
-      <c r="H67" s="150">
+      <c r="H67" s="131">
         <v>1600</v>
       </c>
-      <c r="I67" s="147">
+      <c r="I67" s="69">
         <v>1999</v>
       </c>
-      <c r="J67" s="147">
+      <c r="J67" s="69">
         <v>781</v>
       </c>
-      <c r="K67" s="147">
+      <c r="K67" s="69">
         <v>1998</v>
       </c>
       <c r="L67" s="122">
@@ -7482,26 +7489,41 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A68" s="72"/>
-      <c r="B68" s="41">
+      <c r="A68" s="143">
+        <v>46283</v>
+      </c>
+      <c r="B68" s="144">
         <v>64</v>
       </c>
-      <c r="C68" s="132"/>
-      <c r="D68" s="132"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="69"/>
-      <c r="H68" s="131"/>
-      <c r="I68" s="69"/>
-      <c r="J68" s="69"/>
-      <c r="K68" s="69"/>
+      <c r="C68" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" s="147" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" s="145"/>
+      <c r="F68" s="146">
+        <v>40</v>
+      </c>
+      <c r="G68" s="146">
+        <v>80</v>
+      </c>
+      <c r="H68" s="148">
+        <v>40</v>
+      </c>
+      <c r="I68" s="146">
+        <v>120</v>
+      </c>
+      <c r="J68" s="146">
+        <v>120</v>
+      </c>
+      <c r="K68" s="146"/>
       <c r="L68" s="122">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M68" s="33">
-        <f t="shared" ref="M68:M70" si="80">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N68" s="43">
         <f t="shared" si="79"/>
@@ -7509,11 +7531,11 @@
       </c>
       <c r="O68" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P68" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q68" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7549,26 +7571,39 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A69" s="72"/>
-      <c r="B69" s="41">
+      <c r="A69" s="143">
+        <v>46283</v>
+      </c>
+      <c r="B69" s="144">
         <v>65</v>
       </c>
-      <c r="C69" s="132"/>
-      <c r="D69" s="132"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="131"/>
-      <c r="I69" s="69"/>
-      <c r="J69" s="69"/>
-      <c r="K69" s="69"/>
+      <c r="C69" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D69" s="147" t="s">
+        <v>123</v>
+      </c>
+      <c r="E69" s="145"/>
+      <c r="F69" s="146">
+        <v>40</v>
+      </c>
+      <c r="G69" s="146"/>
+      <c r="H69" s="148"/>
+      <c r="I69" s="146">
+        <v>40</v>
+      </c>
+      <c r="J69" s="146">
+        <v>40</v>
+      </c>
+      <c r="K69" s="146">
+        <v>80</v>
+      </c>
       <c r="L69" s="122">
-        <f t="shared" ref="L69:L100" si="81">SUM(E69:K69)/40</f>
-        <v>0</v>
+        <f t="shared" ref="L69:L100" si="80">SUM(E69:K69)/40</f>
+        <v>5</v>
       </c>
       <c r="M69" s="33">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N69" s="43">
         <f t="shared" si="79"/>
@@ -7576,11 +7611,11 @@
       </c>
       <c r="O69" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P69" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q69" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7616,26 +7651,43 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A70" s="72"/>
-      <c r="B70" s="41">
+      <c r="A70" s="143">
+        <v>46283</v>
+      </c>
+      <c r="B70" s="144">
         <v>66</v>
       </c>
-      <c r="C70" s="132"/>
-      <c r="D70" s="132"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="69"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="131"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="69"/>
-      <c r="K70" s="69"/>
+      <c r="C70" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D70" s="147" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="145"/>
+      <c r="F70" s="146">
+        <v>40</v>
+      </c>
+      <c r="G70" s="146">
+        <v>40</v>
+      </c>
+      <c r="H70" s="148">
+        <v>120</v>
+      </c>
+      <c r="I70" s="146">
+        <v>200</v>
+      </c>
+      <c r="J70" s="146">
+        <v>80</v>
+      </c>
+      <c r="K70" s="146">
+        <v>40</v>
+      </c>
       <c r="L70" s="122">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <f t="shared" si="80"/>
+        <v>13</v>
       </c>
       <c r="M70" s="33">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N70" s="43">
         <f t="shared" si="79"/>
@@ -7643,11 +7695,11 @@
       </c>
       <c r="O70" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P70" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7683,26 +7735,43 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A71" s="72"/>
-      <c r="B71" s="41">
+      <c r="A71" s="143">
+        <v>46283</v>
+      </c>
+      <c r="B71" s="144">
         <v>67</v>
       </c>
-      <c r="C71" s="132"/>
-      <c r="D71" s="132"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="69"/>
-      <c r="G71" s="69"/>
-      <c r="H71" s="131"/>
-      <c r="I71" s="69"/>
-      <c r="J71" s="69"/>
-      <c r="K71" s="69"/>
+      <c r="C71" s="147" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" s="147" t="s">
+        <v>104</v>
+      </c>
+      <c r="E71" s="145"/>
+      <c r="F71" s="146">
+        <v>40</v>
+      </c>
+      <c r="G71" s="146">
+        <v>80</v>
+      </c>
+      <c r="H71" s="148">
+        <v>120</v>
+      </c>
+      <c r="I71" s="146">
+        <v>200</v>
+      </c>
+      <c r="J71" s="146">
+        <v>160</v>
+      </c>
+      <c r="K71" s="146">
+        <v>200</v>
+      </c>
       <c r="L71" s="122">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <f t="shared" si="80"/>
+        <v>20</v>
       </c>
       <c r="M71" s="33">
-        <f t="shared" ref="M71:M102" si="82">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N71" s="43">
         <f t="shared" si="79"/>
@@ -7710,11 +7779,11 @@
       </c>
       <c r="O71" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P71" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q71" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7750,25 +7819,41 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A72" s="72"/>
-      <c r="B72" s="41">
+      <c r="A72" s="143">
+        <v>46283</v>
+      </c>
+      <c r="B72" s="144">
         <v>68</v>
       </c>
-      <c r="C72" s="132"/>
-      <c r="D72" s="132"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="131"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="69"/>
-      <c r="K72" s="69"/>
+      <c r="C72" s="147" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" s="147"/>
+      <c r="E72" s="145"/>
+      <c r="F72" s="146">
+        <v>13</v>
+      </c>
+      <c r="G72" s="146">
+        <v>13</v>
+      </c>
+      <c r="H72" s="148">
+        <v>14</v>
+      </c>
+      <c r="I72" s="146">
+        <v>13</v>
+      </c>
+      <c r="J72" s="146">
+        <v>13</v>
+      </c>
+      <c r="K72" s="146">
+        <v>14</v>
+      </c>
       <c r="L72" s="122">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <f t="shared" si="80"/>
+        <v>2</v>
       </c>
       <c r="M72" s="33">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="M72:M102" si="81">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N72" s="43">
@@ -7777,11 +7862,11 @@
       </c>
       <c r="O72" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P72" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7831,11 +7916,11 @@
       <c r="J73" s="69"/>
       <c r="K73" s="69"/>
       <c r="L73" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N73" s="43">
@@ -7898,11 +7983,11 @@
       <c r="J74" s="69"/>
       <c r="K74" s="69"/>
       <c r="L74" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N74" s="43">
@@ -7965,11 +8050,11 @@
       <c r="J75" s="69"/>
       <c r="K75" s="69"/>
       <c r="L75" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N75" s="43">
@@ -8032,11 +8117,11 @@
       <c r="J76" s="69"/>
       <c r="K76" s="69"/>
       <c r="L76" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N76" s="43">
@@ -8099,11 +8184,11 @@
       <c r="J77" s="69"/>
       <c r="K77" s="69"/>
       <c r="L77" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N77" s="43">
@@ -8166,11 +8251,11 @@
       <c r="J78" s="44"/>
       <c r="K78" s="44"/>
       <c r="L78" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N78" s="43">
@@ -8233,11 +8318,11 @@
       <c r="J79" s="44"/>
       <c r="K79" s="44"/>
       <c r="L79" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M79" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N79" s="43">
@@ -8300,11 +8385,11 @@
       <c r="J80" s="44"/>
       <c r="K80" s="44"/>
       <c r="L80" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N80" s="43">
@@ -8312,11 +8397,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O80" s="67">
-        <f t="shared" ref="O80:O84" si="83">SUM(F80:H80)/20</f>
+        <f t="shared" ref="O80:O84" si="82">SUM(F80:H80)/20</f>
         <v>0</v>
       </c>
       <c r="P80" s="34">
-        <f t="shared" ref="P80:P84" si="84">SUM(I80:K80)/20</f>
+        <f t="shared" ref="P80:P84" si="83">SUM(I80:K80)/20</f>
         <v>0</v>
       </c>
       <c r="Q80" s="45" t="e">
@@ -8332,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="47" t="e">
-        <f t="shared" ref="T80:T84" si="85">SUM(Q80:S80)</f>
+        <f t="shared" ref="T80:T84" si="84">SUM(Q80:S80)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U80" s="48" t="e">
@@ -8340,15 +8425,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="49">
-        <f t="shared" ref="V80:V84" si="86">SUM(F80:H80)*$V$3</f>
+        <f t="shared" ref="V80:V84" si="85">SUM(F80:H80)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W80" s="49">
-        <f t="shared" ref="W80:W84" si="87">SUM(I80:K80)*$W$3</f>
+        <f t="shared" ref="W80:W84" si="86">SUM(I80:K80)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X80" s="50" t="e">
-        <f t="shared" ref="X80:X84" si="88">SUM(U80:W80)</f>
+        <f t="shared" ref="X80:X84" si="87">SUM(U80:W80)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8367,11 +8452,11 @@
       <c r="J81" s="44"/>
       <c r="K81" s="44"/>
       <c r="L81" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M81" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N81" s="43">
@@ -8379,11 +8464,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O81" s="67">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="P81" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="P81" s="34">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q81" s="45" t="e">
@@ -8399,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="47" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="U81" s="48" t="e">
@@ -8407,15 +8492,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V81" s="49">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="W81" s="49">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="W81" s="49">
+      <c r="X81" s="50" t="e">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="X81" s="50" t="e">
-        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8434,11 +8519,11 @@
       <c r="J82" s="44"/>
       <c r="K82" s="44"/>
       <c r="L82" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N82" s="43">
@@ -8446,11 +8531,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O82" s="67">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="P82" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="P82" s="34">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q82" s="45" t="e">
@@ -8466,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="T82" s="47" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="U82" s="48" t="e">
@@ -8474,15 +8559,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V82" s="49">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="W82" s="49">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="W82" s="49">
+      <c r="X82" s="50" t="e">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="X82" s="50" t="e">
-        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8501,11 +8586,11 @@
       <c r="J83" s="44"/>
       <c r="K83" s="44"/>
       <c r="L83" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M83" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N83" s="43">
@@ -8513,11 +8598,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O83" s="67">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="P83" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="P83" s="34">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q83" s="45" t="e">
@@ -8533,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="47" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="U83" s="48" t="e">
@@ -8541,15 +8626,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="49">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="W83" s="49">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="W83" s="49">
+      <c r="X83" s="50" t="e">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="X83" s="50" t="e">
-        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8568,11 +8653,11 @@
       <c r="J84" s="44"/>
       <c r="K84" s="44"/>
       <c r="L84" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M84" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N84" s="43">
@@ -8580,11 +8665,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O84" s="67">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="P84" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="P84" s="34">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="Q84" s="45" t="e">
@@ -8600,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="T84" s="47" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
       <c r="U84" s="48" t="e">
@@ -8608,15 +8693,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="49">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="W84" s="49">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="W84" s="49">
+      <c r="X84" s="50" t="e">
         <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="X84" s="50" t="e">
-        <f t="shared" si="88"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8635,11 +8720,11 @@
       <c r="J85" s="44"/>
       <c r="K85" s="44"/>
       <c r="L85" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N85" s="43">
@@ -8647,11 +8732,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O85" s="67">
-        <f t="shared" ref="O85:O132" si="89">SUM(F85:H85)/20</f>
+        <f t="shared" ref="O85:O132" si="88">SUM(F85:H85)/20</f>
         <v>0</v>
       </c>
       <c r="P85" s="34">
-        <f t="shared" ref="P85:P132" si="90">SUM(I85:K85)/20</f>
+        <f t="shared" ref="P85:P132" si="89">SUM(I85:K85)/20</f>
         <v>0</v>
       </c>
       <c r="Q85" s="45" t="e">
@@ -8667,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="47" t="e">
-        <f t="shared" ref="T85:T132" si="91">SUM(Q85:S85)</f>
+        <f t="shared" ref="T85:T132" si="90">SUM(Q85:S85)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U85" s="48" t="e">
@@ -8675,15 +8760,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V85" s="49">
-        <f t="shared" ref="V85:V132" si="92">SUM(F85:H85)*$V$3</f>
+        <f t="shared" ref="V85:V132" si="91">SUM(F85:H85)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W85" s="49">
-        <f t="shared" ref="W85:W132" si="93">SUM(I85:K85)*$W$3</f>
+        <f t="shared" ref="W85:W132" si="92">SUM(I85:K85)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X85" s="50" t="e">
-        <f t="shared" ref="X85:X132" si="94">SUM(U85:W85)</f>
+        <f t="shared" ref="X85:X132" si="93">SUM(U85:W85)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8702,11 +8787,11 @@
       <c r="J86" s="44"/>
       <c r="K86" s="44"/>
       <c r="L86" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M86" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N86" s="43">
@@ -8714,11 +8799,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O86" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P86" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P86" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q86" s="45" t="e">
@@ -8734,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U86" s="48" t="e">
@@ -8742,15 +8827,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V86" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W86" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W86" s="49">
+      <c r="X86" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X86" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8769,11 +8854,11 @@
       <c r="J87" s="44"/>
       <c r="K87" s="44"/>
       <c r="L87" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M87" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N87" s="43">
@@ -8781,11 +8866,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O87" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P87" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P87" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q87" s="45" t="e">
@@ -8801,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U87" s="48" t="e">
@@ -8809,15 +8894,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V87" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W87" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W87" s="49">
+      <c r="X87" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X87" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8836,11 +8921,11 @@
       <c r="J88" s="44"/>
       <c r="K88" s="44"/>
       <c r="L88" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M88" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N88" s="43">
@@ -8848,11 +8933,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O88" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P88" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P88" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q88" s="45" t="e">
@@ -8868,7 +8953,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U88" s="48" t="e">
@@ -8876,15 +8961,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V88" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W88" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W88" s="49">
+      <c r="X88" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X88" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8903,11 +8988,11 @@
       <c r="J89" s="44"/>
       <c r="K89" s="44"/>
       <c r="L89" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M89" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N89" s="43">
@@ -8915,11 +9000,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O89" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P89" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P89" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q89" s="45" t="e">
@@ -8935,7 +9020,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U89" s="48" t="e">
@@ -8943,15 +9028,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V89" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W89" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W89" s="49">
+      <c r="X89" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X89" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8970,11 +9055,11 @@
       <c r="J90" s="44"/>
       <c r="K90" s="44"/>
       <c r="L90" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N90" s="43">
@@ -8982,11 +9067,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O90" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P90" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P90" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q90" s="45" t="e">
@@ -9002,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U90" s="48" t="e">
@@ -9010,15 +9095,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V90" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W90" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W90" s="49">
+      <c r="X90" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X90" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9037,11 +9122,11 @@
       <c r="J91" s="44"/>
       <c r="K91" s="44"/>
       <c r="L91" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M91" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N91" s="43">
@@ -9049,11 +9134,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O91" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P91" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P91" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q91" s="45" t="e">
@@ -9069,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U91" s="48" t="e">
@@ -9077,15 +9162,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V91" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W91" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W91" s="49">
+      <c r="X91" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X91" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9104,11 +9189,11 @@
       <c r="J92" s="44"/>
       <c r="K92" s="44"/>
       <c r="L92" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M92" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N92" s="43">
@@ -9116,11 +9201,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O92" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P92" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P92" s="34">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="Q92" s="45" t="e">
@@ -9136,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
       <c r="U92" s="48" t="e">
@@ -9144,15 +9229,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V92" s="49">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="W92" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W92" s="49">
+      <c r="X92" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X92" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9171,11 +9256,11 @@
       <c r="J93" s="44"/>
       <c r="K93" s="44"/>
       <c r="L93" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M93" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N93" s="43">
@@ -9183,15 +9268,15 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O93" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P93" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P93" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q93" s="45" t="e">
-        <f t="shared" ref="Q93:Q124" si="95">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" ref="Q93:Q124" si="94">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R93" s="46">
@@ -9203,23 +9288,23 @@
         <v>0</v>
       </c>
       <c r="T93" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U93" s="48" t="e">
+        <f t="shared" ref="U93:U124" si="95">SUM(E93:E93)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V93" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U93" s="48" t="e">
-        <f t="shared" ref="U93:U124" si="96">SUM(E93:E93)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V93" s="49">
+        <v>0</v>
+      </c>
+      <c r="W93" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W93" s="49">
+      <c r="X93" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X93" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9238,11 +9323,11 @@
       <c r="J94" s="44"/>
       <c r="K94" s="44"/>
       <c r="L94" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N94" s="43">
@@ -9250,15 +9335,15 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O94" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P94" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P94" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q94" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R94" s="46">
@@ -9270,23 +9355,23 @@
         <v>0</v>
       </c>
       <c r="T94" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U94" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V94" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U94" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V94" s="49">
+        <v>0</v>
+      </c>
+      <c r="W94" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W94" s="49">
+      <c r="X94" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X94" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9305,11 +9390,11 @@
       <c r="J95" s="44"/>
       <c r="K95" s="44"/>
       <c r="L95" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N95" s="43">
@@ -9317,15 +9402,15 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O95" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P95" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P95" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q95" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R95" s="46">
@@ -9337,23 +9422,23 @@
         <v>0</v>
       </c>
       <c r="T95" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U95" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V95" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U95" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V95" s="49">
+        <v>0</v>
+      </c>
+      <c r="W95" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W95" s="49">
+      <c r="X95" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X95" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9372,11 +9457,11 @@
       <c r="J96" s="44"/>
       <c r="K96" s="44"/>
       <c r="L96" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N96" s="43">
@@ -9384,15 +9469,15 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O96" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P96" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P96" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q96" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R96" s="46">
@@ -9404,23 +9489,23 @@
         <v>0</v>
       </c>
       <c r="T96" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U96" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V96" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U96" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V96" s="49">
+        <v>0</v>
+      </c>
+      <c r="W96" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W96" s="49">
+      <c r="X96" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X96" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9439,11 +9524,11 @@
       <c r="J97" s="44"/>
       <c r="K97" s="44"/>
       <c r="L97" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M97" s="33">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="33">
-        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="N97" s="43">
@@ -9451,15 +9536,15 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O97" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P97" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P97" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q97" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R97" s="46">
@@ -9471,23 +9556,23 @@
         <v>0</v>
       </c>
       <c r="T97" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U97" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V97" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U97" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V97" s="49">
+        <v>0</v>
+      </c>
+      <c r="W97" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W97" s="49">
+      <c r="X97" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X97" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9506,27 +9591,27 @@
       <c r="J98" s="44"/>
       <c r="K98" s="44"/>
       <c r="L98" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="33">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="M98" s="33">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
       <c r="N98" s="43">
-        <f t="shared" ref="N98:N133" si="97">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
+        <f t="shared" ref="N98:N133" si="96">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>9.2011000000000003</v>
       </c>
       <c r="O98" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P98" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P98" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q98" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R98" s="46">
@@ -9538,23 +9623,23 @@
         <v>0</v>
       </c>
       <c r="T98" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U98" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V98" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U98" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V98" s="49">
+        <v>0</v>
+      </c>
+      <c r="W98" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W98" s="49">
+      <c r="X98" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X98" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9573,27 +9658,27 @@
       <c r="J99" s="44"/>
       <c r="K99" s="44"/>
       <c r="L99" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="33">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="M99" s="33">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
       <c r="N99" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O99" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P99" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P99" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q99" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R99" s="46">
@@ -9605,23 +9690,23 @@
         <v>0</v>
       </c>
       <c r="T99" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U99" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V99" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U99" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V99" s="49">
+        <v>0</v>
+      </c>
+      <c r="W99" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W99" s="49">
+      <c r="X99" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X99" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9640,27 +9725,27 @@
       <c r="J100" s="44"/>
       <c r="K100" s="44"/>
       <c r="L100" s="122">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="33">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="M100" s="33">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
       <c r="N100" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O100" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P100" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P100" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q100" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R100" s="46">
@@ -9672,23 +9757,23 @@
         <v>0</v>
       </c>
       <c r="T100" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U100" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V100" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U100" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V100" s="49">
+        <v>0</v>
+      </c>
+      <c r="W100" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W100" s="49">
+      <c r="X100" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X100" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9707,27 +9792,27 @@
       <c r="J101" s="44"/>
       <c r="K101" s="44"/>
       <c r="L101" s="122">
-        <f t="shared" ref="L101:L132" si="98">SUM(E101:K101)/40</f>
+        <f t="shared" ref="L101:L132" si="97">SUM(E101:K101)/40</f>
         <v>0</v>
       </c>
       <c r="M101" s="33">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N101" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O101" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P101" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P101" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q101" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R101" s="46">
@@ -9739,23 +9824,23 @@
         <v>0</v>
       </c>
       <c r="T101" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U101" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V101" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U101" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V101" s="49">
+        <v>0</v>
+      </c>
+      <c r="W101" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W101" s="49">
+      <c r="X101" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X101" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9774,27 +9859,27 @@
       <c r="J102" s="44"/>
       <c r="K102" s="44"/>
       <c r="L102" s="122">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M102" s="33">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N102" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O102" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P102" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P102" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q102" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R102" s="46">
@@ -9806,23 +9891,23 @@
         <v>0</v>
       </c>
       <c r="T102" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U102" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V102" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U102" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V102" s="49">
+        <v>0</v>
+      </c>
+      <c r="W102" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W102" s="49">
+      <c r="X102" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X102" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9841,27 +9926,27 @@
       <c r="J103" s="44"/>
       <c r="K103" s="44"/>
       <c r="L103" s="122">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M103" s="33">
-        <f t="shared" ref="M103:M133" si="99">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M103:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N103" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O103" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P103" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P103" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q103" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R103" s="46">
@@ -9873,23 +9958,23 @@
         <v>0</v>
       </c>
       <c r="T103" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U103" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V103" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U103" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V103" s="49">
+        <v>0</v>
+      </c>
+      <c r="W103" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W103" s="49">
+      <c r="X103" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X103" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9908,27 +9993,27 @@
       <c r="J104" s="44"/>
       <c r="K104" s="44"/>
       <c r="L104" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M104" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N104" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O104" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P104" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P104" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q104" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R104" s="46">
@@ -9940,23 +10025,23 @@
         <v>0</v>
       </c>
       <c r="T104" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U104" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V104" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U104" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V104" s="49">
+        <v>0</v>
+      </c>
+      <c r="W104" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W104" s="49">
+      <c r="X104" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X104" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9975,27 +10060,27 @@
       <c r="J105" s="44"/>
       <c r="K105" s="44"/>
       <c r="L105" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M105" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N105" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O105" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P105" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P105" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q105" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R105" s="46">
@@ -10007,23 +10092,23 @@
         <v>0</v>
       </c>
       <c r="T105" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U105" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V105" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U105" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V105" s="49">
+        <v>0</v>
+      </c>
+      <c r="W105" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W105" s="49">
+      <c r="X105" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X105" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10042,27 +10127,27 @@
       <c r="J106" s="44"/>
       <c r="K106" s="44"/>
       <c r="L106" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M106" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N106" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O106" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P106" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P106" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q106" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R106" s="46">
@@ -10074,23 +10159,23 @@
         <v>0</v>
       </c>
       <c r="T106" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U106" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V106" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U106" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V106" s="49">
+        <v>0</v>
+      </c>
+      <c r="W106" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W106" s="49">
+      <c r="X106" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X106" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10109,27 +10194,27 @@
       <c r="J107" s="44"/>
       <c r="K107" s="44"/>
       <c r="L107" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M107" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N107" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O107" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P107" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P107" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q107" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R107" s="46">
@@ -10141,23 +10226,23 @@
         <v>0</v>
       </c>
       <c r="T107" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U107" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V107" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U107" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V107" s="49">
+        <v>0</v>
+      </c>
+      <c r="W107" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W107" s="49">
+      <c r="X107" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X107" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10176,27 +10261,27 @@
       <c r="J108" s="44"/>
       <c r="K108" s="44"/>
       <c r="L108" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M108" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N108" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O108" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P108" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P108" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q108" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R108" s="46">
@@ -10208,23 +10293,23 @@
         <v>0</v>
       </c>
       <c r="T108" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U108" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V108" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U108" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V108" s="49">
+        <v>0</v>
+      </c>
+      <c r="W108" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W108" s="49">
+      <c r="X108" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X108" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10243,27 +10328,27 @@
       <c r="J109" s="44"/>
       <c r="K109" s="44"/>
       <c r="L109" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M109" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N109" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O109" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P109" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P109" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q109" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R109" s="46">
@@ -10275,23 +10360,23 @@
         <v>0</v>
       </c>
       <c r="T109" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U109" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V109" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U109" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V109" s="49">
+        <v>0</v>
+      </c>
+      <c r="W109" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W109" s="49">
+      <c r="X109" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X109" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10310,27 +10395,27 @@
       <c r="J110" s="44"/>
       <c r="K110" s="44"/>
       <c r="L110" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M110" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N110" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O110" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P110" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q110" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R110" s="46">
@@ -10342,23 +10427,23 @@
         <v>0</v>
       </c>
       <c r="T110" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U110" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V110" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U110" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V110" s="49">
+        <v>0</v>
+      </c>
+      <c r="W110" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W110" s="49">
+      <c r="X110" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X110" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10377,27 +10462,27 @@
       <c r="J111" s="44"/>
       <c r="K111" s="44"/>
       <c r="L111" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M111" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M111" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N111" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O111" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P111" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P111" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q111" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R111" s="46">
@@ -10409,23 +10494,23 @@
         <v>0</v>
       </c>
       <c r="T111" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U111" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V111" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U111" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V111" s="49">
+        <v>0</v>
+      </c>
+      <c r="W111" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W111" s="49">
+      <c r="X111" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X111" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10444,27 +10529,27 @@
       <c r="J112" s="44"/>
       <c r="K112" s="44"/>
       <c r="L112" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M112" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M112" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N112" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O112" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P112" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P112" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q112" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R112" s="46">
@@ -10476,23 +10561,23 @@
         <v>0</v>
       </c>
       <c r="T112" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U112" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V112" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U112" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V112" s="49">
+        <v>0</v>
+      </c>
+      <c r="W112" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W112" s="49">
+      <c r="X112" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X112" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10511,27 +10596,27 @@
       <c r="J113" s="44"/>
       <c r="K113" s="44"/>
       <c r="L113" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M113" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M113" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N113" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O113" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P113" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P113" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q113" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R113" s="46">
@@ -10543,23 +10628,23 @@
         <v>0</v>
       </c>
       <c r="T113" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U113" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V113" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U113" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V113" s="49">
+        <v>0</v>
+      </c>
+      <c r="W113" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W113" s="49">
+      <c r="X113" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X113" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10578,27 +10663,27 @@
       <c r="J114" s="44"/>
       <c r="K114" s="44"/>
       <c r="L114" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M114" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M114" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N114" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O114" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P114" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P114" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q114" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R114" s="46">
@@ -10610,23 +10695,23 @@
         <v>0</v>
       </c>
       <c r="T114" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U114" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V114" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U114" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V114" s="49">
+        <v>0</v>
+      </c>
+      <c r="W114" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W114" s="49">
+      <c r="X114" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X114" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10645,27 +10730,27 @@
       <c r="J115" s="44"/>
       <c r="K115" s="44"/>
       <c r="L115" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M115" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N115" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O115" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P115" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P115" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q115" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R115" s="46">
@@ -10677,23 +10762,23 @@
         <v>0</v>
       </c>
       <c r="T115" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U115" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V115" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U115" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V115" s="49">
+        <v>0</v>
+      </c>
+      <c r="W115" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W115" s="49">
+      <c r="X115" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X115" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10712,27 +10797,27 @@
       <c r="J116" s="44"/>
       <c r="K116" s="44"/>
       <c r="L116" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M116" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N116" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O116" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P116" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P116" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q116" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R116" s="46">
@@ -10744,23 +10829,23 @@
         <v>0</v>
       </c>
       <c r="T116" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U116" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V116" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U116" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V116" s="49">
+        <v>0</v>
+      </c>
+      <c r="W116" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W116" s="49">
+      <c r="X116" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X116" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10779,27 +10864,27 @@
       <c r="J117" s="44"/>
       <c r="K117" s="44"/>
       <c r="L117" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M117" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N117" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O117" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P117" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P117" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q117" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R117" s="46">
@@ -10811,23 +10896,23 @@
         <v>0</v>
       </c>
       <c r="T117" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U117" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V117" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U117" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V117" s="49">
+        <v>0</v>
+      </c>
+      <c r="W117" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W117" s="49">
+      <c r="X117" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X117" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10846,27 +10931,27 @@
       <c r="J118" s="44"/>
       <c r="K118" s="44"/>
       <c r="L118" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M118" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N118" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O118" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P118" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P118" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q118" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R118" s="46">
@@ -10878,23 +10963,23 @@
         <v>0</v>
       </c>
       <c r="T118" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U118" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V118" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U118" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V118" s="49">
+        <v>0</v>
+      </c>
+      <c r="W118" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W118" s="49">
+      <c r="X118" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X118" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10913,27 +10998,27 @@
       <c r="J119" s="44"/>
       <c r="K119" s="44"/>
       <c r="L119" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M119" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N119" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O119" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P119" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P119" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q119" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R119" s="46">
@@ -10945,23 +11030,23 @@
         <v>0</v>
       </c>
       <c r="T119" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U119" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V119" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U119" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V119" s="49">
+        <v>0</v>
+      </c>
+      <c r="W119" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W119" s="49">
+      <c r="X119" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X119" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10980,27 +11065,27 @@
       <c r="J120" s="44"/>
       <c r="K120" s="44"/>
       <c r="L120" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M120" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N120" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O120" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P120" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P120" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q120" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R120" s="46">
@@ -11012,23 +11097,23 @@
         <v>0</v>
       </c>
       <c r="T120" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U120" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V120" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U120" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V120" s="49">
+        <v>0</v>
+      </c>
+      <c r="W120" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W120" s="49">
+      <c r="X120" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X120" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11047,27 +11132,27 @@
       <c r="J121" s="44"/>
       <c r="K121" s="44"/>
       <c r="L121" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M121" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N121" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O121" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P121" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P121" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q121" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R121" s="46">
@@ -11079,23 +11164,23 @@
         <v>0</v>
       </c>
       <c r="T121" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U121" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V121" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U121" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V121" s="49">
+        <v>0</v>
+      </c>
+      <c r="W121" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W121" s="49">
+      <c r="X121" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X121" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11114,27 +11199,27 @@
       <c r="J122" s="44"/>
       <c r="K122" s="44"/>
       <c r="L122" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M122" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N122" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O122" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P122" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P122" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q122" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R122" s="46">
@@ -11146,23 +11231,23 @@
         <v>0</v>
       </c>
       <c r="T122" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U122" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V122" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U122" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V122" s="49">
+        <v>0</v>
+      </c>
+      <c r="W122" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W122" s="49">
+      <c r="X122" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X122" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11181,27 +11266,27 @@
       <c r="J123" s="44"/>
       <c r="K123" s="44"/>
       <c r="L123" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M123" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N123" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O123" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P123" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P123" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q123" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R123" s="46">
@@ -11213,23 +11298,23 @@
         <v>0</v>
       </c>
       <c r="T123" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U123" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V123" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U123" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V123" s="49">
+        <v>0</v>
+      </c>
+      <c r="W123" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W123" s="49">
+      <c r="X123" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X123" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11248,27 +11333,27 @@
       <c r="J124" s="44"/>
       <c r="K124" s="44"/>
       <c r="L124" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M124" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N124" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O124" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P124" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P124" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q124" s="45" t="e">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
       <c r="R124" s="46">
@@ -11280,23 +11365,23 @@
         <v>0</v>
       </c>
       <c r="T124" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U124" s="48" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V124" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U124" s="48" t="e">
-        <f t="shared" si="96"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V124" s="49">
+        <v>0</v>
+      </c>
+      <c r="W124" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W124" s="49">
+      <c r="X124" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X124" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11313,27 +11398,27 @@
       <c r="J125" s="44"/>
       <c r="K125" s="44"/>
       <c r="L125" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M125" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
       <c r="N125" s="43">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>9.2011000000000003</v>
       </c>
       <c r="O125" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P125" s="34">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="P125" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
       <c r="Q125" s="45" t="e">
-        <f t="shared" ref="Q125:Q133" si="100">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" ref="Q125:Q133" si="99">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R125" s="46">
@@ -11345,23 +11430,23 @@
         <v>0</v>
       </c>
       <c r="T125" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U125" s="48" t="e">
+        <f t="shared" ref="U125:U133" si="100">SUM(E125:E125)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V125" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U125" s="48" t="e">
-        <f t="shared" ref="U125:U133" si="101">SUM(E125:E125)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V125" s="49">
+        <v>0</v>
+      </c>
+      <c r="W125" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W125" s="49">
+      <c r="X125" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X125" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11378,27 +11463,27 @@
       <c r="J126" s="44"/>
       <c r="K126" s="44"/>
       <c r="L126" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M126" s="33">
+      <c r="N126" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O126" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P126" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q126" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N126" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O126" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P126" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q126" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R126" s="46">
@@ -11410,23 +11495,23 @@
         <v>0</v>
       </c>
       <c r="T126" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U126" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V126" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U126" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V126" s="49">
+        <v>0</v>
+      </c>
+      <c r="W126" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W126" s="49">
+      <c r="X126" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X126" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11443,27 +11528,27 @@
       <c r="J127" s="44"/>
       <c r="K127" s="44"/>
       <c r="L127" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M127" s="33">
+      <c r="N127" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O127" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P127" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N127" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O127" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P127" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q127" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R127" s="46">
@@ -11475,23 +11560,23 @@
         <v>0</v>
       </c>
       <c r="T127" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U127" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V127" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U127" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V127" s="49">
+        <v>0</v>
+      </c>
+      <c r="W127" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W127" s="49">
+      <c r="X127" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X127" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11508,27 +11593,27 @@
       <c r="J128" s="44"/>
       <c r="K128" s="44"/>
       <c r="L128" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M128" s="33">
+      <c r="N128" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O128" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P128" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q128" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N128" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O128" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P128" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q128" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R128" s="46">
@@ -11540,23 +11625,23 @@
         <v>0</v>
       </c>
       <c r="T128" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U128" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V128" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U128" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V128" s="49">
+        <v>0</v>
+      </c>
+      <c r="W128" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W128" s="49">
+      <c r="X128" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X128" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11573,27 +11658,27 @@
       <c r="J129" s="44"/>
       <c r="K129" s="44"/>
       <c r="L129" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M129" s="33">
+      <c r="N129" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O129" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P129" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q129" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N129" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O129" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P129" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q129" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R129" s="46">
@@ -11605,23 +11690,23 @@
         <v>0</v>
       </c>
       <c r="T129" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U129" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V129" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U129" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V129" s="49">
+        <v>0</v>
+      </c>
+      <c r="W129" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W129" s="49">
+      <c r="X129" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X129" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11638,27 +11723,27 @@
       <c r="J130" s="44"/>
       <c r="K130" s="44"/>
       <c r="L130" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M130" s="33">
+      <c r="N130" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O130" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P130" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q130" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N130" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O130" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P130" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q130" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R130" s="46">
@@ -11670,23 +11755,23 @@
         <v>0</v>
       </c>
       <c r="T130" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U130" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V130" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U130" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V130" s="49">
+        <v>0</v>
+      </c>
+      <c r="W130" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W130" s="49">
+      <c r="X130" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X130" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11703,27 +11788,27 @@
       <c r="J131" s="44"/>
       <c r="K131" s="44"/>
       <c r="L131" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M131" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M131" s="33">
+      <c r="N131" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O131" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P131" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q131" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N131" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O131" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P131" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q131" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R131" s="46">
@@ -11735,23 +11820,23 @@
         <v>0</v>
       </c>
       <c r="T131" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U131" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V131" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U131" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V131" s="49">
+        <v>0</v>
+      </c>
+      <c r="W131" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W131" s="49">
+      <c r="X131" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X131" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11768,27 +11853,27 @@
       <c r="J132" s="44"/>
       <c r="K132" s="44"/>
       <c r="L132" s="122">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="M132" s="33">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="M132" s="33">
+      <c r="N132" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O132" s="67">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="P132" s="34">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q132" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N132" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O132" s="67">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="P132" s="34">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="Q132" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R132" s="46">
@@ -11800,83 +11885,83 @@
         <v>0</v>
       </c>
       <c r="T132" s="47" t="e">
+        <f t="shared" si="90"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U132" s="48" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V132" s="49">
         <f t="shared" si="91"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U132" s="48" t="e">
-        <f t="shared" si="101"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V132" s="49">
+        <v>0</v>
+      </c>
+      <c r="W132" s="49">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="W132" s="49">
+      <c r="X132" s="50" t="e">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="X132" s="50" t="e">
-        <f t="shared" si="94"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="161" t="s">
+      <c r="B133" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="162"/>
+      <c r="C133" s="160"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
-        <f t="shared" ref="E133:K133" si="102">SUM(E6:E61)</f>
+        <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
         <v>2265</v>
       </c>
       <c r="F133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>3118</v>
       </c>
       <c r="G133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>3290</v>
       </c>
       <c r="H133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>4730</v>
       </c>
       <c r="I133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>4955</v>
       </c>
       <c r="J133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>5537</v>
       </c>
       <c r="K133" s="78">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>7540</v>
       </c>
       <c r="L133" s="42">
-        <f t="shared" ref="L133" si="103">SUM(E133:K133)/40</f>
+        <f t="shared" ref="L133" si="102">SUM(E133:K133)/40</f>
         <v>785.875</v>
       </c>
       <c r="M133" s="33">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="N133" s="43">
+        <f t="shared" si="96"/>
+        <v>9.2011000000000003</v>
+      </c>
+      <c r="O133" s="67">
+        <f t="shared" ref="O133:O137" si="103">SUM(F133:H133)/20</f>
+        <v>556.9</v>
+      </c>
+      <c r="P133" s="34">
+        <f t="shared" ref="P133:P137" si="104">SUM(I133:K133)/20</f>
+        <v>901.6</v>
+      </c>
+      <c r="Q133" s="45" t="e">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N133" s="43">
-        <f t="shared" si="97"/>
-        <v>9.2011000000000003</v>
-      </c>
-      <c r="O133" s="67">
-        <f t="shared" ref="O133:O137" si="104">SUM(F133:H133)/20</f>
-        <v>556.9</v>
-      </c>
-      <c r="P133" s="34">
-        <f t="shared" ref="P133:P137" si="105">SUM(I133:K133)/20</f>
-        <v>901.6</v>
-      </c>
-      <c r="Q133" s="45" t="e">
-        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R133" s="46">
@@ -11892,15 +11977,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="U133" s="48" t="e">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="V133" s="49">
-        <f t="shared" ref="V133:V137" si="106">SUM(F133:H133)*$V$3</f>
+        <f t="shared" ref="V133:V137" si="105">SUM(F133:H133)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W133" s="49">
-        <f t="shared" ref="W133:W137" si="107">SUM(I133:K133)*$W$3</f>
+        <f t="shared" ref="W133:W137" si="106">SUM(I133:K133)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X133" s="50" t="e">
@@ -11970,11 +12055,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O135" s="67">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="P135" s="34">
         <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="P135" s="34">
-        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="Q135" s="45" t="e">
@@ -11998,11 +12083,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="49">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="W135" s="49">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="W135" s="49">
-        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="X135" s="50" t="e">
@@ -12038,11 +12123,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O136" s="67">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="P136" s="34">
         <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="P136" s="34">
-        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="Q136" s="45" t="e">
@@ -12066,11 +12151,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V136" s="49">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="W136" s="49">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="W136" s="49">
-        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="X136" s="50" t="e">
@@ -12079,37 +12164,37 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="174" t="s">
+      <c r="B137" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="175"/>
+      <c r="C137" s="173"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
         <v>0</v>
       </c>
       <c r="F137" s="77">
-        <f t="shared" ref="F137:K137" si="108">SUM(F135:F136)</f>
+        <f t="shared" ref="F137:K137" si="107">SUM(F135:F136)</f>
         <v>0</v>
       </c>
       <c r="G137" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="H137" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="I137" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="J137" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="K137" s="77">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="L137" s="106">
@@ -12125,11 +12210,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O137" s="67">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="P137" s="34">
         <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="P137" s="34">
-        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="Q137" s="45" t="e">
@@ -12153,11 +12238,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V137" s="49">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="W137" s="49">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="W137" s="49">
-        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="X137" s="50" t="e">
@@ -12166,37 +12251,37 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="163" t="s">
+      <c r="B138" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="164"/>
+      <c r="C138" s="162"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
         <v>2265</v>
       </c>
       <c r="F138" s="79">
-        <f t="shared" ref="F138:K138" si="109">SUM(F133,F137)</f>
+        <f t="shared" ref="F138:K138" si="108">SUM(F133,F137)</f>
         <v>3118</v>
       </c>
       <c r="G138" s="79">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>3290</v>
       </c>
       <c r="H138" s="79">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>4730</v>
       </c>
       <c r="I138" s="79">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>4955</v>
       </c>
       <c r="J138" s="79">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>5537</v>
       </c>
       <c r="K138" s="79">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>7540</v>
       </c>
       <c r="L138" s="54">
@@ -12205,50 +12290,50 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>890</v>
+        <v>940</v>
       </c>
       <c r="N138" s="55">
-        <f t="shared" ref="N138:X138" si="110">SUM(N5:N137)</f>
+        <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
         <v>947.71329999999978</v>
       </c>
       <c r="O138" s="56">
-        <f t="shared" si="110"/>
-        <v>1419.5</v>
+        <f t="shared" si="109"/>
+        <v>1453.5</v>
       </c>
       <c r="P138" s="58">
-        <f t="shared" si="110"/>
-        <v>2183.1</v>
+        <f t="shared" si="109"/>
+        <v>2249.1</v>
       </c>
       <c r="Q138" s="59" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="R138" s="60">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="S138" s="60">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="T138" s="61" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="U138" s="62" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="V138" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="W138" s="63">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="X138" s="64" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -12300,25 +12385,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="182" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="183"/>
-      <c r="K3" s="184" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="184"/>
-      <c r="O3" s="184"/>
-      <c r="P3" s="184"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -12364,24 +12449,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>678</v>
+        <v>700</v>
       </c>
       <c r="E5" s="73">
-        <v>1030</v>
+        <v>1080</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1808</v>
+        <v>1880</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8192</v>
+        <v>-8120</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -12405,11 +12490,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>27120</v>
+        <v>28000</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>41200</v>
+        <v>43200</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -12417,7 +12502,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>72320</v>
+        <v>75200</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -12425,7 +12510,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-327680</v>
+        <v>-324800</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -12553,11 +12638,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-678</v>
+        <v>-700</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1030</v>
+        <v>-1080</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -12641,14 +12726,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="181"/>
-      <c r="F11" s="181" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="181"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12700,7 +12785,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6008</v>
+        <v>6080</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12752,12 +12837,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>240320</v>
-      </c>
-      <c r="S13" s="176" t="s">
+        <v>243200</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="176"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12846,13 +12931,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="177" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="177"/>
-      <c r="F20" s="177"/>
-      <c r="G20" s="177"/>
-      <c r="H20" s="177"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443D2E77-2F78-422F-954C-A581D6B0C291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74CFDE6-CD8C-4423-8218-0FBF04D1B735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="189">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -580,6 +580,15 @@
   </si>
   <si>
     <t xml:space="preserve">Qamar Ijaz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen SB Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadbagh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Rafaqat Sons </t>
   </si>
 </sst>
 </file>
@@ -1475,7 +1484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1857,6 +1866,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1988,6 +2000,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5682</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{112B31BC-3A79-501B-2D38-5173E97C6ADE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="598237" y="374317"/>
+          <a:ext cx="754313" cy="755315"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2498,13 +2565,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="150">
         <f ca="1">TODAY()</f>
-        <v>46283</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46286</v>
+      </c>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2526,10 +2593,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="151" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2559,13 +2626,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166" t="s">
+      <c r="L2" s="164"/>
+      <c r="M2" s="165"/>
+      <c r="N2" s="166"/>
+      <c r="O2" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="167"/>
+      <c r="P2" s="168"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2584,8 +2651,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="172"/>
+      <c r="B3" s="152"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2613,29 +2680,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="170"/>
+      <c r="M3" s="170"/>
+      <c r="N3" s="171"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="155"/>
+      <c r="S3" s="155"/>
+      <c r="T3" s="156"/>
+      <c r="U3" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="159"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="172"/>
+      <c r="B4" s="153"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -7489,35 +7556,35 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A68" s="143">
+      <c r="A68" s="72">
         <v>46283</v>
       </c>
-      <c r="B68" s="144">
+      <c r="B68" s="41">
         <v>64</v>
       </c>
-      <c r="C68" s="147" t="s">
+      <c r="C68" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D68" s="147" t="s">
+      <c r="D68" s="132" t="s">
         <v>184</v>
       </c>
-      <c r="E68" s="145"/>
-      <c r="F68" s="146">
-        <v>40</v>
-      </c>
-      <c r="G68" s="146">
+      <c r="E68" s="44"/>
+      <c r="F68" s="69">
+        <v>40</v>
+      </c>
+      <c r="G68" s="69">
         <v>80</v>
       </c>
-      <c r="H68" s="148">
-        <v>40</v>
-      </c>
-      <c r="I68" s="146">
+      <c r="H68" s="131">
+        <v>40</v>
+      </c>
+      <c r="I68" s="69">
         <v>120</v>
       </c>
-      <c r="J68" s="146">
+      <c r="J68" s="69">
         <v>120</v>
       </c>
-      <c r="K68" s="146"/>
+      <c r="K68" s="69"/>
       <c r="L68" s="122">
         <f t="shared" si="66"/>
         <v>10</v>
@@ -7571,31 +7638,31 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A69" s="143">
+      <c r="A69" s="72">
         <v>46283</v>
       </c>
-      <c r="B69" s="144">
+      <c r="B69" s="41">
         <v>65</v>
       </c>
-      <c r="C69" s="147" t="s">
+      <c r="C69" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D69" s="147" t="s">
+      <c r="D69" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="E69" s="145"/>
-      <c r="F69" s="146">
-        <v>40</v>
-      </c>
-      <c r="G69" s="146"/>
-      <c r="H69" s="148"/>
-      <c r="I69" s="146">
-        <v>40</v>
-      </c>
-      <c r="J69" s="146">
-        <v>40</v>
-      </c>
-      <c r="K69" s="146">
+      <c r="E69" s="44"/>
+      <c r="F69" s="69">
+        <v>40</v>
+      </c>
+      <c r="G69" s="69"/>
+      <c r="H69" s="131"/>
+      <c r="I69" s="69">
+        <v>40</v>
+      </c>
+      <c r="J69" s="69">
+        <v>40</v>
+      </c>
+      <c r="K69" s="69">
         <v>80</v>
       </c>
       <c r="L69" s="122">
@@ -7651,35 +7718,35 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A70" s="143">
+      <c r="A70" s="72">
         <v>46283</v>
       </c>
-      <c r="B70" s="144">
+      <c r="B70" s="41">
         <v>66</v>
       </c>
-      <c r="C70" s="147" t="s">
+      <c r="C70" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D70" s="147" t="s">
+      <c r="D70" s="132" t="s">
         <v>121</v>
       </c>
-      <c r="E70" s="145"/>
-      <c r="F70" s="146">
-        <v>40</v>
-      </c>
-      <c r="G70" s="146">
-        <v>40</v>
-      </c>
-      <c r="H70" s="148">
+      <c r="E70" s="44"/>
+      <c r="F70" s="69">
+        <v>40</v>
+      </c>
+      <c r="G70" s="69">
+        <v>40</v>
+      </c>
+      <c r="H70" s="131">
         <v>120</v>
       </c>
-      <c r="I70" s="146">
+      <c r="I70" s="69">
         <v>200</v>
       </c>
-      <c r="J70" s="146">
+      <c r="J70" s="69">
         <v>80</v>
       </c>
-      <c r="K70" s="146">
+      <c r="K70" s="69">
         <v>40</v>
       </c>
       <c r="L70" s="122">
@@ -7735,35 +7802,35 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A71" s="143">
+      <c r="A71" s="72">
         <v>46283</v>
       </c>
-      <c r="B71" s="144">
+      <c r="B71" s="41">
         <v>67</v>
       </c>
-      <c r="C71" s="147" t="s">
+      <c r="C71" s="132" t="s">
         <v>103</v>
       </c>
-      <c r="D71" s="147" t="s">
+      <c r="D71" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="E71" s="145"/>
-      <c r="F71" s="146">
-        <v>40</v>
-      </c>
-      <c r="G71" s="146">
+      <c r="E71" s="44"/>
+      <c r="F71" s="69">
+        <v>40</v>
+      </c>
+      <c r="G71" s="69">
         <v>80</v>
       </c>
-      <c r="H71" s="148">
+      <c r="H71" s="131">
         <v>120</v>
       </c>
-      <c r="I71" s="146">
+      <c r="I71" s="69">
         <v>200</v>
       </c>
-      <c r="J71" s="146">
+      <c r="J71" s="69">
         <v>160</v>
       </c>
-      <c r="K71" s="146">
+      <c r="K71" s="69">
         <v>200</v>
       </c>
       <c r="L71" s="122">
@@ -7819,33 +7886,33 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A72" s="143">
+      <c r="A72" s="72">
         <v>46283</v>
       </c>
-      <c r="B72" s="144">
+      <c r="B72" s="41">
         <v>68</v>
       </c>
-      <c r="C72" s="147" t="s">
+      <c r="C72" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="147"/>
-      <c r="E72" s="145"/>
-      <c r="F72" s="146">
+      <c r="D72" s="132"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="69">
         <v>13</v>
       </c>
-      <c r="G72" s="146">
+      <c r="G72" s="69">
         <v>13</v>
       </c>
-      <c r="H72" s="148">
+      <c r="H72" s="131">
         <v>14</v>
       </c>
-      <c r="I72" s="146">
+      <c r="I72" s="69">
         <v>13</v>
       </c>
-      <c r="J72" s="146">
+      <c r="J72" s="69">
         <v>13</v>
       </c>
-      <c r="K72" s="146">
+      <c r="K72" s="69">
         <v>14</v>
       </c>
       <c r="L72" s="122">
@@ -7902,26 +7969,43 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A73" s="72"/>
-      <c r="B73" s="41">
+      <c r="A73" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B73" s="144">
         <v>69</v>
       </c>
-      <c r="C73" s="132"/>
-      <c r="D73" s="132"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="69"/>
-      <c r="G73" s="69"/>
-      <c r="H73" s="131"/>
-      <c r="I73" s="69"/>
-      <c r="J73" s="69"/>
-      <c r="K73" s="69"/>
+      <c r="C73" s="147" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="147" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="145"/>
+      <c r="F73" s="146">
+        <v>40</v>
+      </c>
+      <c r="G73" s="146">
+        <v>40</v>
+      </c>
+      <c r="H73" s="148">
+        <v>40</v>
+      </c>
+      <c r="I73" s="146">
+        <v>40</v>
+      </c>
+      <c r="J73" s="146">
+        <v>40</v>
+      </c>
+      <c r="K73" s="146">
+        <v>40</v>
+      </c>
       <c r="L73" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M73" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N73" s="43">
         <f t="shared" si="79"/>
@@ -7929,11 +8013,11 @@
       </c>
       <c r="O73" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P73" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q73" s="45" t="e">
         <f t="shared" si="71"/>
@@ -7969,26 +8053,43 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A74" s="72"/>
-      <c r="B74" s="41">
+      <c r="A74" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B74" s="144">
         <v>70</v>
       </c>
-      <c r="C74" s="132"/>
-      <c r="D74" s="132"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="69"/>
-      <c r="G74" s="69"/>
-      <c r="H74" s="131"/>
-      <c r="I74" s="69"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="69"/>
+      <c r="C74" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D74" s="147" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="145"/>
+      <c r="F74" s="146">
+        <v>80</v>
+      </c>
+      <c r="G74" s="146">
+        <v>120</v>
+      </c>
+      <c r="H74" s="148">
+        <v>160</v>
+      </c>
+      <c r="I74" s="146">
+        <v>160</v>
+      </c>
+      <c r="J74" s="146">
+        <v>40</v>
+      </c>
+      <c r="K74" s="146">
+        <v>400</v>
+      </c>
       <c r="L74" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M74" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N74" s="43">
         <f t="shared" si="79"/>
@@ -7996,11 +8097,11 @@
       </c>
       <c r="O74" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P74" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q74" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8036,26 +8137,43 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A75" s="72"/>
-      <c r="B75" s="41">
+      <c r="A75" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B75" s="144">
         <v>71</v>
       </c>
-      <c r="C75" s="132"/>
-      <c r="D75" s="132"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="69"/>
-      <c r="G75" s="69"/>
-      <c r="H75" s="131"/>
-      <c r="I75" s="69"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="69"/>
+      <c r="C75" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="147" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="145"/>
+      <c r="F75" s="146">
+        <v>40</v>
+      </c>
+      <c r="G75" s="146">
+        <v>40</v>
+      </c>
+      <c r="H75" s="148">
+        <v>200</v>
+      </c>
+      <c r="I75" s="146">
+        <v>80</v>
+      </c>
+      <c r="J75" s="146">
+        <v>200</v>
+      </c>
+      <c r="K75" s="146">
+        <v>360</v>
+      </c>
       <c r="L75" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M75" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N75" s="43">
         <f t="shared" si="79"/>
@@ -8063,11 +8181,11 @@
       </c>
       <c r="O75" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P75" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q75" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8103,26 +8221,41 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A76" s="72"/>
-      <c r="B76" s="41">
+      <c r="A76" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B76" s="144">
         <v>72</v>
       </c>
-      <c r="C76" s="132"/>
-      <c r="D76" s="132"/>
-      <c r="E76" s="44"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="69"/>
-      <c r="H76" s="131"/>
-      <c r="I76" s="69"/>
-      <c r="J76" s="69"/>
-      <c r="K76" s="69"/>
+      <c r="C76" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D76" s="147" t="s">
+        <v>117</v>
+      </c>
+      <c r="E76" s="145"/>
+      <c r="F76" s="146"/>
+      <c r="G76" s="146">
+        <v>40</v>
+      </c>
+      <c r="H76" s="148">
+        <v>80</v>
+      </c>
+      <c r="I76" s="146">
+        <v>40</v>
+      </c>
+      <c r="J76" s="146">
+        <v>40</v>
+      </c>
+      <c r="K76" s="146">
+        <v>40</v>
+      </c>
       <c r="L76" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M76" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N76" s="43">
         <f t="shared" si="79"/>
@@ -8130,11 +8263,11 @@
       </c>
       <c r="O76" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P76" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q76" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8170,26 +8303,41 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A77" s="72"/>
-      <c r="B77" s="41">
+      <c r="A77" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B77" s="144">
         <v>73</v>
       </c>
-      <c r="C77" s="132"/>
-      <c r="D77" s="132"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="69"/>
-      <c r="H77" s="131"/>
-      <c r="I77" s="69"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69"/>
+      <c r="C77" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D77" s="147" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="145"/>
+      <c r="F77" s="146">
+        <v>40</v>
+      </c>
+      <c r="G77" s="146"/>
+      <c r="H77" s="148">
+        <v>40</v>
+      </c>
+      <c r="I77" s="146">
+        <v>40</v>
+      </c>
+      <c r="J77" s="146">
+        <v>40</v>
+      </c>
+      <c r="K77" s="146">
+        <v>80</v>
+      </c>
       <c r="L77" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M77" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N77" s="43">
         <f t="shared" si="79"/>
@@ -8197,11 +8345,11 @@
       </c>
       <c r="O77" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P77" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q77" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8237,22 +8385,32 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A78" s="72"/>
-      <c r="B78" s="41">
+      <c r="A78" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B78" s="144">
         <v>74</v>
       </c>
-      <c r="C78" s="132"/>
-      <c r="D78" s="132"/>
-      <c r="E78" s="44"/>
-      <c r="F78" s="44"/>
-      <c r="G78" s="44"/>
-      <c r="H78" s="122"/>
-      <c r="I78" s="44"/>
-      <c r="J78" s="44"/>
-      <c r="K78" s="44"/>
+      <c r="C78" s="147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D78" s="147" t="s">
+        <v>116</v>
+      </c>
+      <c r="E78" s="145"/>
+      <c r="F78" s="145"/>
+      <c r="G78" s="145"/>
+      <c r="H78" s="149">
+        <v>40</v>
+      </c>
+      <c r="I78" s="145"/>
+      <c r="J78" s="145"/>
+      <c r="K78" s="145">
+        <v>40</v>
+      </c>
       <c r="L78" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="33">
         <f t="shared" si="81"/>
@@ -8264,11 +8422,11 @@
       </c>
       <c r="O78" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P78" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8304,26 +8462,37 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A79" s="72"/>
-      <c r="B79" s="41">
+      <c r="A79" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B79" s="144">
         <v>75</v>
       </c>
-      <c r="C79" s="132"/>
-      <c r="D79" s="132"/>
-      <c r="E79" s="44"/>
-      <c r="F79" s="44"/>
-      <c r="G79" s="44"/>
-      <c r="H79" s="122"/>
-      <c r="I79" s="44"/>
-      <c r="J79" s="44"/>
-      <c r="K79" s="44"/>
+      <c r="C79" s="147" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79" s="147" t="s">
+        <v>187</v>
+      </c>
+      <c r="E79" s="145"/>
+      <c r="F79" s="145"/>
+      <c r="G79" s="145">
+        <v>40</v>
+      </c>
+      <c r="H79" s="149"/>
+      <c r="I79" s="145"/>
+      <c r="J79" s="145">
+        <v>80</v>
+      </c>
+      <c r="K79" s="145">
+        <v>80</v>
+      </c>
       <c r="L79" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M79" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N79" s="43">
         <f t="shared" si="79"/>
@@ -8331,11 +8500,11 @@
       </c>
       <c r="O79" s="67">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P79" s="34">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q79" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8371,22 +8540,36 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A80" s="72"/>
-      <c r="B80" s="41">
+      <c r="A80" s="143">
+        <v>46284</v>
+      </c>
+      <c r="B80" s="144">
         <v>76</v>
       </c>
-      <c r="C80" s="132"/>
-      <c r="D80" s="132"/>
-      <c r="E80" s="44"/>
-      <c r="F80" s="44"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="122"/>
-      <c r="I80" s="44"/>
-      <c r="J80" s="44"/>
-      <c r="K80" s="44"/>
+      <c r="C80" s="147" t="s">
+        <v>188</v>
+      </c>
+      <c r="D80" s="147" t="s">
+        <v>99</v>
+      </c>
+      <c r="E80" s="145"/>
+      <c r="F80" s="145"/>
+      <c r="G80" s="145">
+        <v>80</v>
+      </c>
+      <c r="H80" s="149">
+        <v>80</v>
+      </c>
+      <c r="I80" s="145">
+        <v>40</v>
+      </c>
+      <c r="J80" s="145"/>
+      <c r="K80" s="145">
+        <v>80</v>
+      </c>
       <c r="L80" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M80" s="33">
         <f t="shared" si="81"/>
@@ -8398,11 +8581,11 @@
       </c>
       <c r="O80" s="67">
         <f t="shared" ref="O80:O84" si="82">SUM(F80:H80)/20</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P80" s="34">
         <f t="shared" ref="P80:P84" si="83">SUM(I80:K80)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q80" s="45" t="e">
         <f t="shared" si="71"/>
@@ -11907,10 +12090,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="159" t="s">
+      <c r="B133" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="160"/>
+      <c r="C133" s="161"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -12164,10 +12347,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="172" t="s">
+      <c r="B137" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="173"/>
+      <c r="C137" s="174"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -12251,10 +12434,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="161" t="s">
+      <c r="B138" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="162"/>
+      <c r="C138" s="163"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -12290,7 +12473,7 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>940</v>
+        <v>1025</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
@@ -12298,11 +12481,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>1453.5</v>
+        <v>1513.5</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>2249.1</v>
+        <v>2347.1</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -12385,25 +12568,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="177" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="181" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="182"/>
+      <c r="K3" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="183"/>
+      <c r="P3" s="183"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -12449,24 +12632,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="E5" s="73">
-        <v>1080</v>
+        <v>1159</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1880</v>
+        <v>1979</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8120</v>
+        <v>-8021</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -12490,11 +12673,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>28000</v>
+        <v>28800</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>43200</v>
+        <v>46360</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -12502,7 +12685,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>75200</v>
+        <v>79160</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -12510,7 +12693,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-324800</v>
+        <v>-320840</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -12638,11 +12821,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-700</v>
+        <v>-720</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1080</v>
+        <v>-1159</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -12726,14 +12909,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="180" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="180"/>
+      <c r="F11" s="180" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="180"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12785,7 +12968,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6080</v>
+        <v>6179</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -12837,12 +13020,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>243200</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>247160</v>
+      </c>
+      <c r="S13" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="175"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12931,13 +13114,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="176" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="176"/>
+      <c r="F20" s="176"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="176"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13163,5 +13346,6 @@
     <mergeCell ref="K3:P3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74CFDE6-CD8C-4423-8218-0FBF04D1B735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608F3B7D-E699-429E-A3E9-C84FE7B93C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1871,6 +1871,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1905,45 +1944,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2565,13 +2565,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="150">
+      <c r="B1" s="163">
         <f ca="1">TODAY()</f>
-        <v>46286</v>
-      </c>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
+        <v>46287</v>
+      </c>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2593,10 +2593,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="164" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2626,13 +2626,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="164"/>
-      <c r="M2" s="165"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="167" t="s">
+      <c r="L2" s="152"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="168"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2651,8 +2651,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="172"/>
-      <c r="B3" s="152"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="165"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2680,29 +2680,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="169" t="s">
+      <c r="L3" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="170"/>
-      <c r="N3" s="171"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="154" t="s">
+      <c r="Q3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="156"/>
-      <c r="U3" s="157" t="s">
+      <c r="R3" s="168"/>
+      <c r="S3" s="168"/>
+      <c r="T3" s="169"/>
+      <c r="U3" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="158"/>
-      <c r="W3" s="158"/>
-      <c r="X3" s="159"/>
+      <c r="V3" s="171"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="172"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="172"/>
-      <c r="B4" s="153"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="166"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -12090,10 +12090,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="160" t="s">
+      <c r="B133" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="161"/>
+      <c r="C133" s="174"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -12347,10 +12347,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="173" t="s">
+      <c r="B137" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="174"/>
+      <c r="C137" s="162"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -12434,10 +12434,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="162" t="s">
+      <c r="B138" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="163"/>
+      <c r="C138" s="151"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -12522,17 +12522,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12658,11 +12658,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>14570</v>
+        <v>10638</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>364.25</v>
+        <v>265.95</v>
       </c>
       <c r="O5" s="75"/>
       <c r="P5" s="142"/>
@@ -12702,11 +12702,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>10551</v>
+        <v>6966</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>263.77499999999998</v>
+        <v>174.15</v>
       </c>
       <c r="O6" s="75"/>
       <c r="P6" s="142"/>
@@ -12737,11 +12737,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>8643</v>
+        <v>3042</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>216.07499999999999</v>
+        <v>76.05</v>
       </c>
       <c r="O7" s="75"/>
       <c r="P7" s="142"/>
@@ -12781,11 +12781,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>10038</v>
+        <v>3339</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>250.95</v>
+        <v>83.474999999999994</v>
       </c>
       <c r="O8" s="75">
         <v>50</v>
@@ -12834,11 +12834,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>9254</v>
+        <v>4356</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>231.35</v>
+        <v>108.9</v>
       </c>
       <c r="O9" s="75">
         <v>23</v>
@@ -12878,11 +12878,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>15938</v>
+        <v>7854</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>398.45</v>
+        <v>196.35</v>
       </c>
       <c r="O10" s="75"/>
       <c r="P10" s="142"/>
@@ -12923,12 +12923,10 @@
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5">
-        <v>1839</v>
-      </c>
+      <c r="M11" s="5"/>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>45.975000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" s="75">
         <v>125</v>
@@ -12976,11 +12974,11 @@
       <c r="L12" s="75"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>70833</v>
+        <v>36195</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>1770.8249999999998</v>
+        <v>904.875</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -13079,7 +13077,7 @@
       <c r="N17" s="115"/>
       <c r="O17" s="116">
         <f>N17-M5</f>
-        <v>-14570</v>
+        <v>-10638</v>
       </c>
     </row>
     <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13093,7 +13091,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="116">
         <f>N18-M6</f>
-        <v>-10551</v>
+        <v>-6966</v>
       </c>
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13110,7 +13108,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="116">
         <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>-8643</v>
+        <v>-3042</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13131,7 +13129,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="116">
         <f t="shared" si="4"/>
-        <v>-10038</v>
+        <v>-3339</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13160,7 +13158,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="116">
         <f t="shared" si="4"/>
-        <v>-9254</v>
+        <v>-4356</v>
       </c>
     </row>
     <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13186,7 +13184,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="116">
         <f t="shared" si="4"/>
-        <v>-15938</v>
+        <v>-7854</v>
       </c>
     </row>
     <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13212,7 +13210,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="116">
         <f t="shared" si="4"/>
-        <v>-1839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13242,7 +13240,7 @@
       </c>
       <c r="O24" s="111">
         <f>SUM(O17:O23)</f>
-        <v>-70833</v>
+        <v>-36195</v>
       </c>
     </row>
     <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13272,7 +13270,7 @@
       </c>
       <c r="O25" s="111">
         <f>O24/40</f>
-        <v>-1770.825</v>
+        <v>-904.875</v>
       </c>
     </row>
     <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608F3B7D-E699-429E-A3E9-C84FE7B93C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0D15A2-A2ED-44CB-B35F-84BF77F7270A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="205">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -589,6 +589,54 @@
   </si>
   <si>
     <t xml:space="preserve">Risen Rafaqat Sons </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Rehmat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatri Chowk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sana Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>Canal Avenue</t>
+  </si>
+  <si>
+    <t>Shehwar Mega Mart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jublee Town </t>
+  </si>
+  <si>
+    <t>Muredky</t>
+  </si>
+  <si>
+    <t>Lutaf Mega Mart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranger Head Quarter </t>
+  </si>
+  <si>
+    <t>Umer Super Maket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Induction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punjab Society </t>
+  </si>
+  <si>
+    <t>Askari Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naqshbandi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweera </t>
   </si>
 </sst>
 </file>
@@ -1484,7 +1532,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1860,7 +1908,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1868,7 +1915,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1972,6 +2019,17 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2565,13 +2623,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="163">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
-      </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
+        <v>46288</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2593,10 +2651,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2626,13 +2684,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="152"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="156"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2651,8 +2709,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="160"/>
-      <c r="B3" s="165"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2680,29 +2738,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="157" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="158"/>
-      <c r="N3" s="159"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="167" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="168"/>
-      <c r="S3" s="168"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="170" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="171"/>
-      <c r="W3" s="171"/>
-      <c r="X3" s="172"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="160"/>
-      <c r="B4" s="166"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -7969,40 +8027,40 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A73" s="143">
+      <c r="A73" s="72">
         <v>46284</v>
       </c>
-      <c r="B73" s="144">
+      <c r="B73" s="41">
         <v>69</v>
       </c>
-      <c r="C73" s="147" t="s">
+      <c r="C73" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="D73" s="147" t="s">
+      <c r="D73" s="132" t="s">
         <v>126</v>
       </c>
-      <c r="E73" s="145"/>
-      <c r="F73" s="146">
-        <v>40</v>
-      </c>
-      <c r="G73" s="146">
-        <v>40</v>
-      </c>
-      <c r="H73" s="148">
-        <v>40</v>
-      </c>
-      <c r="I73" s="146">
-        <v>40</v>
-      </c>
-      <c r="J73" s="146">
-        <v>40</v>
-      </c>
-      <c r="K73" s="146">
+      <c r="E73" s="44"/>
+      <c r="F73" s="69">
+        <v>40</v>
+      </c>
+      <c r="G73" s="69">
+        <v>39</v>
+      </c>
+      <c r="H73" s="131">
+        <v>40</v>
+      </c>
+      <c r="I73" s="69">
+        <v>40</v>
+      </c>
+      <c r="J73" s="69">
+        <v>40</v>
+      </c>
+      <c r="K73" s="69">
         <v>40</v>
       </c>
       <c r="L73" s="122">
         <f t="shared" si="80"/>
-        <v>6</v>
+        <v>5.9749999999999996</v>
       </c>
       <c r="M73" s="33">
         <v>15</v>
@@ -8013,7 +8071,7 @@
       </c>
       <c r="O73" s="67">
         <f t="shared" si="73"/>
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="P73" s="34">
         <f t="shared" si="74"/>
@@ -8053,35 +8111,35 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A74" s="143">
+      <c r="A74" s="72">
         <v>46284</v>
       </c>
-      <c r="B74" s="144">
+      <c r="B74" s="41">
         <v>70</v>
       </c>
-      <c r="C74" s="147" t="s">
+      <c r="C74" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D74" s="147" t="s">
+      <c r="D74" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="E74" s="145"/>
-      <c r="F74" s="146">
+      <c r="E74" s="44"/>
+      <c r="F74" s="69">
         <v>80</v>
       </c>
-      <c r="G74" s="146">
+      <c r="G74" s="69">
         <v>120</v>
       </c>
-      <c r="H74" s="148">
+      <c r="H74" s="131">
         <v>160</v>
       </c>
-      <c r="I74" s="146">
+      <c r="I74" s="69">
         <v>160</v>
       </c>
-      <c r="J74" s="146">
-        <v>40</v>
-      </c>
-      <c r="K74" s="146">
+      <c r="J74" s="69">
+        <v>40</v>
+      </c>
+      <c r="K74" s="69">
         <v>400</v>
       </c>
       <c r="L74" s="122">
@@ -8137,35 +8195,35 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A75" s="143">
+      <c r="A75" s="72">
         <v>46284</v>
       </c>
-      <c r="B75" s="144">
+      <c r="B75" s="41">
         <v>71</v>
       </c>
-      <c r="C75" s="147" t="s">
+      <c r="C75" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D75" s="147" t="s">
+      <c r="D75" s="132" t="s">
         <v>115</v>
       </c>
-      <c r="E75" s="145"/>
-      <c r="F75" s="146">
-        <v>40</v>
-      </c>
-      <c r="G75" s="146">
-        <v>40</v>
-      </c>
-      <c r="H75" s="148">
+      <c r="E75" s="69"/>
+      <c r="F75" s="69">
+        <v>40</v>
+      </c>
+      <c r="G75" s="69">
+        <v>40</v>
+      </c>
+      <c r="H75" s="131">
         <v>200</v>
       </c>
-      <c r="I75" s="146">
+      <c r="I75" s="69">
         <v>80</v>
       </c>
-      <c r="J75" s="146">
+      <c r="J75" s="69">
         <v>200</v>
       </c>
-      <c r="K75" s="146">
+      <c r="K75" s="69">
         <v>360</v>
       </c>
       <c r="L75" s="122">
@@ -8221,33 +8279,33 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A76" s="143">
+      <c r="A76" s="72">
         <v>46284</v>
       </c>
-      <c r="B76" s="144">
+      <c r="B76" s="41">
         <v>72</v>
       </c>
-      <c r="C76" s="147" t="s">
+      <c r="C76" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="147" t="s">
+      <c r="D76" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="145"/>
-      <c r="F76" s="146"/>
-      <c r="G76" s="146">
-        <v>40</v>
-      </c>
-      <c r="H76" s="148">
+      <c r="E76" s="69"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="69">
+        <v>40</v>
+      </c>
+      <c r="H76" s="131">
         <v>80</v>
       </c>
-      <c r="I76" s="146">
-        <v>40</v>
-      </c>
-      <c r="J76" s="146">
-        <v>40</v>
-      </c>
-      <c r="K76" s="146">
+      <c r="I76" s="69">
+        <v>40</v>
+      </c>
+      <c r="J76" s="69">
+        <v>40</v>
+      </c>
+      <c r="K76" s="69">
         <v>40</v>
       </c>
       <c r="L76" s="122">
@@ -8303,33 +8361,33 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A77" s="143">
+      <c r="A77" s="72">
         <v>46284</v>
       </c>
-      <c r="B77" s="144">
+      <c r="B77" s="41">
         <v>73</v>
       </c>
-      <c r="C77" s="147" t="s">
+      <c r="C77" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D77" s="147" t="s">
+      <c r="D77" s="132" t="s">
         <v>141</v>
       </c>
-      <c r="E77" s="145"/>
-      <c r="F77" s="146">
-        <v>40</v>
-      </c>
-      <c r="G77" s="146"/>
-      <c r="H77" s="148">
-        <v>40</v>
-      </c>
-      <c r="I77" s="146">
-        <v>40</v>
-      </c>
-      <c r="J77" s="146">
-        <v>40</v>
-      </c>
-      <c r="K77" s="146">
+      <c r="E77" s="69"/>
+      <c r="F77" s="69">
+        <v>40</v>
+      </c>
+      <c r="G77" s="69"/>
+      <c r="H77" s="131">
+        <v>40</v>
+      </c>
+      <c r="I77" s="69">
+        <v>40</v>
+      </c>
+      <c r="J77" s="69">
+        <v>40</v>
+      </c>
+      <c r="K77" s="69">
         <v>80</v>
       </c>
       <c r="L77" s="122">
@@ -8385,27 +8443,27 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A78" s="143">
+      <c r="A78" s="72">
         <v>46284</v>
       </c>
-      <c r="B78" s="144">
+      <c r="B78" s="41">
         <v>74</v>
       </c>
-      <c r="C78" s="147" t="s">
+      <c r="C78" s="132" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="147" t="s">
+      <c r="D78" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="E78" s="145"/>
-      <c r="F78" s="145"/>
-      <c r="G78" s="145"/>
-      <c r="H78" s="149">
-        <v>40</v>
-      </c>
-      <c r="I78" s="145"/>
-      <c r="J78" s="145"/>
-      <c r="K78" s="145">
+      <c r="E78" s="69"/>
+      <c r="F78" s="69"/>
+      <c r="G78" s="69"/>
+      <c r="H78" s="131">
+        <v>40</v>
+      </c>
+      <c r="I78" s="69"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="69">
         <v>40</v>
       </c>
       <c r="L78" s="122">
@@ -8413,8 +8471,7 @@
         <v>2</v>
       </c>
       <c r="M78" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N78" s="43">
         <f t="shared" si="79"/>
@@ -8462,29 +8519,29 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A79" s="143">
+      <c r="A79" s="72">
         <v>46284</v>
       </c>
-      <c r="B79" s="144">
+      <c r="B79" s="41">
         <v>75</v>
       </c>
-      <c r="C79" s="147" t="s">
+      <c r="C79" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="D79" s="147" t="s">
+      <c r="D79" s="132" t="s">
         <v>187</v>
       </c>
-      <c r="E79" s="145"/>
-      <c r="F79" s="145"/>
-      <c r="G79" s="145">
-        <v>40</v>
-      </c>
-      <c r="H79" s="149"/>
-      <c r="I79" s="145"/>
-      <c r="J79" s="145">
+      <c r="E79" s="69"/>
+      <c r="F79" s="69"/>
+      <c r="G79" s="69">
+        <v>40</v>
+      </c>
+      <c r="H79" s="131"/>
+      <c r="I79" s="69"/>
+      <c r="J79" s="69">
         <v>80</v>
       </c>
-      <c r="K79" s="145">
+      <c r="K79" s="69">
         <v>80</v>
       </c>
       <c r="L79" s="122">
@@ -8540,31 +8597,31 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A80" s="143">
+      <c r="A80" s="72">
         <v>46284</v>
       </c>
-      <c r="B80" s="144">
+      <c r="B80" s="41">
         <v>76</v>
       </c>
-      <c r="C80" s="147" t="s">
+      <c r="C80" s="132" t="s">
         <v>188</v>
       </c>
-      <c r="D80" s="147" t="s">
+      <c r="D80" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="E80" s="145"/>
-      <c r="F80" s="145"/>
-      <c r="G80" s="145">
+      <c r="E80" s="69"/>
+      <c r="F80" s="69"/>
+      <c r="G80" s="69">
         <v>80</v>
       </c>
-      <c r="H80" s="149">
+      <c r="H80" s="131">
         <v>80</v>
       </c>
-      <c r="I80" s="145">
-        <v>40</v>
-      </c>
-      <c r="J80" s="145"/>
-      <c r="K80" s="145">
+      <c r="I80" s="69">
+        <v>40</v>
+      </c>
+      <c r="J80" s="69"/>
+      <c r="K80" s="69">
         <v>80</v>
       </c>
       <c r="L80" s="122">
@@ -8572,8 +8629,7 @@
         <v>7</v>
       </c>
       <c r="M80" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N80" s="43">
         <f t="shared" si="79"/>
@@ -8621,26 +8677,37 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A81" s="72"/>
-      <c r="B81" s="41">
+      <c r="A81" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B81" s="184">
         <v>77</v>
       </c>
-      <c r="C81" s="132"/>
-      <c r="D81" s="132"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="44"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="122"/>
-      <c r="I81" s="44"/>
-      <c r="J81" s="44"/>
-      <c r="K81" s="44"/>
+      <c r="C81" s="185" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="185" t="s">
+        <v>116</v>
+      </c>
+      <c r="E81" s="186"/>
+      <c r="F81" s="186">
+        <v>40</v>
+      </c>
+      <c r="G81" s="186"/>
+      <c r="H81" s="187">
+        <v>27</v>
+      </c>
+      <c r="I81" s="186"/>
+      <c r="J81" s="186"/>
+      <c r="K81" s="186">
+        <v>40</v>
+      </c>
       <c r="L81" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>2.6749999999999998</v>
       </c>
       <c r="M81" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N81" s="43">
         <f t="shared" si="79"/>
@@ -8648,11 +8715,11 @@
       </c>
       <c r="O81" s="67">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P81" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8688,26 +8755,37 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A82" s="72"/>
-      <c r="B82" s="41">
+      <c r="A82" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B82" s="184">
         <v>78</v>
       </c>
-      <c r="C82" s="132"/>
-      <c r="D82" s="132"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="44"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="122"/>
-      <c r="I82" s="44"/>
-      <c r="J82" s="44"/>
-      <c r="K82" s="44"/>
+      <c r="C82" s="185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D82" s="185" t="s">
+        <v>117</v>
+      </c>
+      <c r="E82" s="186"/>
+      <c r="F82" s="186"/>
+      <c r="G82" s="186"/>
+      <c r="H82" s="187"/>
+      <c r="I82" s="186">
+        <v>120</v>
+      </c>
+      <c r="J82" s="186">
+        <v>120</v>
+      </c>
+      <c r="K82" s="186">
+        <v>120</v>
+      </c>
       <c r="L82" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M82" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N82" s="43">
         <f t="shared" si="79"/>
@@ -8719,7 +8797,7 @@
       </c>
       <c r="P82" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q82" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8755,26 +8833,37 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A83" s="72"/>
-      <c r="B83" s="41">
+      <c r="A83" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B83" s="184">
         <v>79</v>
       </c>
-      <c r="C83" s="132"/>
-      <c r="D83" s="132"/>
-      <c r="E83" s="44"/>
-      <c r="F83" s="44"/>
-      <c r="G83" s="44"/>
-      <c r="H83" s="122"/>
-      <c r="I83" s="44"/>
-      <c r="J83" s="44"/>
-      <c r="K83" s="44"/>
+      <c r="C83" s="185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D83" s="185" t="s">
+        <v>117</v>
+      </c>
+      <c r="E83" s="186"/>
+      <c r="F83" s="186"/>
+      <c r="G83" s="186"/>
+      <c r="H83" s="187"/>
+      <c r="I83" s="186">
+        <v>80</v>
+      </c>
+      <c r="J83" s="186">
+        <v>80</v>
+      </c>
+      <c r="K83" s="186">
+        <v>80</v>
+      </c>
       <c r="L83" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M83" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N83" s="43">
         <f t="shared" si="79"/>
@@ -8786,7 +8875,7 @@
       </c>
       <c r="P83" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q83" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8822,26 +8911,43 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A84" s="72"/>
-      <c r="B84" s="41">
+      <c r="A84" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B84" s="184">
         <v>80</v>
       </c>
-      <c r="C84" s="132"/>
-      <c r="D84" s="132"/>
-      <c r="E84" s="44"/>
-      <c r="F84" s="44"/>
-      <c r="G84" s="44"/>
-      <c r="H84" s="122"/>
-      <c r="I84" s="44"/>
-      <c r="J84" s="44"/>
-      <c r="K84" s="44"/>
+      <c r="C84" s="185" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="E84" s="186"/>
+      <c r="F84" s="186">
+        <v>800</v>
+      </c>
+      <c r="G84" s="186">
+        <v>800</v>
+      </c>
+      <c r="H84" s="187">
+        <v>800</v>
+      </c>
+      <c r="I84" s="186">
+        <v>800</v>
+      </c>
+      <c r="J84" s="186">
+        <v>800</v>
+      </c>
+      <c r="K84" s="186">
+        <v>800</v>
+      </c>
       <c r="L84" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M84" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N84" s="43">
         <f t="shared" si="79"/>
@@ -8849,11 +8955,11 @@
       </c>
       <c r="O84" s="67">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P84" s="34">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q84" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8889,26 +8995,43 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A85" s="72"/>
-      <c r="B85" s="41">
+      <c r="A85" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B85" s="184">
         <v>81</v>
       </c>
-      <c r="C85" s="132"/>
-      <c r="D85" s="132"/>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="122"/>
-      <c r="I85" s="44"/>
-      <c r="J85" s="44"/>
-      <c r="K85" s="44"/>
+      <c r="C85" s="185" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="185" t="s">
+        <v>117</v>
+      </c>
+      <c r="E85" s="186"/>
+      <c r="F85" s="186">
+        <v>80</v>
+      </c>
+      <c r="G85" s="186">
+        <v>80</v>
+      </c>
+      <c r="H85" s="187">
+        <v>200</v>
+      </c>
+      <c r="I85" s="186">
+        <v>80</v>
+      </c>
+      <c r="J85" s="186">
+        <v>80</v>
+      </c>
+      <c r="K85" s="186">
+        <v>200</v>
+      </c>
       <c r="L85" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M85" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N85" s="43">
         <f t="shared" si="79"/>
@@ -8916,11 +9039,11 @@
       </c>
       <c r="O85" s="67">
         <f t="shared" ref="O85:O132" si="88">SUM(F85:H85)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P85" s="34">
         <f t="shared" ref="P85:P132" si="89">SUM(I85:K85)/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q85" s="45" t="e">
         <f t="shared" si="71"/>
@@ -8956,26 +9079,43 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A86" s="72"/>
-      <c r="B86" s="41">
+      <c r="A86" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B86" s="184">
         <v>82</v>
       </c>
-      <c r="C86" s="132"/>
-      <c r="D86" s="132"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="44"/>
-      <c r="G86" s="44"/>
-      <c r="H86" s="122"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="44"/>
-      <c r="K86" s="44"/>
+      <c r="C86" s="185" t="s">
+        <v>192</v>
+      </c>
+      <c r="D86" s="185" t="s">
+        <v>193</v>
+      </c>
+      <c r="E86" s="186"/>
+      <c r="F86" s="186">
+        <v>40</v>
+      </c>
+      <c r="G86" s="186">
+        <v>40</v>
+      </c>
+      <c r="H86" s="187">
+        <v>40</v>
+      </c>
+      <c r="I86" s="186">
+        <v>40</v>
+      </c>
+      <c r="J86" s="186">
+        <v>40</v>
+      </c>
+      <c r="K86" s="186">
+        <v>40</v>
+      </c>
       <c r="L86" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M86" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N86" s="43">
         <f t="shared" si="79"/>
@@ -8983,11 +9123,11 @@
       </c>
       <c r="O86" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P86" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q86" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9023,26 +9163,43 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A87" s="72"/>
-      <c r="B87" s="41">
+      <c r="A87" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B87" s="184">
         <v>83</v>
       </c>
-      <c r="C87" s="132"/>
-      <c r="D87" s="132"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="44"/>
-      <c r="G87" s="44"/>
-      <c r="H87" s="122"/>
-      <c r="I87" s="44"/>
-      <c r="J87" s="44"/>
-      <c r="K87" s="44"/>
+      <c r="C87" s="185" t="s">
+        <v>194</v>
+      </c>
+      <c r="D87" s="185" t="s">
+        <v>195</v>
+      </c>
+      <c r="E87" s="186"/>
+      <c r="F87" s="186">
+        <v>120</v>
+      </c>
+      <c r="G87" s="186">
+        <v>160</v>
+      </c>
+      <c r="H87" s="187">
+        <v>240</v>
+      </c>
+      <c r="I87" s="186">
+        <v>160</v>
+      </c>
+      <c r="J87" s="186">
+        <v>120</v>
+      </c>
+      <c r="K87" s="186">
+        <v>400</v>
+      </c>
       <c r="L87" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M87" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N87" s="43">
         <f t="shared" si="79"/>
@@ -9050,11 +9207,11 @@
       </c>
       <c r="O87" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P87" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q87" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9090,26 +9247,43 @@
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A88" s="72"/>
-      <c r="B88" s="41">
+      <c r="A88" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B88" s="184">
         <v>84</v>
       </c>
-      <c r="C88" s="132"/>
-      <c r="D88" s="132"/>
-      <c r="E88" s="44"/>
-      <c r="F88" s="44"/>
-      <c r="G88" s="44"/>
-      <c r="H88" s="122"/>
-      <c r="I88" s="44"/>
-      <c r="J88" s="44"/>
-      <c r="K88" s="44"/>
+      <c r="C88" s="185" t="s">
+        <v>62</v>
+      </c>
+      <c r="D88" s="185" t="s">
+        <v>196</v>
+      </c>
+      <c r="E88" s="186"/>
+      <c r="F88" s="186">
+        <v>153</v>
+      </c>
+      <c r="G88" s="186">
+        <v>117</v>
+      </c>
+      <c r="H88" s="187">
+        <v>320</v>
+      </c>
+      <c r="I88" s="186">
+        <v>137</v>
+      </c>
+      <c r="J88" s="186">
+        <v>120</v>
+      </c>
+      <c r="K88" s="186">
+        <v>320</v>
+      </c>
       <c r="L88" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>29.175000000000001</v>
       </c>
       <c r="M88" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N88" s="43">
         <f t="shared" si="79"/>
@@ -9117,11 +9291,11 @@
       </c>
       <c r="O88" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="P88" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>28.85</v>
       </c>
       <c r="Q88" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9157,26 +9331,39 @@
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A89" s="72"/>
-      <c r="B89" s="41">
+      <c r="A89" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B89" s="184">
         <v>85</v>
       </c>
-      <c r="C89" s="132"/>
-      <c r="D89" s="132"/>
-      <c r="E89" s="44"/>
-      <c r="F89" s="44"/>
-      <c r="G89" s="44"/>
-      <c r="H89" s="122"/>
-      <c r="I89" s="44"/>
-      <c r="J89" s="44"/>
-      <c r="K89" s="44"/>
+      <c r="C89" s="185" t="s">
+        <v>197</v>
+      </c>
+      <c r="D89" s="185" t="s">
+        <v>198</v>
+      </c>
+      <c r="E89" s="186"/>
+      <c r="F89" s="186">
+        <v>80</v>
+      </c>
+      <c r="G89" s="186">
+        <v>80</v>
+      </c>
+      <c r="H89" s="187">
+        <v>80</v>
+      </c>
+      <c r="I89" s="186"/>
+      <c r="J89" s="186"/>
+      <c r="K89" s="186">
+        <v>320</v>
+      </c>
       <c r="L89" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M89" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N89" s="43">
         <f t="shared" si="79"/>
@@ -9184,11 +9371,11 @@
       </c>
       <c r="O89" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P89" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q89" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9224,26 +9411,43 @@
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A90" s="72"/>
-      <c r="B90" s="41">
+      <c r="A90" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B90" s="184">
         <v>86</v>
       </c>
-      <c r="C90" s="121"/>
-      <c r="D90" s="121"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="44"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="122"/>
-      <c r="I90" s="44"/>
-      <c r="J90" s="44"/>
-      <c r="K90" s="44"/>
+      <c r="C90" s="185" t="s">
+        <v>199</v>
+      </c>
+      <c r="D90" s="185" t="s">
+        <v>179</v>
+      </c>
+      <c r="E90" s="186"/>
+      <c r="F90" s="186">
+        <v>80</v>
+      </c>
+      <c r="G90" s="186">
+        <v>80</v>
+      </c>
+      <c r="H90" s="187">
+        <v>80</v>
+      </c>
+      <c r="I90" s="186">
+        <v>80</v>
+      </c>
+      <c r="J90" s="186">
+        <v>80</v>
+      </c>
+      <c r="K90" s="186">
+        <v>80</v>
+      </c>
       <c r="L90" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="M90" s="148">
+        <v>12.5</v>
       </c>
       <c r="N90" s="43">
         <f t="shared" si="79"/>
@@ -9251,11 +9455,11 @@
       </c>
       <c r="O90" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P90" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q90" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9291,26 +9495,43 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A91" s="72"/>
-      <c r="B91" s="41">
+      <c r="A91" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B91" s="184">
         <v>87</v>
       </c>
-      <c r="C91" s="121"/>
-      <c r="D91" s="121"/>
-      <c r="E91" s="44"/>
-      <c r="F91" s="44"/>
-      <c r="G91" s="44"/>
-      <c r="H91" s="122"/>
-      <c r="I91" s="44"/>
-      <c r="J91" s="44"/>
-      <c r="K91" s="44"/>
+      <c r="C91" s="185" t="s">
+        <v>199</v>
+      </c>
+      <c r="D91" s="185" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91" s="186"/>
+      <c r="F91" s="186">
+        <v>40</v>
+      </c>
+      <c r="G91" s="186">
+        <v>40</v>
+      </c>
+      <c r="H91" s="187">
+        <v>40</v>
+      </c>
+      <c r="I91" s="186">
+        <v>40</v>
+      </c>
+      <c r="J91" s="186">
+        <v>40</v>
+      </c>
+      <c r="K91" s="186">
+        <v>40</v>
+      </c>
       <c r="L91" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="M91" s="148">
+        <v>12.5</v>
       </c>
       <c r="N91" s="43">
         <f t="shared" si="79"/>
@@ -9318,11 +9539,11 @@
       </c>
       <c r="O91" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P91" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q91" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9358,26 +9579,43 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A92" s="72"/>
-      <c r="B92" s="41">
+      <c r="A92" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B92" s="184">
         <v>88</v>
       </c>
-      <c r="C92" s="121"/>
-      <c r="D92" s="121"/>
-      <c r="E92" s="44"/>
-      <c r="F92" s="44"/>
-      <c r="G92" s="44"/>
-      <c r="H92" s="122"/>
-      <c r="I92" s="44"/>
-      <c r="J92" s="44"/>
-      <c r="K92" s="44"/>
+      <c r="C92" s="185" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92" s="185" t="s">
+        <v>201</v>
+      </c>
+      <c r="E92" s="186"/>
+      <c r="F92" s="186">
+        <v>80</v>
+      </c>
+      <c r="G92" s="186">
+        <v>80</v>
+      </c>
+      <c r="H92" s="187">
+        <v>80</v>
+      </c>
+      <c r="I92" s="186">
+        <v>80</v>
+      </c>
+      <c r="J92" s="186">
+        <v>80</v>
+      </c>
+      <c r="K92" s="186">
+        <v>80</v>
+      </c>
       <c r="L92" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="M92" s="148">
+        <v>12.5</v>
       </c>
       <c r="N92" s="43">
         <f t="shared" si="79"/>
@@ -9385,11 +9623,11 @@
       </c>
       <c r="O92" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P92" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q92" s="45" t="e">
         <f t="shared" si="71"/>
@@ -9425,26 +9663,43 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A93" s="72"/>
-      <c r="B93" s="41">
+      <c r="A93" s="183">
+        <v>46286</v>
+      </c>
+      <c r="B93" s="184">
         <v>89</v>
       </c>
-      <c r="C93" s="121"/>
-      <c r="D93" s="121"/>
-      <c r="E93" s="44"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="122"/>
-      <c r="I93" s="44"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="44"/>
+      <c r="C93" s="185" t="s">
+        <v>199</v>
+      </c>
+      <c r="D93" s="185" t="s">
+        <v>200</v>
+      </c>
+      <c r="E93" s="186"/>
+      <c r="F93" s="186">
+        <v>40</v>
+      </c>
+      <c r="G93" s="186">
+        <v>40</v>
+      </c>
+      <c r="H93" s="187">
+        <v>40</v>
+      </c>
+      <c r="I93" s="186">
+        <v>40</v>
+      </c>
+      <c r="J93" s="186">
+        <v>40</v>
+      </c>
+      <c r="K93" s="186">
+        <v>40</v>
+      </c>
       <c r="L93" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="M93" s="148">
+        <v>12.5</v>
       </c>
       <c r="N93" s="43">
         <f t="shared" si="79"/>
@@ -9452,11 +9707,11 @@
       </c>
       <c r="O93" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P93" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q93" s="45" t="e">
         <f t="shared" ref="Q93:Q124" si="94">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
@@ -9492,26 +9747,39 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="72"/>
-      <c r="B94" s="41">
+      <c r="A94" s="143">
+        <v>46287</v>
+      </c>
+      <c r="B94" s="144">
         <v>90</v>
       </c>
-      <c r="C94" s="121"/>
-      <c r="D94" s="121"/>
-      <c r="E94" s="44"/>
-      <c r="F94" s="44"/>
-      <c r="G94" s="44"/>
-      <c r="H94" s="122"/>
-      <c r="I94" s="44"/>
-      <c r="J94" s="44"/>
-      <c r="K94" s="44"/>
+      <c r="C94" s="146" t="s">
+        <v>202</v>
+      </c>
+      <c r="D94" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="E94" s="145"/>
+      <c r="F94" s="145"/>
+      <c r="G94" s="145"/>
+      <c r="H94" s="147">
+        <v>80</v>
+      </c>
+      <c r="I94" s="145">
+        <v>80</v>
+      </c>
+      <c r="J94" s="145">
+        <v>80</v>
+      </c>
+      <c r="K94" s="145">
+        <v>120</v>
+      </c>
       <c r="L94" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M94" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N94" s="43">
         <f t="shared" si="79"/>
@@ -9519,11 +9787,11 @@
       </c>
       <c r="O94" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P94" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q94" s="45" t="e">
         <f t="shared" si="94"/>
@@ -9559,26 +9827,43 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="72"/>
-      <c r="B95" s="41">
+      <c r="A95" s="143">
+        <v>46287</v>
+      </c>
+      <c r="B95" s="144">
         <v>91</v>
       </c>
-      <c r="C95" s="121"/>
-      <c r="D95" s="121"/>
-      <c r="E95" s="44"/>
-      <c r="F95" s="44"/>
-      <c r="G95" s="44"/>
-      <c r="H95" s="122"/>
-      <c r="I95" s="44"/>
-      <c r="J95" s="44"/>
-      <c r="K95" s="44"/>
+      <c r="C95" s="146" t="s">
+        <v>203</v>
+      </c>
+      <c r="D95" s="146" t="s">
+        <v>104</v>
+      </c>
+      <c r="E95" s="145"/>
+      <c r="F95" s="145">
+        <v>80</v>
+      </c>
+      <c r="G95" s="145">
+        <v>80</v>
+      </c>
+      <c r="H95" s="147">
+        <v>80</v>
+      </c>
+      <c r="I95" s="145">
+        <v>80</v>
+      </c>
+      <c r="J95" s="145">
+        <v>80</v>
+      </c>
+      <c r="K95" s="145">
+        <v>80</v>
+      </c>
       <c r="L95" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M95" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N95" s="43">
         <f t="shared" si="79"/>
@@ -9586,11 +9871,11 @@
       </c>
       <c r="O95" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P95" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q95" s="45" t="e">
         <f t="shared" si="94"/>
@@ -9626,26 +9911,43 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="72"/>
-      <c r="B96" s="41">
+      <c r="A96" s="143">
+        <v>46287</v>
+      </c>
+      <c r="B96" s="144">
         <v>92</v>
       </c>
-      <c r="C96" s="121"/>
-      <c r="D96" s="121"/>
-      <c r="E96" s="44"/>
-      <c r="F96" s="44"/>
-      <c r="G96" s="44"/>
-      <c r="H96" s="122"/>
-      <c r="I96" s="44"/>
-      <c r="J96" s="44"/>
-      <c r="K96" s="44"/>
+      <c r="C96" s="146" t="s">
+        <v>136</v>
+      </c>
+      <c r="D96" s="146" t="s">
+        <v>114</v>
+      </c>
+      <c r="E96" s="145"/>
+      <c r="F96" s="145">
+        <v>80</v>
+      </c>
+      <c r="G96" s="145">
+        <v>80</v>
+      </c>
+      <c r="H96" s="147">
+        <v>40</v>
+      </c>
+      <c r="I96" s="145">
+        <v>200</v>
+      </c>
+      <c r="J96" s="145">
+        <v>80</v>
+      </c>
+      <c r="K96" s="145">
+        <v>200</v>
+      </c>
       <c r="L96" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M96" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N96" s="43">
         <f t="shared" si="79"/>
@@ -9653,11 +9955,11 @@
       </c>
       <c r="O96" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P96" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q96" s="45" t="e">
         <f t="shared" si="94"/>
@@ -9693,26 +9995,43 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
-      <c r="B97" s="41">
+      <c r="A97" s="143">
+        <v>46287</v>
+      </c>
+      <c r="B97" s="144">
         <v>93</v>
       </c>
-      <c r="C97" s="121"/>
-      <c r="D97" s="121"/>
-      <c r="E97" s="44"/>
-      <c r="F97" s="44"/>
-      <c r="G97" s="44"/>
-      <c r="H97" s="122"/>
-      <c r="I97" s="44"/>
-      <c r="J97" s="44"/>
-      <c r="K97" s="44"/>
+      <c r="C97" s="146" t="s">
+        <v>204</v>
+      </c>
+      <c r="D97" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="E97" s="145"/>
+      <c r="F97" s="145">
+        <v>120</v>
+      </c>
+      <c r="G97" s="145">
+        <v>200</v>
+      </c>
+      <c r="H97" s="147">
+        <v>200</v>
+      </c>
+      <c r="I97" s="145">
+        <v>160</v>
+      </c>
+      <c r="J97" s="145">
+        <v>200</v>
+      </c>
+      <c r="K97" s="145">
+        <v>200</v>
+      </c>
       <c r="L97" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M97" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N97" s="43">
         <f t="shared" si="79"/>
@@ -9720,11 +10039,11 @@
       </c>
       <c r="O97" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="P97" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q97" s="45" t="e">
         <f t="shared" si="94"/>
@@ -9764,15 +10083,15 @@
       <c r="B98" s="41">
         <v>94</v>
       </c>
-      <c r="C98" s="121"/>
-      <c r="D98" s="121"/>
-      <c r="E98" s="44"/>
-      <c r="F98" s="44"/>
-      <c r="G98" s="44"/>
-      <c r="H98" s="122"/>
-      <c r="I98" s="44"/>
-      <c r="J98" s="44"/>
-      <c r="K98" s="44"/>
+      <c r="C98" s="132"/>
+      <c r="D98" s="132"/>
+      <c r="E98" s="69"/>
+      <c r="F98" s="69"/>
+      <c r="G98" s="69"/>
+      <c r="H98" s="131"/>
+      <c r="I98" s="69"/>
+      <c r="J98" s="69"/>
+      <c r="K98" s="69"/>
       <c r="L98" s="122">
         <f t="shared" si="80"/>
         <v>0</v>
@@ -9831,15 +10150,15 @@
       <c r="B99" s="41">
         <v>95</v>
       </c>
-      <c r="C99" s="121"/>
-      <c r="D99" s="121"/>
-      <c r="E99" s="44"/>
-      <c r="F99" s="44"/>
-      <c r="G99" s="44"/>
-      <c r="H99" s="122"/>
-      <c r="I99" s="44"/>
-      <c r="J99" s="44"/>
-      <c r="K99" s="44"/>
+      <c r="C99" s="132"/>
+      <c r="D99" s="132"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="69"/>
+      <c r="G99" s="69"/>
+      <c r="H99" s="131"/>
+      <c r="I99" s="69"/>
+      <c r="J99" s="69"/>
+      <c r="K99" s="69"/>
       <c r="L99" s="122">
         <f t="shared" si="80"/>
         <v>0</v>
@@ -9898,15 +10217,15 @@
       <c r="B100" s="41">
         <v>96</v>
       </c>
-      <c r="C100" s="121"/>
-      <c r="D100" s="121"/>
-      <c r="E100" s="44"/>
-      <c r="F100" s="44"/>
-      <c r="G100" s="44"/>
-      <c r="H100" s="122"/>
-      <c r="I100" s="44"/>
-      <c r="J100" s="44"/>
-      <c r="K100" s="44"/>
+      <c r="C100" s="132"/>
+      <c r="D100" s="132"/>
+      <c r="E100" s="69"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="131"/>
+      <c r="I100" s="69"/>
+      <c r="J100" s="69"/>
+      <c r="K100" s="69"/>
       <c r="L100" s="122">
         <f t="shared" si="80"/>
         <v>0</v>
@@ -9965,15 +10284,15 @@
       <c r="B101" s="41">
         <v>97</v>
       </c>
-      <c r="C101" s="121"/>
-      <c r="D101" s="121"/>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44"/>
-      <c r="G101" s="44"/>
-      <c r="H101" s="122"/>
-      <c r="I101" s="44"/>
-      <c r="J101" s="44"/>
-      <c r="K101" s="44"/>
+      <c r="C101" s="132"/>
+      <c r="D101" s="132"/>
+      <c r="E101" s="69"/>
+      <c r="F101" s="69"/>
+      <c r="G101" s="69"/>
+      <c r="H101" s="131"/>
+      <c r="I101" s="69"/>
+      <c r="J101" s="69"/>
+      <c r="K101" s="69"/>
       <c r="L101" s="122">
         <f t="shared" ref="L101:L132" si="97">SUM(E101:K101)/40</f>
         <v>0</v>
@@ -10032,15 +10351,15 @@
       <c r="B102" s="41">
         <v>98</v>
       </c>
-      <c r="C102" s="121"/>
-      <c r="D102" s="121"/>
-      <c r="E102" s="44"/>
-      <c r="F102" s="44"/>
-      <c r="G102" s="44"/>
-      <c r="H102" s="122"/>
-      <c r="I102" s="44"/>
-      <c r="J102" s="44"/>
-      <c r="K102" s="44"/>
+      <c r="C102" s="132"/>
+      <c r="D102" s="132"/>
+      <c r="E102" s="69"/>
+      <c r="F102" s="69"/>
+      <c r="G102" s="69"/>
+      <c r="H102" s="131"/>
+      <c r="I102" s="69"/>
+      <c r="J102" s="69"/>
+      <c r="K102" s="69"/>
       <c r="L102" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10099,15 +10418,15 @@
       <c r="B103" s="41">
         <v>99</v>
       </c>
-      <c r="C103" s="121"/>
-      <c r="D103" s="121"/>
-      <c r="E103" s="44"/>
-      <c r="F103" s="44"/>
-      <c r="G103" s="44"/>
-      <c r="H103" s="122"/>
-      <c r="I103" s="44"/>
-      <c r="J103" s="44"/>
-      <c r="K103" s="44"/>
+      <c r="C103" s="132"/>
+      <c r="D103" s="132"/>
+      <c r="E103" s="69"/>
+      <c r="F103" s="69"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="131"/>
+      <c r="I103" s="69"/>
+      <c r="J103" s="69"/>
+      <c r="K103" s="69"/>
       <c r="L103" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10166,15 +10485,15 @@
       <c r="B104" s="41">
         <v>100</v>
       </c>
-      <c r="C104" s="121"/>
-      <c r="D104" s="121"/>
-      <c r="E104" s="44"/>
-      <c r="F104" s="44"/>
-      <c r="G104" s="44"/>
-      <c r="H104" s="122"/>
-      <c r="I104" s="44"/>
-      <c r="J104" s="44"/>
-      <c r="K104" s="44"/>
+      <c r="C104" s="132"/>
+      <c r="D104" s="132"/>
+      <c r="E104" s="69"/>
+      <c r="F104" s="69"/>
+      <c r="G104" s="69"/>
+      <c r="H104" s="131"/>
+      <c r="I104" s="69"/>
+      <c r="J104" s="69"/>
+      <c r="K104" s="69"/>
       <c r="L104" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10233,15 +10552,15 @@
       <c r="B105" s="41">
         <v>101</v>
       </c>
-      <c r="C105" s="121"/>
-      <c r="D105" s="121"/>
-      <c r="E105" s="44"/>
-      <c r="F105" s="44"/>
-      <c r="G105" s="44"/>
-      <c r="H105" s="122"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
-      <c r="K105" s="44"/>
+      <c r="C105" s="132"/>
+      <c r="D105" s="132"/>
+      <c r="E105" s="69"/>
+      <c r="F105" s="69"/>
+      <c r="G105" s="69"/>
+      <c r="H105" s="131"/>
+      <c r="I105" s="69"/>
+      <c r="J105" s="69"/>
+      <c r="K105" s="69"/>
       <c r="L105" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10300,15 +10619,15 @@
       <c r="B106" s="41">
         <v>102</v>
       </c>
-      <c r="C106" s="121"/>
-      <c r="D106" s="121"/>
-      <c r="E106" s="44"/>
-      <c r="F106" s="44"/>
-      <c r="G106" s="44"/>
-      <c r="H106" s="122"/>
-      <c r="I106" s="44"/>
-      <c r="J106" s="44"/>
-      <c r="K106" s="44"/>
+      <c r="C106" s="132"/>
+      <c r="D106" s="132"/>
+      <c r="E106" s="69"/>
+      <c r="F106" s="69"/>
+      <c r="G106" s="69"/>
+      <c r="H106" s="131"/>
+      <c r="I106" s="69"/>
+      <c r="J106" s="69"/>
+      <c r="K106" s="69"/>
       <c r="L106" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10367,15 +10686,15 @@
       <c r="B107" s="41">
         <v>103</v>
       </c>
-      <c r="C107" s="121"/>
-      <c r="D107" s="121"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="122"/>
-      <c r="I107" s="44"/>
-      <c r="J107" s="44"/>
-      <c r="K107" s="44"/>
+      <c r="C107" s="132"/>
+      <c r="D107" s="132"/>
+      <c r="E107" s="69"/>
+      <c r="F107" s="69"/>
+      <c r="G107" s="69"/>
+      <c r="H107" s="131"/>
+      <c r="I107" s="69"/>
+      <c r="J107" s="69"/>
+      <c r="K107" s="69"/>
       <c r="L107" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10434,15 +10753,15 @@
       <c r="B108" s="41">
         <v>104</v>
       </c>
-      <c r="C108" s="121"/>
-      <c r="D108" s="121"/>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="44"/>
-      <c r="H108" s="122"/>
-      <c r="I108" s="44"/>
-      <c r="J108" s="44"/>
-      <c r="K108" s="44"/>
+      <c r="C108" s="132"/>
+      <c r="D108" s="132"/>
+      <c r="E108" s="69"/>
+      <c r="F108" s="69"/>
+      <c r="G108" s="69"/>
+      <c r="H108" s="131"/>
+      <c r="I108" s="69"/>
+      <c r="J108" s="69"/>
+      <c r="K108" s="69"/>
       <c r="L108" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10501,15 +10820,15 @@
       <c r="B109" s="41">
         <v>105</v>
       </c>
-      <c r="C109" s="121"/>
-      <c r="D109" s="121"/>
-      <c r="E109" s="44"/>
-      <c r="F109" s="44"/>
-      <c r="G109" s="44"/>
-      <c r="H109" s="122"/>
-      <c r="I109" s="44"/>
-      <c r="J109" s="44"/>
-      <c r="K109" s="44"/>
+      <c r="C109" s="132"/>
+      <c r="D109" s="132"/>
+      <c r="E109" s="69"/>
+      <c r="F109" s="69"/>
+      <c r="G109" s="69"/>
+      <c r="H109" s="131"/>
+      <c r="I109" s="69"/>
+      <c r="J109" s="69"/>
+      <c r="K109" s="69"/>
       <c r="L109" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -10568,15 +10887,15 @@
       <c r="B110" s="41">
         <v>106</v>
       </c>
-      <c r="C110" s="121"/>
-      <c r="D110" s="121"/>
-      <c r="E110" s="44"/>
-      <c r="F110" s="44"/>
-      <c r="G110" s="44"/>
-      <c r="H110" s="122"/>
-      <c r="I110" s="44"/>
-      <c r="J110" s="44"/>
-      <c r="K110" s="44"/>
+      <c r="C110" s="132"/>
+      <c r="D110" s="132"/>
+      <c r="E110" s="69"/>
+      <c r="F110" s="69"/>
+      <c r="G110" s="69"/>
+      <c r="H110" s="131"/>
+      <c r="I110" s="69"/>
+      <c r="J110" s="69"/>
+      <c r="K110" s="69"/>
       <c r="L110" s="122">
         <f t="shared" si="97"/>
         <v>0</v>
@@ -12090,41 +12409,41 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="173" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="174"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
-        <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
+        <f>SUM(E6:E61)</f>
         <v>2265</v>
       </c>
       <c r="F133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(F6:F61)</f>
         <v>3118</v>
       </c>
       <c r="G133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(G6:G61)</f>
         <v>3290</v>
       </c>
       <c r="H133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(H6:H61)</f>
         <v>4730</v>
       </c>
       <c r="I133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(I6:I61)</f>
         <v>4955</v>
       </c>
       <c r="J133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(J6:J61)</f>
         <v>5537</v>
       </c>
       <c r="K133" s="78">
-        <f t="shared" si="101"/>
+        <f>SUM(K6:K61)</f>
         <v>7540</v>
       </c>
       <c r="L133" s="42">
-        <f t="shared" ref="L133" si="102">SUM(E133:K133)/40</f>
+        <f t="shared" ref="L133" si="101">SUM(E133:K133)/40</f>
         <v>785.875</v>
       </c>
       <c r="M133" s="33">
@@ -12136,11 +12455,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O133" s="67">
-        <f t="shared" ref="O133:O137" si="103">SUM(F133:H133)/20</f>
+        <f t="shared" ref="O133:O137" si="102">SUM(F133:H133)/20</f>
         <v>556.9</v>
       </c>
       <c r="P133" s="34">
-        <f t="shared" ref="P133:P137" si="104">SUM(I133:K133)/20</f>
+        <f t="shared" ref="P133:P137" si="103">SUM(I133:K133)/20</f>
         <v>901.6</v>
       </c>
       <c r="Q133" s="45" t="e">
@@ -12164,11 +12483,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V133" s="49">
-        <f t="shared" ref="V133:V137" si="105">SUM(F133:H133)*$V$3</f>
+        <f t="shared" ref="V133:V137" si="104">SUM(F133:H133)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W133" s="49">
-        <f t="shared" ref="W133:W137" si="106">SUM(I133:K133)*$W$3</f>
+        <f t="shared" ref="W133:W137" si="105">SUM(I133:K133)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X133" s="50" t="e">
@@ -12238,11 +12557,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O135" s="67">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="P135" s="34">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="P135" s="34">
-        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q135" s="45" t="e">
@@ -12266,11 +12585,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="49">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="W135" s="49">
         <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="W135" s="49">
-        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X135" s="50" t="e">
@@ -12306,11 +12625,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O136" s="67">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="P136" s="34">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="P136" s="34">
-        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q136" s="45" t="e">
@@ -12334,11 +12653,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V136" s="49">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="W136" s="49">
         <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="W136" s="49">
-        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X136" s="50" t="e">
@@ -12347,37 +12666,37 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="161" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="162"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
         <v>0</v>
       </c>
       <c r="F137" s="77">
-        <f t="shared" ref="F137:K137" si="107">SUM(F135:F136)</f>
+        <f t="shared" ref="F137:K137" si="106">SUM(F135:F136)</f>
         <v>0</v>
       </c>
       <c r="G137" s="77">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="H137" s="77">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="I137" s="77">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="J137" s="77">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="K137" s="77">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="L137" s="106">
@@ -12393,11 +12712,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O137" s="67">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="P137" s="34">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="P137" s="34">
-        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q137" s="45" t="e">
@@ -12421,11 +12740,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V137" s="49">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="W137" s="49">
         <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="W137" s="49">
-        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X137" s="50" t="e">
@@ -12434,37 +12753,37 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="150" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="151"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
         <v>2265</v>
       </c>
       <c r="F138" s="79">
-        <f t="shared" ref="F138:K138" si="108">SUM(F133,F137)</f>
+        <f t="shared" ref="F138:K138" si="107">SUM(F133,F137)</f>
         <v>3118</v>
       </c>
       <c r="G138" s="79">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>3290</v>
       </c>
       <c r="H138" s="79">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>4730</v>
       </c>
       <c r="I138" s="79">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>4955</v>
       </c>
       <c r="J138" s="79">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>5537</v>
       </c>
       <c r="K138" s="79">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>7540</v>
       </c>
       <c r="L138" s="54">
@@ -12473,50 +12792,50 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1025</v>
+        <v>1271</v>
       </c>
       <c r="N138" s="55">
-        <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
+        <f t="shared" ref="N138:X138" si="108">SUM(N5:N137)</f>
         <v>947.71329999999978</v>
       </c>
       <c r="O138" s="56">
-        <f t="shared" si="109"/>
-        <v>1513.5</v>
+        <f t="shared" si="108"/>
+        <v>1816.3000000000002</v>
       </c>
       <c r="P138" s="58">
-        <f t="shared" si="109"/>
-        <v>2347.1</v>
+        <f t="shared" si="108"/>
+        <v>2715.95</v>
       </c>
       <c r="Q138" s="59" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>#VALUE!</v>
       </c>
       <c r="R138" s="60">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="S138" s="60">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="T138" s="61" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>#VALUE!</v>
       </c>
       <c r="U138" s="62" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>#VALUE!</v>
       </c>
       <c r="V138" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="W138" s="63">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X138" s="64" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -12568,25 +12887,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="181" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="182"/>
-      <c r="K3" s="183" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="183"/>
-      <c r="O3" s="183"/>
-      <c r="P3" s="183"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -12632,24 +12951,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>720</v>
+        <v>787</v>
       </c>
       <c r="E5" s="73">
-        <v>1159</v>
+        <v>1430</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>1979</v>
+        <v>2317</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-8021</v>
+        <v>-7683</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -12673,11 +12992,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>28800</v>
+        <v>31480</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>46360</v>
+        <v>57200</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -12685,7 +13004,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>79160</v>
+        <v>92680</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -12693,7 +13012,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-320840</v>
+        <v>-307320</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -12821,11 +13140,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-720</v>
+        <v>-787</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1159</v>
+        <v>-1430</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -12909,14 +13228,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="180"/>
-      <c r="F11" s="180" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="180"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -12966,7 +13285,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6179</v>
+        <v>6517</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -13018,12 +13337,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>247160</v>
-      </c>
-      <c r="S13" s="175" t="s">
+        <v>260680</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="175"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13112,13 +13431,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="176" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="176"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0D15A2-A2ED-44CB-B35F-84BF77F7270A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE63208D-D7FE-41C0-B6FD-1D879941B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="207">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -637,6 +637,12 @@
   </si>
   <si>
     <t xml:space="preserve">Sweera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Rubaika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valencia Cash &amp; Carry </t>
   </si>
 </sst>
 </file>
@@ -1918,6 +1924,42 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1955,42 +1997,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2623,13 +2629,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
-      </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+        <v>46290</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2651,10 +2657,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2684,13 +2690,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="167"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2709,8 +2715,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2738,29 +2744,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="170"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -8677,29 +8683,29 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A81" s="183">
+      <c r="A81" s="72">
         <v>46286</v>
       </c>
-      <c r="B81" s="184">
+      <c r="B81" s="41">
         <v>77</v>
       </c>
-      <c r="C81" s="185" t="s">
+      <c r="C81" s="132" t="s">
         <v>189</v>
       </c>
-      <c r="D81" s="185" t="s">
+      <c r="D81" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="E81" s="186"/>
-      <c r="F81" s="186">
-        <v>40</v>
-      </c>
-      <c r="G81" s="186"/>
-      <c r="H81" s="187">
+      <c r="E81" s="69"/>
+      <c r="F81" s="69">
+        <v>40</v>
+      </c>
+      <c r="G81" s="69"/>
+      <c r="H81" s="131">
         <v>27</v>
       </c>
-      <c r="I81" s="186"/>
-      <c r="J81" s="186"/>
-      <c r="K81" s="186">
+      <c r="I81" s="69"/>
+      <c r="J81" s="69"/>
+      <c r="K81" s="69">
         <v>40</v>
       </c>
       <c r="L81" s="122">
@@ -8755,29 +8761,29 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A82" s="183">
+      <c r="A82" s="72">
         <v>46286</v>
       </c>
-      <c r="B82" s="184">
+      <c r="B82" s="41">
         <v>78</v>
       </c>
-      <c r="C82" s="185" t="s">
+      <c r="C82" s="132" t="s">
         <v>190</v>
       </c>
-      <c r="D82" s="185" t="s">
+      <c r="D82" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E82" s="186"/>
-      <c r="F82" s="186"/>
-      <c r="G82" s="186"/>
-      <c r="H82" s="187"/>
-      <c r="I82" s="186">
+      <c r="E82" s="69"/>
+      <c r="F82" s="69"/>
+      <c r="G82" s="69"/>
+      <c r="H82" s="131"/>
+      <c r="I82" s="69">
         <v>120</v>
       </c>
-      <c r="J82" s="186">
+      <c r="J82" s="69">
         <v>120</v>
       </c>
-      <c r="K82" s="186">
+      <c r="K82" s="69">
         <v>120</v>
       </c>
       <c r="L82" s="122">
@@ -8833,29 +8839,29 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A83" s="183">
+      <c r="A83" s="72">
         <v>46286</v>
       </c>
-      <c r="B83" s="184">
+      <c r="B83" s="41">
         <v>79</v>
       </c>
-      <c r="C83" s="185" t="s">
+      <c r="C83" s="132" t="s">
         <v>190</v>
       </c>
-      <c r="D83" s="185" t="s">
+      <c r="D83" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E83" s="186"/>
-      <c r="F83" s="186"/>
-      <c r="G83" s="186"/>
-      <c r="H83" s="187"/>
-      <c r="I83" s="186">
+      <c r="E83" s="69"/>
+      <c r="F83" s="69"/>
+      <c r="G83" s="69"/>
+      <c r="H83" s="131"/>
+      <c r="I83" s="69">
         <v>80</v>
       </c>
-      <c r="J83" s="186">
+      <c r="J83" s="69">
         <v>80</v>
       </c>
-      <c r="K83" s="186">
+      <c r="K83" s="69">
         <v>80</v>
       </c>
       <c r="L83" s="122">
@@ -8911,35 +8917,35 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A84" s="183">
+      <c r="A84" s="72">
         <v>46286</v>
       </c>
-      <c r="B84" s="184">
+      <c r="B84" s="41">
         <v>80</v>
       </c>
-      <c r="C84" s="185" t="s">
+      <c r="C84" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="D84" s="185" t="s">
+      <c r="D84" s="132" t="s">
         <v>191</v>
       </c>
-      <c r="E84" s="186"/>
-      <c r="F84" s="186">
+      <c r="E84" s="69"/>
+      <c r="F84" s="69">
         <v>800</v>
       </c>
-      <c r="G84" s="186">
+      <c r="G84" s="69">
         <v>800</v>
       </c>
-      <c r="H84" s="187">
+      <c r="H84" s="131">
         <v>800</v>
       </c>
-      <c r="I84" s="186">
+      <c r="I84" s="69">
         <v>800</v>
       </c>
-      <c r="J84" s="186">
+      <c r="J84" s="69">
         <v>800</v>
       </c>
-      <c r="K84" s="186">
+      <c r="K84" s="69">
         <v>800</v>
       </c>
       <c r="L84" s="122">
@@ -8995,35 +9001,35 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A85" s="183">
+      <c r="A85" s="72">
         <v>46286</v>
       </c>
-      <c r="B85" s="184">
+      <c r="B85" s="41">
         <v>81</v>
       </c>
-      <c r="C85" s="185" t="s">
+      <c r="C85" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="D85" s="185" t="s">
+      <c r="D85" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E85" s="186"/>
-      <c r="F85" s="186">
+      <c r="E85" s="69"/>
+      <c r="F85" s="69">
         <v>80</v>
       </c>
-      <c r="G85" s="186">
+      <c r="G85" s="69">
         <v>80</v>
       </c>
-      <c r="H85" s="187">
+      <c r="H85" s="131">
         <v>200</v>
       </c>
-      <c r="I85" s="186">
+      <c r="I85" s="69">
         <v>80</v>
       </c>
-      <c r="J85" s="186">
+      <c r="J85" s="69">
         <v>80</v>
       </c>
-      <c r="K85" s="186">
+      <c r="K85" s="69">
         <v>200</v>
       </c>
       <c r="L85" s="122">
@@ -9079,35 +9085,35 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A86" s="183">
+      <c r="A86" s="72">
         <v>46286</v>
       </c>
-      <c r="B86" s="184">
+      <c r="B86" s="41">
         <v>82</v>
       </c>
-      <c r="C86" s="185" t="s">
+      <c r="C86" s="132" t="s">
         <v>192</v>
       </c>
-      <c r="D86" s="185" t="s">
+      <c r="D86" s="132" t="s">
         <v>193</v>
       </c>
-      <c r="E86" s="186"/>
-      <c r="F86" s="186">
-        <v>40</v>
-      </c>
-      <c r="G86" s="186">
-        <v>40</v>
-      </c>
-      <c r="H86" s="187">
-        <v>40</v>
-      </c>
-      <c r="I86" s="186">
-        <v>40</v>
-      </c>
-      <c r="J86" s="186">
-        <v>40</v>
-      </c>
-      <c r="K86" s="186">
+      <c r="E86" s="69"/>
+      <c r="F86" s="69">
+        <v>40</v>
+      </c>
+      <c r="G86" s="69">
+        <v>40</v>
+      </c>
+      <c r="H86" s="131">
+        <v>40</v>
+      </c>
+      <c r="I86" s="69">
+        <v>40</v>
+      </c>
+      <c r="J86" s="69">
+        <v>40</v>
+      </c>
+      <c r="K86" s="69">
         <v>40</v>
       </c>
       <c r="L86" s="122">
@@ -9163,35 +9169,35 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A87" s="183">
+      <c r="A87" s="72">
         <v>46286</v>
       </c>
-      <c r="B87" s="184">
+      <c r="B87" s="41">
         <v>83</v>
       </c>
-      <c r="C87" s="185" t="s">
+      <c r="C87" s="132" t="s">
         <v>194</v>
       </c>
-      <c r="D87" s="185" t="s">
+      <c r="D87" s="132" t="s">
         <v>195</v>
       </c>
-      <c r="E87" s="186"/>
-      <c r="F87" s="186">
+      <c r="E87" s="69"/>
+      <c r="F87" s="69">
         <v>120</v>
       </c>
-      <c r="G87" s="186">
+      <c r="G87" s="69">
         <v>160</v>
       </c>
-      <c r="H87" s="187">
+      <c r="H87" s="131">
         <v>240</v>
       </c>
-      <c r="I87" s="186">
+      <c r="I87" s="69">
         <v>160</v>
       </c>
-      <c r="J87" s="186">
+      <c r="J87" s="69">
         <v>120</v>
       </c>
-      <c r="K87" s="186">
+      <c r="K87" s="69">
         <v>400</v>
       </c>
       <c r="L87" s="122">
@@ -9247,35 +9253,35 @@
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A88" s="183">
+      <c r="A88" s="72">
         <v>46286</v>
       </c>
-      <c r="B88" s="184">
+      <c r="B88" s="41">
         <v>84</v>
       </c>
-      <c r="C88" s="185" t="s">
+      <c r="C88" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="D88" s="185" t="s">
+      <c r="D88" s="132" t="s">
         <v>196</v>
       </c>
-      <c r="E88" s="186"/>
-      <c r="F88" s="186">
+      <c r="E88" s="69"/>
+      <c r="F88" s="69">
         <v>153</v>
       </c>
-      <c r="G88" s="186">
+      <c r="G88" s="69">
         <v>117</v>
       </c>
-      <c r="H88" s="187">
+      <c r="H88" s="131">
         <v>320</v>
       </c>
-      <c r="I88" s="186">
+      <c r="I88" s="69">
         <v>137</v>
       </c>
-      <c r="J88" s="186">
+      <c r="J88" s="69">
         <v>120</v>
       </c>
-      <c r="K88" s="186">
+      <c r="K88" s="69">
         <v>320</v>
       </c>
       <c r="L88" s="122">
@@ -9331,31 +9337,31 @@
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A89" s="183">
+      <c r="A89" s="72">
         <v>46286</v>
       </c>
-      <c r="B89" s="184">
+      <c r="B89" s="41">
         <v>85</v>
       </c>
-      <c r="C89" s="185" t="s">
+      <c r="C89" s="132" t="s">
         <v>197</v>
       </c>
-      <c r="D89" s="185" t="s">
+      <c r="D89" s="132" t="s">
         <v>198</v>
       </c>
-      <c r="E89" s="186"/>
-      <c r="F89" s="186">
+      <c r="E89" s="69"/>
+      <c r="F89" s="69">
         <v>80</v>
       </c>
-      <c r="G89" s="186">
+      <c r="G89" s="69">
         <v>80</v>
       </c>
-      <c r="H89" s="187">
+      <c r="H89" s="131">
         <v>80</v>
       </c>
-      <c r="I89" s="186"/>
-      <c r="J89" s="186"/>
-      <c r="K89" s="186">
+      <c r="I89" s="69"/>
+      <c r="J89" s="69"/>
+      <c r="K89" s="69">
         <v>320</v>
       </c>
       <c r="L89" s="122">
@@ -9411,35 +9417,35 @@
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A90" s="183">
+      <c r="A90" s="72">
         <v>46286</v>
       </c>
-      <c r="B90" s="184">
+      <c r="B90" s="41">
         <v>86</v>
       </c>
-      <c r="C90" s="185" t="s">
+      <c r="C90" s="132" t="s">
         <v>199</v>
       </c>
-      <c r="D90" s="185" t="s">
+      <c r="D90" s="132" t="s">
         <v>179</v>
       </c>
-      <c r="E90" s="186"/>
-      <c r="F90" s="186">
+      <c r="E90" s="69"/>
+      <c r="F90" s="69">
         <v>80</v>
       </c>
-      <c r="G90" s="186">
+      <c r="G90" s="69">
         <v>80</v>
       </c>
-      <c r="H90" s="187">
+      <c r="H90" s="131">
         <v>80</v>
       </c>
-      <c r="I90" s="186">
+      <c r="I90" s="69">
         <v>80</v>
       </c>
-      <c r="J90" s="186">
+      <c r="J90" s="69">
         <v>80</v>
       </c>
-      <c r="K90" s="186">
+      <c r="K90" s="69">
         <v>80</v>
       </c>
       <c r="L90" s="122">
@@ -9495,35 +9501,35 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A91" s="183">
+      <c r="A91" s="72">
         <v>46286</v>
       </c>
-      <c r="B91" s="184">
+      <c r="B91" s="41">
         <v>87</v>
       </c>
-      <c r="C91" s="185" t="s">
+      <c r="C91" s="132" t="s">
         <v>199</v>
       </c>
-      <c r="D91" s="185" t="s">
+      <c r="D91" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="E91" s="186"/>
-      <c r="F91" s="186">
-        <v>40</v>
-      </c>
-      <c r="G91" s="186">
-        <v>40</v>
-      </c>
-      <c r="H91" s="187">
-        <v>40</v>
-      </c>
-      <c r="I91" s="186">
-        <v>40</v>
-      </c>
-      <c r="J91" s="186">
-        <v>40</v>
-      </c>
-      <c r="K91" s="186">
+      <c r="E91" s="69"/>
+      <c r="F91" s="69">
+        <v>40</v>
+      </c>
+      <c r="G91" s="69">
+        <v>40</v>
+      </c>
+      <c r="H91" s="131">
+        <v>40</v>
+      </c>
+      <c r="I91" s="69">
+        <v>40</v>
+      </c>
+      <c r="J91" s="69">
+        <v>40</v>
+      </c>
+      <c r="K91" s="69">
         <v>40</v>
       </c>
       <c r="L91" s="122">
@@ -9579,35 +9585,35 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A92" s="183">
+      <c r="A92" s="72">
         <v>46286</v>
       </c>
-      <c r="B92" s="184">
+      <c r="B92" s="41">
         <v>88</v>
       </c>
-      <c r="C92" s="185" t="s">
+      <c r="C92" s="132" t="s">
         <v>199</v>
       </c>
-      <c r="D92" s="185" t="s">
+      <c r="D92" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="E92" s="186"/>
-      <c r="F92" s="186">
+      <c r="E92" s="69"/>
+      <c r="F92" s="69">
         <v>80</v>
       </c>
-      <c r="G92" s="186">
+      <c r="G92" s="69">
         <v>80</v>
       </c>
-      <c r="H92" s="187">
+      <c r="H92" s="131">
         <v>80</v>
       </c>
-      <c r="I92" s="186">
+      <c r="I92" s="69">
         <v>80</v>
       </c>
-      <c r="J92" s="186">
+      <c r="J92" s="69">
         <v>80</v>
       </c>
-      <c r="K92" s="186">
+      <c r="K92" s="69">
         <v>80</v>
       </c>
       <c r="L92" s="122">
@@ -9663,35 +9669,35 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A93" s="183">
+      <c r="A93" s="72">
         <v>46286</v>
       </c>
-      <c r="B93" s="184">
+      <c r="B93" s="41">
         <v>89</v>
       </c>
-      <c r="C93" s="185" t="s">
+      <c r="C93" s="132" t="s">
         <v>199</v>
       </c>
-      <c r="D93" s="185" t="s">
+      <c r="D93" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="E93" s="186"/>
-      <c r="F93" s="186">
-        <v>40</v>
-      </c>
-      <c r="G93" s="186">
-        <v>40</v>
-      </c>
-      <c r="H93" s="187">
-        <v>40</v>
-      </c>
-      <c r="I93" s="186">
-        <v>40</v>
-      </c>
-      <c r="J93" s="186">
-        <v>40</v>
-      </c>
-      <c r="K93" s="186">
+      <c r="E93" s="69"/>
+      <c r="F93" s="69">
+        <v>40</v>
+      </c>
+      <c r="G93" s="69">
+        <v>40</v>
+      </c>
+      <c r="H93" s="131">
+        <v>40</v>
+      </c>
+      <c r="I93" s="69">
+        <v>40</v>
+      </c>
+      <c r="J93" s="69">
+        <v>40</v>
+      </c>
+      <c r="K93" s="69">
         <v>40</v>
       </c>
       <c r="L93" s="122">
@@ -9747,31 +9753,31 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="143">
-        <v>46287</v>
-      </c>
-      <c r="B94" s="144">
+      <c r="A94" s="183">
+        <v>46288</v>
+      </c>
+      <c r="B94" s="184">
         <v>90</v>
       </c>
-      <c r="C94" s="146" t="s">
+      <c r="C94" s="185" t="s">
         <v>202</v>
       </c>
-      <c r="D94" s="146" t="s">
+      <c r="D94" s="185" t="s">
         <v>201</v>
       </c>
-      <c r="E94" s="145"/>
-      <c r="F94" s="145"/>
-      <c r="G94" s="145"/>
-      <c r="H94" s="147">
+      <c r="E94" s="186"/>
+      <c r="F94" s="186"/>
+      <c r="G94" s="186"/>
+      <c r="H94" s="187">
         <v>80</v>
       </c>
-      <c r="I94" s="145">
+      <c r="I94" s="186">
         <v>80</v>
       </c>
-      <c r="J94" s="145">
+      <c r="J94" s="186">
         <v>80</v>
       </c>
-      <c r="K94" s="145">
+      <c r="K94" s="186">
         <v>120</v>
       </c>
       <c r="L94" s="122">
@@ -9827,35 +9833,35 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="143">
-        <v>46287</v>
-      </c>
-      <c r="B95" s="144">
+      <c r="A95" s="183">
+        <v>46288</v>
+      </c>
+      <c r="B95" s="184">
         <v>91</v>
       </c>
-      <c r="C95" s="146" t="s">
+      <c r="C95" s="185" t="s">
         <v>203</v>
       </c>
-      <c r="D95" s="146" t="s">
+      <c r="D95" s="185" t="s">
         <v>104</v>
       </c>
-      <c r="E95" s="145"/>
-      <c r="F95" s="145">
+      <c r="E95" s="186"/>
+      <c r="F95" s="186">
         <v>80</v>
       </c>
-      <c r="G95" s="145">
+      <c r="G95" s="186">
         <v>80</v>
       </c>
-      <c r="H95" s="147">
+      <c r="H95" s="187">
         <v>80</v>
       </c>
-      <c r="I95" s="145">
+      <c r="I95" s="186">
         <v>80</v>
       </c>
-      <c r="J95" s="145">
+      <c r="J95" s="186">
         <v>80</v>
       </c>
-      <c r="K95" s="145">
+      <c r="K95" s="186">
         <v>80</v>
       </c>
       <c r="L95" s="122">
@@ -9911,35 +9917,35 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="143">
-        <v>46287</v>
-      </c>
-      <c r="B96" s="144">
+      <c r="A96" s="183">
+        <v>46288</v>
+      </c>
+      <c r="B96" s="184">
         <v>92</v>
       </c>
-      <c r="C96" s="146" t="s">
+      <c r="C96" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="D96" s="146" t="s">
+      <c r="D96" s="185" t="s">
         <v>114</v>
       </c>
-      <c r="E96" s="145"/>
-      <c r="F96" s="145">
+      <c r="E96" s="186"/>
+      <c r="F96" s="186">
         <v>80</v>
       </c>
-      <c r="G96" s="145">
+      <c r="G96" s="186">
         <v>80</v>
       </c>
-      <c r="H96" s="147">
-        <v>40</v>
-      </c>
-      <c r="I96" s="145">
+      <c r="H96" s="187">
+        <v>40</v>
+      </c>
+      <c r="I96" s="186">
         <v>200</v>
       </c>
-      <c r="J96" s="145">
+      <c r="J96" s="186">
         <v>80</v>
       </c>
-      <c r="K96" s="145">
+      <c r="K96" s="186">
         <v>200</v>
       </c>
       <c r="L96" s="122">
@@ -9995,35 +10001,35 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="143">
-        <v>46287</v>
-      </c>
-      <c r="B97" s="144">
+      <c r="A97" s="183">
+        <v>46288</v>
+      </c>
+      <c r="B97" s="184">
         <v>93</v>
       </c>
-      <c r="C97" s="146" t="s">
+      <c r="C97" s="185" t="s">
         <v>204</v>
       </c>
-      <c r="D97" s="146" t="s">
+      <c r="D97" s="185" t="s">
         <v>201</v>
       </c>
-      <c r="E97" s="145"/>
-      <c r="F97" s="145">
+      <c r="E97" s="186"/>
+      <c r="F97" s="186">
         <v>120</v>
       </c>
-      <c r="G97" s="145">
+      <c r="G97" s="186">
         <v>200</v>
       </c>
-      <c r="H97" s="147">
+      <c r="H97" s="187">
         <v>200</v>
       </c>
-      <c r="I97" s="145">
+      <c r="I97" s="186">
         <v>160</v>
       </c>
-      <c r="J97" s="145">
+      <c r="J97" s="186">
         <v>200</v>
       </c>
-      <c r="K97" s="145">
+      <c r="K97" s="186">
         <v>200</v>
       </c>
       <c r="L97" s="122">
@@ -10079,26 +10085,43 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="72"/>
-      <c r="B98" s="41">
+      <c r="A98" s="143">
+        <v>46289</v>
+      </c>
+      <c r="B98" s="144">
         <v>94</v>
       </c>
-      <c r="C98" s="132"/>
-      <c r="D98" s="132"/>
-      <c r="E98" s="69"/>
-      <c r="F98" s="69"/>
-      <c r="G98" s="69"/>
-      <c r="H98" s="131"/>
-      <c r="I98" s="69"/>
-      <c r="J98" s="69"/>
-      <c r="K98" s="69"/>
+      <c r="C98" s="146" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98" s="146" t="s">
+        <v>130</v>
+      </c>
+      <c r="E98" s="145"/>
+      <c r="F98" s="145">
+        <v>80</v>
+      </c>
+      <c r="G98" s="145">
+        <v>80</v>
+      </c>
+      <c r="H98" s="147">
+        <v>40</v>
+      </c>
+      <c r="I98" s="145">
+        <v>80</v>
+      </c>
+      <c r="J98" s="145">
+        <v>80</v>
+      </c>
+      <c r="K98" s="145">
+        <v>80</v>
+      </c>
       <c r="L98" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M98" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N98" s="43">
         <f t="shared" ref="N98:N133" si="96">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
@@ -10106,11 +10129,11 @@
       </c>
       <c r="O98" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P98" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q98" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10146,26 +10169,43 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="72"/>
-      <c r="B99" s="41">
+      <c r="A99" s="143">
+        <v>46289</v>
+      </c>
+      <c r="B99" s="144">
         <v>95</v>
       </c>
-      <c r="C99" s="132"/>
-      <c r="D99" s="132"/>
-      <c r="E99" s="69"/>
-      <c r="F99" s="69"/>
-      <c r="G99" s="69"/>
-      <c r="H99" s="131"/>
-      <c r="I99" s="69"/>
-      <c r="J99" s="69"/>
-      <c r="K99" s="69"/>
+      <c r="C99" s="146" t="s">
+        <v>206</v>
+      </c>
+      <c r="D99" s="146" t="s">
+        <v>130</v>
+      </c>
+      <c r="E99" s="145"/>
+      <c r="F99" s="145">
+        <v>40</v>
+      </c>
+      <c r="G99" s="145">
+        <v>40</v>
+      </c>
+      <c r="H99" s="147">
+        <v>80</v>
+      </c>
+      <c r="I99" s="145">
+        <v>40</v>
+      </c>
+      <c r="J99" s="145">
+        <v>40</v>
+      </c>
+      <c r="K99" s="145">
+        <v>80</v>
+      </c>
       <c r="L99" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M99" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N99" s="43">
         <f t="shared" si="96"/>
@@ -10173,11 +10213,11 @@
       </c>
       <c r="O99" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P99" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q99" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10213,26 +10253,37 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="72"/>
-      <c r="B100" s="41">
+      <c r="A100" s="143">
+        <v>46289</v>
+      </c>
+      <c r="B100" s="144">
         <v>96</v>
       </c>
-      <c r="C100" s="132"/>
-      <c r="D100" s="132"/>
-      <c r="E100" s="69"/>
-      <c r="F100" s="69"/>
-      <c r="G100" s="69"/>
-      <c r="H100" s="131"/>
-      <c r="I100" s="69"/>
-      <c r="J100" s="69"/>
-      <c r="K100" s="69"/>
+      <c r="C100" s="146" t="s">
+        <v>128</v>
+      </c>
+      <c r="D100" s="146" t="s">
+        <v>129</v>
+      </c>
+      <c r="E100" s="145"/>
+      <c r="F100" s="145"/>
+      <c r="G100" s="145"/>
+      <c r="H100" s="147">
+        <v>400</v>
+      </c>
+      <c r="I100" s="145"/>
+      <c r="J100" s="145">
+        <v>800</v>
+      </c>
+      <c r="K100" s="145">
+        <v>400</v>
+      </c>
       <c r="L100" s="122">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M100" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N100" s="43">
         <f t="shared" si="96"/>
@@ -10240,11 +10291,11 @@
       </c>
       <c r="O100" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P100" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q100" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12409,41 +12460,41 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="160"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
-        <f>SUM(E6:E61)</f>
+        <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
         <v>2265</v>
       </c>
       <c r="F133" s="78">
-        <f>SUM(F6:F61)</f>
+        <f t="shared" si="101"/>
         <v>3118</v>
       </c>
       <c r="G133" s="78">
-        <f>SUM(G6:G61)</f>
+        <f t="shared" si="101"/>
         <v>3290</v>
       </c>
       <c r="H133" s="78">
-        <f>SUM(H6:H61)</f>
+        <f t="shared" si="101"/>
         <v>4730</v>
       </c>
       <c r="I133" s="78">
-        <f>SUM(I6:I61)</f>
+        <f t="shared" si="101"/>
         <v>4955</v>
       </c>
       <c r="J133" s="78">
-        <f>SUM(J6:J61)</f>
+        <f t="shared" si="101"/>
         <v>5537</v>
       </c>
       <c r="K133" s="78">
-        <f>SUM(K6:K61)</f>
+        <f t="shared" si="101"/>
         <v>7540</v>
       </c>
       <c r="L133" s="42">
-        <f t="shared" ref="L133" si="101">SUM(E133:K133)/40</f>
+        <f t="shared" ref="L133" si="102">SUM(E133:K133)/40</f>
         <v>785.875</v>
       </c>
       <c r="M133" s="33">
@@ -12455,11 +12506,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O133" s="67">
-        <f t="shared" ref="O133:O137" si="102">SUM(F133:H133)/20</f>
+        <f t="shared" ref="O133:O137" si="103">SUM(F133:H133)/20</f>
         <v>556.9</v>
       </c>
       <c r="P133" s="34">
-        <f t="shared" ref="P133:P137" si="103">SUM(I133:K133)/20</f>
+        <f t="shared" ref="P133:P137" si="104">SUM(I133:K133)/20</f>
         <v>901.6</v>
       </c>
       <c r="Q133" s="45" t="e">
@@ -12483,11 +12534,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V133" s="49">
-        <f t="shared" ref="V133:V137" si="104">SUM(F133:H133)*$V$3</f>
+        <f t="shared" ref="V133:V137" si="105">SUM(F133:H133)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W133" s="49">
-        <f t="shared" ref="W133:W137" si="105">SUM(I133:K133)*$W$3</f>
+        <f t="shared" ref="W133:W137" si="106">SUM(I133:K133)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X133" s="50" t="e">
@@ -12557,11 +12608,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O135" s="67">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="P135" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q135" s="45" t="e">
@@ -12585,11 +12636,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="49">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="W135" s="49">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X135" s="50" t="e">
@@ -12625,11 +12676,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O136" s="67">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="P136" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q136" s="45" t="e">
@@ -12653,11 +12704,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V136" s="49">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="W136" s="49">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X136" s="50" t="e">
@@ -12666,37 +12717,37 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="173"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
         <v>0</v>
       </c>
       <c r="F137" s="77">
-        <f t="shared" ref="F137:K137" si="106">SUM(F135:F136)</f>
+        <f t="shared" ref="F137:K137" si="107">SUM(F135:F136)</f>
         <v>0</v>
       </c>
       <c r="G137" s="77">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="H137" s="77">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="I137" s="77">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="J137" s="77">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="K137" s="77">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="L137" s="106">
@@ -12712,11 +12763,11 @@
         <v>9.2011000000000003</v>
       </c>
       <c r="O137" s="67">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="P137" s="34">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="Q137" s="45" t="e">
@@ -12740,11 +12791,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V137" s="49">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="W137" s="49">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="X137" s="50" t="e">
@@ -12753,37 +12804,37 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="162"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
         <v>2265</v>
       </c>
       <c r="F138" s="79">
-        <f t="shared" ref="F138:K138" si="107">SUM(F133,F137)</f>
+        <f t="shared" ref="F138:K138" si="108">SUM(F133,F137)</f>
         <v>3118</v>
       </c>
       <c r="G138" s="79">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>3290</v>
       </c>
       <c r="H138" s="79">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4730</v>
       </c>
       <c r="I138" s="79">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4955</v>
       </c>
       <c r="J138" s="79">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>5537</v>
       </c>
       <c r="K138" s="79">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>7540</v>
       </c>
       <c r="L138" s="54">
@@ -12792,66 +12843,66 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1271</v>
+        <v>1309</v>
       </c>
       <c r="N138" s="55">
-        <f t="shared" ref="N138:X138" si="108">SUM(N5:N137)</f>
+        <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
         <v>947.71329999999978</v>
       </c>
       <c r="O138" s="56">
-        <f t="shared" si="108"/>
-        <v>1816.3000000000002</v>
+        <f t="shared" si="109"/>
+        <v>1854.3000000000002</v>
       </c>
       <c r="P138" s="58">
-        <f t="shared" si="108"/>
-        <v>2715.95</v>
+        <f t="shared" si="109"/>
+        <v>2795.95</v>
       </c>
       <c r="Q138" s="59" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="R138" s="60">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="S138" s="60">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="T138" s="61" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="U138" s="62" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
       <c r="V138" s="63">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="W138" s="63">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="X138" s="64" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12951,24 +13002,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>787</v>
+        <v>842</v>
       </c>
       <c r="E5" s="73">
-        <v>1430</v>
+        <v>1554</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>2317</v>
+        <v>2496</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-7683</v>
+        <v>-7504</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -12992,11 +13043,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>31480</v>
+        <v>33680</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>57200</v>
+        <v>62160</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -13004,7 +13055,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>92680</v>
+        <v>99840</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -13012,7 +13063,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-307320</v>
+        <v>-300160</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -13140,11 +13191,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-787</v>
+        <v>-842</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1430</v>
+        <v>-1554</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -13285,7 +13336,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6517</v>
+        <v>6696</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -13337,7 +13388,7 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>260680</v>
+        <v>267840</v>
       </c>
       <c r="S13" s="174" t="s">
         <v>83</v>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE63208D-D7FE-41C0-B6FD-1D879941B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA737D8B-B16D-49FD-950C-560370254BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="211">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -643,6 +643,18 @@
   </si>
   <si>
     <t xml:space="preserve">Valencia Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS Departmenral Store Cario Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Behria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Velly </t>
+  </si>
+  <si>
+    <t>Cantt</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2025,17 +2037,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2631,7 +2632,7 @@
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C1" s="149"/>
       <c r="D1" s="149"/>
@@ -7984,7 +7985,7 @@
         <v>2</v>
       </c>
       <c r="M72" s="33">
-        <f t="shared" ref="M72:M102" si="81">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M72" si="81">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N72" s="43">
@@ -9753,31 +9754,31 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="183">
+      <c r="A94" s="72">
         <v>46288</v>
       </c>
-      <c r="B94" s="184">
+      <c r="B94" s="41">
         <v>90</v>
       </c>
-      <c r="C94" s="185" t="s">
+      <c r="C94" s="132" t="s">
         <v>202</v>
       </c>
-      <c r="D94" s="185" t="s">
+      <c r="D94" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="E94" s="186"/>
-      <c r="F94" s="186"/>
-      <c r="G94" s="186"/>
-      <c r="H94" s="187">
+      <c r="E94" s="69"/>
+      <c r="F94" s="69"/>
+      <c r="G94" s="69"/>
+      <c r="H94" s="131">
         <v>80</v>
       </c>
-      <c r="I94" s="186">
+      <c r="I94" s="69">
         <v>80</v>
       </c>
-      <c r="J94" s="186">
+      <c r="J94" s="69">
         <v>80</v>
       </c>
-      <c r="K94" s="186">
+      <c r="K94" s="69">
         <v>120</v>
       </c>
       <c r="L94" s="122">
@@ -9833,35 +9834,35 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="183">
+      <c r="A95" s="72">
         <v>46288</v>
       </c>
-      <c r="B95" s="184">
+      <c r="B95" s="41">
         <v>91</v>
       </c>
-      <c r="C95" s="185" t="s">
+      <c r="C95" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="D95" s="185" t="s">
+      <c r="D95" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="E95" s="186"/>
-      <c r="F95" s="186">
+      <c r="E95" s="69"/>
+      <c r="F95" s="69">
         <v>80</v>
       </c>
-      <c r="G95" s="186">
+      <c r="G95" s="69">
         <v>80</v>
       </c>
-      <c r="H95" s="187">
+      <c r="H95" s="131">
         <v>80</v>
       </c>
-      <c r="I95" s="186">
+      <c r="I95" s="69">
         <v>80</v>
       </c>
-      <c r="J95" s="186">
+      <c r="J95" s="69">
         <v>80</v>
       </c>
-      <c r="K95" s="186">
+      <c r="K95" s="69">
         <v>80</v>
       </c>
       <c r="L95" s="122">
@@ -9917,35 +9918,35 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="183">
+      <c r="A96" s="72">
         <v>46288</v>
       </c>
-      <c r="B96" s="184">
+      <c r="B96" s="41">
         <v>92</v>
       </c>
-      <c r="C96" s="185" t="s">
+      <c r="C96" s="132" t="s">
         <v>136</v>
       </c>
-      <c r="D96" s="185" t="s">
+      <c r="D96" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="E96" s="186"/>
-      <c r="F96" s="186">
+      <c r="E96" s="69"/>
+      <c r="F96" s="69">
         <v>80</v>
       </c>
-      <c r="G96" s="186">
+      <c r="G96" s="69">
         <v>80</v>
       </c>
-      <c r="H96" s="187">
-        <v>40</v>
-      </c>
-      <c r="I96" s="186">
+      <c r="H96" s="131">
+        <v>40</v>
+      </c>
+      <c r="I96" s="69">
         <v>200</v>
       </c>
-      <c r="J96" s="186">
+      <c r="J96" s="69">
         <v>80</v>
       </c>
-      <c r="K96" s="186">
+      <c r="K96" s="69">
         <v>200</v>
       </c>
       <c r="L96" s="122">
@@ -10001,35 +10002,35 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="183">
+      <c r="A97" s="72">
         <v>46288</v>
       </c>
-      <c r="B97" s="184">
+      <c r="B97" s="41">
         <v>93</v>
       </c>
-      <c r="C97" s="185" t="s">
+      <c r="C97" s="132" t="s">
         <v>204</v>
       </c>
-      <c r="D97" s="185" t="s">
+      <c r="D97" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="E97" s="186"/>
-      <c r="F97" s="186">
+      <c r="E97" s="69"/>
+      <c r="F97" s="69">
         <v>120</v>
       </c>
-      <c r="G97" s="186">
+      <c r="G97" s="69">
         <v>200</v>
       </c>
-      <c r="H97" s="187">
+      <c r="H97" s="131">
         <v>200</v>
       </c>
-      <c r="I97" s="186">
+      <c r="I97" s="69">
         <v>160</v>
       </c>
-      <c r="J97" s="186">
+      <c r="J97" s="69">
         <v>200</v>
       </c>
-      <c r="K97" s="186">
+      <c r="K97" s="69">
         <v>200</v>
       </c>
       <c r="L97" s="122">
@@ -10085,35 +10086,35 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="143">
+      <c r="A98" s="72">
         <v>46289</v>
       </c>
-      <c r="B98" s="144">
+      <c r="B98" s="41">
         <v>94</v>
       </c>
-      <c r="C98" s="146" t="s">
+      <c r="C98" s="132" t="s">
         <v>205</v>
       </c>
-      <c r="D98" s="146" t="s">
+      <c r="D98" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E98" s="145"/>
-      <c r="F98" s="145">
+      <c r="E98" s="69"/>
+      <c r="F98" s="69">
         <v>80</v>
       </c>
-      <c r="G98" s="145">
+      <c r="G98" s="69">
         <v>80</v>
       </c>
-      <c r="H98" s="147">
-        <v>40</v>
-      </c>
-      <c r="I98" s="145">
+      <c r="H98" s="131">
+        <v>40</v>
+      </c>
+      <c r="I98" s="69">
         <v>80</v>
       </c>
-      <c r="J98" s="145">
+      <c r="J98" s="69">
         <v>80</v>
       </c>
-      <c r="K98" s="145">
+      <c r="K98" s="69">
         <v>80</v>
       </c>
       <c r="L98" s="122">
@@ -10169,35 +10170,35 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="143">
+      <c r="A99" s="72">
         <v>46289</v>
       </c>
-      <c r="B99" s="144">
+      <c r="B99" s="41">
         <v>95</v>
       </c>
-      <c r="C99" s="146" t="s">
+      <c r="C99" s="132" t="s">
         <v>206</v>
       </c>
-      <c r="D99" s="146" t="s">
+      <c r="D99" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E99" s="145"/>
-      <c r="F99" s="145">
-        <v>40</v>
-      </c>
-      <c r="G99" s="145">
-        <v>40</v>
-      </c>
-      <c r="H99" s="147">
+      <c r="E99" s="69"/>
+      <c r="F99" s="69">
+        <v>40</v>
+      </c>
+      <c r="G99" s="69">
+        <v>40</v>
+      </c>
+      <c r="H99" s="131">
         <v>80</v>
       </c>
-      <c r="I99" s="145">
-        <v>40</v>
-      </c>
-      <c r="J99" s="145">
-        <v>40</v>
-      </c>
-      <c r="K99" s="145">
+      <c r="I99" s="69">
+        <v>40</v>
+      </c>
+      <c r="J99" s="69">
+        <v>40</v>
+      </c>
+      <c r="K99" s="69">
         <v>80</v>
       </c>
       <c r="L99" s="122">
@@ -10253,29 +10254,29 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="143">
+      <c r="A100" s="72">
         <v>46289</v>
       </c>
-      <c r="B100" s="144">
+      <c r="B100" s="41">
         <v>96</v>
       </c>
-      <c r="C100" s="146" t="s">
+      <c r="C100" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="D100" s="146" t="s">
+      <c r="D100" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E100" s="145"/>
-      <c r="F100" s="145"/>
-      <c r="G100" s="145"/>
-      <c r="H100" s="147">
+      <c r="E100" s="69"/>
+      <c r="F100" s="69"/>
+      <c r="G100" s="69"/>
+      <c r="H100" s="131">
         <v>400</v>
       </c>
-      <c r="I100" s="145"/>
-      <c r="J100" s="145">
+      <c r="I100" s="69"/>
+      <c r="J100" s="69">
         <v>800</v>
       </c>
-      <c r="K100" s="145">
+      <c r="K100" s="69">
         <v>400</v>
       </c>
       <c r="L100" s="122">
@@ -10331,26 +10332,37 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="72"/>
-      <c r="B101" s="41">
+      <c r="A101" s="143">
+        <v>46290</v>
+      </c>
+      <c r="B101" s="144">
         <v>97</v>
       </c>
-      <c r="C101" s="132"/>
-      <c r="D101" s="132"/>
-      <c r="E101" s="69"/>
-      <c r="F101" s="69"/>
-      <c r="G101" s="69"/>
-      <c r="H101" s="131"/>
-      <c r="I101" s="69"/>
-      <c r="J101" s="69"/>
-      <c r="K101" s="69"/>
+      <c r="C101" s="146" t="s">
+        <v>207</v>
+      </c>
+      <c r="D101" s="146" t="s">
+        <v>99</v>
+      </c>
+      <c r="E101" s="145"/>
+      <c r="F101" s="145"/>
+      <c r="G101" s="145"/>
+      <c r="H101" s="147"/>
+      <c r="I101" s="145">
+        <v>80</v>
+      </c>
+      <c r="J101" s="145">
+        <v>80</v>
+      </c>
+      <c r="K101" s="145">
+        <v>120</v>
+      </c>
       <c r="L101" s="122">
         <f t="shared" ref="L101:L132" si="97">SUM(E101:K101)/40</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M101" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N101" s="43">
         <f t="shared" si="96"/>
@@ -10362,7 +10374,7 @@
       </c>
       <c r="P101" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q101" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10398,26 +10410,43 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="72"/>
-      <c r="B102" s="41">
+      <c r="A102" s="143">
+        <v>46290</v>
+      </c>
+      <c r="B102" s="144">
         <v>98</v>
       </c>
-      <c r="C102" s="132"/>
-      <c r="D102" s="132"/>
-      <c r="E102" s="69"/>
-      <c r="F102" s="69"/>
-      <c r="G102" s="69"/>
-      <c r="H102" s="131"/>
-      <c r="I102" s="69"/>
-      <c r="J102" s="69"/>
-      <c r="K102" s="69"/>
+      <c r="C102" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="D102" s="146" t="s">
+        <v>104</v>
+      </c>
+      <c r="E102" s="145"/>
+      <c r="F102" s="145">
+        <v>40</v>
+      </c>
+      <c r="G102" s="145">
+        <v>80</v>
+      </c>
+      <c r="H102" s="147">
+        <v>120</v>
+      </c>
+      <c r="I102" s="145">
+        <v>120</v>
+      </c>
+      <c r="J102" s="145">
+        <v>120</v>
+      </c>
+      <c r="K102" s="145">
+        <v>240</v>
+      </c>
       <c r="L102" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M102" s="33">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N102" s="43">
         <f t="shared" si="96"/>
@@ -10425,11 +10454,11 @@
       </c>
       <c r="O102" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P102" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q102" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10465,26 +10494,37 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="72"/>
-      <c r="B103" s="41">
+      <c r="A103" s="143">
+        <v>46290</v>
+      </c>
+      <c r="B103" s="144">
         <v>99</v>
       </c>
-      <c r="C103" s="132"/>
-      <c r="D103" s="132"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="69"/>
-      <c r="G103" s="69"/>
-      <c r="H103" s="131"/>
-      <c r="I103" s="69"/>
-      <c r="J103" s="69"/>
-      <c r="K103" s="69"/>
+      <c r="C103" s="146" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" s="146" t="s">
+        <v>179</v>
+      </c>
+      <c r="E103" s="145"/>
+      <c r="F103" s="145"/>
+      <c r="G103" s="145"/>
+      <c r="H103" s="147"/>
+      <c r="I103" s="145">
+        <v>80</v>
+      </c>
+      <c r="J103" s="145">
+        <v>80</v>
+      </c>
+      <c r="K103" s="145">
+        <v>80</v>
+      </c>
       <c r="L103" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M103" s="33">
-        <f t="shared" ref="M103:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N103" s="43">
         <f t="shared" si="96"/>
@@ -10496,7 +10536,7 @@
       </c>
       <c r="P103" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q103" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10532,26 +10572,43 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="72"/>
-      <c r="B104" s="41">
+      <c r="A104" s="143">
+        <v>46290</v>
+      </c>
+      <c r="B104" s="144">
         <v>100</v>
       </c>
-      <c r="C104" s="132"/>
-      <c r="D104" s="132"/>
-      <c r="E104" s="69"/>
-      <c r="F104" s="69"/>
-      <c r="G104" s="69"/>
-      <c r="H104" s="131"/>
-      <c r="I104" s="69"/>
-      <c r="J104" s="69"/>
-      <c r="K104" s="69"/>
+      <c r="C104" s="146" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" s="146" t="s">
+        <v>117</v>
+      </c>
+      <c r="E104" s="145"/>
+      <c r="F104" s="145">
+        <v>400</v>
+      </c>
+      <c r="G104" s="145">
+        <v>400</v>
+      </c>
+      <c r="H104" s="147">
+        <v>400</v>
+      </c>
+      <c r="I104" s="145">
+        <v>400</v>
+      </c>
+      <c r="J104" s="145">
+        <v>400</v>
+      </c>
+      <c r="K104" s="145">
+        <v>400</v>
+      </c>
       <c r="L104" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M104" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N104" s="43">
         <f t="shared" si="96"/>
@@ -10559,11 +10616,11 @@
       </c>
       <c r="O104" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P104" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q104" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10599,26 +10656,43 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="72"/>
-      <c r="B105" s="41">
+      <c r="A105" s="143">
+        <v>46290</v>
+      </c>
+      <c r="B105" s="144">
         <v>101</v>
       </c>
-      <c r="C105" s="132"/>
-      <c r="D105" s="132"/>
-      <c r="E105" s="69"/>
-      <c r="F105" s="69"/>
-      <c r="G105" s="69"/>
-      <c r="H105" s="131"/>
-      <c r="I105" s="69"/>
-      <c r="J105" s="69"/>
-      <c r="K105" s="69"/>
+      <c r="C105" s="146" t="s">
+        <v>209</v>
+      </c>
+      <c r="D105" s="146" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" s="145"/>
+      <c r="F105" s="145">
+        <v>120</v>
+      </c>
+      <c r="G105" s="145">
+        <v>120</v>
+      </c>
+      <c r="H105" s="147">
+        <v>120</v>
+      </c>
+      <c r="I105" s="145">
+        <v>80</v>
+      </c>
+      <c r="J105" s="145">
+        <v>80</v>
+      </c>
+      <c r="K105" s="145">
+        <v>80</v>
+      </c>
       <c r="L105" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M105" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N105" s="43">
         <f t="shared" si="96"/>
@@ -10626,11 +10700,11 @@
       </c>
       <c r="O105" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P105" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q105" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10684,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="33">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="M106:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N106" s="43">
@@ -12843,7 +12917,7 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1309</v>
+        <v>1365</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
@@ -12851,11 +12925,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>1854.3000000000002</v>
+        <v>1944.3000000000002</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>2795.95</v>
+        <v>2917.95</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -13002,24 +13076,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>842</v>
+        <v>884</v>
       </c>
       <c r="E5" s="73">
-        <v>1554</v>
+        <v>1660</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>2496</v>
+        <v>2644</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-7504</v>
+        <v>-7356</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -13043,11 +13117,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>33680</v>
+        <v>35360</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>62160</v>
+        <v>66400</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -13055,7 +13129,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>99840</v>
+        <v>105760</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -13063,7 +13137,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-300160</v>
+        <v>-294240</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -13191,11 +13265,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-842</v>
+        <v>-884</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1554</v>
+        <v>-1660</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -13336,7 +13410,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6696</v>
+        <v>6844</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -13388,7 +13462,7 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>267840</v>
+        <v>273760</v>
       </c>
       <c r="S13" s="174" t="s">
         <v>83</v>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA737D8B-B16D-49FD-950C-560370254BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6103DFD4-6B4E-4FCB-8621-C853017ABAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="213">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -655,6 +655,12 @@
   </si>
   <si>
     <t>Cantt</t>
+  </si>
+  <si>
+    <t>Euro Academy Road</t>
+  </si>
+  <si>
+    <t>Academy Road</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1936,6 +1942,45 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1972,45 +2017,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2037,6 +2043,17 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2630,13 +2647,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46293</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2658,10 +2675,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2691,13 +2708,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="167"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2716,8 +2733,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2745,29 +2762,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="170"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -10332,29 +10349,29 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="143">
+      <c r="A101" s="183">
         <v>46290</v>
       </c>
-      <c r="B101" s="144">
+      <c r="B101" s="184">
         <v>97</v>
       </c>
-      <c r="C101" s="146" t="s">
+      <c r="C101" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="D101" s="146" t="s">
+      <c r="D101" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E101" s="145"/>
-      <c r="F101" s="145"/>
-      <c r="G101" s="145"/>
-      <c r="H101" s="147"/>
-      <c r="I101" s="145">
+      <c r="E101" s="186"/>
+      <c r="F101" s="186"/>
+      <c r="G101" s="186"/>
+      <c r="H101" s="187"/>
+      <c r="I101" s="186">
         <v>80</v>
       </c>
-      <c r="J101" s="145">
+      <c r="J101" s="186">
         <v>80</v>
       </c>
-      <c r="K101" s="145">
+      <c r="K101" s="186">
         <v>120</v>
       </c>
       <c r="L101" s="122">
@@ -10410,35 +10427,35 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="143">
+      <c r="A102" s="183">
         <v>46290</v>
       </c>
-      <c r="B102" s="144">
+      <c r="B102" s="184">
         <v>98</v>
       </c>
-      <c r="C102" s="146" t="s">
+      <c r="C102" s="185" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="146" t="s">
+      <c r="D102" s="185" t="s">
         <v>104</v>
       </c>
-      <c r="E102" s="145"/>
-      <c r="F102" s="145">
-        <v>40</v>
-      </c>
-      <c r="G102" s="145">
+      <c r="E102" s="186"/>
+      <c r="F102" s="186">
+        <v>40</v>
+      </c>
+      <c r="G102" s="186">
         <v>80</v>
       </c>
-      <c r="H102" s="147">
+      <c r="H102" s="187">
         <v>120</v>
       </c>
-      <c r="I102" s="145">
+      <c r="I102" s="186">
         <v>120</v>
       </c>
-      <c r="J102" s="145">
+      <c r="J102" s="186">
         <v>120</v>
       </c>
-      <c r="K102" s="145">
+      <c r="K102" s="186">
         <v>240</v>
       </c>
       <c r="L102" s="122">
@@ -10494,29 +10511,29 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="143">
+      <c r="A103" s="183">
         <v>46290</v>
       </c>
-      <c r="B103" s="144">
+      <c r="B103" s="184">
         <v>99</v>
       </c>
-      <c r="C103" s="146" t="s">
+      <c r="C103" s="185" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="146" t="s">
+      <c r="D103" s="185" t="s">
         <v>179</v>
       </c>
-      <c r="E103" s="145"/>
-      <c r="F103" s="145"/>
-      <c r="G103" s="145"/>
-      <c r="H103" s="147"/>
-      <c r="I103" s="145">
+      <c r="E103" s="186"/>
+      <c r="F103" s="186"/>
+      <c r="G103" s="186"/>
+      <c r="H103" s="187"/>
+      <c r="I103" s="186">
         <v>80</v>
       </c>
-      <c r="J103" s="145">
+      <c r="J103" s="186">
         <v>80</v>
       </c>
-      <c r="K103" s="145">
+      <c r="K103" s="186">
         <v>80</v>
       </c>
       <c r="L103" s="122">
@@ -10572,35 +10589,35 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="143">
+      <c r="A104" s="183">
         <v>46290</v>
       </c>
-      <c r="B104" s="144">
+      <c r="B104" s="184">
         <v>100</v>
       </c>
-      <c r="C104" s="146" t="s">
+      <c r="C104" s="185" t="s">
         <v>208</v>
       </c>
-      <c r="D104" s="146" t="s">
+      <c r="D104" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="E104" s="145"/>
-      <c r="F104" s="145">
+      <c r="E104" s="186"/>
+      <c r="F104" s="186">
         <v>400</v>
       </c>
-      <c r="G104" s="145">
+      <c r="G104" s="186">
         <v>400</v>
       </c>
-      <c r="H104" s="147">
+      <c r="H104" s="187">
         <v>400</v>
       </c>
-      <c r="I104" s="145">
+      <c r="I104" s="186">
         <v>400</v>
       </c>
-      <c r="J104" s="145">
+      <c r="J104" s="186">
         <v>400</v>
       </c>
-      <c r="K104" s="145">
+      <c r="K104" s="186">
         <v>400</v>
       </c>
       <c r="L104" s="122">
@@ -10656,35 +10673,35 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="143">
+      <c r="A105" s="183">
         <v>46290</v>
       </c>
-      <c r="B105" s="144">
+      <c r="B105" s="184">
         <v>101</v>
       </c>
-      <c r="C105" s="146" t="s">
+      <c r="C105" s="185" t="s">
         <v>209</v>
       </c>
-      <c r="D105" s="146" t="s">
+      <c r="D105" s="185" t="s">
         <v>210</v>
       </c>
-      <c r="E105" s="145"/>
-      <c r="F105" s="145">
+      <c r="E105" s="186"/>
+      <c r="F105" s="186">
         <v>120</v>
       </c>
-      <c r="G105" s="145">
+      <c r="G105" s="186">
         <v>120</v>
       </c>
-      <c r="H105" s="147">
+      <c r="H105" s="187">
         <v>120</v>
       </c>
-      <c r="I105" s="145">
+      <c r="I105" s="186">
         <v>80</v>
       </c>
-      <c r="J105" s="145">
+      <c r="J105" s="186">
         <v>80</v>
       </c>
-      <c r="K105" s="145">
+      <c r="K105" s="186">
         <v>80</v>
       </c>
       <c r="L105" s="122">
@@ -10740,26 +10757,43 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A106" s="72"/>
-      <c r="B106" s="41">
+      <c r="A106" s="143">
+        <v>46291</v>
+      </c>
+      <c r="B106" s="144">
         <v>102</v>
       </c>
-      <c r="C106" s="132"/>
-      <c r="D106" s="132"/>
-      <c r="E106" s="69"/>
-      <c r="F106" s="69"/>
-      <c r="G106" s="69"/>
-      <c r="H106" s="131"/>
-      <c r="I106" s="69"/>
-      <c r="J106" s="69"/>
-      <c r="K106" s="69"/>
+      <c r="C106" s="146" t="s">
+        <v>211</v>
+      </c>
+      <c r="D106" s="146" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" s="145"/>
+      <c r="F106" s="145">
+        <v>40</v>
+      </c>
+      <c r="G106" s="145">
+        <v>40</v>
+      </c>
+      <c r="H106" s="147">
+        <v>40</v>
+      </c>
+      <c r="I106" s="145">
+        <v>40</v>
+      </c>
+      <c r="J106" s="145">
+        <v>40</v>
+      </c>
+      <c r="K106" s="145">
+        <v>40</v>
+      </c>
       <c r="L106" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M106" s="33">
-        <f t="shared" ref="M106:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N106" s="43">
         <f t="shared" si="96"/>
@@ -10767,11 +10801,11 @@
       </c>
       <c r="O106" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P106" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q106" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10825,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="33">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="M106:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N107" s="43">
@@ -12534,10 +12568,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="159" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="160"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -12791,10 +12825,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="172" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="173"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -12878,10 +12912,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="161" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="162"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -12917,7 +12951,7 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1365</v>
+        <v>1379</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
@@ -12925,11 +12959,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>1944.3000000000002</v>
+        <v>1950.3000000000002</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>2917.95</v>
+        <v>2923.95</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -12966,17 +13000,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6103DFD4-6B4E-4FCB-8621-C853017ABAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE26C33-EC18-4DB3-8104-A77C895A4E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1556,7 +1556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1942,6 +1942,42 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1981,42 +2017,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2043,17 +2043,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2647,13 +2636,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
         <v>46293</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2675,10 +2664,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2708,13 +2697,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="167"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2733,8 +2722,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2762,29 +2751,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="170"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -10349,29 +10338,29 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="183">
+      <c r="A101" s="72">
         <v>46290</v>
       </c>
-      <c r="B101" s="184">
+      <c r="B101" s="41">
         <v>97</v>
       </c>
-      <c r="C101" s="185" t="s">
+      <c r="C101" s="132" t="s">
         <v>207</v>
       </c>
-      <c r="D101" s="185" t="s">
+      <c r="D101" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="E101" s="186"/>
-      <c r="F101" s="186"/>
-      <c r="G101" s="186"/>
-      <c r="H101" s="187"/>
-      <c r="I101" s="186">
+      <c r="E101" s="69"/>
+      <c r="F101" s="69"/>
+      <c r="G101" s="69"/>
+      <c r="H101" s="131"/>
+      <c r="I101" s="69">
         <v>80</v>
       </c>
-      <c r="J101" s="186">
+      <c r="J101" s="69">
         <v>80</v>
       </c>
-      <c r="K101" s="186">
+      <c r="K101" s="69">
         <v>120</v>
       </c>
       <c r="L101" s="122">
@@ -10427,35 +10416,35 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="183">
+      <c r="A102" s="72">
         <v>46290</v>
       </c>
-      <c r="B102" s="184">
+      <c r="B102" s="41">
         <v>98</v>
       </c>
-      <c r="C102" s="185" t="s">
+      <c r="C102" s="132" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="185" t="s">
+      <c r="D102" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="E102" s="186"/>
-      <c r="F102" s="186">
-        <v>40</v>
-      </c>
-      <c r="G102" s="186">
+      <c r="E102" s="69"/>
+      <c r="F102" s="69">
+        <v>40</v>
+      </c>
+      <c r="G102" s="69">
         <v>80</v>
       </c>
-      <c r="H102" s="187">
+      <c r="H102" s="131">
         <v>120</v>
       </c>
-      <c r="I102" s="186">
+      <c r="I102" s="69">
         <v>120</v>
       </c>
-      <c r="J102" s="186">
+      <c r="J102" s="69">
         <v>120</v>
       </c>
-      <c r="K102" s="186">
+      <c r="K102" s="69">
         <v>240</v>
       </c>
       <c r="L102" s="122">
@@ -10511,29 +10500,29 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="183">
+      <c r="A103" s="72">
         <v>46290</v>
       </c>
-      <c r="B103" s="184">
+      <c r="B103" s="41">
         <v>99</v>
       </c>
-      <c r="C103" s="185" t="s">
+      <c r="C103" s="132" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="185" t="s">
+      <c r="D103" s="132" t="s">
         <v>179</v>
       </c>
-      <c r="E103" s="186"/>
-      <c r="F103" s="186"/>
-      <c r="G103" s="186"/>
-      <c r="H103" s="187"/>
-      <c r="I103" s="186">
+      <c r="E103" s="69"/>
+      <c r="F103" s="69"/>
+      <c r="G103" s="69"/>
+      <c r="H103" s="131"/>
+      <c r="I103" s="69">
         <v>80</v>
       </c>
-      <c r="J103" s="186">
+      <c r="J103" s="69">
         <v>80</v>
       </c>
-      <c r="K103" s="186">
+      <c r="K103" s="69">
         <v>80</v>
       </c>
       <c r="L103" s="122">
@@ -10589,35 +10578,35 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="183">
+      <c r="A104" s="72">
         <v>46290</v>
       </c>
-      <c r="B104" s="184">
+      <c r="B104" s="41">
         <v>100</v>
       </c>
-      <c r="C104" s="185" t="s">
+      <c r="C104" s="132" t="s">
         <v>208</v>
       </c>
-      <c r="D104" s="185" t="s">
+      <c r="D104" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E104" s="186"/>
-      <c r="F104" s="186">
+      <c r="E104" s="69"/>
+      <c r="F104" s="69">
         <v>400</v>
       </c>
-      <c r="G104" s="186">
+      <c r="G104" s="69">
         <v>400</v>
       </c>
-      <c r="H104" s="187">
+      <c r="H104" s="131">
         <v>400</v>
       </c>
-      <c r="I104" s="186">
+      <c r="I104" s="69">
         <v>400</v>
       </c>
-      <c r="J104" s="186">
+      <c r="J104" s="69">
         <v>400</v>
       </c>
-      <c r="K104" s="186">
+      <c r="K104" s="69">
         <v>400</v>
       </c>
       <c r="L104" s="122">
@@ -10673,35 +10662,35 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="183">
+      <c r="A105" s="72">
         <v>46290</v>
       </c>
-      <c r="B105" s="184">
+      <c r="B105" s="41">
         <v>101</v>
       </c>
-      <c r="C105" s="185" t="s">
+      <c r="C105" s="132" t="s">
         <v>209</v>
       </c>
-      <c r="D105" s="185" t="s">
+      <c r="D105" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="E105" s="186"/>
-      <c r="F105" s="186">
+      <c r="E105" s="69"/>
+      <c r="F105" s="69">
         <v>120</v>
       </c>
-      <c r="G105" s="186">
+      <c r="G105" s="69">
         <v>120</v>
       </c>
-      <c r="H105" s="187">
+      <c r="H105" s="131">
         <v>120</v>
       </c>
-      <c r="I105" s="186">
+      <c r="I105" s="69">
         <v>80</v>
       </c>
-      <c r="J105" s="186">
+      <c r="J105" s="69">
         <v>80</v>
       </c>
-      <c r="K105" s="186">
+      <c r="K105" s="69">
         <v>80</v>
       </c>
       <c r="L105" s="122">
@@ -10859,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="33">
-        <f t="shared" ref="M106:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M107:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N107" s="43">
@@ -12568,10 +12557,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="160"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -12825,10 +12814,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="173"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -12912,10 +12901,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="162"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -13000,17 +12989,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13136,11 +13125,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>10638</v>
+        <v>12171</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>265.95</v>
+        <v>304.27499999999998</v>
       </c>
       <c r="O5" s="75"/>
       <c r="P5" s="142"/>
@@ -13180,11 +13169,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>6966</v>
+        <v>12154</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>174.15</v>
+        <v>303.85000000000002</v>
       </c>
       <c r="O6" s="75"/>
       <c r="P6" s="142"/>
@@ -13215,11 +13204,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>3042</v>
+        <v>9169</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>76.05</v>
+        <v>229.22499999999999</v>
       </c>
       <c r="O7" s="75"/>
       <c r="P7" s="142"/>
@@ -13259,11 +13248,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>3339</v>
+        <v>8692</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>83.474999999999994</v>
+        <v>217.3</v>
       </c>
       <c r="O8" s="75">
         <v>50</v>
@@ -13312,11 +13301,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>4356</v>
+        <v>5183</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>108.9</v>
+        <v>129.57499999999999</v>
       </c>
       <c r="O9" s="75">
         <v>23</v>
@@ -13356,11 +13345,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>7854</v>
+        <v>9154</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>196.35</v>
+        <v>228.85</v>
       </c>
       <c r="O10" s="75"/>
       <c r="P10" s="142"/>
@@ -13452,11 +13441,11 @@
       <c r="L12" s="75"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>36195</v>
+        <v>56523</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>904.875</v>
+        <v>1413.075</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -13555,7 +13544,7 @@
       <c r="N17" s="115"/>
       <c r="O17" s="116">
         <f>N17-M5</f>
-        <v>-10638</v>
+        <v>-12171</v>
       </c>
     </row>
     <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13569,7 +13558,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="116">
         <f>N18-M6</f>
-        <v>-6966</v>
+        <v>-12154</v>
       </c>
     </row>
     <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13586,7 +13575,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="116">
         <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>-3042</v>
+        <v>-9169</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13607,7 +13596,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="116">
         <f t="shared" si="4"/>
-        <v>-3339</v>
+        <v>-8692</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13636,7 +13625,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="116">
         <f t="shared" si="4"/>
-        <v>-4356</v>
+        <v>-5183</v>
       </c>
     </row>
     <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13662,7 +13651,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="116">
         <f t="shared" si="4"/>
-        <v>-7854</v>
+        <v>-9154</v>
       </c>
     </row>
     <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -13718,7 +13707,7 @@
       </c>
       <c r="O24" s="111">
         <f>SUM(O17:O23)</f>
-        <v>-36195</v>
+        <v>-56523</v>
       </c>
     </row>
     <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13748,7 +13737,7 @@
       </c>
       <c r="O25" s="111">
         <f>O24/40</f>
-        <v>-904.875</v>
+        <v>-1413.075</v>
       </c>
     </row>
     <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE26C33-EC18-4DB3-8104-A77C895A4E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F817ED-40B6-457B-A234-93028415C315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="228">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -661,6 +661,51 @@
   </si>
   <si>
     <t>Academy Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Season </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Karim Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Karim Model Town Induction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aslam Cash &amp; Carry </t>
+  </si>
+  <si>
+    <t>College Road</t>
+  </si>
+  <si>
+    <t>Euro College Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galaxy Mart </t>
+  </si>
+  <si>
+    <t>Euro K2</t>
+  </si>
+  <si>
+    <t>Euro Store G1</t>
+  </si>
+  <si>
+    <t>Nishat Colony</t>
+  </si>
+  <si>
+    <t>Euro Nishat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risen Fateh Gher </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Departmental </t>
+  </si>
+  <si>
+    <t>Link Road</t>
   </si>
 </sst>
 </file>
@@ -1556,7 +1601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1940,6 +1985,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2636,13 +2699,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="157">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46295</v>
+      </c>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2664,10 +2727,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="179" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="158" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2697,13 +2760,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166" t="s">
+      <c r="L2" s="171"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="167"/>
+      <c r="P2" s="175"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2722,8 +2785,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="179"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2751,29 +2814,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="170"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="178"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="164" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="165"/>
+      <c r="W3" s="165"/>
+      <c r="X3" s="166"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="179"/>
+      <c r="B4" s="160"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -10746,35 +10809,35 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A106" s="143">
+      <c r="A106" s="72">
         <v>46291</v>
       </c>
-      <c r="B106" s="144">
+      <c r="B106" s="41">
         <v>102</v>
       </c>
-      <c r="C106" s="146" t="s">
+      <c r="C106" s="132" t="s">
         <v>211</v>
       </c>
-      <c r="D106" s="146" t="s">
+      <c r="D106" s="132" t="s">
         <v>212</v>
       </c>
-      <c r="E106" s="145"/>
-      <c r="F106" s="145">
-        <v>40</v>
-      </c>
-      <c r="G106" s="145">
-        <v>40</v>
-      </c>
-      <c r="H106" s="147">
-        <v>40</v>
-      </c>
-      <c r="I106" s="145">
-        <v>40</v>
-      </c>
-      <c r="J106" s="145">
-        <v>40</v>
-      </c>
-      <c r="K106" s="145">
+      <c r="E106" s="69"/>
+      <c r="F106" s="69">
+        <v>40</v>
+      </c>
+      <c r="G106" s="69">
+        <v>40</v>
+      </c>
+      <c r="H106" s="131">
+        <v>40</v>
+      </c>
+      <c r="I106" s="69">
+        <v>40</v>
+      </c>
+      <c r="J106" s="69">
+        <v>40</v>
+      </c>
+      <c r="K106" s="69">
         <v>40</v>
       </c>
       <c r="L106" s="122">
@@ -10830,26 +10893,41 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="72"/>
-      <c r="B107" s="41">
+      <c r="A107" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B107" s="144">
         <v>103</v>
       </c>
-      <c r="C107" s="132"/>
-      <c r="D107" s="132"/>
-      <c r="E107" s="69"/>
-      <c r="F107" s="69"/>
-      <c r="G107" s="69"/>
-      <c r="H107" s="131"/>
-      <c r="I107" s="69"/>
-      <c r="J107" s="69"/>
-      <c r="K107" s="69"/>
+      <c r="C107" s="146" t="s">
+        <v>213</v>
+      </c>
+      <c r="D107" s="146" t="s">
+        <v>133</v>
+      </c>
+      <c r="E107" s="145"/>
+      <c r="F107" s="145">
+        <v>120</v>
+      </c>
+      <c r="G107" s="145"/>
+      <c r="H107" s="147">
+        <v>120</v>
+      </c>
+      <c r="I107" s="145">
+        <v>120</v>
+      </c>
+      <c r="J107" s="145">
+        <v>80</v>
+      </c>
+      <c r="K107" s="145">
+        <v>80</v>
+      </c>
       <c r="L107" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M107" s="33">
-        <f t="shared" ref="M107:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N107" s="43">
         <f t="shared" si="96"/>
@@ -10857,11 +10935,11 @@
       </c>
       <c r="O107" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P107" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q107" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10897,26 +10975,43 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="72"/>
-      <c r="B108" s="41">
+      <c r="A108" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B108" s="144">
         <v>104</v>
       </c>
-      <c r="C108" s="132"/>
-      <c r="D108" s="132"/>
-      <c r="E108" s="69"/>
-      <c r="F108" s="69"/>
-      <c r="G108" s="69"/>
-      <c r="H108" s="131"/>
-      <c r="I108" s="69"/>
-      <c r="J108" s="69"/>
-      <c r="K108" s="69"/>
+      <c r="C108" s="146" t="s">
+        <v>214</v>
+      </c>
+      <c r="D108" s="146" t="s">
+        <v>113</v>
+      </c>
+      <c r="E108" s="145"/>
+      <c r="F108" s="145">
+        <v>120</v>
+      </c>
+      <c r="G108" s="145">
+        <v>120</v>
+      </c>
+      <c r="H108" s="147">
+        <v>200</v>
+      </c>
+      <c r="I108" s="145">
+        <v>120</v>
+      </c>
+      <c r="J108" s="145">
+        <v>120</v>
+      </c>
+      <c r="K108" s="145">
+        <v>200</v>
+      </c>
       <c r="L108" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M108" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N108" s="43">
         <f t="shared" si="96"/>
@@ -10924,11 +11019,11 @@
       </c>
       <c r="O108" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P108" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q108" s="45" t="e">
         <f t="shared" si="94"/>
@@ -10964,26 +11059,43 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="72"/>
-      <c r="B109" s="41">
+      <c r="A109" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B109" s="144">
         <v>105</v>
       </c>
-      <c r="C109" s="132"/>
-      <c r="D109" s="132"/>
-      <c r="E109" s="69"/>
-      <c r="F109" s="69"/>
-      <c r="G109" s="69"/>
-      <c r="H109" s="131"/>
-      <c r="I109" s="69"/>
-      <c r="J109" s="69"/>
-      <c r="K109" s="69"/>
+      <c r="C109" s="146" t="s">
+        <v>215</v>
+      </c>
+      <c r="D109" s="146" t="s">
+        <v>113</v>
+      </c>
+      <c r="E109" s="145"/>
+      <c r="F109" s="145">
+        <v>40</v>
+      </c>
+      <c r="G109" s="145">
+        <v>40</v>
+      </c>
+      <c r="H109" s="147">
+        <v>40</v>
+      </c>
+      <c r="I109" s="145">
+        <v>40</v>
+      </c>
+      <c r="J109" s="145">
+        <v>40</v>
+      </c>
+      <c r="K109" s="145">
+        <v>40</v>
+      </c>
       <c r="L109" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M109" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N109" s="43">
         <f t="shared" si="96"/>
@@ -10991,11 +11103,11 @@
       </c>
       <c r="O109" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P109" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q109" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11031,26 +11143,43 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="72"/>
-      <c r="B110" s="41">
+      <c r="A110" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="144">
         <v>106</v>
       </c>
-      <c r="C110" s="132"/>
-      <c r="D110" s="132"/>
-      <c r="E110" s="69"/>
-      <c r="F110" s="69"/>
-      <c r="G110" s="69"/>
-      <c r="H110" s="131"/>
-      <c r="I110" s="69"/>
-      <c r="J110" s="69"/>
-      <c r="K110" s="69"/>
+      <c r="C110" s="146" t="s">
+        <v>216</v>
+      </c>
+      <c r="D110" s="146" t="s">
+        <v>217</v>
+      </c>
+      <c r="E110" s="145"/>
+      <c r="F110" s="145">
+        <v>40</v>
+      </c>
+      <c r="G110" s="145">
+        <v>80</v>
+      </c>
+      <c r="H110" s="147">
+        <v>120</v>
+      </c>
+      <c r="I110" s="145">
+        <v>40</v>
+      </c>
+      <c r="J110" s="145">
+        <v>80</v>
+      </c>
+      <c r="K110" s="145">
+        <v>120</v>
+      </c>
       <c r="L110" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M110" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N110" s="43">
         <f t="shared" si="96"/>
@@ -11058,11 +11187,11 @@
       </c>
       <c r="O110" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P110" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q110" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11098,26 +11227,43 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="72"/>
-      <c r="B111" s="41">
+      <c r="A111" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B111" s="144">
         <v>107</v>
       </c>
-      <c r="C111" s="121"/>
-      <c r="D111" s="121"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="122"/>
-      <c r="I111" s="44"/>
-      <c r="J111" s="44"/>
-      <c r="K111" s="44"/>
+      <c r="C111" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="D111" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="E111" s="150"/>
+      <c r="F111" s="150">
+        <v>80</v>
+      </c>
+      <c r="G111" s="150">
+        <v>80</v>
+      </c>
+      <c r="H111" s="151">
+        <v>120</v>
+      </c>
+      <c r="I111" s="150">
+        <v>80</v>
+      </c>
+      <c r="J111" s="150">
+        <v>80</v>
+      </c>
+      <c r="K111" s="150">
+        <v>120</v>
+      </c>
       <c r="L111" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M111" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N111" s="43">
         <f t="shared" si="96"/>
@@ -11125,11 +11271,11 @@
       </c>
       <c r="O111" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P111" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q111" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11165,26 +11311,43 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="72"/>
-      <c r="B112" s="41">
+      <c r="A112" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="144">
         <v>108</v>
       </c>
-      <c r="C112" s="121"/>
-      <c r="D112" s="121"/>
-      <c r="E112" s="44"/>
-      <c r="F112" s="44"/>
-      <c r="G112" s="44"/>
-      <c r="H112" s="122"/>
-      <c r="I112" s="44"/>
-      <c r="J112" s="44"/>
-      <c r="K112" s="44"/>
+      <c r="C112" s="149" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" s="149" t="s">
+        <v>113</v>
+      </c>
+      <c r="E112" s="150"/>
+      <c r="F112" s="150">
+        <v>120</v>
+      </c>
+      <c r="G112" s="150">
+        <v>120</v>
+      </c>
+      <c r="H112" s="151">
+        <v>180</v>
+      </c>
+      <c r="I112" s="150">
+        <v>120</v>
+      </c>
+      <c r="J112" s="150">
+        <v>120</v>
+      </c>
+      <c r="K112" s="150">
+        <v>200</v>
+      </c>
       <c r="L112" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="M112" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N112" s="43">
         <f t="shared" si="96"/>
@@ -11192,11 +11355,11 @@
       </c>
       <c r="O112" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P112" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q112" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11232,26 +11395,43 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="72"/>
-      <c r="B113" s="41">
+      <c r="A113" s="143">
+        <v>46293</v>
+      </c>
+      <c r="B113" s="144">
         <v>109</v>
       </c>
-      <c r="C113" s="121"/>
-      <c r="D113" s="121"/>
-      <c r="E113" s="44"/>
-      <c r="F113" s="44"/>
-      <c r="G113" s="44"/>
-      <c r="H113" s="122"/>
-      <c r="I113" s="44"/>
-      <c r="J113" s="44"/>
-      <c r="K113" s="44"/>
+      <c r="C113" s="149" t="s">
+        <v>220</v>
+      </c>
+      <c r="D113" s="149" t="s">
+        <v>133</v>
+      </c>
+      <c r="E113" s="150"/>
+      <c r="F113" s="150">
+        <v>80</v>
+      </c>
+      <c r="G113" s="150">
+        <v>80</v>
+      </c>
+      <c r="H113" s="151">
+        <v>80</v>
+      </c>
+      <c r="I113" s="150">
+        <v>80</v>
+      </c>
+      <c r="J113" s="150">
+        <v>80</v>
+      </c>
+      <c r="K113" s="150">
+        <v>80</v>
+      </c>
       <c r="L113" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M113" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N113" s="43">
         <f t="shared" si="96"/>
@@ -11259,11 +11439,11 @@
       </c>
       <c r="O113" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P113" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q113" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11299,26 +11479,43 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="72"/>
-      <c r="B114" s="41">
+      <c r="A114" s="152">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="153">
         <v>110</v>
       </c>
-      <c r="C114" s="121"/>
-      <c r="D114" s="121"/>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="122"/>
-      <c r="I114" s="44"/>
-      <c r="J114" s="44"/>
-      <c r="K114" s="44"/>
+      <c r="C114" s="154" t="s">
+        <v>221</v>
+      </c>
+      <c r="D114" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="E114" s="155"/>
+      <c r="F114" s="155">
+        <v>80</v>
+      </c>
+      <c r="G114" s="155">
+        <v>80</v>
+      </c>
+      <c r="H114" s="156">
+        <v>80</v>
+      </c>
+      <c r="I114" s="155">
+        <v>80</v>
+      </c>
+      <c r="J114" s="155">
+        <v>80</v>
+      </c>
+      <c r="K114" s="155">
+        <v>80</v>
+      </c>
       <c r="L114" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M114" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N114" s="43">
         <f t="shared" si="96"/>
@@ -11326,11 +11523,11 @@
       </c>
       <c r="O114" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P114" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q114" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11366,26 +11563,43 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="72"/>
-      <c r="B115" s="41">
+      <c r="A115" s="152">
+        <v>46294</v>
+      </c>
+      <c r="B115" s="153">
         <v>111</v>
       </c>
-      <c r="C115" s="121"/>
-      <c r="D115" s="121"/>
-      <c r="E115" s="44"/>
-      <c r="F115" s="44"/>
-      <c r="G115" s="44"/>
-      <c r="H115" s="122"/>
-      <c r="I115" s="44"/>
-      <c r="J115" s="44"/>
-      <c r="K115" s="44"/>
+      <c r="C115" s="154" t="s">
+        <v>222</v>
+      </c>
+      <c r="D115" s="154" t="s">
+        <v>179</v>
+      </c>
+      <c r="E115" s="155"/>
+      <c r="F115" s="155">
+        <v>131</v>
+      </c>
+      <c r="G115" s="155">
+        <v>120</v>
+      </c>
+      <c r="H115" s="156">
+        <v>200</v>
+      </c>
+      <c r="I115" s="155">
+        <v>200</v>
+      </c>
+      <c r="J115" s="155">
+        <v>106</v>
+      </c>
+      <c r="K115" s="155">
+        <v>200</v>
+      </c>
       <c r="L115" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>23.925000000000001</v>
       </c>
       <c r="M115" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N115" s="43">
         <f t="shared" si="96"/>
@@ -11393,11 +11607,11 @@
       </c>
       <c r="O115" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="P115" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="Q115" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11433,26 +11647,43 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="72"/>
-      <c r="B116" s="41">
+      <c r="A116" s="152">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="153">
         <v>112</v>
       </c>
-      <c r="C116" s="121"/>
-      <c r="D116" s="121"/>
-      <c r="E116" s="44"/>
-      <c r="F116" s="44"/>
-      <c r="G116" s="44"/>
-      <c r="H116" s="122"/>
-      <c r="I116" s="44"/>
-      <c r="J116" s="44"/>
-      <c r="K116" s="44"/>
+      <c r="C116" s="154" t="s">
+        <v>224</v>
+      </c>
+      <c r="D116" s="154" t="s">
+        <v>223</v>
+      </c>
+      <c r="E116" s="155"/>
+      <c r="F116" s="155">
+        <v>40</v>
+      </c>
+      <c r="G116" s="155">
+        <v>40</v>
+      </c>
+      <c r="H116" s="156">
+        <v>40</v>
+      </c>
+      <c r="I116" s="155">
+        <v>40</v>
+      </c>
+      <c r="J116" s="155">
+        <v>40</v>
+      </c>
+      <c r="K116" s="155">
+        <v>40</v>
+      </c>
       <c r="L116" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M116" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N116" s="43">
         <f t="shared" si="96"/>
@@ -11460,11 +11691,11 @@
       </c>
       <c r="O116" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P116" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q116" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11500,26 +11731,37 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="72"/>
-      <c r="B117" s="41">
+      <c r="A117" s="152">
+        <v>46294</v>
+      </c>
+      <c r="B117" s="153">
         <v>113</v>
       </c>
-      <c r="C117" s="121"/>
-      <c r="D117" s="121"/>
-      <c r="E117" s="44"/>
-      <c r="F117" s="44"/>
-      <c r="G117" s="44"/>
-      <c r="H117" s="122"/>
-      <c r="I117" s="44"/>
-      <c r="J117" s="44"/>
-      <c r="K117" s="44"/>
+      <c r="C117" s="154" t="s">
+        <v>225</v>
+      </c>
+      <c r="D117" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="E117" s="155"/>
+      <c r="F117" s="155"/>
+      <c r="G117" s="155"/>
+      <c r="H117" s="156"/>
+      <c r="I117" s="155">
+        <v>680</v>
+      </c>
+      <c r="J117" s="155">
+        <v>680</v>
+      </c>
+      <c r="K117" s="155">
+        <v>680</v>
+      </c>
       <c r="L117" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M117" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N117" s="43">
         <f t="shared" si="96"/>
@@ -11531,7 +11773,7 @@
       </c>
       <c r="P117" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Q117" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11567,26 +11809,43 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="72"/>
-      <c r="B118" s="41">
+      <c r="A118" s="152">
+        <v>46294</v>
+      </c>
+      <c r="B118" s="153">
         <v>114</v>
       </c>
-      <c r="C118" s="121"/>
-      <c r="D118" s="121"/>
-      <c r="E118" s="44"/>
-      <c r="F118" s="44"/>
-      <c r="G118" s="44"/>
-      <c r="H118" s="122"/>
-      <c r="I118" s="44"/>
-      <c r="J118" s="44"/>
-      <c r="K118" s="44"/>
+      <c r="C118" s="154" t="s">
+        <v>226</v>
+      </c>
+      <c r="D118" s="154" t="s">
+        <v>227</v>
+      </c>
+      <c r="E118" s="155"/>
+      <c r="F118" s="155">
+        <v>79</v>
+      </c>
+      <c r="G118" s="155">
+        <v>80</v>
+      </c>
+      <c r="H118" s="156">
+        <v>200</v>
+      </c>
+      <c r="I118" s="155">
+        <v>80</v>
+      </c>
+      <c r="J118" s="155">
+        <v>80</v>
+      </c>
+      <c r="K118" s="155">
+        <v>200</v>
+      </c>
       <c r="L118" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>17.975000000000001</v>
       </c>
       <c r="M118" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N118" s="43">
         <f t="shared" si="96"/>
@@ -11594,11 +11853,11 @@
       </c>
       <c r="O118" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>17.95</v>
       </c>
       <c r="P118" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q118" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11652,7 +11911,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="33">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="M119:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N119" s="43">
@@ -12557,10 +12816,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="159" t="s">
+      <c r="B133" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="160"/>
+      <c r="C133" s="168"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -12814,10 +13073,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="172" t="s">
+      <c r="B137" s="180" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="173"/>
+      <c r="C137" s="181"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -12901,10 +13160,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="161" t="s">
+      <c r="B138" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="162"/>
+      <c r="C138" s="170"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -12940,7 +13199,7 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1379</v>
+        <v>1540</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
@@ -12948,11 +13207,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>1950.3000000000002</v>
+        <v>2107.8000000000002</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>2923.95</v>
+        <v>3189.25</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -13035,25 +13294,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="184" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="189"/>
+      <c r="K3" s="190" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="190"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -13099,24 +13358,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>884</v>
+        <v>1047</v>
       </c>
       <c r="E5" s="73">
-        <v>1660</v>
+        <v>1877</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>2644</v>
+        <v>3024</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-7356</v>
+        <v>-6976</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -13140,11 +13399,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>35360</v>
+        <v>41880</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>66400</v>
+        <v>75080</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -13152,7 +13411,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>105760</v>
+        <v>120960</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -13160,7 +13419,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-294240</v>
+        <v>-279040</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -13288,11 +13547,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-884</v>
+        <v>-1047</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1660</v>
+        <v>-1877</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -13376,14 +13635,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="187" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="187"/>
+      <c r="F11" s="187" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="187"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -13433,7 +13692,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>6844</v>
+        <v>7224</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -13485,12 +13744,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>273760</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>288960</v>
+      </c>
+      <c r="S13" s="182" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="182"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13579,13 +13838,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="183"/>
+      <c r="F20" s="183"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="183"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F817ED-40B6-457B-A234-93028415C315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE20F019-6F58-4437-8E52-D201215CD330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="231">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -706,6 +706,15 @@
   </si>
   <si>
     <t>Link Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aster Super Market </t>
+  </si>
+  <si>
+    <t>Canal Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Rachna </t>
   </si>
 </sst>
 </file>
@@ -1977,13 +1986,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1994,15 +1996,43 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2041,45 +2071,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2106,6 +2097,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2699,13 +2708,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="157">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
-      </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
+        <v>46296</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2727,10 +2736,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2760,13 +2769,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="171"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="173"/>
-      <c r="O2" s="174" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="175"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2785,8 +2794,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="179"/>
-      <c r="B3" s="159"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2814,29 +2823,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="176" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="177"/>
-      <c r="N3" s="178"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="161" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="164" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="165"/>
-      <c r="W3" s="165"/>
-      <c r="X3" s="166"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="179"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -9522,7 +9531,7 @@
         <f t="shared" si="80"/>
         <v>12</v>
       </c>
-      <c r="M90" s="148">
+      <c r="M90" s="145">
         <v>12.5</v>
       </c>
       <c r="N90" s="43">
@@ -9606,7 +9615,7 @@
         <f t="shared" si="80"/>
         <v>6</v>
       </c>
-      <c r="M91" s="148">
+      <c r="M91" s="145">
         <v>12.5</v>
       </c>
       <c r="N91" s="43">
@@ -9690,7 +9699,7 @@
         <f t="shared" si="80"/>
         <v>12</v>
       </c>
-      <c r="M92" s="148">
+      <c r="M92" s="145">
         <v>12.5</v>
       </c>
       <c r="N92" s="43">
@@ -9774,7 +9783,7 @@
         <f t="shared" si="80"/>
         <v>6</v>
       </c>
-      <c r="M93" s="148">
+      <c r="M93" s="145">
         <v>12.5</v>
       </c>
       <c r="N93" s="43">
@@ -10893,33 +10902,33 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="143">
+      <c r="A107" s="183">
         <v>46293</v>
       </c>
-      <c r="B107" s="144">
+      <c r="B107" s="184">
         <v>103</v>
       </c>
-      <c r="C107" s="146" t="s">
+      <c r="C107" s="185" t="s">
         <v>213</v>
       </c>
-      <c r="D107" s="146" t="s">
+      <c r="D107" s="185" t="s">
         <v>133</v>
       </c>
-      <c r="E107" s="145"/>
-      <c r="F107" s="145">
+      <c r="E107" s="186"/>
+      <c r="F107" s="186">
         <v>120</v>
       </c>
-      <c r="G107" s="145"/>
-      <c r="H107" s="147">
+      <c r="G107" s="186"/>
+      <c r="H107" s="187">
         <v>120</v>
       </c>
-      <c r="I107" s="145">
+      <c r="I107" s="186">
         <v>120</v>
       </c>
-      <c r="J107" s="145">
-        <v>80</v>
-      </c>
-      <c r="K107" s="145">
+      <c r="J107" s="186">
+        <v>80</v>
+      </c>
+      <c r="K107" s="186">
         <v>80</v>
       </c>
       <c r="L107" s="122">
@@ -10975,35 +10984,35 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="143">
+      <c r="A108" s="183">
         <v>46293</v>
       </c>
-      <c r="B108" s="144">
+      <c r="B108" s="184">
         <v>104</v>
       </c>
-      <c r="C108" s="146" t="s">
+      <c r="C108" s="185" t="s">
         <v>214</v>
       </c>
-      <c r="D108" s="146" t="s">
+      <c r="D108" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="E108" s="145"/>
-      <c r="F108" s="145">
+      <c r="E108" s="186"/>
+      <c r="F108" s="186">
         <v>120</v>
       </c>
-      <c r="G108" s="145">
+      <c r="G108" s="186">
         <v>120</v>
       </c>
-      <c r="H108" s="147">
+      <c r="H108" s="187">
         <v>200</v>
       </c>
-      <c r="I108" s="145">
+      <c r="I108" s="186">
         <v>120</v>
       </c>
-      <c r="J108" s="145">
+      <c r="J108" s="186">
         <v>120</v>
       </c>
-      <c r="K108" s="145">
+      <c r="K108" s="186">
         <v>200</v>
       </c>
       <c r="L108" s="122">
@@ -11059,35 +11068,35 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="143">
+      <c r="A109" s="183">
         <v>46293</v>
       </c>
-      <c r="B109" s="144">
+      <c r="B109" s="184">
         <v>105</v>
       </c>
-      <c r="C109" s="146" t="s">
+      <c r="C109" s="185" t="s">
         <v>215</v>
       </c>
-      <c r="D109" s="146" t="s">
+      <c r="D109" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="E109" s="145"/>
-      <c r="F109" s="145">
-        <v>40</v>
-      </c>
-      <c r="G109" s="145">
-        <v>40</v>
-      </c>
-      <c r="H109" s="147">
-        <v>40</v>
-      </c>
-      <c r="I109" s="145">
-        <v>40</v>
-      </c>
-      <c r="J109" s="145">
-        <v>40</v>
-      </c>
-      <c r="K109" s="145">
+      <c r="E109" s="186"/>
+      <c r="F109" s="186">
+        <v>40</v>
+      </c>
+      <c r="G109" s="186">
+        <v>40</v>
+      </c>
+      <c r="H109" s="187">
+        <v>40</v>
+      </c>
+      <c r="I109" s="186">
+        <v>40</v>
+      </c>
+      <c r="J109" s="186">
+        <v>40</v>
+      </c>
+      <c r="K109" s="186">
         <v>40</v>
       </c>
       <c r="L109" s="122">
@@ -11143,35 +11152,35 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="143">
+      <c r="A110" s="183">
         <v>46293</v>
       </c>
-      <c r="B110" s="144">
+      <c r="B110" s="184">
         <v>106</v>
       </c>
-      <c r="C110" s="146" t="s">
+      <c r="C110" s="185" t="s">
         <v>216</v>
       </c>
-      <c r="D110" s="146" t="s">
+      <c r="D110" s="185" t="s">
         <v>217</v>
       </c>
-      <c r="E110" s="145"/>
-      <c r="F110" s="145">
-        <v>40</v>
-      </c>
-      <c r="G110" s="145">
-        <v>80</v>
-      </c>
-      <c r="H110" s="147">
+      <c r="E110" s="186"/>
+      <c r="F110" s="186">
+        <v>40</v>
+      </c>
+      <c r="G110" s="186">
+        <v>80</v>
+      </c>
+      <c r="H110" s="187">
         <v>120</v>
       </c>
-      <c r="I110" s="145">
-        <v>40</v>
-      </c>
-      <c r="J110" s="145">
-        <v>80</v>
-      </c>
-      <c r="K110" s="145">
+      <c r="I110" s="186">
+        <v>40</v>
+      </c>
+      <c r="J110" s="186">
+        <v>80</v>
+      </c>
+      <c r="K110" s="186">
         <v>120</v>
       </c>
       <c r="L110" s="122">
@@ -11227,35 +11236,35 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="143">
+      <c r="A111" s="183">
         <v>46293</v>
       </c>
-      <c r="B111" s="144">
+      <c r="B111" s="184">
         <v>107</v>
       </c>
-      <c r="C111" s="149" t="s">
+      <c r="C111" s="188" t="s">
         <v>218</v>
       </c>
-      <c r="D111" s="149" t="s">
+      <c r="D111" s="188" t="s">
         <v>217</v>
       </c>
-      <c r="E111" s="150"/>
-      <c r="F111" s="150">
-        <v>80</v>
-      </c>
-      <c r="G111" s="150">
-        <v>80</v>
-      </c>
-      <c r="H111" s="151">
+      <c r="E111" s="189"/>
+      <c r="F111" s="189">
+        <v>80</v>
+      </c>
+      <c r="G111" s="189">
+        <v>80</v>
+      </c>
+      <c r="H111" s="190">
         <v>120</v>
       </c>
-      <c r="I111" s="150">
-        <v>80</v>
-      </c>
-      <c r="J111" s="150">
-        <v>80</v>
-      </c>
-      <c r="K111" s="150">
+      <c r="I111" s="189">
+        <v>80</v>
+      </c>
+      <c r="J111" s="189">
+        <v>80</v>
+      </c>
+      <c r="K111" s="189">
         <v>120</v>
       </c>
       <c r="L111" s="122">
@@ -11311,35 +11320,35 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="143">
+      <c r="A112" s="183">
         <v>46293</v>
       </c>
-      <c r="B112" s="144">
+      <c r="B112" s="184">
         <v>108</v>
       </c>
-      <c r="C112" s="149" t="s">
+      <c r="C112" s="188" t="s">
         <v>219</v>
       </c>
-      <c r="D112" s="149" t="s">
+      <c r="D112" s="188" t="s">
         <v>113</v>
       </c>
-      <c r="E112" s="150"/>
-      <c r="F112" s="150">
+      <c r="E112" s="189"/>
+      <c r="F112" s="189">
         <v>120</v>
       </c>
-      <c r="G112" s="150">
+      <c r="G112" s="189">
         <v>120</v>
       </c>
-      <c r="H112" s="151">
+      <c r="H112" s="190">
         <v>180</v>
       </c>
-      <c r="I112" s="150">
+      <c r="I112" s="189">
         <v>120</v>
       </c>
-      <c r="J112" s="150">
+      <c r="J112" s="189">
         <v>120</v>
       </c>
-      <c r="K112" s="150">
+      <c r="K112" s="189">
         <v>200</v>
       </c>
       <c r="L112" s="122">
@@ -11395,35 +11404,35 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="143">
+      <c r="A113" s="183">
         <v>46293</v>
       </c>
-      <c r="B113" s="144">
+      <c r="B113" s="184">
         <v>109</v>
       </c>
-      <c r="C113" s="149" t="s">
+      <c r="C113" s="188" t="s">
         <v>220</v>
       </c>
-      <c r="D113" s="149" t="s">
+      <c r="D113" s="188" t="s">
         <v>133</v>
       </c>
-      <c r="E113" s="150"/>
-      <c r="F113" s="150">
-        <v>80</v>
-      </c>
-      <c r="G113" s="150">
-        <v>80</v>
-      </c>
-      <c r="H113" s="151">
-        <v>80</v>
-      </c>
-      <c r="I113" s="150">
-        <v>80</v>
-      </c>
-      <c r="J113" s="150">
-        <v>80</v>
-      </c>
-      <c r="K113" s="150">
+      <c r="E113" s="189"/>
+      <c r="F113" s="189">
+        <v>80</v>
+      </c>
+      <c r="G113" s="189">
+        <v>80</v>
+      </c>
+      <c r="H113" s="190">
+        <v>80</v>
+      </c>
+      <c r="I113" s="189">
+        <v>80</v>
+      </c>
+      <c r="J113" s="189">
+        <v>80</v>
+      </c>
+      <c r="K113" s="189">
         <v>80</v>
       </c>
       <c r="L113" s="122">
@@ -11479,35 +11488,35 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="152">
+      <c r="A114" s="183">
         <v>46294</v>
       </c>
-      <c r="B114" s="153">
+      <c r="B114" s="184">
         <v>110</v>
       </c>
-      <c r="C114" s="154" t="s">
+      <c r="C114" s="188" t="s">
         <v>221</v>
       </c>
-      <c r="D114" s="154" t="s">
+      <c r="D114" s="188" t="s">
         <v>114</v>
       </c>
-      <c r="E114" s="155"/>
-      <c r="F114" s="155">
-        <v>80</v>
-      </c>
-      <c r="G114" s="155">
-        <v>80</v>
-      </c>
-      <c r="H114" s="156">
-        <v>80</v>
-      </c>
-      <c r="I114" s="155">
-        <v>80</v>
-      </c>
-      <c r="J114" s="155">
-        <v>80</v>
-      </c>
-      <c r="K114" s="155">
+      <c r="E114" s="189"/>
+      <c r="F114" s="189">
+        <v>80</v>
+      </c>
+      <c r="G114" s="189">
+        <v>80</v>
+      </c>
+      <c r="H114" s="190">
+        <v>80</v>
+      </c>
+      <c r="I114" s="189">
+        <v>80</v>
+      </c>
+      <c r="J114" s="189">
+        <v>80</v>
+      </c>
+      <c r="K114" s="189">
         <v>80</v>
       </c>
       <c r="L114" s="122">
@@ -11563,35 +11572,35 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="152">
+      <c r="A115" s="183">
         <v>46294</v>
       </c>
-      <c r="B115" s="153">
+      <c r="B115" s="184">
         <v>111</v>
       </c>
-      <c r="C115" s="154" t="s">
+      <c r="C115" s="188" t="s">
         <v>222</v>
       </c>
-      <c r="D115" s="154" t="s">
+      <c r="D115" s="188" t="s">
         <v>179</v>
       </c>
-      <c r="E115" s="155"/>
-      <c r="F115" s="155">
+      <c r="E115" s="189"/>
+      <c r="F115" s="189">
         <v>131</v>
       </c>
-      <c r="G115" s="155">
+      <c r="G115" s="189">
         <v>120</v>
       </c>
-      <c r="H115" s="156">
+      <c r="H115" s="190">
         <v>200</v>
       </c>
-      <c r="I115" s="155">
+      <c r="I115" s="189">
         <v>200</v>
       </c>
-      <c r="J115" s="155">
+      <c r="J115" s="189">
         <v>106</v>
       </c>
-      <c r="K115" s="155">
+      <c r="K115" s="189">
         <v>200</v>
       </c>
       <c r="L115" s="122">
@@ -11647,35 +11656,35 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="152">
+      <c r="A116" s="183">
         <v>46294</v>
       </c>
-      <c r="B116" s="153">
+      <c r="B116" s="184">
         <v>112</v>
       </c>
-      <c r="C116" s="154" t="s">
+      <c r="C116" s="188" t="s">
         <v>224</v>
       </c>
-      <c r="D116" s="154" t="s">
+      <c r="D116" s="188" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="155"/>
-      <c r="F116" s="155">
-        <v>40</v>
-      </c>
-      <c r="G116" s="155">
-        <v>40</v>
-      </c>
-      <c r="H116" s="156">
-        <v>40</v>
-      </c>
-      <c r="I116" s="155">
-        <v>40</v>
-      </c>
-      <c r="J116" s="155">
-        <v>40</v>
-      </c>
-      <c r="K116" s="155">
+      <c r="E116" s="189"/>
+      <c r="F116" s="189">
+        <v>40</v>
+      </c>
+      <c r="G116" s="189">
+        <v>40</v>
+      </c>
+      <c r="H116" s="190">
+        <v>40</v>
+      </c>
+      <c r="I116" s="189">
+        <v>40</v>
+      </c>
+      <c r="J116" s="189">
+        <v>40</v>
+      </c>
+      <c r="K116" s="189">
         <v>40</v>
       </c>
       <c r="L116" s="122">
@@ -11731,29 +11740,29 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="152">
+      <c r="A117" s="183">
         <v>46294</v>
       </c>
-      <c r="B117" s="153">
+      <c r="B117" s="184">
         <v>113</v>
       </c>
-      <c r="C117" s="154" t="s">
+      <c r="C117" s="188" t="s">
         <v>225</v>
       </c>
-      <c r="D117" s="154" t="s">
+      <c r="D117" s="188" t="s">
         <v>140</v>
       </c>
-      <c r="E117" s="155"/>
-      <c r="F117" s="155"/>
-      <c r="G117" s="155"/>
-      <c r="H117" s="156"/>
-      <c r="I117" s="155">
+      <c r="E117" s="189"/>
+      <c r="F117" s="189"/>
+      <c r="G117" s="189"/>
+      <c r="H117" s="190"/>
+      <c r="I117" s="189">
         <v>680</v>
       </c>
-      <c r="J117" s="155">
+      <c r="J117" s="189">
         <v>680</v>
       </c>
-      <c r="K117" s="155">
+      <c r="K117" s="189">
         <v>680</v>
       </c>
       <c r="L117" s="122">
@@ -11809,35 +11818,35 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="152">
+      <c r="A118" s="183">
         <v>46294</v>
       </c>
-      <c r="B118" s="153">
+      <c r="B118" s="184">
         <v>114</v>
       </c>
-      <c r="C118" s="154" t="s">
+      <c r="C118" s="188" t="s">
         <v>226</v>
       </c>
-      <c r="D118" s="154" t="s">
+      <c r="D118" s="188" t="s">
         <v>227</v>
       </c>
-      <c r="E118" s="155"/>
-      <c r="F118" s="155">
+      <c r="E118" s="189"/>
+      <c r="F118" s="189">
         <v>79</v>
       </c>
-      <c r="G118" s="155">
-        <v>80</v>
-      </c>
-      <c r="H118" s="156">
+      <c r="G118" s="189">
+        <v>80</v>
+      </c>
+      <c r="H118" s="190">
         <v>200</v>
       </c>
-      <c r="I118" s="155">
-        <v>80</v>
-      </c>
-      <c r="J118" s="155">
-        <v>80</v>
-      </c>
-      <c r="K118" s="155">
+      <c r="I118" s="189">
+        <v>80</v>
+      </c>
+      <c r="J118" s="189">
+        <v>80</v>
+      </c>
+      <c r="K118" s="189">
         <v>200</v>
       </c>
       <c r="L118" s="122">
@@ -11893,26 +11902,43 @@
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A119" s="72"/>
-      <c r="B119" s="41">
+      <c r="A119" s="143">
+        <v>46295</v>
+      </c>
+      <c r="B119" s="144">
         <v>115</v>
       </c>
-      <c r="C119" s="121"/>
-      <c r="D119" s="121"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-      <c r="G119" s="44"/>
-      <c r="H119" s="122"/>
-      <c r="I119" s="44"/>
-      <c r="J119" s="44"/>
-      <c r="K119" s="44"/>
+      <c r="C119" s="146" t="s">
+        <v>228</v>
+      </c>
+      <c r="D119" s="146" t="s">
+        <v>229</v>
+      </c>
+      <c r="E119" s="147"/>
+      <c r="F119" s="147">
+        <v>80</v>
+      </c>
+      <c r="G119" s="147">
+        <v>80</v>
+      </c>
+      <c r="H119" s="148">
+        <v>120</v>
+      </c>
+      <c r="I119" s="147">
+        <v>80</v>
+      </c>
+      <c r="J119" s="147">
+        <v>80</v>
+      </c>
+      <c r="K119" s="147">
+        <v>120</v>
+      </c>
       <c r="L119" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M119" s="33">
-        <f t="shared" ref="M119:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N119" s="43">
         <f t="shared" si="96"/>
@@ -11920,11 +11946,11 @@
       </c>
       <c r="O119" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P119" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q119" s="45" t="e">
         <f t="shared" si="94"/>
@@ -11960,26 +11986,37 @@
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A120" s="72"/>
-      <c r="B120" s="41">
+      <c r="A120" s="143">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="144">
         <v>116</v>
       </c>
-      <c r="C120" s="121"/>
-      <c r="D120" s="121"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
-      <c r="H120" s="122"/>
-      <c r="I120" s="44"/>
-      <c r="J120" s="44"/>
-      <c r="K120" s="44"/>
+      <c r="C120" s="146" t="s">
+        <v>230</v>
+      </c>
+      <c r="D120" s="146" t="s">
+        <v>138</v>
+      </c>
+      <c r="E120" s="147"/>
+      <c r="F120" s="147"/>
+      <c r="G120" s="147"/>
+      <c r="H120" s="148"/>
+      <c r="I120" s="147">
+        <v>120</v>
+      </c>
+      <c r="J120" s="147">
+        <v>120</v>
+      </c>
+      <c r="K120" s="147">
+        <v>160</v>
+      </c>
       <c r="L120" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M120" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N120" s="43">
         <f t="shared" si="96"/>
@@ -11991,7 +12028,7 @@
       </c>
       <c r="P120" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q120" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12027,26 +12064,43 @@
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A121" s="72"/>
-      <c r="B121" s="41">
+      <c r="A121" s="143">
+        <v>46295</v>
+      </c>
+      <c r="B121" s="144">
         <v>117</v>
       </c>
-      <c r="C121" s="121"/>
-      <c r="D121" s="121"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="44"/>
-      <c r="G121" s="44"/>
-      <c r="H121" s="122"/>
-      <c r="I121" s="44"/>
-      <c r="J121" s="44"/>
-      <c r="K121" s="44"/>
+      <c r="C121" s="146" t="s">
+        <v>136</v>
+      </c>
+      <c r="D121" s="146" t="s">
+        <v>138</v>
+      </c>
+      <c r="E121" s="147"/>
+      <c r="F121" s="147">
+        <v>120</v>
+      </c>
+      <c r="G121" s="147">
+        <v>120</v>
+      </c>
+      <c r="H121" s="148">
+        <v>160</v>
+      </c>
+      <c r="I121" s="147">
+        <v>160</v>
+      </c>
+      <c r="J121" s="147">
+        <v>160</v>
+      </c>
+      <c r="K121" s="147">
+        <v>200</v>
+      </c>
       <c r="L121" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M121" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N121" s="43">
         <f t="shared" si="96"/>
@@ -12054,11 +12108,11 @@
       </c>
       <c r="O121" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P121" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q121" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12094,26 +12148,41 @@
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A122" s="72"/>
-      <c r="B122" s="41">
+      <c r="A122" s="143">
+        <v>46295</v>
+      </c>
+      <c r="B122" s="144">
         <v>118</v>
       </c>
-      <c r="C122" s="121"/>
-      <c r="D122" s="121"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
-      <c r="H122" s="122"/>
-      <c r="I122" s="44"/>
-      <c r="J122" s="44"/>
-      <c r="K122" s="44"/>
+      <c r="C122" s="146" t="s">
+        <v>136</v>
+      </c>
+      <c r="D122" s="146" t="s">
+        <v>173</v>
+      </c>
+      <c r="E122" s="147"/>
+      <c r="F122" s="147">
+        <v>200</v>
+      </c>
+      <c r="G122" s="147">
+        <v>120</v>
+      </c>
+      <c r="H122" s="148">
+        <v>120</v>
+      </c>
+      <c r="I122" s="147">
+        <v>120</v>
+      </c>
+      <c r="J122" s="147"/>
+      <c r="K122" s="147">
+        <v>120</v>
+      </c>
       <c r="L122" s="122">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M122" s="33">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N122" s="43">
         <f t="shared" si="96"/>
@@ -12121,11 +12190,11 @@
       </c>
       <c r="O122" s="67">
         <f t="shared" si="88"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P122" s="34">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q122" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12161,7 +12230,9 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A123" s="72"/>
+      <c r="A123" s="183">
+        <v>46295</v>
+      </c>
       <c r="B123" s="41">
         <v>119</v>
       </c>
@@ -12179,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="33">
-        <f t="shared" si="98"/>
+        <f t="shared" ref="M119:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N123" s="43">
@@ -12228,7 +12299,9 @@
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A124" s="72"/>
+      <c r="A124" s="183">
+        <v>46295</v>
+      </c>
       <c r="B124" s="41">
         <v>120</v>
       </c>
@@ -12816,10 +12889,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="167" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="168"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -13073,10 +13146,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="180" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="181"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -13160,10 +13233,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="169" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="170"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -13199,7 +13272,7 @@
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>1540</v>
+        <v>1594</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="109">SUM(N5:N137)</f>
@@ -13207,11 +13280,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>2107.8000000000002</v>
+        <v>2163.8000000000002</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>3189.25</v>
+        <v>3261.25</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -13248,17 +13321,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13294,25 +13367,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="184" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="188" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="189"/>
-      <c r="K3" s="190" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="190"/>
-      <c r="M3" s="190"/>
-      <c r="N3" s="190"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="190"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="93"/>
@@ -13358,24 +13431,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="82">
-        <v>1047</v>
+        <v>1079</v>
       </c>
       <c r="E5" s="73">
-        <v>1877</v>
+        <v>1941</v>
       </c>
       <c r="F5" s="73">
         <v>100</v>
       </c>
       <c r="G5" s="96">
         <f>SUM(D5:F5)</f>
-        <v>3024</v>
+        <v>3120</v>
       </c>
       <c r="H5" s="89">
         <v>10000</v>
       </c>
       <c r="I5" s="90">
         <f>G5-H5</f>
-        <v>-6976</v>
+        <v>-6880</v>
       </c>
       <c r="K5" s="141" t="s">
         <v>1</v>
@@ -13399,11 +13472,11 @@
       </c>
       <c r="D6" s="98">
         <f>D5*40</f>
-        <v>41880</v>
+        <v>43160</v>
       </c>
       <c r="E6" s="98">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>75080</v>
+        <v>77640</v>
       </c>
       <c r="F6" s="98">
         <f t="shared" si="1"/>
@@ -13411,7 +13484,7 @@
       </c>
       <c r="G6" s="99">
         <f>SUM(D6:F6)</f>
-        <v>120960</v>
+        <v>124800</v>
       </c>
       <c r="H6" s="91">
         <f>H5*40</f>
@@ -13419,7 +13492,7 @@
       </c>
       <c r="I6" s="92">
         <f>G6-H6</f>
-        <v>-279040</v>
+        <v>-275200</v>
       </c>
       <c r="K6" s="141" t="s">
         <v>2</v>
@@ -13547,11 +13620,11 @@
       </c>
       <c r="D9" s="100">
         <f>D8-D5</f>
-        <v>-1047</v>
+        <v>-1079</v>
       </c>
       <c r="E9" s="100">
         <f>E8-E5</f>
-        <v>-1877</v>
+        <v>-1941</v>
       </c>
       <c r="K9" s="141" t="s">
         <v>5</v>
@@ -13635,14 +13708,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="187" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="187"/>
-      <c r="F11" s="187" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="187"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="141" t="s">
         <v>7</v>
       </c>
@@ -13692,7 +13765,7 @@
       </c>
       <c r="G12" s="85">
         <f>D12+G5</f>
-        <v>7224</v>
+        <v>7320</v>
       </c>
       <c r="K12" s="141" t="s">
         <v>11</v>
@@ -13744,12 +13817,12 @@
       </c>
       <c r="G13" s="85">
         <f>G12*40</f>
-        <v>288960</v>
-      </c>
-      <c r="S13" s="182" t="s">
+        <v>292800</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="182"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="123">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13838,13 +13911,13 @@
       </c>
     </row>
     <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="183" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="183"/>
-      <c r="F20" s="183"/>
-      <c r="G20" s="183"/>
-      <c r="H20" s="183"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/Sep_2026/daily Reports/LMT Orders.xlsx
+++ b/Sep_2026/daily Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE20F019-6F58-4437-8E52-D201215CD330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A23E75-99FC-47F0-818F-D771816976CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1610,7 +1610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1996,6 +1996,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2035,42 +2071,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2098,24 +2098,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2708,13 +2697,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="162">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
-      </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
+        <v>46297</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2736,10 +2725,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="171" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2769,13 +2758,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="151"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="154" t="s">
+      <c r="L2" s="163"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="167"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2794,8 +2783,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="159"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2823,29 +2812,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="157"/>
-      <c r="N3" s="158"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="170"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="166" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="168"/>
-      <c r="U3" s="169" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="171"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="159"/>
-      <c r="B4" s="165"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -4729,8 +4718,7 @@
       <c r="J28" s="69"/>
       <c r="K28" s="70"/>
       <c r="L28" s="42">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" s="33">
         <v>8</v>
@@ -5499,30 +5487,30 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="72">
+      <c r="A38" s="143">
         <v>46277</v>
       </c>
-      <c r="B38" s="41">
+      <c r="B38" s="144">
         <v>34</v>
       </c>
-      <c r="C38" s="140" t="s">
+      <c r="C38" s="183" t="s">
         <v>96</v>
       </c>
-      <c r="D38" s="140" t="s">
+      <c r="D38" s="183" t="s">
         <v>140</v>
       </c>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="44">
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="147">
         <v>400</v>
       </c>
-      <c r="J38" s="69">
+      <c r="J38" s="184">
         <v>200</v>
       </c>
-      <c r="K38" s="70"/>
-      <c r="L38" s="42">
+      <c r="K38" s="185"/>
+      <c r="L38" s="186">
         <f t="shared" si="66"/>
         <v>15</v>
       </c>
@@ -5575,34 +5563,34 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="72">
+      <c r="A39" s="143">
         <v>46277</v>
       </c>
-      <c r="B39" s="41">
+      <c r="B39" s="144">
         <v>35</v>
       </c>
-      <c r="C39" s="140" t="s">
+      <c r="C39" s="183" t="s">
         <v>120</v>
       </c>
-      <c r="D39" s="140" t="s">
+      <c r="D39" s="183" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44">
-        <v>40</v>
-      </c>
-      <c r="G39" s="69"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="44">
+      <c r="E39" s="147"/>
+      <c r="F39" s="147">
+        <v>40</v>
+      </c>
+      <c r="G39" s="184"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="147">
         <v>120</v>
       </c>
-      <c r="J39" s="69">
-        <v>80</v>
-      </c>
-      <c r="K39" s="70">
+      <c r="J39" s="184">
+        <v>80</v>
+      </c>
+      <c r="K39" s="185">
         <v>280</v>
       </c>
-      <c r="L39" s="42">
+      <c r="L39" s="186">
         <f t="shared" si="66"/>
         <v>13</v>
       </c>
@@ -5655,38 +5643,38 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="72">
+      <c r="A40" s="143">
         <v>46277</v>
       </c>
-      <c r="B40" s="41">
+      <c r="B40" s="144">
         <v>36</v>
       </c>
-      <c r="C40" s="140" t="s">
+      <c r="C40" s="183" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="140" t="s">
+      <c r="D40" s="183" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44">
-        <v>80</v>
-      </c>
-      <c r="G40" s="69">
-        <v>80</v>
-      </c>
-      <c r="H40" s="43">
+      <c r="E40" s="147"/>
+      <c r="F40" s="147">
+        <v>80</v>
+      </c>
+      <c r="G40" s="184">
+        <v>80</v>
+      </c>
+      <c r="H40" s="50">
         <v>120</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="147">
         <v>120</v>
       </c>
-      <c r="J40" s="69">
-        <v>80</v>
-      </c>
-      <c r="K40" s="70">
+      <c r="J40" s="184">
+        <v>80</v>
+      </c>
+      <c r="K40" s="185">
         <v>120</v>
       </c>
-      <c r="L40" s="42">
+      <c r="L40" s="186">
         <f t="shared" si="66"/>
         <v>15</v>
       </c>
@@ -5739,38 +5727,38 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="72">
+      <c r="A41" s="143">
         <v>46277</v>
       </c>
-      <c r="B41" s="41">
+      <c r="B41" s="144">
         <v>37</v>
       </c>
-      <c r="C41" s="140" t="s">
+      <c r="C41" s="183" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="140" t="s">
+      <c r="D41" s="183" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44">
+      <c r="E41" s="147"/>
+      <c r="F41" s="147">
         <v>120</v>
       </c>
-      <c r="G41" s="69">
-        <v>80</v>
-      </c>
-      <c r="H41" s="43">
-        <v>80</v>
-      </c>
-      <c r="I41" s="44">
+      <c r="G41" s="184">
+        <v>80</v>
+      </c>
+      <c r="H41" s="50">
+        <v>80</v>
+      </c>
+      <c r="I41" s="147">
         <v>120</v>
       </c>
-      <c r="J41" s="69">
-        <v>80</v>
-      </c>
-      <c r="K41" s="70">
+      <c r="J41" s="184">
+        <v>80</v>
+      </c>
+      <c r="K41" s="185">
         <v>120</v>
       </c>
-      <c r="L41" s="42">
+      <c r="L41" s="186">
         <f t="shared" si="66"/>
         <v>15</v>
       </c>
@@ -5823,36 +5811,36 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="72">
+      <c r="A42" s="143">
         <v>46280</v>
       </c>
-      <c r="B42" s="41">
+      <c r="B42" s="144">
         <v>38</v>
       </c>
-      <c r="C42" s="140" t="s">
+      <c r="C42" s="183" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="140" t="s">
+      <c r="D42" s="183" t="s">
         <v>145</v>
       </c>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44">
+      <c r="E42" s="147"/>
+      <c r="F42" s="147">
         <v>120</v>
       </c>
-      <c r="G42" s="69">
-        <v>40</v>
-      </c>
-      <c r="H42" s="43">
-        <v>80</v>
-      </c>
-      <c r="I42" s="44">
+      <c r="G42" s="184">
+        <v>40</v>
+      </c>
+      <c r="H42" s="50">
+        <v>80</v>
+      </c>
+      <c r="I42" s="147">
         <v>120</v>
       </c>
-      <c r="J42" s="69">
+      <c r="J42" s="184">
         <v>120</v>
       </c>
-      <c r="K42" s="70"/>
-      <c r="L42" s="42">
+      <c r="K42" s="185"/>
+      <c r="L42" s="186">
         <f t="shared" si="66"/>
         <v>12</v>
       </c>
@@ -5905,38 +5893,38 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A43" s="72">
+      <c r="A43" s="143">
         <v>46280</v>
       </c>
-      <c r="B43" s="41">
+      <c r="B43" s="144">
         <v>39</v>
       </c>
-      <c r="C43" s="140" t="s">
+      <c r="C43" s="183" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="140" t="s">
+      <c r="D43" s="183" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44">
-        <v>40</v>
-      </c>
-      <c r="G43" s="69">
-        <v>40</v>
-      </c>
-      <c r="H43" s="43">
-        <v>40</v>
-      </c>
-      <c r="I43" s="44">
-        <v>40</v>
-      </c>
-      <c r="J43" s="69">
-        <v>40</v>
-      </c>
-      <c r="K43" s="70">
-        <v>40</v>
-      </c>
-      <c r="L43" s="42">
+      <c r="E43" s="147"/>
+      <c r="F43" s="147">
+        <v>40</v>
+      </c>
+      <c r="G43" s="184">
+        <v>40</v>
+      </c>
+      <c r="H43" s="50">
+        <v>40</v>
+      </c>
+      <c r="I43" s="147">
+        <v>40</v>
+      </c>
+      <c r="J43" s="184">
+        <v>40</v>
+      </c>
+      <c r="K43" s="185">
+        <v>40</v>
+      </c>
+      <c r="L43" s="186">
         <f t="shared" si="66"/>
         <v>6</v>
       </c>
@@ -5989,36 +5977,36 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="72">
+      <c r="A44" s="143">
         <v>46280</v>
       </c>
-      <c r="B44" s="41">
-        <v>40</v>
-      </c>
-      <c r="C44" s="140" t="s">
+      <c r="B44" s="144">
+        <v>40</v>
+      </c>
+      <c r="C44" s="183" t="s">
         <v>125</v>
       </c>
-      <c r="D44" s="140" t="s">
+      <c r="D44" s="183" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44">
+      <c r="E44" s="147"/>
+      <c r="F44" s="147">
         <v>118</v>
       </c>
-      <c r="G44" s="69">
-        <v>40</v>
-      </c>
-      <c r="H44" s="43">
-        <v>80</v>
-      </c>
-      <c r="I44" s="44">
+      <c r="G44" s="184">
+        <v>40</v>
+      </c>
+      <c r="H44" s="50">
+        <v>80</v>
+      </c>
+      <c r="I44" s="147">
         <v>117</v>
       </c>
-      <c r="J44" s="69">
+      <c r="J44" s="184">
         <v>117</v>
       </c>
-      <c r="K44" s="70"/>
-      <c r="L44" s="42">
+      <c r="K44" s="185"/>
+      <c r="L44" s="186">
         <f t="shared" si="66"/>
         <v>11.8</v>
       </c>
@@ -6071,36 +6059,36 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="72">
+      <c r="A45" s="143">
         <v>46280</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="144">
         <v>41</v>
       </c>
-      <c r="C45" s="140" t="s">
+      <c r="C45" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="140" t="s">
+      <c r="D45" s="187" t="s">
         <v>145</v>
       </c>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44">
-        <v>80</v>
-      </c>
-      <c r="G45" s="69">
-        <v>80</v>
-      </c>
-      <c r="H45" s="43">
-        <v>80</v>
-      </c>
-      <c r="I45" s="44"/>
-      <c r="J45" s="69">
-        <v>40</v>
-      </c>
-      <c r="K45" s="70">
-        <v>40</v>
-      </c>
-      <c r="L45" s="42">
+      <c r="E45" s="147"/>
+      <c r="F45" s="147">
+        <v>80</v>
+      </c>
+      <c r="G45" s="184">
+        <v>80</v>
+      </c>
+      <c r="H45" s="50">
+        <v>80</v>
+      </c>
+      <c r="I45" s="147"/>
+      <c r="J45" s="184">
+        <v>40</v>
+      </c>
+      <c r="K45" s="185">
+        <v>40</v>
+      </c>
+      <c r="L45" s="186">
         <f t="shared" si="66"/>
         <v>8</v>
       </c>
@@ -6153,32 +6141,32 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="72">
+      <c r="A46" s="143">
         <v>46280</v>
       </c>
-      <c r="B46" s="41">
+      <c r="B46" s="144">
         <v>42</v>
       </c>
-      <c r="C46" s="140" t="s">
+      <c r="C46" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="140" t="s">
+      <c r="D46" s="187" t="s">
         <v>148</v>
       </c>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="43">
-        <v>40</v>
-      </c>
-      <c r="I46" s="44"/>
-      <c r="J46" s="69">
-        <v>40</v>
-      </c>
-      <c r="K46" s="70">
-        <v>40</v>
-      </c>
-      <c r="L46" s="42">
+      <c r="E46" s="147"/>
+      <c r="F46" s="147"/>
+      <c r="G46" s="184"/>
+      <c r="H46" s="50">
+        <v>40</v>
+      </c>
+      <c r="I46" s="147"/>
+      <c r="J46" s="184">
+        <v>40</v>
+      </c>
+      <c r="K46" s="185">
+        <v>40</v>
+      </c>
+      <c r="L46" s="186">
         <f t="shared" si="66"/>
         <v>3</v>
       </c>
@@ -6231,36 +6219,36 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="72">
+      <c r="A47" s="143">
         <v>46280</v>
       </c>
-      <c r="B47" s="41">
+      <c r="B47" s="144">
         <v>43</v>
       </c>
-      <c r="C47" s="140" t="s">
+      <c r="C47" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="140" t="s">
+      <c r="D47" s="187" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44">
-        <v>40</v>
-      </c>
-      <c r="G47" s="69">
-        <v>40</v>
-      </c>
-      <c r="H47" s="43">
-        <v>40</v>
-      </c>
-      <c r="I47" s="44"/>
-      <c r="J47" s="69">
-        <v>40</v>
-      </c>
-      <c r="K47" s="70">
-        <v>40</v>
-      </c>
-      <c r="L47" s="42">
+      <c r="E47" s="147"/>
+      <c r="F47" s="147">
+        <v>40</v>
+      </c>
+      <c r="G47" s="184">
+        <v>40</v>
+      </c>
+      <c r="H47" s="50">
+        <v>40</v>
+      </c>
+      <c r="I47" s="147"/>
+      <c r="J47" s="184">
+        <v>40</v>
+      </c>
+      <c r="K47" s="185">
+        <v>40</v>
+      </c>
+      <c r="L47" s="186">
         <f t="shared" si="66"/>
         <v>5</v>
       </c>
@@ -6295,32 +6283,32 @@
       <c r="X47" s="50"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="72">
+      <c r="A48" s="143">
         <v>46280</v>
       </c>
-      <c r="B48" s="41">
+      <c r="B48" s="144">
         <v>44</v>
       </c>
-      <c r="C48" s="140" t="s">
+      <c r="C48" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="140" t="s">
+      <c r="D48" s="187" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44">
-        <v>40</v>
-      </c>
-      <c r="G48" s="69">
-        <v>40</v>
-      </c>
-      <c r="H48" s="43">
-        <v>40</v>
-      </c>
-      <c r="I48" s="44"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="70"/>
-      <c r="L48" s="42">
+      <c r="E48" s="147"/>
+      <c r="F48" s="147">
+        <v>40</v>
+      </c>
+      <c r="G48" s="184">
+        <v>40</v>
+      </c>
+      <c r="H48" s="50">
+        <v>40</v>
+      </c>
+      <c r="I48" s="147"/>
+      <c r="J48" s="184"/>
+      <c r="K48" s="185"/>
+      <c r="L48" s="186">
         <f t="shared" si="66"/>
         <v>3</v>
       </c>
@@ -6355,38 +6343,38 @@
       <c r="X48" s="50"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="72">
+      <c r="A49" s="143">
         <v>46280</v>
       </c>
-      <c r="B49" s="41">
+      <c r="B49" s="144">
         <v>45</v>
       </c>
-      <c r="C49" s="140" t="s">
+      <c r="C49" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="140" t="s">
+      <c r="D49" s="187" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44">
-        <v>40</v>
-      </c>
-      <c r="G49" s="69">
-        <v>40</v>
-      </c>
-      <c r="H49" s="43">
-        <v>40</v>
-      </c>
-      <c r="I49" s="44">
+      <c r="E49" s="147"/>
+      <c r="F49" s="147">
+        <v>40</v>
+      </c>
+      <c r="G49" s="184">
+        <v>40</v>
+      </c>
+      <c r="H49" s="50">
+        <v>40</v>
+      </c>
+      <c r="I49" s="147">
         <v>20</v>
       </c>
-      <c r="J49" s="69">
+      <c r="J49" s="184">
         <v>20</v>
       </c>
-      <c r="K49" s="70">
+      <c r="K49" s="185">
         <v>20</v>
       </c>
-      <c r="L49" s="42">
+      <c r="L49" s="186">
         <f t="shared" si="66"/>
         <v>4.5</v>
       </c>
@@ -8059,8 +8047,7 @@
         <v>14</v>
       </c>
       <c r="L72" s="122">
-        <f t="shared" si="80"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="33">
         <f t="shared" ref="M72" si="81">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
@@ -10902,33 +10889,33 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="183">
+      <c r="A107" s="72">
         <v>46293</v>
       </c>
-      <c r="B107" s="184">
+      <c r="B107" s="41">
         <v>103</v>
       </c>
-      <c r="C107" s="185" t="s">
+      <c r="C107" s="132" t="s">
         <v>213</v>
       </c>
-      <c r="D107" s="185" t="s">
+      <c r="D107" s="132" t="s">
         <v>133</v>
       </c>
-      <c r="E107" s="186"/>
-      <c r="F107" s="186">
+      <c r="E107" s="69"/>
+      <c r="F107" s="69">
         <v>120</v>
       </c>
-      <c r="G107" s="186"/>
-      <c r="H107" s="187">
+      <c r="G107" s="69"/>
+      <c r="H107" s="131">
         <v>120</v>
       </c>
-      <c r="I107" s="186">
+      <c r="I107" s="69">
         <v>120</v>
       </c>
-      <c r="J107" s="186">
-        <v>80</v>
-      </c>
-      <c r="K107" s="186">
+      <c r="J107" s="69">
+        <v>80</v>
+      </c>
+      <c r="K107" s="69">
         <v>80</v>
       </c>
       <c r="L107" s="122">
@@ -10984,35 +10971,35 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="183">
+      <c r="A108" s="72">
         <v>46293</v>
       </c>
-      <c r="B108" s="184">
+      <c r="B108" s="41">
         <v>104</v>
       </c>
-      <c r="C108" s="185" t="s">
+      <c r="C108" s="132" t="s">
         <v>214</v>
       </c>
-      <c r="D108" s="185" t="s">
+      <c r="D108" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="E108" s="186"/>
-      <c r="F108" s="186">
+      <c r="E108" s="69"/>
+      <c r="F108" s="69">
         <v>120</v>
       </c>
-      <c r="G108" s="186">
+      <c r="G108" s="69">
         <v>120</v>
       </c>
-      <c r="H108" s="187">
+      <c r="H108" s="131">
         <v>200</v>
       </c>
-      <c r="I108" s="186">
+      <c r="I108" s="69">
         <v>120</v>
       </c>
-      <c r="J108" s="186">
+      <c r="J108" s="69">
         <v>120</v>
       </c>
-      <c r="K108" s="186">
+      <c r="K108" s="69">
         <v>200</v>
       </c>
       <c r="L108" s="122">
@@ -11068,35 +11055,35 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="183">
+      <c r="A109" s="72">
         <v>46293</v>
       </c>
-      <c r="B109" s="184">
+      <c r="B109" s="41">
         <v>105</v>
       </c>
-      <c r="C109" s="185" t="s">
+      <c r="C109" s="132" t="s">
         <v>215</v>
       </c>
-      <c r="D109" s="185" t="s">
+      <c r="D109" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="E109" s="186"/>
-      <c r="F109" s="186">
-        <v>40</v>
-      </c>
-      <c r="G109" s="186">
-        <v>40</v>
-      </c>
-      <c r="H109" s="187">
-        <v>40</v>
-      </c>
-      <c r="I109" s="186">
-        <v>40</v>
-      </c>
-      <c r="J109" s="186">
-        <v>40</v>
-      </c>
-      <c r="K109" s="186">
+      <c r="E109" s="69"/>
+      <c r="F109" s="69">
+        <v>40</v>
+      </c>
+      <c r="G109" s="69">
+        <v>40</v>
+      </c>
+      <c r="H109" s="131">
+        <v>40</v>
+      </c>
+      <c r="I109" s="69">
+        <v>40</v>
+      </c>
+      <c r="J109" s="69">
+        <v>40</v>
+      </c>
+      <c r="K109" s="69">
         <v>40</v>
       </c>
       <c r="L109" s="122">
@@ -11152,35 +11139,35 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="183">
+      <c r="A110" s="72">
         <v>46293</v>
       </c>
-      <c r="B110" s="184">
+      <c r="B110" s="41">
         <v>106</v>
       </c>
-      <c r="C110" s="185" t="s">
+      <c r="C110" s="132" t="s">
         <v>216</v>
       </c>
-      <c r="D110" s="185" t="s">
+      <c r="D110" s="132" t="s">
         <v>217</v>
       </c>
-      <c r="E110" s="186"/>
-      <c r="F110" s="186">
-        <v>40</v>
-      </c>
-      <c r="G110" s="186">
-        <v>80</v>
-      </c>
-      <c r="H110" s="187">
+      <c r="E110" s="69"/>
+      <c r="F110" s="69">
+        <v>40</v>
+      </c>
+      <c r="G110" s="69">
+        <v>80</v>
+      </c>
+      <c r="H110" s="131">
         <v>120</v>
       </c>
-      <c r="I110" s="186">
-        <v>40</v>
-      </c>
-      <c r="J110" s="186">
-        <v>80</v>
-      </c>
-      <c r="K110" s="186">
+      <c r="I110" s="69">
+        <v>40</v>
+      </c>
+      <c r="J110" s="69">
+        <v>80</v>
+      </c>
+      <c r="K110" s="69">
         <v>120</v>
       </c>
       <c r="L110" s="122">
@@ -11236,35 +11223,35 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="183">
+      <c r="A111" s="72">
         <v>46293</v>
       </c>
-      <c r="B111" s="184">
+      <c r="B111" s="41">
         <v>107</v>
       </c>
-      <c r="C111" s="188" t="s">
+      <c r="C111" s="121" t="s">
         <v>218</v>
       </c>
-      <c r="D111" s="188" t="s">
+      <c r="D111" s="121" t="s">
         <v>217</v>
       </c>
-      <c r="E111" s="189"/>
-      <c r="F111" s="189">
-        <v>80</v>
-      </c>
-      <c r="G111" s="189">
-        <v>80</v>
-      </c>
-      <c r="H111" s="190">
+      <c r="E111" s="44"/>
+      <c r="F111" s="44">
+        <v>80</v>
+      </c>
+      <c r="G111" s="44">
+        <v>80</v>
+      </c>
+      <c r="H111" s="122">
         <v>120</v>
       </c>
-      <c r="I111" s="189">
-        <v>80</v>
-      </c>
-      <c r="J111" s="189">
-        <v>80</v>
-      </c>
-      <c r="K111" s="189">
+      <c r="I111" s="44">
+        <v>80</v>
+      </c>
+      <c r="J111" s="44">
+        <v>80</v>
+      </c>
+      <c r="K111" s="44">
         <v>120</v>
       </c>
       <c r="L111" s="122">
@@ -11320,35 +11307,35 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="183">
+      <c r="A112" s="72">
         <v>46293</v>
       </c>
-      <c r="B112" s="184">
+      <c r="B112" s="41">
         <v>108</v>
       </c>
-      <c r="C112" s="188" t="s">
+      <c r="C112" s="121" t="s">
         <v>219</v>
       </c>
-      <c r="D112" s="188" t="s">
+      <c r="D112" s="121" t="s">
         <v>113</v>
       </c>
-      <c r="E112" s="189"/>
-      <c r="F112" s="189">
+      <c r="E112" s="44"/>
+      <c r="F112" s="44">
         <v>120</v>
       </c>
-      <c r="G112" s="189">
+      <c r="G112" s="44">
         <v>120</v>
       </c>
-      <c r="H112" s="190">
+      <c r="H112" s="122">
         <v>180</v>
       </c>
-      <c r="I112" s="189">
+      <c r="I112" s="44">
         <v>120</v>
       </c>
-      <c r="J112" s="189">
+      <c r="J112" s="44">
         <v>120</v>
       </c>
-      <c r="K112" s="189">
+      <c r="K112" s="44">
         <v>200</v>
       </c>
       <c r="L112" s="122">
@@ -11404,35 +11391,35 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="183">
+      <c r="A113" s="72">
         <v>46293</v>
       </c>
-      <c r="B113" s="184">
+      <c r="B113" s="41">
         <v>109</v>
       </c>
-      <c r="C113" s="188" t="s">
+      <c r="C113" s="121" t="s">
         <v>220</v>
       </c>
-      <c r="D113" s="188" t="s">
+      <c r="D113" s="121" t="s">
         <v>133</v>
       </c>
-      <c r="E113" s="189"/>
-      <c r="F113" s="189">
-        <v>80</v>
-      </c>
-      <c r="G113" s="189">
-        <v>80</v>
-      </c>
-      <c r="H113" s="190">
-        <v>80</v>
-      </c>
-      <c r="I113" s="189">
-        <v>80</v>
-      </c>
-      <c r="J113" s="189">
-        <v>80</v>
-      </c>
-      <c r="K113" s="189">
+      <c r="E113" s="44"/>
+      <c r="F113" s="44">
+        <v>80</v>
+      </c>
+      <c r="G113" s="44">
+        <v>80</v>
+      </c>
+      <c r="H113" s="122">
+        <v>80</v>
+      </c>
+      <c r="I113" s="44">
+        <v>80</v>
+      </c>
+      <c r="J113" s="44">
+        <v>80</v>
+      </c>
+      <c r="K113" s="44">
         <v>80</v>
       </c>
       <c r="L113" s="122">
@@ -11488,35 +11475,35 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="183">
+      <c r="A114" s="72">
         <v>46294</v>
       </c>
-      <c r="B114" s="184">
+      <c r="B114" s="41">
         <v>110</v>
       </c>
-      <c r="C114" s="188" t="s">
+      <c r="C114" s="121" t="s">
         <v>221</v>
       </c>
-      <c r="D114" s="188" t="s">
+      <c r="D114" s="121" t="s">
         <v>114</v>
       </c>
-      <c r="E114" s="189"/>
-      <c r="F114" s="189">
-        <v>80</v>
-      </c>
-      <c r="G114" s="189">
-        <v>80</v>
-      </c>
-      <c r="H114" s="190">
-        <v>80</v>
-      </c>
-      <c r="I114" s="189">
-        <v>80</v>
-      </c>
-      <c r="J114" s="189">
-        <v>80</v>
-      </c>
-      <c r="K114" s="189">
+      <c r="E114" s="44"/>
+      <c r="F114" s="44">
+        <v>80</v>
+      </c>
+      <c r="G114" s="44">
+        <v>80</v>
+      </c>
+      <c r="H114" s="122">
+        <v>80</v>
+      </c>
+      <c r="I114" s="44">
+        <v>80</v>
+      </c>
+      <c r="J114" s="44">
+        <v>80</v>
+      </c>
+      <c r="K114" s="44">
         <v>80</v>
       </c>
       <c r="L114" s="122">
@@ -11572,35 +11559,35 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="183">
+      <c r="A115" s="72">
         <v>46294</v>
       </c>
-      <c r="B115" s="184">
+      <c r="B115" s="41">
         <v>111</v>
       </c>
-      <c r="C115" s="188" t="s">
+      <c r="C115" s="121" t="s">
         <v>222</v>
       </c>
-      <c r="D115" s="188" t="s">
+      <c r="D115" s="121" t="s">
         <v>179</v>
       </c>
-      <c r="E115" s="189"/>
-      <c r="F115" s="189">
+      <c r="E115" s="44"/>
+      <c r="F115" s="44">
         <v>131</v>
       </c>
-      <c r="G115" s="189">
+      <c r="G115" s="44">
         <v>120</v>
       </c>
-      <c r="H115" s="190">
+      <c r="H115" s="122">
         <v>200</v>
       </c>
-      <c r="I115" s="189">
+      <c r="I115" s="44">
         <v>200</v>
       </c>
-      <c r="J115" s="189">
+      <c r="J115" s="44">
         <v>106</v>
       </c>
-      <c r="K115" s="189">
+      <c r="K115" s="44">
         <v>200</v>
       </c>
       <c r="L115" s="122">
@@ -11656,35 +11643,35 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="183">
+      <c r="A116" s="72">
         <v>46294</v>
       </c>
-      <c r="B116" s="184">
+      <c r="B116" s="41">
         <v>112</v>
       </c>
-      <c r="C116" s="188" t="s">
+      <c r="C116" s="121" t="s">
         <v>224</v>
       </c>
-      <c r="D116" s="188" t="s">
+      <c r="D116" s="121" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="189"/>
-      <c r="F116" s="189">
-        <v>40</v>
-      </c>
-      <c r="G116" s="189">
-        <v>40</v>
-      </c>
-      <c r="H116" s="190">
-        <v>40</v>
-      </c>
-      <c r="I116" s="189">
-        <v>40</v>
-      </c>
-      <c r="J116" s="189">
-        <v>40</v>
-      </c>
-      <c r="K116" s="189">
+      <c r="E116" s="44"/>
+      <c r="F116" s="44">
+        <v>40</v>
+      </c>
+      <c r="G116" s="44">
+        <v>40</v>
+      </c>
+      <c r="H116" s="122">
+        <v>40</v>
+      </c>
+      <c r="I116" s="44">
+        <v>40</v>
+      </c>
+      <c r="J116" s="44">
+        <v>40</v>
+      </c>
+      <c r="K116" s="44">
         <v>40</v>
       </c>
       <c r="L116" s="122">
@@ -11740,29 +11727,29 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="183">
+      <c r="A117" s="72">
         <v>46294</v>
       </c>
-      <c r="B117" s="184">
+      <c r="B117" s="41">
         <v>113</v>
       </c>
-      <c r="C117" s="188" t="s">
+      <c r="C117" s="121" t="s">
         <v>225</v>
       </c>
-      <c r="D117" s="188" t="s">
+      <c r="D117" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="E117" s="189"/>
-      <c r="F117" s="189"/>
-      <c r="G117" s="189"/>
-      <c r="H117" s="190"/>
-      <c r="I117" s="189">
+      <c r="E117" s="44"/>
+      <c r="F117" s="44"/>
+      <c r="G117" s="44"/>
+      <c r="H117" s="122"/>
+      <c r="I117" s="44">
         <v>680</v>
       </c>
-      <c r="J117" s="189">
+      <c r="J117" s="44">
         <v>680</v>
       </c>
-      <c r="K117" s="189">
+      <c r="K117" s="44">
         <v>680</v>
       </c>
       <c r="L117" s="122">
@@ -11818,35 +11805,35 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="183">
+      <c r="A118" s="72">
         <v>46294</v>
       </c>
-      <c r="B118" s="184">
+      <c r="B118" s="41">
         <v>114</v>
       </c>
-      <c r="C118" s="188" t="s">
+      <c r="C118" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="D118" s="188" t="s">
+      <c r="D118" s="121" t="s">
         <v>227</v>
       </c>
-      <c r="E118" s="189"/>
-      <c r="F118" s="189">
+      <c r="E118" s="44"/>
+      <c r="F118" s="44">
         <v>79</v>
       </c>
-      <c r="G118" s="189">
-        <v>80</v>
-      </c>
-      <c r="H118" s="190">
+      <c r="G118" s="44">
+        <v>80</v>
+      </c>
+      <c r="H118" s="122">
         <v>200</v>
       </c>
-      <c r="I118" s="189">
-        <v>80</v>
-      </c>
-      <c r="J118" s="189">
-        <v>80</v>
-      </c>
-      <c r="K118" s="189">
+      <c r="I118" s="44">
+        <v>80</v>
+      </c>
+      <c r="J118" s="44">
+        <v>80</v>
+      </c>
+      <c r="K118" s="44">
         <v>200</v>
       </c>
       <c r="L118" s="122">
@@ -12081,23 +12068,23 @@
         <v>120</v>
       </c>
       <c r="G121" s="147">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="H121" s="148">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I121" s="147">
         <v>160</v>
       </c>
       <c r="J121" s="147">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K121" s="147">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L121" s="122">
         <f t="shared" si="97"/>
-        <v>23</v>
+        <v>20.375</v>
       </c>
       <c r="M121" s="33">
         <v>14</v>
@@ -12108,11 +12095,11 @@
       </c>
       <c r="O121" s="67">
         <f t="shared" si="88"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P121" s="34">
         <f t="shared" si="89"/>
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="Q121" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12171,15 +12158,15 @@
         <v>120</v>
       </c>
       <c r="I122" s="147">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J122" s="147"/>
       <c r="K122" s="147">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L122" s="122">
         <f t="shared" si="97"/>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="M122" s="33">
         <v>14</v>
@@ -12194,7 +12181,7 @@
       </c>
       <c r="P122" s="34">
         <f t="shared" si="89"/>
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="Q122" s="45" t="e">
         <f t="shared" si="94"/>
@@ -12230,7 +12217,7 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A123" s="183">
+      <c r="A123" s="72">
         <v>46295</v>
       </c>
       <c r="B123" s="41">
@@ -12250,7 +12237,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="33">
-        <f t="shared" ref="M119:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M123:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N123" s="43">
@@ -12299,7 +12286,7 @@
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A124" s="183">
+      <c r="A124" s="72">
         <v>46295</v>
       </c>
       <c r="B124" s="41">
@@ -12889,10 +12876,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="172" t="s">
+      <c r="B133" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="173"/>
+      <c r="C133" s="160"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="101">SUM(E6:E61)</f>
@@ -13146,10 +13133,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="160" t="s">
+      <c r="B137" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="161"/>
+      <c r="C137" s="173"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -13233,10 +13220,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="149" t="s">
+      <c r="B138" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="150"/>
+      <c r="C138" s="162"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -13280,11 +13267,11 @@
       </c>
       <c r="O138" s="56">
         <f t="shared" si="109"/>
-        <v>2163.8000000000002</v>
+        <v>2158.8000000000002</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="109"/>
-        <v>3261.25</v>
+        <v>3260.9</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="109"/>
@@ -13321,17 +13308,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
